--- a/Results/GWP 20a/ammonia climate change GWP 20a results.xlsx
+++ b/Results/GWP 20a/ammonia climate change GWP 20a results.xlsx
@@ -586,25 +586,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.029517151457778</v>
+        <v>3.029517151457775</v>
       </c>
       <c r="C2" t="n">
         <v>3.00105003712397</v>
       </c>
       <c r="D2" t="n">
-        <v>3.020369228257387</v>
+        <v>3.020369228257385</v>
       </c>
       <c r="E2" t="n">
-        <v>3.011186103055958</v>
+        <v>3.011186103055957</v>
       </c>
       <c r="F2" t="n">
-        <v>3.017219728720156</v>
+        <v>3.017219728720153</v>
       </c>
       <c r="G2" t="n">
-        <v>3.064889695315812</v>
+        <v>3.064889695315811</v>
       </c>
       <c r="H2" t="n">
-        <v>3.03697262941384</v>
+        <v>3.036972629413836</v>
       </c>
       <c r="I2" t="n">
         <v>3.019283356439285</v>
@@ -613,52 +613,52 @@
         <v>3.040020745117327</v>
       </c>
       <c r="K2" t="n">
-        <v>3.030433839321331</v>
+        <v>3.03043383932133</v>
       </c>
       <c r="L2" t="n">
-        <v>3.040168824394939</v>
+        <v>3.04016882439494</v>
       </c>
       <c r="M2" t="n">
-        <v>3.055195460566963</v>
+        <v>3.055195460566962</v>
       </c>
       <c r="N2" t="n">
-        <v>3.033119206965479</v>
+        <v>3.033119206965476</v>
       </c>
       <c r="O2" t="n">
         <v>3.435897779488248</v>
       </c>
       <c r="P2" t="n">
-        <v>3.032847669678686</v>
+        <v>3.032847669678684</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.023936094341046</v>
+        <v>3.023936094341043</v>
       </c>
       <c r="R2" t="n">
-        <v>3.022267043547053</v>
+        <v>3.02226704354705</v>
       </c>
       <c r="S2" t="n">
-        <v>3.042710880890489</v>
+        <v>3.042710880890488</v>
       </c>
       <c r="T2" t="n">
-        <v>3.029829481957866</v>
+        <v>3.029829481957865</v>
       </c>
       <c r="U2" t="n">
         <v>3.821550331817575</v>
       </c>
       <c r="V2" t="n">
-        <v>3.015314385586324</v>
+        <v>3.015314385586323</v>
       </c>
       <c r="W2" t="n">
-        <v>3.812902444353944</v>
+        <v>3.812902444353943</v>
       </c>
       <c r="X2" t="n">
         <v>3.028953670778078</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.028957112433593</v>
+        <v>3.028957112433592</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.313585699584029</v>
+        <v>3.313585699584028</v>
       </c>
       <c r="AA2" t="n">
         <v>3.037851675340054</v>
@@ -674,34 +674,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.263099018184492</v>
+        <v>2.263099018184493</v>
       </c>
       <c r="C3" t="n">
-        <v>2.110193046485066</v>
+        <v>2.110193046485065</v>
       </c>
       <c r="D3" t="n">
-        <v>2.199218586381105</v>
+        <v>2.199218586381104</v>
       </c>
       <c r="E3" t="n">
         <v>2.133161338178871</v>
       </c>
       <c r="F3" t="n">
-        <v>2.176875745374095</v>
+        <v>2.176875745374094</v>
       </c>
       <c r="G3" t="n">
-        <v>2.515250863812788</v>
+        <v>2.515250863812786</v>
       </c>
       <c r="H3" t="n">
-        <v>2.318786720798127</v>
+        <v>2.318786720798129</v>
       </c>
       <c r="I3" t="n">
-        <v>2.191554854252254</v>
+        <v>2.191554854252255</v>
       </c>
       <c r="J3" t="n">
         <v>2.338599386767199</v>
       </c>
       <c r="K3" t="n">
-        <v>2.271153047305724</v>
+        <v>2.271153047305723</v>
       </c>
       <c r="L3" t="n">
         <v>2.33996281080916</v>
@@ -710,49 +710,49 @@
         <v>2.452174948315057</v>
       </c>
       <c r="N3" t="n">
-        <v>2.290048251373359</v>
+        <v>2.290048251373357</v>
       </c>
       <c r="O3" t="n">
-        <v>2.937593241613298</v>
+        <v>2.937593241613296</v>
       </c>
       <c r="P3" t="n">
         <v>2.286985058115052</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.224513136533405</v>
+        <v>2.224513136533406</v>
       </c>
       <c r="R3" t="n">
         <v>2.213070350263941</v>
       </c>
       <c r="S3" t="n">
-        <v>2.357410726088568</v>
+        <v>2.357410726088567</v>
       </c>
       <c r="T3" t="n">
         <v>2.266996344996164</v>
       </c>
       <c r="U3" t="n">
-        <v>3.659025132449852</v>
+        <v>3.659025132449849</v>
       </c>
       <c r="V3" t="n">
-        <v>2.162204721269573</v>
+        <v>2.162204721269574</v>
       </c>
       <c r="W3" t="n">
-        <v>3.623400164752125</v>
+        <v>3.623400164752122</v>
       </c>
       <c r="X3" t="n">
-        <v>2.260494574329967</v>
+        <v>2.260494574329965</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.260076602584245</v>
+        <v>2.260076602584244</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.714491494126179</v>
+        <v>2.714491494126178</v>
       </c>
       <c r="AA3" t="n">
         <v>2.323675046011652</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.371169982639352</v>
+        <v>2.37116998263935</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6710028568488212</v>
+        <v>0.6710028568488194</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4502102604342577</v>
+        <v>0.4502102604342557</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5676728560478166</v>
+        <v>0.5676728560478153</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4639452324513853</v>
+        <v>0.4639452324513842</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5320978099334195</v>
+        <v>0.5320978099334183</v>
       </c>
       <c r="G4" t="n">
         <v>1.070552011899414</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7552159100518487</v>
+        <v>0.7552159100518474</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5554074343366684</v>
+        <v>0.5554074343366682</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7891761587619537</v>
+        <v>0.7891761587619518</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6813572679649033</v>
+        <v>0.6813572679649015</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7913184026857152</v>
+        <v>0.791318402685713</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9671846727114044</v>
+        <v>0.9671846727114023</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7116897308357076</v>
+        <v>0.7116897308357059</v>
       </c>
       <c r="O4" t="n">
-        <v>0.679204041043633</v>
+        <v>0.6792040410436314</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7086225922680648</v>
+        <v>0.7086225922680629</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6079622493021984</v>
+        <v>0.6079622493021981</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5891095527827575</v>
+        <v>0.589109552782756</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8200321002067026</v>
+        <v>0.8200321002067018</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6745307735264393</v>
+        <v>0.6745307735264381</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8465719188847229</v>
+        <v>0.8465719188847201</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5074208387888034</v>
+        <v>0.5074208387888022</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8072834680955187</v>
+        <v>0.8072834680955167</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6646380833577107</v>
+        <v>0.6646380833577088</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6591258585429772</v>
+        <v>0.6591258585429751</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.634147774074599</v>
+        <v>0.6341477740745969</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.7651451381695707</v>
+        <v>0.7651451381695693</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.837490008365725</v>
+        <v>0.837490008365723</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.144374678477945</v>
+        <v>7.144374678477942</v>
       </c>
       <c r="C5" t="n">
-        <v>3.358212550693711</v>
+        <v>3.35821255069371</v>
       </c>
       <c r="D5" t="n">
-        <v>5.900822133228702</v>
+        <v>5.900822133228699</v>
       </c>
       <c r="E5" t="n">
-        <v>3.504795617175103</v>
+        <v>3.504795617175097</v>
       </c>
       <c r="F5" t="n">
-        <v>5.264829292448488</v>
+        <v>5.264829292448467</v>
       </c>
       <c r="G5" t="n">
-        <v>15.00989363579997</v>
+        <v>15.00989363579995</v>
       </c>
       <c r="H5" t="n">
         <v>10.31279622132313</v>
       </c>
       <c r="I5" t="n">
-        <v>5.705049430285595</v>
+        <v>5.705049430285589</v>
       </c>
       <c r="J5" t="n">
-        <v>9.851509680100243</v>
+        <v>9.851509680100238</v>
       </c>
       <c r="K5" t="n">
-        <v>8.251298652796546</v>
+        <v>8.251298652796557</v>
       </c>
       <c r="L5" t="n">
-        <v>10.06787501766785</v>
+        <v>10.06787501766784</v>
       </c>
       <c r="M5" t="n">
-        <v>14.58051070939805</v>
+        <v>14.58051070939806</v>
       </c>
       <c r="N5" t="n">
-        <v>10.93190211160768</v>
+        <v>10.93190211160765</v>
       </c>
       <c r="O5" t="n">
-        <v>7.134295624133704</v>
+        <v>7.134295624133706</v>
       </c>
       <c r="P5" t="n">
-        <v>7.970879206807584</v>
+        <v>7.970879206807577</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.615670641458705</v>
+        <v>6.615670641458692</v>
       </c>
       <c r="R5" t="n">
-        <v>6.514953604752876</v>
+        <v>6.514953604752875</v>
       </c>
       <c r="S5" t="n">
-        <v>10.23311214020523</v>
+        <v>10.23311214020522</v>
       </c>
       <c r="T5" t="n">
-        <v>8.206918547187401</v>
+        <v>8.206918547187389</v>
       </c>
       <c r="U5" t="n">
-        <v>11.0723353995537</v>
+        <v>11.07233539955368</v>
       </c>
       <c r="V5" t="n">
-        <v>4.19083556072038</v>
+        <v>4.190835560720376</v>
       </c>
       <c r="W5" t="n">
-        <v>10.47531341963528</v>
+        <v>10.47531341963526</v>
       </c>
       <c r="X5" t="n">
-        <v>7.858482053432625</v>
+        <v>7.858482053432613</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.596244357661733</v>
+        <v>7.596244357661712</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.631834225339736</v>
+        <v>6.631834225339718</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.689296192203233</v>
+        <v>9.68929619220323</v>
       </c>
       <c r="AB5" t="n">
-        <v>12.16009557577808</v>
+        <v>12.16009557577805</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.700719569381154</v>
+        <v>0.8190574999557473</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5982649035411854</v>
+        <v>0.5982649035411838</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5973895685801455</v>
+        <v>0.5973895685801367</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6119998755583131</v>
+        <v>0.4936619449837059</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5618145224657486</v>
+        <v>0.680152453040346</v>
       </c>
       <c r="G6" t="n">
-        <v>1.100268724431743</v>
+        <v>1.218606655006341</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9032705531587757</v>
+        <v>0.9032705531587752</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7034620774435976</v>
+        <v>0.5851241468689899</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8188928712942738</v>
+        <v>0.9372308018688804</v>
       </c>
       <c r="K6" t="n">
-        <v>0.711073980497228</v>
+        <v>0.7110739804972237</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9393730457926437</v>
+        <v>0.821035115218035</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9969013852437338</v>
+        <v>0.9969013852437248</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7425224161859965</v>
+        <v>0.742522416186002</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8333329340446011</v>
+        <v>0.8333329340446007</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8627524116863554</v>
+        <v>0.8627524116863536</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.637678961834531</v>
+        <v>0.6376789618345206</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7371641958896853</v>
+        <v>0.618826265315077</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9680867433136314</v>
+        <v>0.9680867433136299</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7042474860587692</v>
+        <v>0.7042474860587598</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8818397313140569</v>
+        <v>0.8818397313140464</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6554754818957316</v>
+        <v>0.65547548189573</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8431002843301399</v>
+        <v>0.9614129468517739</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8126927264646373</v>
+        <v>0.8126927264646371</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6978213692588242</v>
+        <v>0.6978213692588291</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6638644866069281</v>
+        <v>0.6638644866069187</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.9131997812764985</v>
+        <v>0.7948618507018915</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8695896039968181</v>
+        <v>0.8695896039968168</v>
       </c>
     </row>
     <row r="7">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8108593483221667</v>
+        <v>0.8108593483221643</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5900667519076018</v>
+        <v>0.5900667519076008</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7075293475211605</v>
+        <v>0.7075293475211595</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6038017239247294</v>
+        <v>0.6038017239247291</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6719543014067634</v>
+        <v>0.6719543014067627</v>
       </c>
       <c r="G7" t="n">
         <v>1.210408503372757</v>
@@ -1047,64 +1047,64 @@
         <v>0.8950724015251923</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6952639258100139</v>
+        <v>0.6952639258100133</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9290326502352978</v>
+        <v>0.9290326502352967</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8212137594382479</v>
+        <v>0.821213759438247</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9311748941590613</v>
+        <v>0.93117489415906</v>
       </c>
       <c r="M7" t="n">
-        <v>1.107041164184749</v>
+        <v>1.107041164184748</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8515462223090515</v>
+        <v>0.8515462223090504</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8186765229481747</v>
+        <v>0.8186765229481735</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8480950741726042</v>
+        <v>0.8480950741726037</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.7478187407755441</v>
+        <v>0.7478187407755436</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7289660442561013</v>
+        <v>0.7289660442561007</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9598885916800477</v>
+        <v>0.9598885916800461</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8143872649997841</v>
+        <v>0.8143872649997831</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9916937703125007</v>
+        <v>0.9916937703125004</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6472773302621485</v>
+        <v>0.6472773302621476</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9471399595688649</v>
+        <v>0.9471399595688632</v>
       </c>
       <c r="X7" t="n">
-        <v>0.8044945748310551</v>
+        <v>0.8044945748310544</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8045334499133241</v>
+        <v>0.8045334499133229</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.7740042655479432</v>
+        <v>0.7740042655479422</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.9050016296429159</v>
+        <v>0.9050016296429148</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9773464998390693</v>
+        <v>0.9773464998390674</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.87418565166947</v>
+        <v>0.8741856516694688</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8139684922463961</v>
+        <v>0.8139684922463933</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9314310878599545</v>
+        <v>0.9314310878599521</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8277034642635227</v>
+        <v>0.7422017807670164</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7602963811394728</v>
+        <v>0.7602963811394712</v>
       </c>
       <c r="G8" t="n">
-        <v>1.434310243711551</v>
+        <v>1.467606606615473</v>
       </c>
       <c r="H8" t="n">
-        <v>1.118974141863986</v>
+        <v>1.118974141863985</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9191656661488085</v>
+        <v>0.9191656661488067</v>
       </c>
       <c r="J8" t="n">
-        <v>1.152934390574091</v>
+        <v>1.152934390574089</v>
       </c>
       <c r="K8" t="n">
-        <v>1.045115499777043</v>
+        <v>1.04511549977704</v>
       </c>
       <c r="L8" t="n">
-        <v>1.155076634497854</v>
+        <v>1.155076634497851</v>
       </c>
       <c r="M8" t="n">
-        <v>1.330942904523542</v>
+        <v>1.330942904523553</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9509751352655318</v>
+        <v>0.950975135265531</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9526956591601935</v>
+        <v>0.9526956591601911</v>
       </c>
       <c r="P8" t="n">
-        <v>0.973729440878111</v>
+        <v>0.9737294408781095</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.779588305828277</v>
+        <v>0.7795883058282754</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9528677845948947</v>
+        <v>0.9528677845948936</v>
       </c>
       <c r="S8" t="n">
-        <v>1.18379033201884</v>
+        <v>1.183790332018839</v>
       </c>
       <c r="T8" t="n">
-        <v>1.038289005338577</v>
+        <v>1.038289005338576</v>
       </c>
       <c r="U8" t="n">
-        <v>1.117142997375633</v>
+        <v>1.13758267945637</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8711790706009414</v>
+        <v>0.8273753808649573</v>
       </c>
       <c r="W8" t="n">
-        <v>1.171073257471006</v>
+        <v>1.171073257471003</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8509811976842303</v>
+        <v>0.8509811976842282</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18822197398523</v>
+        <v>1.188221973985227</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.9979060058867362</v>
+        <v>0.8343477977229556</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.12890336998171</v>
+        <v>1.128903369981707</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.368982711111934</v>
+        <v>1.368982711111931</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.253757284531687</v>
+        <v>1.253757284531686</v>
       </c>
       <c r="C9" t="n">
-        <v>1.207828120927378</v>
+        <v>1.207828120927376</v>
       </c>
       <c r="D9" t="n">
         <v>1.325290716540936</v>
       </c>
       <c r="E9" t="n">
-        <v>1.221563092944506</v>
+        <v>1.181205371588274</v>
       </c>
       <c r="F9" t="n">
-        <v>1.289715670426539</v>
+        <v>0.8866076555227338</v>
       </c>
       <c r="G9" t="n">
-        <v>1.828169872392535</v>
+        <v>1.828169931780441</v>
       </c>
       <c r="H9" t="n">
-        <v>1.512833770544969</v>
+        <v>1.512833770544967</v>
       </c>
       <c r="I9" t="n">
-        <v>1.31302529482979</v>
+        <v>1.313025294829789</v>
       </c>
       <c r="J9" t="n">
         <v>1.546794019255072</v>
       </c>
       <c r="K9" t="n">
-        <v>1.438975128458023</v>
+        <v>1.438975128458022</v>
       </c>
       <c r="L9" t="n">
-        <v>1.548936263178836</v>
+        <v>1.548936263178833</v>
       </c>
       <c r="M9" t="n">
-        <v>1.724802533204523</v>
+        <v>1.724802533204521</v>
       </c>
       <c r="N9" t="n">
-        <v>1.469307591328829</v>
+        <v>1.469307591328828</v>
       </c>
       <c r="O9" t="n">
-        <v>1.494771493274935</v>
+        <v>1.494771493274933</v>
       </c>
       <c r="P9" t="n">
         <v>1.536793073539015</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.365580169183229</v>
+        <v>1.365580169183227</v>
       </c>
       <c r="R9" t="n">
         <v>1.346727413275877</v>
       </c>
       <c r="S9" t="n">
-        <v>1.577649960699823</v>
+        <v>1.577649960699822</v>
       </c>
       <c r="T9" t="n">
         <v>1.432148634019559</v>
       </c>
       <c r="U9" t="n">
-        <v>1.609740879274846</v>
+        <v>1.609740879274845</v>
       </c>
       <c r="V9" t="n">
-        <v>1.265038699281924</v>
+        <v>1.466827217213708</v>
       </c>
       <c r="W9" t="n">
         <v>1.564901328588638</v>
       </c>
       <c r="X9" t="n">
-        <v>1.42225594385083</v>
+        <v>1.422255943850829</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.422294818933101</v>
+        <v>1.422294818933099</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.391765634567718</v>
+        <v>1.286338557628559</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.522762998662689</v>
+        <v>1.522762998662688</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.595107868858845</v>
+        <v>1.595107868858843</v>
       </c>
     </row>
   </sheetData>
@@ -1449,82 +1449,82 @@
         <v>2.903683044453699</v>
       </c>
       <c r="C2" t="n">
-        <v>2.89301658347706</v>
+        <v>2.893016583477059</v>
       </c>
       <c r="D2" t="n">
-        <v>2.907865591575817</v>
+        <v>2.907865591575815</v>
       </c>
       <c r="E2" t="n">
-        <v>2.905175234512541</v>
+        <v>2.905175234512539</v>
       </c>
       <c r="F2" t="n">
-        <v>2.894642706673326</v>
+        <v>2.894642706673324</v>
       </c>
       <c r="G2" t="n">
-        <v>2.912506801323143</v>
+        <v>2.912506801323141</v>
       </c>
       <c r="H2" t="n">
-        <v>2.912522883293942</v>
+        <v>2.912522883293939</v>
       </c>
       <c r="I2" t="n">
-        <v>2.905394564035774</v>
+        <v>2.905394564035773</v>
       </c>
       <c r="J2" t="n">
-        <v>2.909181919030815</v>
+        <v>2.909181919030814</v>
       </c>
       <c r="K2" t="n">
-        <v>2.905477693931033</v>
+        <v>2.905477693931031</v>
       </c>
       <c r="L2" t="n">
-        <v>2.883696471206874</v>
+        <v>2.883696471206872</v>
       </c>
       <c r="M2" t="n">
-        <v>2.903446582506074</v>
+        <v>2.903446582506072</v>
       </c>
       <c r="N2" t="n">
-        <v>2.905725311275334</v>
+        <v>2.905725311275333</v>
       </c>
       <c r="O2" t="n">
-        <v>3.235392262995643</v>
+        <v>3.235392262995642</v>
       </c>
       <c r="P2" t="n">
-        <v>2.904416942119513</v>
+        <v>2.904416942119512</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.907130063889787</v>
+        <v>2.907130063889786</v>
       </c>
       <c r="R2" t="n">
-        <v>2.872859422491606</v>
+        <v>2.872859422491605</v>
       </c>
       <c r="S2" t="n">
         <v>2.897212260888517</v>
       </c>
       <c r="T2" t="n">
-        <v>2.898898040074533</v>
+        <v>2.898898040074532</v>
       </c>
       <c r="U2" t="n">
-        <v>3.669813017002518</v>
+        <v>3.669813017002517</v>
       </c>
       <c r="V2" t="n">
-        <v>2.915261483392442</v>
+        <v>2.91526148339244</v>
       </c>
       <c r="W2" t="n">
-        <v>3.691972339635396</v>
+        <v>3.691972339635393</v>
       </c>
       <c r="X2" t="n">
-        <v>2.950315331453848</v>
+        <v>2.950315331453846</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.930703898051856</v>
+        <v>2.930703898051854</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.179746736463553</v>
+        <v>3.179746736463551</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.942013832636399</v>
+        <v>2.942013832636397</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.90753694693643</v>
+        <v>2.907536946936429</v>
       </c>
     </row>
     <row r="3">
@@ -1534,37 +1534,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.945592116436682</v>
+        <v>1.945592116436683</v>
       </c>
       <c r="C3" t="n">
-        <v>1.937070543803009</v>
+        <v>1.93707054380301</v>
       </c>
       <c r="D3" t="n">
         <v>1.975364186104035</v>
       </c>
       <c r="E3" t="n">
-        <v>1.95619932110013</v>
+        <v>1.956199321100129</v>
       </c>
       <c r="F3" t="n">
         <v>1.880908673385139</v>
       </c>
       <c r="G3" t="n">
-        <v>2.008194326537207</v>
+        <v>2.008194326537206</v>
       </c>
       <c r="H3" t="n">
-        <v>2.008791085732488</v>
+        <v>2.008791085732487</v>
       </c>
       <c r="I3" t="n">
         <v>1.957719170876368</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9846367197438</v>
+        <v>1.984636719743798</v>
       </c>
       <c r="K3" t="n">
         <v>1.958371138735983</v>
       </c>
       <c r="L3" t="n">
-        <v>1.803716689577728</v>
+        <v>1.803716689577727</v>
       </c>
       <c r="M3" t="n">
         <v>1.948259964177406</v>
@@ -1576,22 +1576,22 @@
         <v>2.461446865539132</v>
       </c>
       <c r="P3" t="n">
-        <v>1.950818525086785</v>
+        <v>1.950818525086784</v>
       </c>
       <c r="Q3" t="n">
         <v>1.970097789247949</v>
       </c>
       <c r="R3" t="n">
-        <v>1.724667406239513</v>
+        <v>1.724667406239514</v>
       </c>
       <c r="S3" t="n">
-        <v>1.899693442694608</v>
+        <v>1.899693442694609</v>
       </c>
       <c r="T3" t="n">
-        <v>1.911231300796276</v>
+        <v>1.911231300796275</v>
       </c>
       <c r="U3" t="n">
-        <v>3.253710272144193</v>
+        <v>3.253710272144192</v>
       </c>
       <c r="V3" t="n">
         <v>2.027762261477225</v>
@@ -1600,10 +1600,10 @@
         <v>3.450941143817617</v>
       </c>
       <c r="X3" t="n">
-        <v>2.277891908492331</v>
+        <v>2.27789190849233</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.138509701676236</v>
+        <v>2.138509701676235</v>
       </c>
       <c r="Z3" t="n">
         <v>2.452952388883699</v>
@@ -1612,7 +1612,7 @@
         <v>2.219234125422251</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.973164731825625</v>
+        <v>1.973164731825626</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1445039884565507</v>
+        <v>0.1445039884565515</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1633035363945424</v>
+        <v>0.1633035363945418</v>
       </c>
       <c r="D4" t="n">
-        <v>0.191747782267597</v>
+        <v>0.191747782267598</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1613589616125183</v>
+        <v>0.1613589616125196</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04238921446638035</v>
+        <v>0.04238921446638068</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2441723814256118</v>
+        <v>0.2441723814256137</v>
       </c>
       <c r="H4" t="n">
-        <v>0.244354034683842</v>
+        <v>0.244354034683843</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1638363894739841</v>
+        <v>0.1638363894739852</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2063955936692334</v>
+        <v>0.2063955936692337</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1647753798825848</v>
+        <v>0.1647753798825858</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.08125355064426021</v>
+        <v>-0.08125355064425938</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1499782906949194</v>
+        <v>0.1499782906949204</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1115677676272808</v>
+        <v>0.1115677676272723</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07862734545811979</v>
+        <v>0.07862734545812079</v>
       </c>
       <c r="P4" t="n">
-        <v>0.152793700201539</v>
+        <v>0.1527937002015394</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1834396586944515</v>
+        <v>0.183439658694451</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.203663001171949</v>
+        <v>-0.2036630011719477</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0714135113803081</v>
+        <v>0.07141351138030867</v>
       </c>
       <c r="T4" t="n">
-        <v>0.09045516278311774</v>
+        <v>0.09045516278311781</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2290333186851029</v>
+        <v>0.2290333186851031</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2738166043212406</v>
+        <v>0.2738166043212411</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5650431902155226</v>
+        <v>0.5650431902155231</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6712371220350875</v>
+        <v>0.6712371220350896</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4442661825003346</v>
+        <v>0.4442661825003344</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2518544164595403</v>
+        <v>0.2518544164595413</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5774678740138742</v>
+        <v>0.5774678740138756</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1882256214908018</v>
+        <v>0.1882256214908034</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.2464989677763299</v>
+        <v>-0.2464989677763295</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05489211406296834</v>
+        <v>0.05489211406296668</v>
       </c>
       <c r="D5" t="n">
-        <v>0.548157316267216</v>
+        <v>0.5481573162672171</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02951703662963139</v>
+        <v>0.0295170366296314</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.136572315825953</v>
+        <v>-2.136572315825947</v>
       </c>
       <c r="G5" t="n">
-        <v>1.322804971767942</v>
+        <v>1.322804971767944</v>
       </c>
       <c r="H5" t="n">
-        <v>1.575792448571777</v>
+        <v>1.575792448571778</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04974694010129832</v>
+        <v>0.04974694010129876</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7476041286109096</v>
+        <v>0.7476041286109085</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09675652404273805</v>
+        <v>0.09675652404273927</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.840493875375526</v>
+        <v>-3.840493875375524</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.18594664244367</v>
+        <v>-0.185946642443669</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1115677676272808</v>
+        <v>0.1115677676272723</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.25348050447325</v>
+        <v>-1.253480504473247</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1058182991884491</v>
+        <v>-0.1058182991884464</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3924569141505762</v>
+        <v>0.3924569141505768</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.888938293893631</v>
+        <v>-6.888938293893637</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.392240005532329</v>
+        <v>-1.392240005532325</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.311269257421651</v>
+        <v>-1.311269257421653</v>
       </c>
       <c r="U5" t="n">
-        <v>1.183832225138986</v>
+        <v>1.183832225138987</v>
       </c>
       <c r="V5" t="n">
-        <v>1.823793467239982</v>
+        <v>1.823793467239986</v>
       </c>
       <c r="W5" t="n">
-        <v>7.124744309747865</v>
+        <v>7.124744309747867</v>
       </c>
       <c r="X5" t="n">
-        <v>8.801638025342784</v>
+        <v>8.801638025342774</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.18714578827741</v>
+        <v>5.187145788277408</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.405997568064686</v>
+        <v>1.405997568064687</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.449148417728312</v>
+        <v>7.44914841772832</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.5080684920126317</v>
+        <v>0.5080684920126342</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.207379693872436</v>
+        <v>0.159114468740321</v>
       </c>
       <c r="C6" t="n">
-        <v>0.226179241810426</v>
+        <v>0.1779140166783117</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2546234876834813</v>
+        <v>0.254623487683484</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2242346670284033</v>
+        <v>0.1759694418962892</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1052649198822649</v>
+        <v>0.05699969475015081</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2587828617093818</v>
+        <v>0.3070480868414976</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2589645149676121</v>
+        <v>0.3072297400997274</v>
       </c>
       <c r="I6" t="n">
-        <v>0.178446869757754</v>
+        <v>0.2267120948898706</v>
       </c>
       <c r="J6" t="n">
-        <v>0.221006073953002</v>
+        <v>0.269271299085119</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2276510852984701</v>
+        <v>0.1793858601663557</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.06664307036049003</v>
+        <v>-0.0183778452283743</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1645887709786894</v>
+        <v>0.2128539961108064</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1115677676272808</v>
+        <v>0.1115677676272723</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1479361054701723</v>
+        <v>0.1479361054701732</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1651939177745231</v>
+        <v>0.222028360217273</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2463153641103358</v>
+        <v>0.2463153641103372</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1890525208881787</v>
+        <v>-0.1407872957560632</v>
       </c>
       <c r="S6" t="n">
-        <v>0.08602399166407754</v>
+        <v>0.1342892167961941</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1533308681990019</v>
+        <v>0.1050656430668865</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2490945765230552</v>
+        <v>0.2973598016551706</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2884270846050106</v>
+        <v>0.3366923097371262</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5840189134481656</v>
+        <v>0.5840189134481659</v>
       </c>
       <c r="X6" t="n">
-        <v>0.685847602318858</v>
+        <v>0.6858476023188593</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4667292116705174</v>
+        <v>0.4667292116705112</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3147301218754249</v>
+        <v>0.2664648967433106</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5920783542976443</v>
+        <v>0.5920783542976448</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2030261318785347</v>
+        <v>0.2030261318785352</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.223026724224157</v>
+        <v>0.223026724224158</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2418262721621483</v>
+        <v>0.2418262721621479</v>
       </c>
       <c r="D7" t="n">
-        <v>0.270270518035203</v>
+        <v>0.2702705180352039</v>
       </c>
       <c r="E7" t="n">
-        <v>0.239881697380125</v>
+        <v>0.2398816973801257</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1209119502339864</v>
+        <v>0.1209119502339872</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3226951171932176</v>
+        <v>0.3226951171932196</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3228767704514486</v>
+        <v>0.3228767704514494</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2423591252415901</v>
+        <v>0.2423591252415908</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2849183294368397</v>
+        <v>0.2849183294368399</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2432981156501915</v>
+        <v>0.2432981156501925</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00273081487665465</v>
+        <v>-0.002730814876653664</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2285010264625257</v>
+        <v>0.2285010264625266</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1115677676272808</v>
+        <v>0.1115677676272723</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1568170237358403</v>
+        <v>0.156817023735841</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2309833784792584</v>
+        <v>0.2309833784792598</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2619623944620572</v>
+        <v>0.2619623944620575</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1251402654043433</v>
+        <v>-0.1251402654043424</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1499362471479137</v>
+        <v>0.1499362471479143</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1689778985507236</v>
+        <v>0.1689778985507237</v>
       </c>
       <c r="U7" t="n">
-        <v>0.311271776819089</v>
+        <v>0.3112717768190899</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3523393400888475</v>
+        <v>0.3523393400888477</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6435659259831287</v>
+        <v>0.6435659259831296</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7497598578026939</v>
+        <v>0.7497598578026951</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5282396958221225</v>
+        <v>0.5282396958221224</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3303771522271464</v>
+        <v>0.3303771522271473</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6559906097814806</v>
+        <v>0.655990609781482</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.266748357258408</v>
+        <v>0.2667483572584098</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2435143226586922</v>
+        <v>0.2435143226586937</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3426431182779648</v>
+        <v>0.3426431182779651</v>
       </c>
       <c r="D8" t="n">
-        <v>0.371087364151019</v>
+        <v>0.3710873641510211</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3406985434959408</v>
+        <v>0.2979255886840039</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1539139066214407</v>
+        <v>0.1539139066214411</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4235119633090337</v>
+        <v>0.4401687561060241</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4236936165672638</v>
+        <v>0.4236936165672658</v>
       </c>
       <c r="I8" t="n">
-        <v>0.343175971357406</v>
+        <v>0.3431759713574081</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3857351755526553</v>
+        <v>0.3857351755526558</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3441149617660072</v>
+        <v>0.3441149617660087</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09808603123916049</v>
+        <v>0.09808603123916262</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3293178725783416</v>
+        <v>0.329317872578232</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1115677676272808</v>
+        <v>0.1115677676272723</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2128102750763315</v>
+        <v>0.2128102750763331</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2827820765386526</v>
+        <v>0.2827820765386543</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2666634623205836</v>
+        <v>0.2666634623205843</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.02432341928852688</v>
+        <v>-0.02432341928852511</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2507530932637302</v>
+        <v>0.2507530932637316</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2697947446665399</v>
+        <v>0.2697947446665411</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3633730209609808</v>
+        <v>0.3735295306310576</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4531561862046627</v>
+        <v>0.4300025986307969</v>
       </c>
       <c r="W8" t="n">
-        <v>0.744398559027687</v>
+        <v>0.7443985590276887</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7618232607848973</v>
+        <v>0.7618232607848989</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.7070673754822121</v>
+        <v>0.7070673754822128</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.4311939983429628</v>
+        <v>0.3493725936510246</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7568074558972973</v>
+        <v>0.7568074558972988</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.4514758195341771</v>
+        <v>0.4514758195341784</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2976264797458433</v>
+        <v>0.2976264797458424</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3663545689767603</v>
+        <v>0.3663545689767608</v>
       </c>
       <c r="D9" t="n">
-        <v>0.394798814849816</v>
+        <v>0.3947988148498164</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3644099941947393</v>
+        <v>0.3528867222575309</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2454402470486014</v>
+        <v>0.1303412787193179</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4472234140078321</v>
+        <v>0.4472234552691716</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4474050672660617</v>
+        <v>0.4474050672660612</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3668874220562057</v>
+        <v>0.3668874220562036</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4094466262514549</v>
+        <v>0.4094466262514526</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3678264124648052</v>
+        <v>0.3678264124648044</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1217974819379599</v>
+        <v>0.1217974819379585</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3530293232771413</v>
+        <v>0.3530293232771389</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1115677676272808</v>
+        <v>0.1115677676272723</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2982246861842717</v>
+        <v>0.2982246861842721</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3759895700885187</v>
+        <v>0.3759895700885185</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3864907325380114</v>
+        <v>0.3864907325380115</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.00061196858972834</v>
+        <v>-0.0006119685897296723</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2744645439625285</v>
+        <v>0.2744645439625277</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2935061953653361</v>
+        <v>0.2935061953653363</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4375351288215038</v>
+        <v>0.4375351288215041</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4768676369034596</v>
+        <v>0.5344841549963967</v>
       </c>
       <c r="W9" t="n">
         <v>0.7680942227977425</v>
       </c>
       <c r="X9" t="n">
-        <v>0.8742881546173082</v>
+        <v>0.8742881546173064</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.6527679926367344</v>
+        <v>0.6527679926367348</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.454905449041758</v>
+        <v>0.4248029948456668</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.7805189065960951</v>
+        <v>0.7805189065960947</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3912766540730235</v>
+        <v>0.3912766540730214</v>
       </c>
     </row>
   </sheetData>
@@ -2306,22 +2306,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.014525911090847</v>
+        <v>3.014525911090848</v>
       </c>
       <c r="C2" t="n">
         <v>2.989282037650697</v>
       </c>
       <c r="D2" t="n">
-        <v>3.013234786634416</v>
+        <v>3.013234786634417</v>
       </c>
       <c r="E2" t="n">
-        <v>3.001667207839652</v>
+        <v>3.001667207839651</v>
       </c>
       <c r="F2" t="n">
         <v>3.004317915601563</v>
       </c>
       <c r="G2" t="n">
-        <v>3.054439635897063</v>
+        <v>3.054439635897065</v>
       </c>
       <c r="H2" t="n">
         <v>3.020143604686298</v>
@@ -2330,25 +2330,25 @@
         <v>3.004672464093312</v>
       </c>
       <c r="J2" t="n">
-        <v>3.030370960993766</v>
+        <v>3.030370960993768</v>
       </c>
       <c r="K2" t="n">
-        <v>3.017000604273383</v>
+        <v>3.017000604273382</v>
       </c>
       <c r="L2" t="n">
-        <v>3.026836965503007</v>
+        <v>3.026836965503008</v>
       </c>
       <c r="M2" t="n">
-        <v>3.042473813625784</v>
+        <v>3.042473813625783</v>
       </c>
       <c r="N2" t="n">
         <v>3.018969970784519</v>
       </c>
       <c r="O2" t="n">
-        <v>3.41376075547337</v>
+        <v>3.413760755473371</v>
       </c>
       <c r="P2" t="n">
-        <v>3.029239909967548</v>
+        <v>3.029239909967549</v>
       </c>
       <c r="Q2" t="n">
         <v>3.010293797269318</v>
@@ -2366,25 +2366,25 @@
         <v>3.800687437193624</v>
       </c>
       <c r="V2" t="n">
-        <v>3.000308169743693</v>
+        <v>3.000308169743694</v>
       </c>
       <c r="W2" t="n">
-        <v>3.801105521605746</v>
+        <v>3.801105521605745</v>
       </c>
       <c r="X2" t="n">
         <v>3.022041513852848</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.018193182460537</v>
+        <v>3.018193182460539</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.294641577102796</v>
+        <v>3.294641577102798</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.02106814979868</v>
+        <v>3.021068149798683</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.03436875728794</v>
+        <v>3.034368757287941</v>
       </c>
     </row>
     <row r="3">
@@ -2394,79 +2394,79 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.213982526598385</v>
+        <v>2.213982526598388</v>
       </c>
       <c r="C3" t="n">
         <v>2.085330583970418</v>
       </c>
       <c r="D3" t="n">
-        <v>2.206110318079139</v>
+        <v>2.20611031807914</v>
       </c>
       <c r="E3" t="n">
-        <v>2.122978990967154</v>
+        <v>2.122978990967153</v>
       </c>
       <c r="F3" t="n">
-        <v>2.142303238351376</v>
+        <v>2.142303238351377</v>
       </c>
       <c r="G3" t="n">
-        <v>2.49822868319308</v>
+        <v>2.498228683193081</v>
       </c>
       <c r="H3" t="n">
-        <v>2.256084909399209</v>
+        <v>2.25608490939921</v>
       </c>
       <c r="I3" t="n">
-        <v>2.14489797745684</v>
+        <v>2.144897977456842</v>
       </c>
       <c r="J3" t="n">
-        <v>2.327421970196205</v>
+        <v>2.327421970196206</v>
       </c>
       <c r="K3" t="n">
-        <v>2.232224802543841</v>
+        <v>2.232224802543843</v>
       </c>
       <c r="L3" t="n">
-        <v>2.302586984306731</v>
+        <v>2.302586984306732</v>
       </c>
       <c r="M3" t="n">
         <v>2.418796186581197</v>
       </c>
       <c r="N3" t="n">
-        <v>2.246782440025402</v>
+        <v>2.246782440025404</v>
       </c>
       <c r="O3" t="n">
-        <v>2.881393320175516</v>
+        <v>2.881393320175517</v>
       </c>
       <c r="P3" t="n">
-        <v>2.318844437534676</v>
+        <v>2.31884443753468</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.184810980219705</v>
+        <v>2.184810980219706</v>
       </c>
       <c r="R3" t="n">
-        <v>2.17635330539214</v>
+        <v>2.176353305392141</v>
       </c>
       <c r="S3" t="n">
-        <v>2.340698068951061</v>
+        <v>2.340698068951062</v>
       </c>
       <c r="T3" t="n">
-        <v>2.209274749834122</v>
+        <v>2.209274749834124</v>
       </c>
       <c r="U3" t="n">
-        <v>3.592546631257755</v>
+        <v>3.592546631257756</v>
       </c>
       <c r="V3" t="n">
-        <v>2.112887403349101</v>
+        <v>2.112887403349104</v>
       </c>
       <c r="W3" t="n">
-        <v>3.624445120987657</v>
+        <v>3.624445120987655</v>
       </c>
       <c r="X3" t="n">
-        <v>2.268897857464208</v>
+        <v>2.268897857464209</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.240896380126588</v>
+        <v>2.24089638012659</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.664302651011677</v>
+        <v>2.664302651011676</v>
       </c>
       <c r="AA3" t="n">
         <v>2.261517815783976</v>
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5915291525438036</v>
+        <v>0.5915291525438037</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4102383582859013</v>
+        <v>0.4102383582859004</v>
       </c>
       <c r="D4" t="n">
-        <v>0.576945307861821</v>
+        <v>0.5769453078618212</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4462841840257973</v>
+        <v>0.4462841840257969</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4762251475824175</v>
+        <v>0.4762251475824164</v>
       </c>
       <c r="G4" t="n">
-        <v>1.042373035450572</v>
+        <v>1.04237303545057</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6549835859711566</v>
+        <v>0.6549835859711571</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4802299358970746</v>
+        <v>0.4802299358970731</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7700126205277765</v>
+        <v>0.7700126205277762</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6194819504556607</v>
+        <v>0.6194819504556595</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7305881754939604</v>
+        <v>0.7305881754939588</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9130990730762321</v>
+        <v>0.9130990730762302</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6417268511522579</v>
+        <v>0.6417268511522557</v>
       </c>
       <c r="O4" t="n">
         <v>0.6094487707200756</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7577305386300623</v>
+        <v>0.7577305386300608</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.54372548006108</v>
+        <v>0.5437254800610782</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5296415333179061</v>
+        <v>0.5296415333179071</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7922270304583935</v>
+        <v>0.7922270304583934</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5819577977423108</v>
+        <v>0.5819577977423094</v>
       </c>
       <c r="U4" t="n">
-        <v>0.751306136587133</v>
+        <v>0.7513061365871346</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4276145585595642</v>
+        <v>0.4276145585595631</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8204394057415032</v>
+        <v>0.8204394057415014</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6764213430886702</v>
+        <v>0.6764213430886694</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6272414497295503</v>
+        <v>0.6272414497295513</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.5660774265112298</v>
+        <v>0.5660774265112291</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.6654267483272889</v>
+        <v>0.6654267483272883</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8142102257713675</v>
+        <v>0.8142102257713654</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.515285415645715</v>
+        <v>5.51528541564571</v>
       </c>
       <c r="C5" t="n">
-        <v>2.575945927976269</v>
+        <v>2.575945927976265</v>
       </c>
       <c r="D5" t="n">
-        <v>5.986231654814095</v>
+        <v>5.986231654814092</v>
       </c>
       <c r="E5" t="n">
-        <v>3.197061404797794</v>
+        <v>3.197061404797795</v>
       </c>
       <c r="F5" t="n">
-        <v>3.988987854051694</v>
+        <v>3.988987854051696</v>
       </c>
       <c r="G5" t="n">
-        <v>13.69493565048394</v>
+        <v>13.69493565048393</v>
       </c>
       <c r="H5" t="n">
-        <v>7.8321762976956</v>
+        <v>7.832176297695618</v>
       </c>
       <c r="I5" t="n">
-        <v>4.100475517989571</v>
+        <v>4.100475517989567</v>
       </c>
       <c r="J5" t="n">
-        <v>9.094935958611945</v>
+        <v>9.094935958611957</v>
       </c>
       <c r="K5" t="n">
-        <v>6.366531233371115</v>
+        <v>6.366531233371113</v>
       </c>
       <c r="L5" t="n">
-        <v>8.556068628749642</v>
+        <v>8.556068628749651</v>
       </c>
       <c r="M5" t="n">
-        <v>12.79143390544705</v>
+        <v>12.79143390544708</v>
       </c>
       <c r="N5" t="n">
-        <v>8.748625033562318</v>
+        <v>8.748625033562307</v>
       </c>
       <c r="O5" t="n">
-        <v>5.685471183873943</v>
+        <v>5.685471183873944</v>
       </c>
       <c r="P5" t="n">
-        <v>8.572918406061186</v>
+        <v>8.572918406061191</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.186068542373926</v>
+        <v>5.186068542373928</v>
       </c>
       <c r="R5" t="n">
-        <v>5.16519153223577</v>
+        <v>5.165191532235784</v>
       </c>
       <c r="S5" t="n">
-        <v>9.25686545760453</v>
+        <v>9.256865457604571</v>
       </c>
       <c r="T5" t="n">
-        <v>6.079496859421574</v>
+        <v>6.079496859421569</v>
       </c>
       <c r="U5" t="n">
-        <v>8.86391553896031</v>
+        <v>8.863915538960283</v>
       </c>
       <c r="V5" t="n">
-        <v>2.685440426132013</v>
+        <v>2.685440426132006</v>
       </c>
       <c r="W5" t="n">
         <v>10.33511393430827</v>
       </c>
       <c r="X5" t="n">
-        <v>7.830124339222668</v>
+        <v>7.830124339222693</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.710267390386812</v>
+        <v>6.710267390386841</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.201006245067556</v>
+        <v>5.201006245067547</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.381373442795491</v>
+        <v>7.381373442795499</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.20926485037393</v>
+        <v>11.20926485037391</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7231524471062524</v>
+        <v>0.6166258638661175</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5418616528483507</v>
+        <v>0.5418616528483516</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6020420191841354</v>
+        <v>0.7085686024242707</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4713808953481113</v>
+        <v>0.4713808953481108</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6078484421448667</v>
+        <v>0.5013218589047308</v>
       </c>
       <c r="G6" t="n">
-        <v>1.17399633001302</v>
+        <v>1.067469746772885</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6800802972934713</v>
+        <v>0.7866068805336067</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5053266472193889</v>
+        <v>0.5053266472193887</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9016359150902254</v>
+        <v>0.9016359150902253</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6445786617779751</v>
+        <v>0.7511052450181104</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7556848868162741</v>
+        <v>0.7556848868162747</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9381957843985447</v>
+        <v>0.9381957843985437</v>
       </c>
       <c r="N6" t="n">
-        <v>0.667507747874747</v>
+        <v>0.6675077478747684</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7464447417678793</v>
+        <v>0.7464447417678798</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8947175863682104</v>
+        <v>0.8947175863682133</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5688221913833936</v>
+        <v>0.6753487746235287</v>
       </c>
       <c r="R6" t="n">
-        <v>0.554738244640221</v>
+        <v>0.6612648278803559</v>
       </c>
       <c r="S6" t="n">
-        <v>0.817323741780708</v>
+        <v>0.9238503250208439</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7135810923047599</v>
+        <v>0.6070545090646247</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8886406511126768</v>
+        <v>0.7821140678725396</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5592378531220128</v>
+        <v>0.5592378531220136</v>
       </c>
       <c r="W6" t="n">
-        <v>0.957438504994967</v>
+        <v>0.9574385049949673</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7015180544109844</v>
+        <v>0.8080446376511187</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6605865449729519</v>
+        <v>0.6605865449729766</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5911741378335443</v>
+        <v>0.6977007210736791</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.7970500428897376</v>
+        <v>0.6905234596496032</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8415029994114276</v>
+        <v>0.8415029994114267</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7163234238534367</v>
+        <v>0.7163234238534352</v>
       </c>
       <c r="C7" t="n">
         <v>0.535032629595535</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7017395791714541</v>
+        <v>0.7017395791714546</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5710784553354308</v>
+        <v>0.5710784553354304</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6010194188920502</v>
+        <v>0.60101941889205</v>
       </c>
       <c r="G7" t="n">
-        <v>1.167167306760205</v>
+        <v>1.167167306760203</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7797778572807904</v>
+        <v>0.7797778572807915</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6050242072067079</v>
+        <v>0.6050242072067078</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8948068918374097</v>
+        <v>0.8948068918374089</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7442762217652942</v>
+        <v>0.744276221765294</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8553824468035933</v>
+        <v>0.8553824468035925</v>
       </c>
       <c r="M7" t="n">
         <v>1.037893344385864</v>
       </c>
       <c r="N7" t="n">
-        <v>0.76652112246189</v>
+        <v>0.7665211224618907</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7338839812078671</v>
+        <v>0.733883981207867</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8821657491178516</v>
+        <v>0.8821657491178524</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6685197513707136</v>
+        <v>0.6685197513707128</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6544358046275409</v>
+        <v>0.6544358046275407</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9170213017680267</v>
+        <v>0.9170213017680268</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7067520690519428</v>
+        <v>0.7067520690519432</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8814915457611567</v>
+        <v>0.8814915457611568</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5524088298691973</v>
+        <v>0.5524088298691967</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9452336770511357</v>
+        <v>0.9452336770511354</v>
       </c>
       <c r="X7" t="n">
-        <v>0.8012156143983036</v>
+        <v>0.8012156143983032</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.7577469410022775</v>
+        <v>0.7577469410022788</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6908716978208632</v>
+        <v>0.6908716978208629</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.790221019636922</v>
+        <v>0.7902210196369215</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9390044970810009</v>
+        <v>0.939004497081</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7723683018449038</v>
+        <v>0.772368301844902</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7342603065920092</v>
+        <v>0.7342603065920077</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9009672561679295</v>
+        <v>0.9009672561679297</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7703061323319048</v>
+        <v>0.6940655155107206</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6793705035437331</v>
+        <v>0.6793705035437321</v>
       </c>
       <c r="G8" t="n">
-        <v>1.366394983756681</v>
+        <v>1.39608486987153</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9790055342772647</v>
+        <v>0.9790055342772646</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8042518842031819</v>
+        <v>0.8042518842031823</v>
       </c>
       <c r="J8" t="n">
-        <v>1.094034568833884</v>
+        <v>1.094034568833882</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9435038987617687</v>
+        <v>0.943503898761767</v>
       </c>
       <c r="L8" t="n">
-        <v>1.054610123800068</v>
+        <v>1.054610123800067</v>
       </c>
       <c r="M8" t="n">
-        <v>1.237121021382338</v>
+        <v>1.237121021382329</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8547581762424458</v>
+        <v>0.8547581762424437</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8529812827323446</v>
+        <v>0.8529812827323426</v>
       </c>
       <c r="P8" t="n">
-        <v>0.993786472721342</v>
+        <v>0.9937864727213409</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6964259413975257</v>
+        <v>0.6964259413975243</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8536634816240148</v>
+        <v>0.8536634816240147</v>
       </c>
       <c r="S8" t="n">
-        <v>1.116248978764502</v>
+        <v>1.116248978764504</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9059797460484186</v>
+        <v>0.9059797460484158</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9929604300179041</v>
+        <v>1.011183899193548</v>
       </c>
       <c r="V8" t="n">
-        <v>0.751636506865672</v>
+        <v>0.7125358069492982</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14448949346735</v>
+        <v>1.144489493467349</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8422447923992852</v>
+        <v>0.8422447923992857</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.099389692305237</v>
+        <v>1.099389692305241</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.8900993748173377</v>
+        <v>0.7442568818194691</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.9894486966333965</v>
+        <v>0.9894486966333945</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.287798580293256</v>
+        <v>1.287798580293253</v>
       </c>
     </row>
     <row r="9">
@@ -2925,25 +2925,25 @@
         <v>1.065582485198938</v>
       </c>
       <c r="C9" t="n">
-        <v>1.027702333580095</v>
+        <v>1.027702333580094</v>
       </c>
       <c r="D9" t="n">
-        <v>1.194409283156014</v>
+        <v>1.194409283156016</v>
       </c>
       <c r="E9" t="n">
-        <v>1.06374815931999</v>
+        <v>1.030649607137067</v>
       </c>
       <c r="F9" t="n">
-        <v>1.09368912287661</v>
+        <v>0.763088384636054</v>
       </c>
       <c r="G9" t="n">
-        <v>1.659837010744763</v>
+        <v>1.659837061676386</v>
       </c>
       <c r="H9" t="n">
         <v>1.272447561265351</v>
       </c>
       <c r="I9" t="n">
-        <v>1.097693911191266</v>
+        <v>1.097693911191267</v>
       </c>
       <c r="J9" t="n">
         <v>1.387476595821969</v>
@@ -2961,31 +2961,31 @@
         <v>1.25919082644645</v>
       </c>
       <c r="O9" t="n">
-        <v>1.274438913014941</v>
+        <v>1.274438913014942</v>
       </c>
       <c r="P9" t="n">
-        <v>1.433056795759119</v>
+        <v>1.43305679575912</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.161189506286895</v>
+        <v>1.161189506286893</v>
       </c>
       <c r="R9" t="n">
-        <v>1.147105508612101</v>
+        <v>1.1471055086121</v>
       </c>
       <c r="S9" t="n">
-        <v>1.409691005752587</v>
+        <v>1.409691005752588</v>
       </c>
       <c r="T9" t="n">
-        <v>1.199421773036504</v>
+        <v>1.199421773036503</v>
       </c>
       <c r="U9" t="n">
-        <v>1.374481331844419</v>
+        <v>1.37448133184442</v>
       </c>
       <c r="V9" t="n">
-        <v>1.045078533853758</v>
+        <v>1.210571212420967</v>
       </c>
       <c r="W9" t="n">
-        <v>1.437903381035696</v>
+        <v>1.437903381035697</v>
       </c>
       <c r="X9" t="n">
         <v>1.293885318382863</v>
@@ -2994,7 +2994,7 @@
         <v>1.250416644986838</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.183541401805424</v>
+        <v>1.097077557090371</v>
       </c>
       <c r="AA9" t="n">
         <v>1.282890723621482</v>
@@ -3169,46 +3169,46 @@
         <v>3.004461522372055</v>
       </c>
       <c r="C2" t="n">
-        <v>2.986088133746044</v>
+        <v>2.986088133746045</v>
       </c>
       <c r="D2" t="n">
         <v>3.012077744015567</v>
       </c>
       <c r="E2" t="n">
-        <v>2.997074426008705</v>
+        <v>2.997074426008706</v>
       </c>
       <c r="F2" t="n">
-        <v>2.995715568935441</v>
+        <v>2.995715568935442</v>
       </c>
       <c r="G2" t="n">
-        <v>3.046582188767973</v>
+        <v>3.046582188767974</v>
       </c>
       <c r="H2" t="n">
-        <v>3.011504973500459</v>
+        <v>3.01150497350046</v>
       </c>
       <c r="I2" t="n">
         <v>3.001245374598829</v>
       </c>
       <c r="J2" t="n">
-        <v>3.023674032871155</v>
+        <v>3.023674032871156</v>
       </c>
       <c r="K2" t="n">
         <v>3.010015992951109</v>
       </c>
       <c r="L2" t="n">
-        <v>3.017117430566018</v>
+        <v>3.017117430566019</v>
       </c>
       <c r="M2" t="n">
-        <v>3.031727821250707</v>
+        <v>3.031727821250708</v>
       </c>
       <c r="N2" t="n">
         <v>3.00783775106837</v>
       </c>
       <c r="O2" t="n">
-        <v>3.39415612297884</v>
+        <v>3.394156122978841</v>
       </c>
       <c r="P2" t="n">
-        <v>3.024530012592383</v>
+        <v>3.024530012592384</v>
       </c>
       <c r="Q2" t="n">
         <v>2.995478381325885</v>
@@ -3217,31 +3217,31 @@
         <v>3.001772016351285</v>
       </c>
       <c r="S2" t="n">
-        <v>3.024363992454243</v>
+        <v>3.024363992454244</v>
       </c>
       <c r="T2" t="n">
         <v>3.006960585789981</v>
       </c>
       <c r="U2" t="n">
-        <v>3.786018250906675</v>
+        <v>3.786018250906677</v>
       </c>
       <c r="V2" t="n">
         <v>3.000075877271722</v>
       </c>
       <c r="W2" t="n">
-        <v>3.788459942473353</v>
+        <v>3.788459942473355</v>
       </c>
       <c r="X2" t="n">
-        <v>3.025046383576482</v>
+        <v>3.025046383576484</v>
       </c>
       <c r="Y2" t="n">
         <v>3.024586549025551</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.288555869064394</v>
+        <v>3.288555869064393</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.015667963051718</v>
+        <v>3.015667963051719</v>
       </c>
       <c r="AB2" t="n">
         <v>3.02721069411092</v>
@@ -3257,7 +3257,7 @@
         <v>2.173059757386417</v>
       </c>
       <c r="C3" t="n">
-        <v>2.09453550446405</v>
+        <v>2.094535504464051</v>
       </c>
       <c r="D3" t="n">
         <v>2.228442853667764</v>
@@ -3269,49 +3269,49 @@
         <v>2.111374502855864</v>
       </c>
       <c r="G3" t="n">
-        <v>2.472468785825284</v>
+        <v>2.472468785825285</v>
       </c>
       <c r="H3" t="n">
-        <v>2.224984486459965</v>
+        <v>2.224984486459966</v>
       </c>
       <c r="I3" t="n">
-        <v>2.151066998670873</v>
+        <v>2.151066998670874</v>
       </c>
       <c r="J3" t="n">
-        <v>2.310127182743762</v>
+        <v>2.310127182743765</v>
       </c>
       <c r="K3" t="n">
         <v>2.212578918197877</v>
       </c>
       <c r="L3" t="n">
-        <v>2.263783147142165</v>
+        <v>2.263783147142166</v>
       </c>
       <c r="M3" t="n">
         <v>2.372929694476344</v>
       </c>
       <c r="N3" t="n">
-        <v>2.197912388989842</v>
+        <v>2.197912388989841</v>
       </c>
       <c r="O3" t="n">
-        <v>2.825446253079725</v>
+        <v>2.825446253079728</v>
       </c>
       <c r="P3" t="n">
-        <v>2.315670518064922</v>
+        <v>2.315670518064923</v>
       </c>
       <c r="Q3" t="n">
         <v>2.109497106333171</v>
       </c>
       <c r="R3" t="n">
-        <v>2.15497202164024</v>
+        <v>2.154972021640239</v>
       </c>
       <c r="S3" t="n">
-        <v>2.31465845625416</v>
+        <v>2.314658456254162</v>
       </c>
       <c r="T3" t="n">
         <v>2.191929495386156</v>
       </c>
       <c r="U3" t="n">
-        <v>3.538095018000248</v>
+        <v>3.53809501800025</v>
       </c>
       <c r="V3" t="n">
         <v>2.141595922249938</v>
@@ -3323,16 +3323,16 @@
         <v>2.320992281252635</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.317163466559465</v>
+        <v>2.317163466559466</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.661623366804278</v>
+        <v>2.661623366804279</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.253630665787899</v>
+        <v>2.253630665787898</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.337096293171879</v>
+        <v>2.33709629317188</v>
       </c>
     </row>
     <row r="4">
@@ -3345,82 +3345,82 @@
         <v>0.5194924583398972</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4189311713353026</v>
+        <v>0.4189311713353023</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6055211854383975</v>
+        <v>0.6055211854383972</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4360518066836359</v>
+        <v>0.4360518066836363</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4207028909359773</v>
+        <v>0.4207028909359777</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9952647617456543</v>
+        <v>0.995264761745654</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5990514789828287</v>
+        <v>0.599051478982829</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4831645897402288</v>
+        <v>0.4831645897402297</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7360551541890911</v>
+        <v>0.7360551541890907</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5822327587130135</v>
+        <v>0.5822327587130141</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6624467633961182</v>
+        <v>0.6624467633961186</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8339478684495217</v>
+        <v>0.833947868449522</v>
       </c>
       <c r="N4" t="n">
-        <v>0.557628514606717</v>
+        <v>0.5576285146067166</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5392102682237352</v>
+        <v>0.5392102682237375</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7461752873401194</v>
+        <v>0.7461752873401216</v>
       </c>
       <c r="Q4" t="n">
         <v>0.4180237477743471</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4891132506013964</v>
+        <v>0.4891132506013963</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7443000135068096</v>
+        <v>0.7443000135068099</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5477205292713196</v>
+        <v>0.5477205292713206</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6691212197734867</v>
+        <v>0.6691212197734892</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4669220013426289</v>
+        <v>0.4669220013426283</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7707420260707237</v>
+        <v>0.7707420260707232</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7520079351479014</v>
+        <v>0.7520079351479034</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7423895446102687</v>
+        <v>0.7423895446102702</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.5609520387196583</v>
+        <v>0.5609520387196578</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.6460743610340999</v>
+        <v>0.6460743610341003</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7752084129551088</v>
+        <v>0.7752084129551091</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.250880017482547</v>
+        <v>4.250880017482555</v>
       </c>
       <c r="C5" t="n">
         <v>2.716515263958426</v>
       </c>
       <c r="D5" t="n">
-        <v>6.30400520972464</v>
+        <v>6.304005209724657</v>
       </c>
       <c r="E5" t="n">
-        <v>3.034732089323252</v>
+        <v>3.034732089323258</v>
       </c>
       <c r="F5" t="n">
-        <v>2.884545147431711</v>
+        <v>2.88454514743171</v>
       </c>
       <c r="G5" t="n">
-        <v>12.03954429175319</v>
+        <v>12.03954429175318</v>
       </c>
       <c r="H5" t="n">
-        <v>6.515812912789053</v>
+        <v>6.515812912789048</v>
       </c>
       <c r="I5" t="n">
-        <v>4.106400647423945</v>
+        <v>4.106400647423959</v>
       </c>
       <c r="J5" t="n">
-        <v>8.061101969583662</v>
+        <v>8.061101969583666</v>
       </c>
       <c r="K5" t="n">
-        <v>5.296611026910784</v>
+        <v>5.296611026910789</v>
       </c>
       <c r="L5" t="n">
-        <v>6.985278898383141</v>
+        <v>6.985278898383148</v>
       </c>
       <c r="M5" t="n">
-        <v>10.72135891000642</v>
+        <v>10.72135891000643</v>
       </c>
       <c r="N5" t="n">
-        <v>6.870557366239943</v>
+        <v>6.870557366239977</v>
       </c>
       <c r="O5" t="n">
-        <v>4.364862723036246</v>
+        <v>4.364862723036253</v>
       </c>
       <c r="P5" t="n">
-        <v>7.939330597422596</v>
+        <v>7.939330597422645</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.741507863735047</v>
+        <v>2.741507863735054</v>
       </c>
       <c r="R5" t="n">
-        <v>4.287457058936381</v>
+        <v>4.287457058936383</v>
       </c>
       <c r="S5" t="n">
-        <v>7.9957291920384</v>
+        <v>7.995729192038427</v>
       </c>
       <c r="T5" t="n">
-        <v>5.285879565295793</v>
+        <v>5.285879565295808</v>
       </c>
       <c r="U5" t="n">
-        <v>6.986474419157248</v>
+        <v>6.986474419157287</v>
       </c>
       <c r="V5" t="n">
-        <v>3.287079100036929</v>
+        <v>3.287079100036909</v>
       </c>
       <c r="W5" t="n">
-        <v>9.004767830683637</v>
+        <v>9.004767830683626</v>
       </c>
       <c r="X5" t="n">
-        <v>8.890512286180906</v>
+        <v>8.890512286180927</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.515202744283023</v>
+        <v>8.515202744283048</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.712802498494617</v>
+        <v>4.712802498494623</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.795433390165973</v>
+        <v>6.795433390165971</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.992378700188789</v>
+        <v>9.992378700188778</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6406812015236064</v>
+        <v>0.54506922317303</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4445079361684331</v>
+        <v>0.444507936168434</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7267099286221055</v>
+        <v>0.7267099286221075</v>
       </c>
       <c r="E6" t="n">
-        <v>0.461628571516767</v>
+        <v>0.4616285715167681</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4462796557691087</v>
+        <v>0.5418916341196871</v>
       </c>
       <c r="G6" t="n">
-        <v>1.116453504929362</v>
+        <v>1.020841526578786</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6246282438159602</v>
+        <v>0.62462824381596</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6043533329239392</v>
+        <v>0.5087413545733611</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8572438973727989</v>
+        <v>0.8572438973728007</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6078095235461437</v>
+        <v>0.7034215018967238</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7836355065798275</v>
+        <v>0.6880235282292488</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9551366116332307</v>
+        <v>0.9551366116332306</v>
       </c>
       <c r="N6" t="n">
         <v>0.583859055334176</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6651811636259912</v>
+        <v>0.565440808951196</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8721273352708784</v>
+        <v>0.8721273352708806</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5392124909580551</v>
+        <v>0.5392124909580569</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6103019937851053</v>
+        <v>0.6103019937851057</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7698767783399384</v>
+        <v>0.7698767783399407</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5732972941044512</v>
+        <v>0.5732972941044526</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7947343107077328</v>
+        <v>0.6991223323571579</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5881107445263383</v>
+        <v>0.5881107445263382</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8967158406222331</v>
+        <v>0.8013625678895197</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7775846999810334</v>
+        <v>0.7775846999810357</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.7749376884100043</v>
+        <v>0.7749376884100051</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6821407819033669</v>
+        <v>0.5865288035527889</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6716511258672307</v>
+        <v>0.7672631042178081</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8026740053563399</v>
+        <v>0.8026740053563408</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.629343297354217</v>
+        <v>0.6293432973542171</v>
       </c>
       <c r="C7" t="n">
         <v>0.5287820103496221</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7153720244527165</v>
+        <v>0.7153720244527172</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5459026456979558</v>
+        <v>0.5459026456979561</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5305537299502973</v>
+        <v>0.5305537299502975</v>
       </c>
       <c r="G7" t="n">
-        <v>1.105115600759971</v>
+        <v>1.105115600759972</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7089023179971466</v>
+        <v>0.7089023179971471</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5930154287545477</v>
+        <v>0.5930154287545497</v>
       </c>
       <c r="J7" t="n">
-        <v>0.845905993203409</v>
+        <v>0.8459059932034101</v>
       </c>
       <c r="K7" t="n">
-        <v>0.692083597727332</v>
+        <v>0.6920835977273336</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7722976024104367</v>
+        <v>0.7722976024104375</v>
       </c>
       <c r="M7" t="n">
-        <v>0.94379870746384</v>
+        <v>0.9437987074638402</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6674793536210361</v>
+        <v>0.6674793536210367</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6487267838486566</v>
+        <v>0.6487267838486578</v>
       </c>
       <c r="P7" t="n">
-        <v>0.855691802965037</v>
+        <v>0.8556918029650412</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5278745867886657</v>
+        <v>0.5278745867886666</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5989640896157155</v>
+        <v>0.5989640896157157</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8541508525211279</v>
+        <v>0.8541508525211295</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6575713682856396</v>
+        <v>0.657571368285641</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7827590448910969</v>
+        <v>0.7827590448910993</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5767728403569473</v>
+        <v>0.5767728403569482</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8805928650850421</v>
+        <v>0.880592865085042</v>
       </c>
       <c r="X7" t="n">
-        <v>0.8618587741622203</v>
+        <v>0.8618587741622215</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8566647313751269</v>
+        <v>0.8566647313751281</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.670802877733977</v>
+        <v>0.6708028777339776</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.755925200048419</v>
+        <v>0.7559252000484195</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8850592519694283</v>
+        <v>0.8850592519694279</v>
       </c>
     </row>
     <row r="8">
@@ -3694,82 +3694,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6776546892267045</v>
+        <v>0.6776546892267041</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7023809178829905</v>
+        <v>0.7023809178829913</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8889709319860849</v>
+        <v>0.8889709319860859</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7195015532313249</v>
+        <v>0.652789646911605</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5983834524857571</v>
+        <v>0.5983834524857577</v>
       </c>
       <c r="G8" t="n">
-        <v>1.278714508293342</v>
+        <v>1.304693690830408</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8825012255305166</v>
+        <v>0.8825012255305175</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7666143362879186</v>
+        <v>0.7666143362879191</v>
       </c>
       <c r="J8" t="n">
-        <v>1.019504900736778</v>
+        <v>1.01950490073678</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8656825052607009</v>
+        <v>0.8656825052607027</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9458965099438053</v>
+        <v>0.9458965099438067</v>
       </c>
       <c r="M8" t="n">
-        <v>1.117397614997209</v>
+        <v>1.117397614997196</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7439594763481245</v>
+        <v>0.7439594763481253</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7522303152490959</v>
+        <v>0.7522303152490972</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9526531946687593</v>
+        <v>0.9526531946687623</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5515641223117047</v>
+        <v>0.5515641223117054</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7725629971490843</v>
+        <v>0.7725629971490857</v>
       </c>
       <c r="S8" t="n">
-        <v>1.027749760054495</v>
+        <v>1.027749760054499</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8311702758190077</v>
+        <v>0.8311702758190096</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8796793822534855</v>
+        <v>0.8956093026040137</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7503717478903178</v>
+        <v>0.7158697510967524</v>
       </c>
       <c r="W8" t="n">
-        <v>1.054216395110185</v>
+        <v>1.054216395110186</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8970311593873133</v>
+        <v>0.8970311593873149</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.15443240872545</v>
+        <v>1.154432408725452</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.844401785267346</v>
+        <v>0.7167869896888343</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.9295241075817883</v>
+        <v>0.9295241075817893</v>
       </c>
       <c r="AB8" t="n">
         <v>1.189531445893212</v>
@@ -3782,28 +3782,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9207359062422041</v>
+        <v>0.9207359062422042</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9419317492796515</v>
+        <v>0.9419317492796514</v>
       </c>
       <c r="D9" t="n">
-        <v>1.128521763382745</v>
+        <v>1.128521763382746</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9590523846279845</v>
+        <v>0.9309513752228976</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9437034688803261</v>
+        <v>0.6630199863124161</v>
       </c>
       <c r="G9" t="n">
-        <v>1.518265339690003</v>
+        <v>1.518265391133209</v>
       </c>
       <c r="H9" t="n">
         <v>1.122052056927177</v>
       </c>
       <c r="I9" t="n">
-        <v>1.006165167684576</v>
+        <v>1.006165167684577</v>
       </c>
       <c r="J9" t="n">
         <v>1.25905573213344</v>
@@ -3815,19 +3815,19 @@
         <v>1.185447341340466</v>
       </c>
       <c r="M9" t="n">
-        <v>1.356948446393871</v>
+        <v>1.35694844639387</v>
       </c>
       <c r="N9" t="n">
-        <v>1.080629092551068</v>
+        <v>1.080629092551067</v>
       </c>
       <c r="O9" t="n">
         <v>1.10256106812809</v>
       </c>
       <c r="P9" t="n">
-        <v>1.318301557039536</v>
+        <v>1.318301557039537</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9410243771619015</v>
+        <v>0.9410243771619013</v>
       </c>
       <c r="R9" t="n">
         <v>1.012113828545745</v>
@@ -3839,28 +3839,28 @@
         <v>1.070721107215669</v>
       </c>
       <c r="U9" t="n">
-        <v>1.196546145468373</v>
+        <v>1.196546145468375</v>
       </c>
       <c r="V9" t="n">
-        <v>0.989922579286978</v>
+        <v>1.130427605398371</v>
       </c>
       <c r="W9" t="n">
         <v>1.293742604015072</v>
       </c>
       <c r="X9" t="n">
-        <v>1.27500851309225</v>
+        <v>1.275008513092251</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.269814470305156</v>
+        <v>1.269814470305157</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.083952616664007</v>
+        <v>1.010543914742631</v>
       </c>
       <c r="AA9" t="n">
         <v>1.169074938978449</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.298208990899458</v>
+        <v>1.298208990899459</v>
       </c>
     </row>
   </sheetData>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.996197650045963</v>
+        <v>2.996197650045962</v>
       </c>
       <c r="C2" t="n">
         <v>2.981618302793335</v>
@@ -4038,19 +4038,19 @@
         <v>2.98703970837939</v>
       </c>
       <c r="F2" t="n">
-        <v>2.991549453756451</v>
+        <v>2.991549453756452</v>
       </c>
       <c r="G2" t="n">
         <v>3.03161975548442</v>
       </c>
       <c r="H2" t="n">
-        <v>3.002704845886673</v>
+        <v>3.002704845886672</v>
       </c>
       <c r="I2" t="n">
         <v>2.995999909367459</v>
       </c>
       <c r="J2" t="n">
-        <v>3.013363057621168</v>
+        <v>3.013363057621167</v>
       </c>
       <c r="K2" t="n">
         <v>3.008489833163484</v>
@@ -4065,13 +4065,13 @@
         <v>2.99859353903736</v>
       </c>
       <c r="O2" t="n">
-        <v>3.375823748679801</v>
+        <v>3.375823748679799</v>
       </c>
       <c r="P2" t="n">
-        <v>3.015836776185737</v>
+        <v>3.015836776185736</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.992831400444062</v>
+        <v>2.992831400444063</v>
       </c>
       <c r="R2" t="n">
         <v>2.994454743736578</v>
@@ -4089,22 +4089,22 @@
         <v>3.00270860966322</v>
       </c>
       <c r="W2" t="n">
-        <v>3.779102781868701</v>
+        <v>3.779102781868702</v>
       </c>
       <c r="X2" t="n">
-        <v>3.020593795065113</v>
+        <v>3.020593795065112</v>
       </c>
       <c r="Y2" t="n">
         <v>3.037819482443747</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.276777993790597</v>
+        <v>3.276777993790596</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.011440896589035</v>
+        <v>3.011440896589036</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.017126130848846</v>
+        <v>3.017126130848845</v>
       </c>
     </row>
     <row r="3">
@@ -4114,31 +4114,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.154082243936775</v>
+        <v>2.154082243936776</v>
       </c>
       <c r="C3" t="n">
-        <v>2.104415172951753</v>
+        <v>2.104415172951752</v>
       </c>
       <c r="D3" t="n">
-        <v>2.163460044312281</v>
+        <v>2.163460044312282</v>
       </c>
       <c r="E3" t="n">
         <v>2.089186064912585</v>
       </c>
       <c r="F3" t="n">
-        <v>2.121772900909309</v>
+        <v>2.12177290090931</v>
       </c>
       <c r="G3" t="n">
-        <v>2.405431967140041</v>
+        <v>2.40543196714004</v>
       </c>
       <c r="H3" t="n">
-        <v>2.202249559387649</v>
+        <v>2.202249559387648</v>
       </c>
       <c r="I3" t="n">
         <v>2.15367026575878</v>
       </c>
       <c r="J3" t="n">
-        <v>2.276460963403592</v>
+        <v>2.276460963403593</v>
       </c>
       <c r="K3" t="n">
         <v>2.241725073995902</v>
@@ -4147,25 +4147,25 @@
         <v>2.226776084961259</v>
       </c>
       <c r="M3" t="n">
-        <v>2.318713071783407</v>
+        <v>2.318713071783406</v>
       </c>
       <c r="N3" t="n">
-        <v>2.172078421593502</v>
+        <v>2.172078421593501</v>
       </c>
       <c r="O3" t="n">
         <v>2.77736998449239</v>
       </c>
       <c r="P3" t="n">
-        <v>2.293388334262338</v>
+        <v>2.293388334262339</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.130617357289229</v>
+        <v>2.13061735728923</v>
       </c>
       <c r="R3" t="n">
         <v>2.14285636474036</v>
       </c>
       <c r="S3" t="n">
-        <v>2.282700479234167</v>
+        <v>2.282700479234166</v>
       </c>
       <c r="T3" t="n">
         <v>2.173115634493192</v>
@@ -4177,7 +4177,7 @@
         <v>2.200069565706428</v>
       </c>
       <c r="W3" t="n">
-        <v>3.585016891974581</v>
+        <v>3.585016891974582</v>
       </c>
       <c r="X3" t="n">
         <v>2.328861016512149</v>
@@ -4192,7 +4192,7 @@
         <v>2.263689991750078</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.304824509403475</v>
+        <v>2.304824509403474</v>
       </c>
     </row>
     <row r="4">
@@ -4202,82 +4202,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4824528929032864</v>
+        <v>0.4824528929032859</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4283098587183588</v>
+        <v>0.4283098587183589</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4961688559928658</v>
+        <v>0.4961688559928659</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3790097289180531</v>
+        <v>0.3790097289180533</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4299493775373434</v>
+        <v>0.4299493775373432</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8825618688042404</v>
+        <v>0.8825618688042403</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5559546633820959</v>
+        <v>0.5559546633820954</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4802193209744013</v>
+        <v>0.480219320974402</v>
       </c>
       <c r="J4" t="n">
         <v>0.6759891540163162</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6212987558993038</v>
+        <v>0.6212987558993044</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5972636017914933</v>
+        <v>0.5972636017914936</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7423317188519397</v>
+        <v>0.7423317188519393</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5095155612245426</v>
+        <v>0.5095155612245422</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4757354414055011</v>
+        <v>0.4757354414055006</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7042858570964063</v>
+        <v>0.7042858570964061</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4444295550985315</v>
+        <v>0.4444295550985317</v>
       </c>
       <c r="R4" t="n">
         <v>0.4627659643622767</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6866128311540083</v>
+        <v>0.6866128311540081</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5107675794632582</v>
+        <v>0.5107675794632575</v>
       </c>
       <c r="U4" t="n">
         <v>0.6908181809305095</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5536203868935974</v>
+        <v>0.5536203868935975</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7662207495264759</v>
+        <v>0.7662207495264758</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7580185736757731</v>
+        <v>0.7580185736757729</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.9499188700053717</v>
+        <v>0.9499188700053725</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.5179622034254079</v>
+        <v>0.5179622034254078</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.6546323748471885</v>
+        <v>0.6546323748471892</v>
       </c>
       <c r="AB4" t="n">
         <v>0.7175338091422727</v>
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.713188526497301</v>
+        <v>3.713188526497306</v>
       </c>
       <c r="C5" t="n">
-        <v>3.048360798765799</v>
+        <v>3.048360798765801</v>
       </c>
       <c r="D5" t="n">
-        <v>4.324418532904727</v>
+        <v>4.324418532904734</v>
       </c>
       <c r="E5" t="n">
-        <v>2.124344566359891</v>
+        <v>2.124344566359896</v>
       </c>
       <c r="F5" t="n">
         <v>3.232875567971309</v>
       </c>
       <c r="G5" t="n">
-        <v>10.03337050419145</v>
+        <v>10.03337050419147</v>
       </c>
       <c r="H5" t="n">
-        <v>5.907195812256417</v>
+        <v>5.907195812256428</v>
       </c>
       <c r="I5" t="n">
-        <v>4.191549618790944</v>
+        <v>4.191549618790947</v>
       </c>
       <c r="J5" t="n">
-        <v>7.073894644462063</v>
+        <v>7.073894644462064</v>
       </c>
       <c r="K5" t="n">
-        <v>6.123772653847677</v>
+        <v>6.123772653847683</v>
       </c>
       <c r="L5" t="n">
-        <v>5.821828257405916</v>
+        <v>5.821828257405921</v>
       </c>
       <c r="M5" t="n">
-        <v>8.839153622629514</v>
+        <v>8.839153622629516</v>
       </c>
       <c r="N5" t="n">
-        <v>7.079301301114688</v>
+        <v>7.079301301114704</v>
       </c>
       <c r="O5" t="n">
         <v>3.546769519611418</v>
       </c>
       <c r="P5" t="n">
-        <v>7.191343511575704</v>
+        <v>7.191343511575716</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.330994889558022</v>
+        <v>3.330994889558035</v>
       </c>
       <c r="R5" t="n">
-        <v>3.993770268550097</v>
+        <v>3.993770268550109</v>
       </c>
       <c r="S5" t="n">
-        <v>7.126927808081172</v>
+        <v>7.126927808081179</v>
       </c>
       <c r="T5" t="n">
-        <v>4.806167310536141</v>
+        <v>4.806167310536143</v>
       </c>
       <c r="U5" t="n">
-        <v>7.26327568764047</v>
+        <v>7.263275687640431</v>
       </c>
       <c r="V5" t="n">
-        <v>4.761923735330457</v>
+        <v>4.761923735330461</v>
       </c>
       <c r="W5" t="n">
-        <v>9.134382683999236</v>
+        <v>9.134382683999231</v>
       </c>
       <c r="X5" t="n">
-        <v>8.930226645490213</v>
+        <v>8.930226645490221</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.57530163475537</v>
+        <v>12.57530163475539</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.007244869597876</v>
+        <v>4.007244869597875</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.18130564318434</v>
+        <v>7.181305643184355</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.953870218638183</v>
+        <v>8.953870218638189</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5118133837647919</v>
+        <v>0.6009406332876814</v>
       </c>
       <c r="C6" t="n">
         <v>0.4576703495798647</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5255293468543712</v>
+        <v>0.5255293468543714</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4083702197795581</v>
+        <v>0.4974974693024487</v>
       </c>
       <c r="F6" t="n">
-        <v>0.459309868398849</v>
+        <v>0.4593098683988491</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9119223596657458</v>
+        <v>1.001049609188637</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6744424037664907</v>
+        <v>0.5853151542436009</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5095798118359076</v>
+        <v>0.5095798118359078</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7053496448778226</v>
+        <v>0.7944768944007119</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7397864962836984</v>
+        <v>0.7397864962836986</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6266240926529996</v>
+        <v>0.7157513421758889</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7716922097134453</v>
+        <v>0.7716922097134442</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5400712590843675</v>
+        <v>0.5400712590843622</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5062911392653118</v>
+        <v>0.5991224847796439</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8276493797184509</v>
+        <v>0.731068227635386</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5629172954829263</v>
+        <v>0.562917295482927</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5812537047466729</v>
+        <v>0.5812537047466727</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8051005715384034</v>
+        <v>0.8051005715384031</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5401280703247635</v>
+        <v>0.6292553198476534</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8119776881346924</v>
+        <v>0.7228504386118024</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6721081272779924</v>
+        <v>0.5829808777551028</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8896112412308939</v>
+        <v>0.889611241230894</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7873790645372768</v>
+        <v>0.7873790645372784</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9855473812636023</v>
+        <v>0.9855473812635986</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6364499438098034</v>
+        <v>0.6364499438098036</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.7731201152315844</v>
+        <v>0.7731201152315847</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7487768128145222</v>
+        <v>0.7487768128145221</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5882581580458346</v>
+        <v>0.5882581580458345</v>
       </c>
       <c r="C7" t="n">
-        <v>0.534115123860908</v>
+        <v>0.5341151238609082</v>
       </c>
       <c r="D7" t="n">
         <v>0.6019741211354144</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4848149940606017</v>
+        <v>0.4848149940606015</v>
       </c>
       <c r="F7" t="n">
         <v>0.535754642679892</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9883671339467872</v>
+        <v>0.9883671339467879</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6617599285246443</v>
+        <v>0.6617599285246439</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5860245861169507</v>
+        <v>0.586024586116951</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7817944191588652</v>
+        <v>0.7817944191588648</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7271040210418515</v>
+        <v>0.727104021041852</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7030688669340428</v>
+        <v>0.7030688669340432</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8481369839944873</v>
+        <v>0.8481369839944872</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6153208263670914</v>
+        <v>0.6153208263670911</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5812066523964425</v>
+        <v>0.5812066523964419</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8097570680873486</v>
+        <v>0.8097570680873492</v>
       </c>
       <c r="Q7" t="n">
         <v>0.5502348202410801</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5685712295048263</v>
+        <v>0.568571229504826</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7924180962965571</v>
+        <v>0.7924180962965576</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6165728446058061</v>
+        <v>0.6165728446058059</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7981121573892306</v>
+        <v>0.7981121573892312</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6594256520361462</v>
+        <v>0.6594256520361457</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8720260146690244</v>
+        <v>0.8720260146690235</v>
       </c>
       <c r="X7" t="n">
-        <v>0.8638238388183214</v>
+        <v>0.8638238388183208</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.058395901967707</v>
+        <v>1.058395901967709</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6237674685679572</v>
+        <v>0.6237674685679563</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.7604376399897376</v>
+        <v>0.7604376399897382</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8233390742848229</v>
+        <v>0.8233390742848224</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6326301055396591</v>
+        <v>0.6326301055396588</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6974566522661538</v>
+        <v>0.6974566522661535</v>
       </c>
       <c r="D8" t="n">
         <v>0.7653156495406604</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6481565224658482</v>
+        <v>0.5848087300322315</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5986606604422881</v>
+        <v>0.5986606604422879</v>
       </c>
       <c r="G8" t="n">
-        <v>1.151708662352035</v>
+        <v>1.176377779961457</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8251014569298915</v>
+        <v>0.8251014569298907</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7493661145221968</v>
+        <v>0.7493661145221971</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9451359475641117</v>
+        <v>0.9451359475641116</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8904455494470983</v>
+        <v>0.8904455494470989</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8664103953392899</v>
+        <v>0.8664103953392894</v>
       </c>
       <c r="M8" t="n">
-        <v>1.011478512399735</v>
+        <v>1.011478512399705</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6864410263651088</v>
+        <v>0.6864410263651083</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6780041282890835</v>
+        <v>0.6780041282890831</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9003423079575558</v>
+        <v>0.9003423079575557</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5712265297626865</v>
+        <v>0.5712265297626872</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7319127579100722</v>
+        <v>0.7319127579100719</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9557596247018042</v>
+        <v>0.9557596247018043</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7799143730110534</v>
+        <v>0.7799143730110528</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8888112452902182</v>
+        <v>0.9039113214632002</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8227671804413932</v>
+        <v>0.7895252947429923</v>
       </c>
       <c r="W8" t="n">
         <v>1.035390923913659</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8957193467700426</v>
+        <v>0.8957193467700435</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.338900606796016</v>
+        <v>1.338900606796018</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.7871089969732035</v>
+        <v>0.6659294950254572</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.9237791683949846</v>
+        <v>0.9237791683949843</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.110954277940282</v>
+        <v>1.110954277940281</v>
       </c>
     </row>
     <row r="9">
@@ -4642,28 +4642,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8439704780565128</v>
+        <v>0.8439704780565127</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9000565934645985</v>
+        <v>0.9000565934645987</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9679155907391043</v>
+        <v>0.9679155907391039</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8507564636642916</v>
+        <v>0.8253160537327529</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9016961122835818</v>
+        <v>0.647587790266825</v>
       </c>
       <c r="G9" t="n">
-        <v>1.354308603550477</v>
+        <v>1.354308640183167</v>
       </c>
       <c r="H9" t="n">
         <v>1.027701398128334</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9519660557206395</v>
+        <v>0.9519660557206391</v>
       </c>
       <c r="J9" t="n">
         <v>1.147735888762555</v>
@@ -4675,13 +4675,13 @@
         <v>1.069010336537732</v>
       </c>
       <c r="M9" t="n">
-        <v>1.214078453598177</v>
+        <v>1.214078453598176</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9812622959707803</v>
+        <v>0.9812622959707796</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9840120207668328</v>
+        <v>0.9840120207668319</v>
       </c>
       <c r="P9" t="n">
         <v>1.220507042947953</v>
@@ -4690,31 +4690,31 @@
         <v>0.9161763264774587</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9345126991085149</v>
+        <v>0.9345126991085143</v>
       </c>
       <c r="S9" t="n">
         <v>1.158359565900247</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9825143142094942</v>
+        <v>0.9825143142094953</v>
       </c>
       <c r="U9" t="n">
         <v>1.165236682496535</v>
       </c>
       <c r="V9" t="n">
-        <v>1.025367121639836</v>
+        <v>1.152569123534637</v>
       </c>
       <c r="W9" t="n">
-        <v>1.237967484272713</v>
+        <v>1.237967484272712</v>
       </c>
       <c r="X9" t="n">
-        <v>1.229765308422009</v>
+        <v>1.22976530842201</v>
       </c>
       <c r="Y9" t="n">
         <v>1.424337371571397</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.9897089381716463</v>
+        <v>0.9232505774719237</v>
       </c>
       <c r="AA9" t="n">
         <v>1.126379109593427</v>
@@ -4886,82 +4886,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.929303146848722</v>
+        <v>2.929303146848725</v>
       </c>
       <c r="C2" t="n">
         <v>2.920843911762379</v>
       </c>
       <c r="D2" t="n">
-        <v>2.934856233817719</v>
+        <v>2.93485623381772</v>
       </c>
       <c r="E2" t="n">
-        <v>2.925817958404967</v>
+        <v>2.925817958404968</v>
       </c>
       <c r="F2" t="n">
         <v>2.926845505071711</v>
       </c>
       <c r="G2" t="n">
-        <v>2.944119990629819</v>
+        <v>2.94411999062982</v>
       </c>
       <c r="H2" t="n">
-        <v>2.933143209806445</v>
+        <v>2.933143209806447</v>
       </c>
       <c r="I2" t="n">
-        <v>2.930541326481007</v>
+        <v>2.93054132648101</v>
       </c>
       <c r="J2" t="n">
-        <v>2.937383076244428</v>
+        <v>2.937383076244431</v>
       </c>
       <c r="K2" t="n">
-        <v>2.936125722671817</v>
+        <v>2.936125722671818</v>
       </c>
       <c r="L2" t="n">
-        <v>2.928506719718971</v>
+        <v>2.928506719718972</v>
       </c>
       <c r="M2" t="n">
-        <v>2.941003278922258</v>
+        <v>2.941003278922257</v>
       </c>
       <c r="N2" t="n">
-        <v>2.932579329073904</v>
+        <v>2.932579329073905</v>
       </c>
       <c r="O2" t="n">
-        <v>3.284433558664378</v>
+        <v>3.28443355866438</v>
       </c>
       <c r="P2" t="n">
-        <v>2.931217481305689</v>
+        <v>2.93121748130569</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.929472867972615</v>
+        <v>2.929472867972617</v>
       </c>
       <c r="R2" t="n">
-        <v>2.91509141466986</v>
+        <v>2.915091414669865</v>
       </c>
       <c r="S2" t="n">
-        <v>2.935335026056152</v>
+        <v>2.935335026056159</v>
       </c>
       <c r="T2" t="n">
-        <v>2.928579252324324</v>
+        <v>2.928579252324325</v>
       </c>
       <c r="U2" t="n">
-        <v>3.701533405941499</v>
+        <v>3.701533405941505</v>
       </c>
       <c r="V2" t="n">
-        <v>2.92944916689298</v>
+        <v>2.929449166892982</v>
       </c>
       <c r="W2" t="n">
-        <v>3.715848905475077</v>
+        <v>3.715848905475082</v>
       </c>
       <c r="X2" t="n">
-        <v>2.942789750409483</v>
+        <v>2.942789750409489</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.933320063376998</v>
+        <v>2.933320063377</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.198227346092242</v>
+        <v>3.198227346092243</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.944605562718902</v>
+        <v>2.944605562718903</v>
       </c>
       <c r="AB2" t="n">
         <v>2.937879793012642</v>
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.006906762477029</v>
+        <v>2.006906762477032</v>
       </c>
       <c r="C3" t="n">
-        <v>1.999120309856943</v>
+        <v>1.999120309856942</v>
       </c>
       <c r="D3" t="n">
-        <v>2.046814673132824</v>
+        <v>2.046814673132828</v>
       </c>
       <c r="E3" t="n">
-        <v>1.982168628914962</v>
+        <v>1.982168628914964</v>
       </c>
       <c r="F3" t="n">
-        <v>1.989530833322794</v>
+        <v>1.989530833322798</v>
       </c>
       <c r="G3" t="n">
-        <v>2.111774522487396</v>
+        <v>2.1117745224874</v>
       </c>
       <c r="H3" t="n">
-        <v>2.034727668646229</v>
+        <v>2.034727668646231</v>
       </c>
       <c r="I3" t="n">
-        <v>2.015986312068545</v>
+        <v>2.015986312068546</v>
       </c>
       <c r="J3" t="n">
-        <v>2.06430150238702</v>
+        <v>2.064301502387022</v>
       </c>
       <c r="K3" t="n">
-        <v>2.05553536661674</v>
+        <v>2.055535366616747</v>
       </c>
       <c r="L3" t="n">
-        <v>2.001259834462445</v>
+        <v>2.001259834462449</v>
       </c>
       <c r="M3" t="n">
         <v>2.093826361128636</v>
       </c>
       <c r="N3" t="n">
-        <v>2.030397154740901</v>
+        <v>2.030397154740906</v>
       </c>
       <c r="O3" t="n">
-        <v>2.589500039291572</v>
+        <v>2.589500039291574</v>
       </c>
       <c r="P3" t="n">
-        <v>2.020535681529564</v>
+        <v>2.020535681529569</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.008223536186601</v>
+        <v>2.008223536186607</v>
       </c>
       <c r="R3" t="n">
-        <v>1.905273916294272</v>
+        <v>1.905273916294274</v>
       </c>
       <c r="S3" t="n">
-        <v>2.049449291982127</v>
+        <v>2.04944929198213</v>
       </c>
       <c r="T3" t="n">
-        <v>2.001895857391885</v>
+        <v>2.00189585739189</v>
       </c>
       <c r="U3" t="n">
-        <v>3.368827603270972</v>
+        <v>3.368827603270975</v>
       </c>
       <c r="V3" t="n">
-        <v>2.007941302952074</v>
+        <v>2.007941302952081</v>
       </c>
       <c r="W3" t="n">
-        <v>3.510324203045392</v>
+        <v>3.510324203045397</v>
       </c>
       <c r="X3" t="n">
-        <v>2.103459306170404</v>
+        <v>2.103459306170406</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.035683178767873</v>
+        <v>2.035683178767878</v>
       </c>
       <c r="Z3" t="n">
         <v>2.456635395893753</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.116260651921442</v>
+        <v>2.116260651921447</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.068092103127417</v>
+        <v>2.068092103127416</v>
       </c>
     </row>
     <row r="4">
@@ -5062,16 +5062,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2404293835003441</v>
+        <v>0.2404293835003443</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2528147204928204</v>
+        <v>0.2528147204928208</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3031540553613925</v>
+        <v>0.3031540553613922</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2010625767622217</v>
+        <v>0.2010625767622215</v>
       </c>
       <c r="F4" t="n">
         <v>0.2126691890579193</v>
@@ -5080,67 +5080,67 @@
         <v>0.4077924500927288</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2838046611240613</v>
+        <v>0.2838046611240603</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2544151920377892</v>
+        <v>0.2544151920377881</v>
       </c>
       <c r="J4" t="n">
         <v>0.3313850481765145</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3174935159621401</v>
+        <v>0.3174935159621389</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2314333726952331</v>
+        <v>0.2314333726952326</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3790301084597992</v>
+        <v>0.3790301084598</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2774353688520464</v>
+        <v>0.2774353688520462</v>
       </c>
       <c r="O4" t="n">
-        <v>0.232980123828235</v>
+        <v>0.2329801238282346</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2620526718291434</v>
+        <v>0.2620526718291429</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2423464616702923</v>
+        <v>0.2423464616702915</v>
       </c>
       <c r="R4" t="n">
-        <v>0.07990133082034287</v>
+        <v>0.07990133082034195</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3085622339498769</v>
+        <v>0.3085622339498775</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2322526618393304</v>
+        <v>0.2322526618393293</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4178469545352539</v>
+        <v>0.4178469545352547</v>
       </c>
       <c r="V4" t="n">
-        <v>0.239998548430217</v>
+        <v>0.2399985484302168</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6622572471736833</v>
+        <v>0.662257247173683</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3927667748633397</v>
+        <v>0.3927667748633394</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2832873898056369</v>
+        <v>0.2832873898056363</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2525626191885531</v>
+        <v>0.2525626191885513</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4132772102131093</v>
+        <v>0.4132772102131098</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3364576670718322</v>
+        <v>0.3364576670718317</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9913014168904342</v>
+        <v>0.9913014168904355</v>
       </c>
       <c r="C5" t="n">
         <v>1.312998048892962</v>
       </c>
       <c r="D5" t="n">
-        <v>2.33037561223636</v>
+        <v>2.330375612236361</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3224998128200818</v>
+        <v>0.3224998128200814</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5578361348116825</v>
+        <v>0.5578361348116949</v>
       </c>
       <c r="G5" t="n">
-        <v>3.665931452297928</v>
+        <v>3.665931452297937</v>
       </c>
       <c r="H5" t="n">
-        <v>2.041787169961278</v>
+        <v>2.041787169961279</v>
       </c>
       <c r="I5" t="n">
-        <v>1.390666191023085</v>
+        <v>1.390666191023084</v>
       </c>
       <c r="J5" t="n">
-        <v>2.565309609364149</v>
+        <v>2.565309609364151</v>
       </c>
       <c r="K5" t="n">
-        <v>2.412573306853377</v>
+        <v>2.41257330685337</v>
       </c>
       <c r="L5" t="n">
-        <v>0.841901304583011</v>
+        <v>0.8419013045830086</v>
       </c>
       <c r="M5" t="n">
-        <v>3.564630144074134</v>
+        <v>3.564630144074131</v>
       </c>
       <c r="N5" t="n">
         <v>4.10109359523655</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8525262779010663</v>
+        <v>0.8525262779010547</v>
       </c>
       <c r="P5" t="n">
-        <v>1.381364885969121</v>
+        <v>1.381364885969129</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.08620427178953</v>
+        <v>1.086204271789528</v>
       </c>
       <c r="R5" t="n">
-        <v>-2.156849439352785</v>
+        <v>-2.156849439352784</v>
       </c>
       <c r="S5" t="n">
-        <v>1.997418647431829</v>
+        <v>1.997418647431826</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9232152497965314</v>
+        <v>0.9232152497965329</v>
       </c>
       <c r="U5" t="n">
-        <v>4.244020094674261</v>
+        <v>4.244020094674255</v>
       </c>
       <c r="V5" t="n">
-        <v>1.016173873759253</v>
+        <v>1.016173873759244</v>
       </c>
       <c r="W5" t="n">
         <v>9.073872070492907</v>
       </c>
       <c r="X5" t="n">
-        <v>4.037405484969278</v>
+        <v>4.037405484969272</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.908985045244405</v>
+        <v>1.908985045244413</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.179962967975663</v>
+        <v>1.179962967975662</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.33723309612959</v>
+        <v>4.337233096129592</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.048700525406087</v>
+        <v>3.048700525406081</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2574421616315026</v>
+        <v>0.2574421616314958</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3341377222257723</v>
+        <v>0.3341377222257722</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3844770570943444</v>
+        <v>0.3201668334925439</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2823855784951728</v>
+        <v>0.2180753548933729</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2939921907908697</v>
+        <v>0.2939921907908712</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4248052282238863</v>
+        <v>0.4891154518256796</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3008174392552155</v>
+        <v>0.3008174392552116</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3357381937707395</v>
+        <v>0.2714279701689395</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3483978263076698</v>
+        <v>0.3483978263076657</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3988165176950914</v>
+        <v>0.3345062940932907</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3127563744281846</v>
+        <v>0.2484461508263836</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3960428865909548</v>
+        <v>0.4603531101927513</v>
       </c>
       <c r="N6" t="n">
-        <v>0.294923566092717</v>
+        <v>0.2949235660927129</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3200743209650285</v>
+        <v>0.3200743209650293</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3491285625542145</v>
+        <v>0.276646051045583</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3236694634032433</v>
+        <v>0.3236694634032425</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1612243325532933</v>
+        <v>0.09691410895149365</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3898852356828287</v>
+        <v>0.3255750120810291</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2492654399704846</v>
+        <v>0.3135756635722805</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5016848700227009</v>
+        <v>0.4373746464209026</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2570113265613766</v>
+        <v>0.3213215501631684</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6845209207294221</v>
+        <v>0.6845209207294244</v>
       </c>
       <c r="X6" t="n">
-        <v>0.409779552994501</v>
+        <v>0.4097795529944911</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.30517092209007</v>
+        <v>0.3051709220900654</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2695753973197049</v>
+        <v>0.3338856209215018</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4302899883442681</v>
+        <v>0.4946002119460614</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3542792879737491</v>
+        <v>0.3542792879737488</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3338090649107834</v>
+        <v>0.3338090649107835</v>
       </c>
       <c r="C7" t="n">
         <v>0.3461944019032597</v>
       </c>
       <c r="D7" t="n">
-        <v>0.396533736771831</v>
+        <v>0.3965337367718313</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2944422581726602</v>
+        <v>0.2944422581726601</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3060488704683583</v>
+        <v>0.3060488704683578</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5011721315031675</v>
+        <v>0.5011721315031673</v>
       </c>
       <c r="H7" t="n">
-        <v>0.377184342534499</v>
+        <v>0.3771843425344991</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3477948734482273</v>
+        <v>0.3477948734482271</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4247647295869535</v>
+        <v>0.4247647295869532</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4108731973725779</v>
+        <v>0.4108731973725777</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3248130541056712</v>
+        <v>0.3248130541056711</v>
       </c>
       <c r="M7" t="n">
-        <v>0.472409789870238</v>
+        <v>0.4724097898702381</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3708150502624846</v>
+        <v>0.3708150502624847</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3260020863349774</v>
+        <v>0.3260020863349764</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3550746343358843</v>
+        <v>0.3550746343358854</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3357261430807308</v>
+        <v>0.3357261430807307</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1732810122307819</v>
+        <v>0.173281012230781</v>
       </c>
       <c r="S7" t="n">
         <v>0.4019419153603165</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3256323432497677</v>
+        <v>0.3256323432497676</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5124435213437841</v>
+        <v>0.5124435213437843</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3333782298406555</v>
+        <v>0.3333782298406557</v>
       </c>
       <c r="W7" t="n">
-        <v>0.75563692858412</v>
+        <v>0.7556369285841215</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4861464562737791</v>
+        <v>0.4861464562737788</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3791819849705717</v>
+        <v>0.3791819849705723</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3459423005989889</v>
+        <v>0.3459423005989897</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5066568916235488</v>
+        <v>0.5066568916235487</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.42983734848227</v>
+        <v>0.4298373484822696</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3642991136439364</v>
+        <v>0.3642991136439368</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4767437629568968</v>
+        <v>0.4767437629568971</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5270830978254704</v>
+        <v>0.5270830978254688</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4249916192262972</v>
+        <v>0.3717129869972336</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3521269906327582</v>
+        <v>0.3521269906327594</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6317214925568057</v>
+        <v>0.6524694427845963</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5077337035881356</v>
+        <v>0.5077337035881363</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4783442345018656</v>
+        <v>0.4783442345018645</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5553140906405906</v>
+        <v>0.5553140906405905</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5414225584262164</v>
+        <v>0.5414225584262151</v>
       </c>
       <c r="L8" t="n">
-        <v>0.455362415159309</v>
+        <v>0.4553624151593092</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6029591509238753</v>
+        <v>0.6029591509237473</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4238017046863362</v>
+        <v>0.4238017046863354</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4006613648654962</v>
+        <v>0.4006613648654967</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4245091145655899</v>
+        <v>0.4245091145655892</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3465522532234906</v>
+        <v>0.3465522532234904</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3038303732844174</v>
+        <v>0.3038303732844184</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5324912764139552</v>
+        <v>0.5324912764139546</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4561817043034062</v>
+        <v>0.4561817043034053</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5820353653614072</v>
+        <v>0.5947245790920436</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4639275908942954</v>
+        <v>0.435776118832934</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8862059540725344</v>
+        <v>0.8862059540725336</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5061432011582385</v>
+        <v>0.5061432011582386</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6079714204136785</v>
+        <v>0.6079714204136784</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.4764916616526294</v>
+        <v>0.3745736962423512</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6372062526771871</v>
+        <v>0.637206252677186</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.6649070279976411</v>
+        <v>0.6649070279976405</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.543428126595163</v>
+        <v>0.5434281265951632</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6489036590482352</v>
+        <v>0.6489036590482358</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6992429939168074</v>
+        <v>0.6992429939168077</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5971515153176351</v>
+        <v>0.5756666887412336</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6087581276133341</v>
+        <v>0.3941598019778079</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8038813886481422</v>
+        <v>0.8038814027249208</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6798935996794752</v>
+        <v>0.6798935996794753</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6505041305932022</v>
+        <v>0.6505041305932026</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7274739867319291</v>
+        <v>0.7274739867319282</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7135824545175536</v>
+        <v>0.7135824545175532</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6275223112506465</v>
+        <v>0.6275223112506474</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7751190470152132</v>
+        <v>0.7751190470152137</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6735243074074591</v>
+        <v>0.6735243074074598</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6599190500098818</v>
+        <v>0.6599190500098824</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6957009379613901</v>
+        <v>0.6957009379613895</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.638435414302484</v>
+        <v>0.6384354143024834</v>
       </c>
       <c r="R9" t="n">
         <v>0.4759902693757574</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7046511725052936</v>
+        <v>0.7046511725052925</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6283416003947438</v>
+        <v>0.6283416003947437</v>
       </c>
       <c r="U9" t="n">
         <v>0.8164508068451661</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6360874869856319</v>
+        <v>0.7435115298456699</v>
       </c>
       <c r="W9" t="n">
-        <v>1.058346185729096</v>
+        <v>1.058346185729097</v>
       </c>
       <c r="X9" t="n">
-        <v>0.788855713418755</v>
+        <v>0.7888557134187548</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.6818912421155479</v>
+        <v>0.681891242115548</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6486515577439657</v>
+        <v>0.5925264533741184</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8093661487685239</v>
+        <v>0.8093661487685245</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.7325466056272454</v>
+        <v>0.7325466056272463</v>
       </c>
     </row>
   </sheetData>
@@ -5749,43 +5749,43 @@
         <v>2.897637829218847</v>
       </c>
       <c r="C2" t="n">
-        <v>2.898432500372413</v>
+        <v>2.898432500372414</v>
       </c>
       <c r="D2" t="n">
         <v>2.909477951653687</v>
       </c>
       <c r="E2" t="n">
-        <v>2.890758700351968</v>
+        <v>2.890758700351969</v>
       </c>
       <c r="F2" t="n">
-        <v>2.89425040288291</v>
+        <v>2.894250402882909</v>
       </c>
       <c r="G2" t="n">
-        <v>2.916191873068617</v>
+        <v>2.916191873068616</v>
       </c>
       <c r="H2" t="n">
-        <v>2.909300934741067</v>
+        <v>2.909300934741068</v>
       </c>
       <c r="I2" t="n">
-        <v>2.904677911114008</v>
+        <v>2.904677911114009</v>
       </c>
       <c r="J2" t="n">
-        <v>2.910083749922876</v>
+        <v>2.910083749922877</v>
       </c>
       <c r="K2" t="n">
         <v>2.904956460940483</v>
       </c>
       <c r="L2" t="n">
-        <v>2.890490939532484</v>
+        <v>2.890490939532483</v>
       </c>
       <c r="M2" t="n">
-        <v>2.905290609932532</v>
+        <v>2.905290609932533</v>
       </c>
       <c r="N2" t="n">
-        <v>2.913334492684345</v>
+        <v>2.913334492684346</v>
       </c>
       <c r="O2" t="n">
-        <v>3.248105350616297</v>
+        <v>3.248105350616296</v>
       </c>
       <c r="P2" t="n">
         <v>2.897840457664246</v>
@@ -5797,7 +5797,7 @@
         <v>2.875337174982684</v>
       </c>
       <c r="S2" t="n">
-        <v>2.904590495720519</v>
+        <v>2.90459049572052</v>
       </c>
       <c r="T2" t="n">
         <v>2.901223125127236</v>
@@ -5809,22 +5809,22 @@
         <v>2.910234703199872</v>
       </c>
       <c r="W2" t="n">
-        <v>3.666703217888018</v>
+        <v>3.666703217888016</v>
       </c>
       <c r="X2" t="n">
-        <v>2.945473966744225</v>
+        <v>2.945473966744227</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.918631426230129</v>
+        <v>2.91863142623013</v>
       </c>
       <c r="Z2" t="n">
         <v>3.169676073623196</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.936029891098234</v>
+        <v>2.936029891098233</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.90644734627159</v>
+        <v>2.906447346271592</v>
       </c>
     </row>
     <row r="3">
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.902590156881386</v>
+        <v>1.902590156881385</v>
       </c>
       <c r="C3" t="n">
         <v>1.965006432524328</v>
@@ -5843,7 +5843,7 @@
         <v>1.986836260655402</v>
       </c>
       <c r="E3" t="n">
-        <v>1.85333205779132</v>
+        <v>1.853332057791319</v>
       </c>
       <c r="F3" t="n">
         <v>1.878154888322956</v>
@@ -5855,7 +5855,7 @@
         <v>1.985681448617139</v>
       </c>
       <c r="I3" t="n">
-        <v>1.952586077145544</v>
+        <v>1.952586077145543</v>
       </c>
       <c r="J3" t="n">
         <v>1.990993425700428</v>
@@ -5864,19 +5864,19 @@
         <v>1.95466236334774</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8526931894361</v>
+        <v>1.852693189436099</v>
       </c>
       <c r="M3" t="n">
-        <v>1.961027779383064</v>
+        <v>1.961027779383065</v>
       </c>
       <c r="N3" t="n">
-        <v>2.014291335908974</v>
+        <v>2.014291335908975</v>
       </c>
       <c r="O3" t="n">
-        <v>2.529254093441245</v>
+        <v>2.529254093441244</v>
       </c>
       <c r="P3" t="n">
-        <v>1.904065246436141</v>
+        <v>1.904065246436142</v>
       </c>
       <c r="Q3" t="n">
         <v>1.97227578506562</v>
@@ -5891,13 +5891,13 @@
         <v>1.928018289403925</v>
       </c>
       <c r="U3" t="n">
-        <v>3.211780995872602</v>
+        <v>3.211780995872601</v>
       </c>
       <c r="V3" t="n">
         <v>1.992073243187481</v>
       </c>
       <c r="W3" t="n">
-        <v>3.342104887841315</v>
+        <v>3.342104887841313</v>
       </c>
       <c r="X3" t="n">
         <v>2.243220850964328</v>
@@ -5909,10 +5909,10 @@
         <v>2.409215794370634</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.176355460766222</v>
+        <v>2.176355460766223</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.965143141797708</v>
+        <v>1.965143141797709</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06735450516461415</v>
+        <v>0.06735450516461521</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1937631187222491</v>
+        <v>0.1937631187222502</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2010941347915406</v>
+        <v>0.2010941347915401</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.01034841994239898</v>
+        <v>-0.0103484199423975</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02909196640707633</v>
+        <v>0.02909196640707504</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2769309657296242</v>
+        <v>0.2769309657296259</v>
       </c>
       <c r="H4" t="n">
-        <v>0.199094647331692</v>
+        <v>0.1990946473316908</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1468754687681413</v>
+        <v>0.1468754687681414</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2076760095585959</v>
+        <v>0.2076760095585956</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1500218171974239</v>
+        <v>0.1500218171974247</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.01337290157453586</v>
+        <v>-0.0133729015745379</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1611311575441017</v>
+        <v>0.1611311575441042</v>
       </c>
       <c r="N4" t="n">
-        <v>0.244655539829344</v>
+        <v>0.2446555398293443</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1669883639487497</v>
+        <v>0.1669883639487496</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0696432866690722</v>
+        <v>0.06964328666907035</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1780751303292246</v>
+        <v>0.1780751303292261</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1845416432406496</v>
+        <v>-0.1845416432406487</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1458880716856182</v>
+        <v>0.1458880716856206</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1078520717674843</v>
+        <v>0.1078520717674881</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1868509598103068</v>
+        <v>0.1868509598103064</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2078975261123304</v>
+        <v>0.2078975261123308</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4189278264702472</v>
+        <v>0.4189278264702466</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6076856842242344</v>
+        <v>0.6076856842242362</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3031140672639909</v>
+        <v>0.3031140672639907</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1865762926173621</v>
+        <v>0.1865762926173644</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5010105053133229</v>
+        <v>0.5010105053133265</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1666865076850411</v>
+        <v>0.1666865076850448</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.402918545062878</v>
+        <v>-1.402918545062881</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7011380777499781</v>
+        <v>0.7011380777499729</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8290755779060249</v>
+        <v>0.8290755779060247</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.860871417872131</v>
+        <v>-2.860871417872141</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.213894528498048</v>
+        <v>-2.213894528498044</v>
       </c>
       <c r="G5" t="n">
-        <v>1.852346204481064</v>
+        <v>1.852346204481062</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8499731779805093</v>
+        <v>0.8499731779805144</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1257536448517811</v>
+        <v>-0.1257536448517724</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8635832122727716</v>
+        <v>0.8635832122727702</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.02436562855085722</v>
+        <v>-0.02436562855084456</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.255102789201241</v>
+        <v>-2.25510278920124</v>
       </c>
       <c r="M5" t="n">
-        <v>0.169706326720858</v>
+        <v>0.1697063267208614</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6202818601253253</v>
+        <v>0.6202818601253242</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2346581270886462</v>
+        <v>0.2346581270886496</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.34745048607197</v>
+        <v>-1.347450486071966</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4137117862370281</v>
+        <v>0.4137117862370327</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.276667518589782</v>
+        <v>-6.2766675185898</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0724671845867505</v>
+        <v>-0.07246718458675239</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.769725280787299</v>
+        <v>-0.7697252807872939</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5638500537811112</v>
+        <v>0.563850053781115</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8935298931067531</v>
+        <v>0.8935298931067602</v>
       </c>
       <c r="W5" t="n">
-        <v>4.435540034479218</v>
+        <v>4.435540034479223</v>
       </c>
       <c r="X5" t="n">
-        <v>7.750445373070655</v>
+        <v>7.750445373070665</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.668616426365003</v>
+        <v>2.668616426365007</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5341741124648561</v>
+        <v>0.5341741124648565</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.142237878224797</v>
+        <v>6.142237878224781</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2370202123979514</v>
+        <v>0.2370202123979518</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07791239929365498</v>
+        <v>0.07791239929365709</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2547799394327074</v>
+        <v>0.2043210128512911</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2116520289205826</v>
+        <v>0.2116520289205813</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05066840076805885</v>
+        <v>0.0506684007680602</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09010878711753527</v>
+        <v>0.09010878711753773</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3379477864400821</v>
+        <v>0.2874888598586661</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2601114680421492</v>
+        <v>0.2096525414607348</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1574333628971829</v>
+        <v>0.1574333628971871</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2686928302690542</v>
+        <v>0.2182339036876375</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1605797113264639</v>
+        <v>0.1605797113264663</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0476439191359222</v>
+        <v>0.04764391913592333</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1716890516731422</v>
+        <v>0.2221479782545605</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2562673354982142</v>
+        <v>0.256267335498231</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1786001596176204</v>
+        <v>0.1786001596176223</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1354989218078179</v>
+        <v>0.07909966385509372</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2390919510396836</v>
+        <v>0.1886330244582684</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1235248225301913</v>
+        <v>-0.1235248225301901</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2069048923960763</v>
+        <v>0.1564459658146629</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1688688924779425</v>
+        <v>0.168868892477943</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1987816276141745</v>
+        <v>0.1987816276141742</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2184554202413729</v>
+        <v>0.2689143468227892</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4337257162457239</v>
+        <v>0.4337257162457195</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6182435783532768</v>
+        <v>0.618243578353278</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3176476902250891</v>
+        <v>0.3176476902250859</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2475931133278198</v>
+        <v>0.2475931133278221</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5115683994423639</v>
+        <v>0.5620273260237805</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1782183281918452</v>
+        <v>0.1782183281918455</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1437729930553526</v>
+        <v>0.1437729930553535</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2701816066129865</v>
+        <v>0.2701816066129836</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2775126226822782</v>
+        <v>0.2775126226822828</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06607006794833861</v>
+        <v>0.06607006794833956</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1055104542978147</v>
+        <v>0.1055104542978177</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3533494536203616</v>
+        <v>0.3533494536203634</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2755131352224286</v>
+        <v>0.275513135222429</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2232939566588787</v>
+        <v>0.2232939566588807</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2840944974493338</v>
+        <v>0.2840944974493349</v>
       </c>
       <c r="K7" t="n">
-        <v>0.226440305088161</v>
+        <v>0.2264403050881616</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06304558631620283</v>
+        <v>0.06304558631620061</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2375496454348386</v>
+        <v>0.2375496454348394</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3210740277200832</v>
+        <v>0.3210740277200811</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2430738605574524</v>
+        <v>0.2430738605574548</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1457287832777729</v>
+        <v>0.1457287832777721</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2544936182199631</v>
+        <v>0.2544936182199637</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1081231553499125</v>
+        <v>-0.1081231553499118</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2223065595763555</v>
+        <v>0.2223065595763571</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1842705596582216</v>
+        <v>0.1842705596582211</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2627415286832089</v>
+        <v>0.2627415286832095</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2843160140030691</v>
+        <v>0.2843160140030687</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4953463143609858</v>
+        <v>0.4953463143609839</v>
       </c>
       <c r="X7" t="n">
-        <v>0.684104172114973</v>
+        <v>0.6841041721149744</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3809053288295539</v>
+        <v>0.3809053288295521</v>
       </c>
       <c r="Z7" t="n">
         <v>0.2629947805080992</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5774289932040598</v>
+        <v>0.5774289932040604</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2431049955757802</v>
+        <v>0.2431049955757827</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1619366494028333</v>
+        <v>0.1619366494028377</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3650660088519171</v>
+        <v>0.3650660088519166</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3723970249212101</v>
+        <v>0.3723970249212115</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1609544701872701</v>
+        <v>0.1201029361309719</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1356263061943375</v>
+        <v>0.135626306194337</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4482338558592932</v>
+        <v>0.4641424023038768</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3703975374613601</v>
+        <v>0.3703975374613613</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3181783588978098</v>
+        <v>0.3181783588978122</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3789788996882652</v>
+        <v>0.378978899688265</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3213247073270935</v>
+        <v>0.3213247073270932</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1579299885551328</v>
+        <v>0.1579299885551355</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3324340476737699</v>
+        <v>0.3324340476734533</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3564870167773727</v>
+        <v>0.3564870167773704</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2951631015924432</v>
+        <v>0.295163101592447</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1938118962107256</v>
+        <v>0.1938118962107243</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2575798969487672</v>
+        <v>0.2575798969487692</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.01323875311098099</v>
+        <v>-0.01323875311097855</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3171909618152863</v>
+        <v>0.3171909618152879</v>
       </c>
       <c r="T8" t="n">
-        <v>0.279154961897153</v>
+        <v>0.2791549618971537</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3111758695179687</v>
+        <v>0.3208653213839475</v>
       </c>
       <c r="V8" t="n">
-        <v>0.379200416242</v>
+        <v>0.3568914471943851</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5902457943696426</v>
+        <v>0.5902457943696432</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6942220596173641</v>
+        <v>0.6942220596173678</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5499930304790168</v>
+        <v>0.5499930304790158</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3578791827470299</v>
+        <v>0.2797333096165657</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6723133954429908</v>
+        <v>0.6723133954429918</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.4181306321318258</v>
+        <v>0.4181306321318287</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2970377825326316</v>
+        <v>0.2970377825326319</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4942022568904967</v>
+        <v>0.4942022568904965</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5015332729597882</v>
+        <v>0.5015332729597879</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2900907182258491</v>
+        <v>0.2737605703130376</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3295311045753253</v>
+        <v>0.1664195069157041</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5773701038978726</v>
+        <v>0.5773701248961862</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4995337854999394</v>
+        <v>0.4995337854999429</v>
       </c>
       <c r="I9" t="n">
-        <v>0.44731460693639</v>
+        <v>0.4473146069363935</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5081151477268451</v>
+        <v>0.5081151477268441</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4504609553656721</v>
+        <v>0.4504609553656725</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2870662365937132</v>
+        <v>0.287066236593711</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4615702957123489</v>
+        <v>0.461570295712353</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5450946779975929</v>
+        <v>0.5450946779975965</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4908759296964263</v>
+        <v>0.4908759296964278</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3986304785412336</v>
+        <v>0.3986304785412347</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4785142894957855</v>
+        <v>0.4785142894957859</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1158974949275981</v>
+        <v>0.1158974949276018</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4463272098538652</v>
+        <v>0.4463272098538676</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4082912099357319</v>
+        <v>0.4082912099357354</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4886628716533808</v>
+        <v>0.4886628716533856</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5083366642805796</v>
+        <v>0.5899874319749646</v>
       </c>
       <c r="W9" t="n">
-        <v>0.719366964638495</v>
+        <v>0.7193669646384931</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9081248223924845</v>
+        <v>0.9081248223924872</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.6049259791070647</v>
+        <v>0.6049259791070637</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.4870154307856088</v>
+        <v>0.4443559469178981</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.80144964348157</v>
+        <v>0.8014496434815748</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.4671256458532911</v>
+        <v>0.4671256458532916</v>
       </c>
     </row>
   </sheetData>
@@ -6612,7 +6612,7 @@
         <v>2.88294287305254</v>
       </c>
       <c r="D2" t="n">
-        <v>2.896368396941211</v>
+        <v>2.89636839694121</v>
       </c>
       <c r="E2" t="n">
         <v>2.880202827693149</v>
@@ -6627,22 +6627,22 @@
         <v>2.902321409055248</v>
       </c>
       <c r="I2" t="n">
-        <v>2.899170809419021</v>
+        <v>2.89917080941902</v>
       </c>
       <c r="J2" t="n">
-        <v>2.900114846202644</v>
+        <v>2.900114846202645</v>
       </c>
       <c r="K2" t="n">
-        <v>2.897843543223921</v>
+        <v>2.897843543223922</v>
       </c>
       <c r="L2" t="n">
         <v>2.878481308430799</v>
       </c>
       <c r="M2" t="n">
-        <v>2.899053930155555</v>
+        <v>2.899053930155554</v>
       </c>
       <c r="N2" t="n">
-        <v>2.906394950078571</v>
+        <v>2.906394950078572</v>
       </c>
       <c r="O2" t="n">
         <v>3.222660698417593</v>
@@ -6654,22 +6654,22 @@
         <v>2.899817251343609</v>
       </c>
       <c r="R2" t="n">
-        <v>2.868067491583403</v>
+        <v>2.868067491583402</v>
       </c>
       <c r="S2" t="n">
-        <v>2.892054412097681</v>
+        <v>2.89205441209768</v>
       </c>
       <c r="T2" t="n">
         <v>2.895128074791678</v>
       </c>
       <c r="U2" t="n">
-        <v>3.638858769314698</v>
+        <v>3.638858769314695</v>
       </c>
       <c r="V2" t="n">
         <v>2.903685788997231</v>
       </c>
       <c r="W2" t="n">
-        <v>3.645521475479025</v>
+        <v>3.645521475479026</v>
       </c>
       <c r="X2" t="n">
         <v>2.949236469581324</v>
@@ -6694,16 +6694,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.842844636098444</v>
+        <v>1.842844636098445</v>
       </c>
       <c r="C3" t="n">
-        <v>1.916045292004714</v>
+        <v>1.916045292004713</v>
       </c>
       <c r="D3" t="n">
         <v>1.945483469005108</v>
       </c>
       <c r="E3" t="n">
-        <v>1.830629997430826</v>
+        <v>1.830629997430825</v>
       </c>
       <c r="F3" t="n">
         <v>1.885521192033417</v>
@@ -6715,25 +6715,25 @@
         <v>1.988069526588972</v>
       </c>
       <c r="I3" t="n">
-        <v>1.965486027834552</v>
+        <v>1.965486027834551</v>
       </c>
       <c r="J3" t="n">
         <v>1.972168965355027</v>
       </c>
       <c r="K3" t="n">
-        <v>1.956022231689927</v>
+        <v>1.956022231689926</v>
       </c>
       <c r="L3" t="n">
-        <v>1.818989313749224</v>
+        <v>1.818989313749223</v>
       </c>
       <c r="M3" t="n">
         <v>1.968068430553348</v>
       </c>
       <c r="N3" t="n">
-        <v>2.017001992873141</v>
+        <v>2.017001992873142</v>
       </c>
       <c r="O3" t="n">
-        <v>2.460059468997066</v>
+        <v>2.460059468997065</v>
       </c>
       <c r="P3" t="n">
         <v>1.878625893918507</v>
@@ -6742,25 +6742,25 @@
         <v>1.970056608737996</v>
       </c>
       <c r="R3" t="n">
-        <v>1.742774448469456</v>
+        <v>1.742774448469455</v>
       </c>
       <c r="S3" t="n">
-        <v>1.914947272266589</v>
+        <v>1.914947272266588</v>
       </c>
       <c r="T3" t="n">
-        <v>1.936612344947703</v>
+        <v>1.936612344947702</v>
       </c>
       <c r="U3" t="n">
-        <v>3.194085206224864</v>
+        <v>3.194085206224863</v>
       </c>
       <c r="V3" t="n">
         <v>1.997475293241283</v>
       </c>
       <c r="W3" t="n">
-        <v>3.297410434442975</v>
+        <v>3.297410434442976</v>
       </c>
       <c r="X3" t="n">
-        <v>2.321805984363232</v>
+        <v>2.321805984363231</v>
       </c>
       <c r="Y3" t="n">
         <v>2.020367095315731</v>
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.02841105728537764</v>
+        <v>-0.02841105728537803</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1199182322173766</v>
+        <v>0.1199182322173773</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1348432216137155</v>
+        <v>0.1348432216137148</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04775431957240094</v>
+        <v>-0.04775431957240093</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04016599898592503</v>
+        <v>0.04016599898592584</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2398799044897731</v>
+        <v>0.2398799044897739</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2020852319625974</v>
+        <v>0.2020852319625976</v>
       </c>
       <c r="I4" t="n">
         <v>0.1664977597239641</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1769278565024149</v>
+        <v>0.176927856502414</v>
       </c>
       <c r="K4" t="n">
-        <v>0.151505677477721</v>
+        <v>0.1515056774777205</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.06719967157864834</v>
+        <v>-0.06719967157864898</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1714685538662286</v>
+        <v>0.1714685538662284</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2480977517424563</v>
+        <v>0.2480977517424564</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08479360352738628</v>
+        <v>0.08479360352738675</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02828734826971993</v>
+        <v>0.02828734826972001</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1737996186401756</v>
+        <v>0.1737996186401758</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1848285234624474</v>
+        <v>-0.184828523462447</v>
       </c>
       <c r="S4" t="n">
-        <v>0.08611477827495068</v>
+        <v>0.08611477827495073</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1208332123583407</v>
+        <v>0.1208332123583409</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1810790247990498</v>
+        <v>0.1810790247990496</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2159393251782863</v>
+        <v>0.2159393251782862</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3728660986447612</v>
+        <v>0.3728660986447618</v>
       </c>
       <c r="X4" t="n">
-        <v>0.732012422598763</v>
+        <v>0.7320124225987632</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2521826156495724</v>
+        <v>0.2521826156495739</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1088897548349726</v>
+        <v>0.1088897548349737</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5381590772074126</v>
+        <v>0.5381590772074129</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1700082845810353</v>
+        <v>0.1700082845810355</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.784918746915535</v>
+        <v>-2.784918746915537</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4191171121540774</v>
+        <v>-0.4191171121540778</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1636459247114085</v>
+        <v>-0.1636459247114088</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.123188638915668</v>
+        <v>-3.123188638915672</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.91090749005334</v>
+        <v>-1.910907490053342</v>
       </c>
       <c r="G5" t="n">
-        <v>1.505108780993884</v>
+        <v>1.505108780993883</v>
       </c>
       <c r="H5" t="n">
-        <v>1.077002973761293</v>
+        <v>1.077002973761291</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3970466333119842</v>
+        <v>0.3970466333119793</v>
       </c>
       <c r="J5" t="n">
         <v>0.5570650585937331</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1365348027179467</v>
+        <v>0.1365348027179451</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.132398170878376</v>
+        <v>-3.132398170878371</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4842118439640709</v>
+        <v>0.4842118439640704</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6845367423491595</v>
+        <v>0.684536742349158</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9034220988522532</v>
+        <v>-0.9034220988522539</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.804758839818986</v>
+        <v>-1.804758839818983</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5038527705300617</v>
+        <v>0.5038527705300615</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.192787851401754</v>
+        <v>-6.192787851401768</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8944152442030574</v>
+        <v>-0.8944152442030541</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.421221715971666</v>
+        <v>-0.4212217159716674</v>
       </c>
       <c r="U5" t="n">
-        <v>0.618646648487319</v>
+        <v>0.6186466484873184</v>
       </c>
       <c r="V5" t="n">
         <v>1.176031092521726</v>
       </c>
       <c r="W5" t="n">
-        <v>3.89151204850473</v>
+        <v>3.891512048504718</v>
       </c>
       <c r="X5" t="n">
-        <v>9.880282914698681</v>
+        <v>9.880282914698682</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.946924792264561</v>
+        <v>1.946924792264563</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.5062732381901742</v>
+        <v>-0.506273238190176</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.991620515431712</v>
+        <v>6.991620515431699</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4698834062420406</v>
+        <v>0.4698834062420409</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02585352593229059</v>
+        <v>0.02585352593229068</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1741828154350446</v>
+        <v>0.1741828154350445</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1891078048313842</v>
+        <v>0.189107804831384</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00651026364526755</v>
+        <v>0.006510263645267099</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04886634032276185</v>
+        <v>0.09443058220359347</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2485802458266104</v>
+        <v>0.2941444877074422</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2107855732994346</v>
+        <v>0.2107855732994343</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2207623429416325</v>
+        <v>0.1751981010608011</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2311924397200835</v>
+        <v>0.1856281978392518</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1602060188145583</v>
+        <v>0.2057702606953894</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.01293508836098012</v>
+        <v>-0.01293508836098094</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2257331370838969</v>
+        <v>0.2257331370838977</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2579873511565853</v>
+        <v>0.2579873511565858</v>
       </c>
       <c r="O6" t="n">
-        <v>0.09468320294151814</v>
+        <v>0.1438042036487577</v>
       </c>
       <c r="P6" t="n">
-        <v>0.08728807002071426</v>
+        <v>0.08728807002071413</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2280642018578437</v>
+        <v>0.2280642018578443</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1305639402447792</v>
+        <v>-0.1761281821256112</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09481511961178762</v>
+        <v>0.09481511961178719</v>
       </c>
       <c r="T6" t="n">
         <v>0.1750977955760092</v>
       </c>
       <c r="U6" t="n">
-        <v>0.236472241098285</v>
+        <v>0.2364722410982846</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2246396665151236</v>
+        <v>0.2246396665151235</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4318997477347095</v>
+        <v>0.4318997477347087</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7862770058164322</v>
+        <v>0.7407127639355998</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2646746623496748</v>
+        <v>0.2646746623496747</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.163154338052641</v>
+        <v>0.1175900961718093</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.592423660425081</v>
+        <v>0.5468594185442494</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1799057809115747</v>
+        <v>0.1799057809115749</v>
       </c>
     </row>
     <row r="7">
@@ -7046,58 +7046,58 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04452886766439751</v>
+        <v>0.04452886766439729</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1928581571671519</v>
+        <v>0.1928581571671517</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2077831465634905</v>
+        <v>0.2077831465634902</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02518560537737424</v>
+        <v>0.0251856053773739</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1131059239356996</v>
+        <v>0.1131059239356993</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3128198294395482</v>
+        <v>0.3128198294395488</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2750251569123726</v>
+        <v>0.2750251569123722</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2394376846737395</v>
+        <v>0.239437684673739</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2498677814521901</v>
+        <v>0.24986778145219</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2244456024274963</v>
+        <v>0.2244456024274961</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005740253371126658</v>
+        <v>0.005740253371126325</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2444084788160038</v>
+        <v>0.2444084788160036</v>
       </c>
       <c r="N7" t="n">
-        <v>0.321037676692232</v>
+        <v>0.3210376766922313</v>
       </c>
       <c r="O7" t="n">
         <v>0.157400752613111</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1008944973554449</v>
+        <v>0.100894497355445</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2467395435899511</v>
+        <v>0.2467395435899508</v>
       </c>
       <c r="R7" t="n">
         <v>-0.1118885985126723</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1590547032247257</v>
+        <v>0.1590547032247255</v>
       </c>
       <c r="T7" t="n">
         <v>0.1937731373081156</v>
@@ -7106,25 +7106,25 @@
         <v>0.2528699059303612</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2888792501280614</v>
+        <v>0.2888792501280617</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4458060235945368</v>
+        <v>0.4458060235945363</v>
       </c>
       <c r="X7" t="n">
-        <v>0.8049523475485383</v>
+        <v>0.8049523475485381</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3262511736809139</v>
+        <v>0.3262511736809142</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1818296797847481</v>
+        <v>0.1818296797847478</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.611099002157188</v>
+        <v>0.611099002157187</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2429482095308102</v>
+        <v>0.2429482095308101</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05910583212358914</v>
+        <v>0.05910583212358936</v>
       </c>
       <c r="C8" t="n">
-        <v>0.277820146215169</v>
+        <v>0.2778201462151682</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2927451356115078</v>
+        <v>0.2927451356115071</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1101475944253905</v>
+        <v>0.07266964506347665</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1386480526158483</v>
+        <v>0.1386480526158476</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3977818184875653</v>
+        <v>0.4123766118494309</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3599871459603901</v>
+        <v>0.35998714596039</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3243996737217568</v>
+        <v>0.3243996737217557</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3348297705002077</v>
+        <v>0.3348297705002063</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3094075914755134</v>
+        <v>0.3094075914755136</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09070224241914326</v>
+        <v>0.09070224241914403</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3293704678640207</v>
+        <v>0.329370467863591</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3514394965199278</v>
+        <v>0.3514394965199277</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2031289565342919</v>
+        <v>0.2031289565342914</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1429474056043042</v>
+        <v>0.1429474056043032</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2474842442624466</v>
+        <v>0.2474842442624467</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.02692660946465567</v>
+        <v>-0.02692660946465564</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2440166922727428</v>
+        <v>0.2440166922727425</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2787351263561327</v>
+        <v>0.2787351263561333</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2953830061272787</v>
+        <v>0.3042483302240019</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3738412391760787</v>
+        <v>0.3529414974105478</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5307818452961418</v>
+        <v>0.5307818452961405</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8121479755692586</v>
+        <v>0.8121479755692579</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4786169234283937</v>
+        <v>0.4786169234283935</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2667916688327647</v>
+        <v>0.1950992062775399</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6960609912052051</v>
+        <v>0.6960609912052036</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.401433242244138</v>
+        <v>0.4014332422441377</v>
       </c>
     </row>
     <row r="9">
@@ -7222,22 +7222,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1785192843394636</v>
+        <v>0.1785192843394634</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3905083114336847</v>
+        <v>0.3905083114336844</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4054333008300238</v>
+        <v>0.4054333008300233</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2228357596439065</v>
+        <v>0.2081433450845632</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3107560782022321</v>
+        <v>0.1640030201793354</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5104699837060807</v>
+        <v>0.5104699748832354</v>
       </c>
       <c r="H9" t="n">
         <v>0.4726753111789058</v>
@@ -7246,58 +7246,58 @@
         <v>0.4370878389402729</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4475179357187236</v>
+        <v>0.4475179357187229</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4220957566940291</v>
+        <v>0.4220957566940298</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2033904076376599</v>
+        <v>0.2033904076376596</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4420586330825371</v>
+        <v>0.4420586330825373</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5186878309587646</v>
+        <v>0.5186878309587644</v>
       </c>
       <c r="O9" t="n">
-        <v>0.376480424679464</v>
+        <v>0.3764804246794638</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3245623507525107</v>
+        <v>0.3245623507525104</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4443896890336383</v>
+        <v>0.444389689033639</v>
       </c>
       <c r="R9" t="n">
-        <v>0.08576155575386055</v>
+        <v>0.08576155575385966</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3567048574912589</v>
+        <v>0.3567048574912585</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3914232915746496</v>
+        <v>0.391423291574649</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4527977370969253</v>
+        <v>0.4527977370969248</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4865294043945945</v>
+        <v>0.5599913686322292</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6434561778610705</v>
+        <v>0.6434561778610698</v>
       </c>
       <c r="X9" t="n">
         <v>1.002602501815072</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5239013279474474</v>
+        <v>0.5239013279474479</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.3794798340512807</v>
+        <v>0.3410986696249058</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8087491564237208</v>
+        <v>0.8087491564237201</v>
       </c>
       <c r="AB9" t="n">
         <v>0.4405983637973434</v>
@@ -7466,40 +7466,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.988842409346831</v>
+        <v>2.98884240934683</v>
       </c>
       <c r="C2" t="n">
-        <v>2.970252045994636</v>
+        <v>2.970252045994637</v>
       </c>
       <c r="D2" t="n">
-        <v>2.991264285416626</v>
+        <v>2.991264285416625</v>
       </c>
       <c r="E2" t="n">
         <v>2.980201134449723</v>
       </c>
       <c r="F2" t="n">
-        <v>2.979752547564899</v>
+        <v>2.979752547564898</v>
       </c>
       <c r="G2" t="n">
-        <v>3.035705475486149</v>
+        <v>3.035705475486148</v>
       </c>
       <c r="H2" t="n">
-        <v>3.000048186752244</v>
+        <v>3.000048186752245</v>
       </c>
       <c r="I2" t="n">
         <v>2.98109153391319</v>
       </c>
       <c r="J2" t="n">
-        <v>3.008314140475691</v>
+        <v>3.00831414047569</v>
       </c>
       <c r="K2" t="n">
-        <v>2.989018293620278</v>
+        <v>2.989018293620277</v>
       </c>
       <c r="L2" t="n">
-        <v>3.003728465680889</v>
+        <v>3.003728465680887</v>
       </c>
       <c r="M2" t="n">
-        <v>3.023207496809601</v>
+        <v>3.0232074968096</v>
       </c>
       <c r="N2" t="n">
         <v>2.994281576634469</v>
@@ -7511,25 +7511,25 @@
         <v>2.999630351589457</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.984810473104714</v>
+        <v>2.984810473104713</v>
       </c>
       <c r="R2" t="n">
-        <v>2.976281774316339</v>
+        <v>2.976281774316338</v>
       </c>
       <c r="S2" t="n">
         <v>2.999295285042836</v>
       </c>
       <c r="T2" t="n">
-        <v>2.983957336079185</v>
+        <v>2.983957336079184</v>
       </c>
       <c r="U2" t="n">
-        <v>3.771086625004213</v>
+        <v>3.771086625004214</v>
       </c>
       <c r="V2" t="n">
-        <v>2.983591350866595</v>
+        <v>2.983591350866594</v>
       </c>
       <c r="W2" t="n">
-        <v>3.772682147875634</v>
+        <v>3.772682147875633</v>
       </c>
       <c r="X2" t="n">
         <v>3.003045474865894</v>
@@ -7560,16 +7560,16 @@
         <v>2.047180315770126</v>
       </c>
       <c r="D3" t="n">
-        <v>2.145854730903217</v>
+        <v>2.145854730903215</v>
       </c>
       <c r="E3" t="n">
         <v>2.066489385044821</v>
       </c>
       <c r="F3" t="n">
-        <v>2.063438303708371</v>
+        <v>2.06343830370837</v>
       </c>
       <c r="G3" t="n">
-        <v>2.460300278594259</v>
+        <v>2.46030027859426</v>
       </c>
       <c r="H3" t="n">
         <v>2.209155042921613</v>
@@ -7578,10 +7578,10 @@
         <v>2.073041319539205</v>
       </c>
       <c r="J3" t="n">
-        <v>2.266237833124204</v>
+        <v>2.266237833124203</v>
       </c>
       <c r="K3" t="n">
-        <v>2.129133765633241</v>
+        <v>2.12913376563324</v>
       </c>
       <c r="L3" t="n">
         <v>2.233961265721906</v>
@@ -7593,10 +7593,10 @@
         <v>2.167181127625297</v>
       </c>
       <c r="O3" t="n">
-        <v>2.765178034901608</v>
+        <v>2.765178034901607</v>
       </c>
       <c r="P3" t="n">
-        <v>2.204539979463295</v>
+        <v>2.204539979463294</v>
       </c>
       <c r="Q3" t="n">
         <v>2.099419136399383</v>
@@ -7608,7 +7608,7 @@
         <v>2.201658061837664</v>
       </c>
       <c r="T3" t="n">
-        <v>2.093540319187581</v>
+        <v>2.09354031918758</v>
       </c>
       <c r="U3" t="n">
         <v>3.515236117886608</v>
@@ -7620,10 +7620,10 @@
         <v>3.559824687646417</v>
       </c>
       <c r="X3" t="n">
-        <v>2.229953961094443</v>
+        <v>2.229953961094444</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.215344394394402</v>
+        <v>2.215344394394401</v>
       </c>
       <c r="Z3" t="n">
         <v>2.583064282339437</v>
@@ -7632,7 +7632,7 @@
         <v>2.227045289528088</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.304545177277348</v>
+        <v>2.304545177277349</v>
       </c>
     </row>
     <row r="4">
@@ -7642,82 +7642,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.447642968858527</v>
+        <v>0.4476429688585269</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3436691620394625</v>
+        <v>0.3436691620394627</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4749991731848766</v>
+        <v>0.4749991731848762</v>
       </c>
       <c r="E4" t="n">
         <v>0.3500357937128364</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3449687984885853</v>
+        <v>0.3449687984885857</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9769828589775993</v>
+        <v>0.9769828589776004</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5742173795649674</v>
+        <v>0.5742173795649679</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3600932652566684</v>
+        <v>0.3600932652566689</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6671186573697352</v>
+        <v>0.6671186573697354</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4496296626378509</v>
+        <v>0.449629662637851</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6157878230759283</v>
+        <v>0.6157878230759285</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8407503846039817</v>
+        <v>0.8407503846039829</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5090808655129719</v>
+        <v>0.509080865512972</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4576401570287837</v>
+        <v>0.457640157028784</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5694977391875918</v>
+        <v>0.5694977391875917</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4021003942215063</v>
+        <v>0.4021003942215068</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3057648180115261</v>
+        <v>0.3057648180115263</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5657130084052787</v>
+        <v>0.5657130084052813</v>
       </c>
       <c r="T4" t="n">
-        <v>0.39246381905572</v>
+        <v>0.3924638190557203</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6402558420315773</v>
+        <v>0.6402558420315774</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3851941206724316</v>
+        <v>0.3851941206724318</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7311647932030073</v>
+        <v>0.7311647932030079</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6080731276292808</v>
+        <v>0.6080731276292817</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.58039978346583</v>
+        <v>0.580399783465829</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.4480983253757073</v>
+        <v>0.448098325375708</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.6040826525320042</v>
+        <v>0.6040826525320054</v>
       </c>
       <c r="AB4" t="n">
         <v>0.7240101698392294</v>
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.391789453832873</v>
+        <v>3.39178945383287</v>
       </c>
       <c r="C5" t="n">
-        <v>1.737898165381947</v>
+        <v>1.737898165381946</v>
       </c>
       <c r="D5" t="n">
-        <v>4.411188519881677</v>
+        <v>4.411188519881663</v>
       </c>
       <c r="E5" t="n">
-        <v>1.821991140752787</v>
+        <v>1.82199114075279</v>
       </c>
       <c r="F5" t="n">
-        <v>1.809888920318658</v>
+        <v>1.809888920318657</v>
       </c>
       <c r="G5" t="n">
         <v>12.38243857209159</v>
       </c>
       <c r="H5" t="n">
-        <v>6.625988320740018</v>
+        <v>6.625988320740007</v>
       </c>
       <c r="I5" t="n">
-        <v>2.121779541828029</v>
+        <v>2.121779541828035</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3276954025386</v>
+        <v>7.327695402538609</v>
       </c>
       <c r="K5" t="n">
-        <v>3.547086321225297</v>
+        <v>3.547086321225292</v>
       </c>
       <c r="L5" t="n">
-        <v>6.599954063683453</v>
+        <v>6.599954063683457</v>
       </c>
       <c r="M5" t="n">
-        <v>10.90265766777911</v>
+        <v>10.9026576677791</v>
       </c>
       <c r="N5" t="n">
-        <v>7.051768993276213</v>
+        <v>7.051768993276221</v>
       </c>
       <c r="O5" t="n">
-        <v>3.482249631435741</v>
+        <v>3.482249631435729</v>
       </c>
       <c r="P5" t="n">
-        <v>5.628579283336181</v>
+        <v>5.62857928333616</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.824594013333971</v>
+        <v>2.824594013333977</v>
       </c>
       <c r="R5" t="n">
-        <v>1.051697459140108</v>
+        <v>1.051697459140111</v>
       </c>
       <c r="S5" t="n">
-        <v>5.284208046755995</v>
+        <v>5.284208046755992</v>
       </c>
       <c r="T5" t="n">
         <v>2.759214287085642</v>
       </c>
       <c r="U5" t="n">
-        <v>7.188286736390323</v>
+        <v>7.188286736390332</v>
       </c>
       <c r="V5" t="n">
-        <v>2.340456085921093</v>
+        <v>2.340456085921089</v>
       </c>
       <c r="W5" t="n">
         <v>9.073108961012441</v>
       </c>
       <c r="X5" t="n">
-        <v>6.936399963315957</v>
+        <v>6.936399963315976</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.236119041227123</v>
+        <v>6.236119041227113</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.426953906030759</v>
+        <v>3.426953906030758</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.645558944525323</v>
+        <v>6.645558944525329</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.77125175486975</v>
+        <v>9.771251754869741</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.569254445204155</v>
+        <v>0.5692544452041547</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3654667041015304</v>
+        <v>0.3654667041015305</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5966106495305045</v>
+        <v>0.5966106495305042</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4716472700584645</v>
+        <v>0.4716472700584647</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4665802748342127</v>
+        <v>0.4665802748342133</v>
       </c>
       <c r="G6" t="n">
         <v>0.9987804010396679</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6958288559105956</v>
+        <v>0.6958288559105958</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3818908073187365</v>
+        <v>0.3818908073187369</v>
       </c>
       <c r="J6" t="n">
-        <v>0.788730133715362</v>
+        <v>0.6889161994318028</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4714272046999184</v>
+        <v>0.4714272046999192</v>
       </c>
       <c r="L6" t="n">
-        <v>0.637585365137996</v>
+        <v>0.7373992994215561</v>
       </c>
       <c r="M6" t="n">
-        <v>0.962361860949609</v>
+        <v>0.9623618609496095</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5316573170020378</v>
+        <v>0.5316573170020369</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4802166085178337</v>
+        <v>0.4802166085178488</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6965963708719387</v>
+        <v>0.6965963708719389</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4238979362835748</v>
+        <v>0.5237118705671349</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4273762943571542</v>
+        <v>0.4273762943571547</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6873244847509073</v>
+        <v>0.6873244847509091</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5140752954013478</v>
+        <v>0.4142613611177882</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7672100849727056</v>
+        <v>0.7672100849727055</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4069916627344999</v>
+        <v>0.5068055970180598</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7583734056306657</v>
+        <v>0.7583734056306596</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7296846039749091</v>
+        <v>0.62987066969135</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6100396470396418</v>
+        <v>0.6100396470396403</v>
       </c>
       <c r="Z6" t="n">
         <v>0.4698958674377763</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.7256941288776324</v>
+        <v>0.7256941288776328</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7480371351227764</v>
+        <v>0.7480371351227771</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5626648446000272</v>
+        <v>0.5626648446000275</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4586910377809633</v>
+        <v>0.4586910377809637</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5900210489263781</v>
+        <v>0.5900210489263776</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4650576694543374</v>
+        <v>0.4650576694543376</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4599906742300865</v>
+        <v>0.4599906742300868</v>
       </c>
       <c r="G7" t="n">
         <v>1.092004734719102</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6892392553064697</v>
+        <v>0.6892392553064692</v>
       </c>
       <c r="I7" t="n">
         <v>0.4751151409981701</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7821405331112355</v>
+        <v>0.782140533111236</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5646515383793518</v>
+        <v>0.5646515383793526</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7308096988174293</v>
+        <v>0.7308096988174299</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9557722603454823</v>
+        <v>0.955772260345483</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6241027412544726</v>
+        <v>0.6241027412544733</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5723032671066483</v>
+        <v>0.5723032671066487</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6841608492654555</v>
+        <v>0.6841608492654547</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5171222699630078</v>
+        <v>0.5171222699630074</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4207866937530274</v>
+        <v>0.4207866937530276</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6807348841467813</v>
+        <v>0.6807348841467821</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5074856947972209</v>
+        <v>0.5074856947972215</v>
       </c>
       <c r="U7" t="n">
-        <v>0.760083030554653</v>
+        <v>0.7600830305546534</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5002159964139334</v>
+        <v>0.5002159964139337</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8461866689445077</v>
+        <v>0.8461866689445081</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7230950033707824</v>
+        <v>0.7230950033707837</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.7007644258028317</v>
+        <v>0.7007644258028323</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5631202011172088</v>
+        <v>0.5631202011172091</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.719104528273506</v>
+        <v>0.7191045282735063</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8390320455807305</v>
+        <v>0.8390320455807307</v>
       </c>
     </row>
     <row r="8">
@@ -7994,82 +7994,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6108561430865366</v>
+        <v>0.6108561430865359</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6370715766064231</v>
+        <v>0.6370715766064238</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7684015877518376</v>
+        <v>0.7684015877518378</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6434382082797969</v>
+        <v>0.574116278161302</v>
       </c>
       <c r="F8" t="n">
-        <v>0.528463934795778</v>
+        <v>0.5284639347957775</v>
       </c>
       <c r="G8" t="n">
-        <v>1.270385273544559</v>
+        <v>1.297380860624427</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8676197941319289</v>
+        <v>0.8676197941319284</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6534956798236289</v>
+        <v>0.6534956798236298</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9605210719366948</v>
+        <v>0.9605210719366959</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7430320772048111</v>
+        <v>0.7430320772048113</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9091902376428891</v>
+        <v>0.9091902376428903</v>
       </c>
       <c r="M8" t="n">
-        <v>1.134152799170943</v>
+        <v>1.134152799170873</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7015648386057195</v>
+        <v>0.7015648386057201</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6778573940467748</v>
+        <v>0.6778573940467755</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7829168830933182</v>
+        <v>0.7829168830933192</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5397284113256192</v>
+        <v>0.5397284113256194</v>
       </c>
       <c r="R8" t="n">
-        <v>0.599167232578487</v>
+        <v>0.5991672325784865</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8591154229722398</v>
+        <v>0.8591154229722411</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6858662336226803</v>
+        <v>0.6858662336226804</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8587593136485937</v>
+        <v>0.8753189136107878</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6785965352393919</v>
+        <v>0.642861114572172</v>
       </c>
       <c r="W8" t="n">
         <v>1.024592793585206</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7576332472384721</v>
+        <v>0.7576332472384738</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.008352265811547</v>
+        <v>1.008352265811548</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.741500739942667</v>
+        <v>0.6088931676337336</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8974850670989654</v>
+        <v>0.8974850670989656</v>
       </c>
       <c r="AB8" t="n">
         <v>1.153406132093613</v>
@@ -8082,79 +8082,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.890169538653133</v>
+        <v>0.8901695386531334</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9201065816848232</v>
+        <v>0.9201065816848235</v>
       </c>
       <c r="D9" t="n">
         <v>1.051436592830238</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9264732133581971</v>
+        <v>0.895567149006168</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9214062181339457</v>
+        <v>0.6127051384435632</v>
       </c>
       <c r="G9" t="n">
-        <v>1.553420278622959</v>
+        <v>1.553420296279026</v>
       </c>
       <c r="H9" t="n">
         <v>1.150654799210328</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9365306849020294</v>
+        <v>0.9365306849020295</v>
       </c>
       <c r="J9" t="n">
-        <v>1.243556077015095</v>
+        <v>1.243556077015096</v>
       </c>
       <c r="K9" t="n">
-        <v>1.026067082283211</v>
+        <v>1.026067082283212</v>
       </c>
       <c r="L9" t="n">
-        <v>1.192225242721288</v>
+        <v>1.192225242721289</v>
       </c>
       <c r="M9" t="n">
-        <v>1.417187804249341</v>
+        <v>1.417187804249342</v>
       </c>
       <c r="N9" t="n">
         <v>1.085518285158332</v>
       </c>
       <c r="O9" t="n">
-        <v>1.078455480480651</v>
+        <v>1.078455480480652</v>
       </c>
       <c r="P9" t="n">
         <v>1.19996449148088</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9785378315229283</v>
+        <v>0.9785378315229293</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8822022376568864</v>
+        <v>0.8822022376568871</v>
       </c>
       <c r="S9" t="n">
-        <v>1.14215042805064</v>
+        <v>1.142150428050642</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9689012387010794</v>
+        <v>0.9689012387010797</v>
       </c>
       <c r="U9" t="n">
         <v>1.222036028272437</v>
       </c>
       <c r="V9" t="n">
-        <v>0.961631540317793</v>
+        <v>1.116161645333968</v>
       </c>
       <c r="W9" t="n">
-        <v>1.307602212848366</v>
+        <v>1.307602212848367</v>
       </c>
       <c r="X9" t="n">
-        <v>1.184510547274642</v>
+        <v>1.184510547274643</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.162179969706692</v>
+        <v>1.162179969706693</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.024535745021068</v>
+        <v>0.943799417389471</v>
       </c>
       <c r="AA9" t="n">
         <v>1.180520072177365</v>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.941127694755776</v>
+        <v>2.941127694755778</v>
       </c>
       <c r="C2" t="n">
         <v>2.934233675651778</v>
@@ -8335,37 +8335,37 @@
         <v>2.947085878019756</v>
       </c>
       <c r="E2" t="n">
-        <v>2.940881432457334</v>
+        <v>2.940881432457335</v>
       </c>
       <c r="F2" t="n">
-        <v>2.931281816022701</v>
+        <v>2.931281816022702</v>
       </c>
       <c r="G2" t="n">
-        <v>2.994629227492147</v>
+        <v>2.994629227492148</v>
       </c>
       <c r="H2" t="n">
-        <v>2.961688848611113</v>
+        <v>2.961688848611114</v>
       </c>
       <c r="I2" t="n">
         <v>2.940736527896773</v>
       </c>
       <c r="J2" t="n">
-        <v>2.960625114920471</v>
+        <v>2.960625114920472</v>
       </c>
       <c r="K2" t="n">
-        <v>2.943762881469306</v>
+        <v>2.943762881469308</v>
       </c>
       <c r="L2" t="n">
-        <v>2.925644342423812</v>
+        <v>2.925644342423813</v>
       </c>
       <c r="M2" t="n">
-        <v>2.943463117298433</v>
+        <v>2.943463117298434</v>
       </c>
       <c r="N2" t="n">
-        <v>2.94601054823396</v>
+        <v>2.946010548233961</v>
       </c>
       <c r="O2" t="n">
-        <v>3.293294532245244</v>
+        <v>3.293294532245243</v>
       </c>
       <c r="P2" t="n">
         <v>2.95397110277461</v>
@@ -8374,10 +8374,10 @@
         <v>2.943732403917937</v>
       </c>
       <c r="R2" t="n">
-        <v>2.916951699702322</v>
+        <v>2.916951699702323</v>
       </c>
       <c r="S2" t="n">
-        <v>2.93507736568144</v>
+        <v>2.935077365681442</v>
       </c>
       <c r="T2" t="n">
         <v>2.934481963196045</v>
@@ -8386,22 +8386,22 @@
         <v>3.706270690996383</v>
       </c>
       <c r="V2" t="n">
-        <v>2.950526157354794</v>
+        <v>2.950526157354796</v>
       </c>
       <c r="W2" t="n">
-        <v>3.722043298316712</v>
+        <v>3.722043298316714</v>
       </c>
       <c r="X2" t="n">
         <v>2.978272088045762</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.98934066054443</v>
+        <v>2.989340660544431</v>
       </c>
       <c r="Z2" t="n">
         <v>3.216836674208999</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.958523323772424</v>
+        <v>2.958523323772425</v>
       </c>
       <c r="AB2" t="n">
         <v>2.968260584793798</v>
@@ -8417,19 +8417,19 @@
         <v>1.976354063993925</v>
       </c>
       <c r="C3" t="n">
-        <v>1.978848431690388</v>
+        <v>1.978848431690387</v>
       </c>
       <c r="D3" t="n">
         <v>2.018855249280557</v>
       </c>
       <c r="E3" t="n">
-        <v>1.974542992452752</v>
+        <v>1.974542992452751</v>
       </c>
       <c r="F3" t="n">
         <v>1.905955951965369</v>
       </c>
       <c r="G3" t="n">
-        <v>2.355477761710544</v>
+        <v>2.355477761710542</v>
       </c>
       <c r="H3" t="n">
         <v>2.123772511576104</v>
@@ -8438,25 +8438,25 @@
         <v>1.973441933025993</v>
       </c>
       <c r="J3" t="n">
-        <v>2.11466795301807</v>
+        <v>2.114667953018071</v>
       </c>
       <c r="K3" t="n">
-        <v>1.995153541879948</v>
+        <v>1.995153541879947</v>
       </c>
       <c r="L3" t="n">
         <v>1.866511329389131</v>
       </c>
       <c r="M3" t="n">
-        <v>1.997928063330642</v>
+        <v>1.997928063330641</v>
       </c>
       <c r="N3" t="n">
         <v>2.011158414497967</v>
       </c>
       <c r="O3" t="n">
-        <v>2.548624032836565</v>
+        <v>2.548624032836566</v>
       </c>
       <c r="P3" t="n">
-        <v>2.067604003000768</v>
+        <v>2.067604003000767</v>
       </c>
       <c r="Q3" t="n">
         <v>1.994897509192326</v>
@@ -8468,7 +8468,7 @@
         <v>1.933526681716131</v>
       </c>
       <c r="T3" t="n">
-        <v>1.928733001643431</v>
+        <v>1.92873300164343</v>
       </c>
       <c r="U3" t="n">
         <v>3.284265053952141</v>
@@ -8477,13 +8477,13 @@
         <v>2.04307093391766</v>
       </c>
       <c r="W3" t="n">
-        <v>3.436884954516594</v>
+        <v>3.436884954516595</v>
       </c>
       <c r="X3" t="n">
-        <v>2.241410032721011</v>
+        <v>2.241410032721012</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.320264283931874</v>
+        <v>2.320264283931873</v>
       </c>
       <c r="Z3" t="n">
         <v>2.475318559530773</v>
@@ -8492,7 +8492,7 @@
         <v>2.100466809355773</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.169597517818783</v>
+        <v>2.169597517818782</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1889115543501872</v>
+        <v>0.1889115543501877</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2174085996493239</v>
+        <v>0.2174085996493226</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2562119752165638</v>
+        <v>0.2562119752165631</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1861299084030198</v>
+        <v>0.1861299084030187</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07769782473212161</v>
+        <v>0.0776978247321202</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7932359785285351</v>
+        <v>0.7932359785285321</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4211592457443009</v>
+        <v>0.4211592457443006</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1844931447320872</v>
+        <v>0.1844931447320879</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4087354132428856</v>
+        <v>0.4087354132428857</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2186772005252677</v>
+        <v>0.2186772005252662</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01401996706669796</v>
+        <v>0.01401996706669581</v>
       </c>
       <c r="M4" t="n">
-        <v>0.224344662643094</v>
+        <v>0.2243446626430927</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2440656306098669</v>
+        <v>0.2440656306098674</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1699812742560956</v>
+        <v>0.1699812742560933</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3339837561825156</v>
+        <v>0.3339837561825177</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2183329425621677</v>
+        <v>0.218332942562167</v>
       </c>
       <c r="R4" t="n">
         <v>-0.08416743128573968</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1205703041666866</v>
+        <v>0.120570304166687</v>
       </c>
       <c r="T4" t="n">
         <v>0.1138449591954619</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2780195080055828</v>
+        <v>0.2780195080055825</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2923265801464742</v>
+        <v>0.2923265801464739</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5420053007717486</v>
+        <v>0.5420053007717491</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6084745638256926</v>
+        <v>0.6084745638256909</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7298497918702226</v>
+        <v>0.7298497918702227</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2798651704525058</v>
+        <v>0.2798651704525047</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.3854031864779566</v>
+        <v>0.3854031864779569</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4934344105251673</v>
+        <v>0.4934344105251682</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1621573059510544</v>
+        <v>-0.1621573059510543</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3259347030213116</v>
+        <v>0.3259347030213094</v>
       </c>
       <c r="D5" t="n">
         <v>1.016415768809732</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2390726761512471</v>
+        <v>-0.2390726761512493</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.195273158161957</v>
+        <v>-2.195273158161963</v>
       </c>
       <c r="G5" t="n">
-        <v>9.117052714931988</v>
+        <v>9.117052714931953</v>
       </c>
       <c r="H5" t="n">
-        <v>4.29401561046507</v>
+        <v>4.294015610465067</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3026743738929759</v>
+        <v>-0.3026743738929742</v>
       </c>
       <c r="J5" t="n">
-        <v>3.297209213506023</v>
+        <v>3.297209213506013</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3601612828333697</v>
+        <v>0.3601612828333701</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.911964278367106</v>
+        <v>-2.911964278367112</v>
       </c>
       <c r="M5" t="n">
-        <v>0.457829228546173</v>
+        <v>0.4578292285461722</v>
       </c>
       <c r="N5" t="n">
-        <v>1.317756056339153</v>
+        <v>1.317756056339143</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.419837639762164</v>
+        <v>-0.4198376397621438</v>
       </c>
       <c r="P5" t="n">
-        <v>2.189084907878057</v>
+        <v>2.189084907878068</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3341141857151422</v>
+        <v>0.3341141857151397</v>
       </c>
       <c r="R5" t="n">
-        <v>-5.433663720853644</v>
+        <v>-5.433663720853643</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.187372428678781</v>
+        <v>-1.187372428678784</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.588371693600122</v>
+        <v>-1.588371693600126</v>
       </c>
       <c r="U5" t="n">
-        <v>1.355359323857703</v>
+        <v>1.355359323857702</v>
       </c>
       <c r="V5" t="n">
-        <v>1.525930066792821</v>
+        <v>1.525930066792822</v>
       </c>
       <c r="W5" t="n">
-        <v>6.074613559250488</v>
+        <v>6.07461355925049</v>
       </c>
       <c r="X5" t="n">
-        <v>7.23497017159596</v>
+        <v>7.234970171595956</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.372284892631473</v>
+        <v>9.372284892631491</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.280093263951034</v>
+        <v>1.280093263951031</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.292016156307004</v>
+        <v>3.292016156307011</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.564404893775738</v>
+        <v>5.56440489377573</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2818093172880458</v>
+        <v>0.2034356240352989</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3103063625871809</v>
+        <v>0.3103063625871802</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2707360449016764</v>
+        <v>0.2707360449016739</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2006539780881316</v>
+        <v>0.279027671340876</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09222189441722982</v>
+        <v>0.1705955876699775</v>
       </c>
       <c r="G6" t="n">
-        <v>0.886133741466391</v>
+        <v>0.8077600482136428</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4356833154294118</v>
+        <v>0.514057008682158</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1990172144171994</v>
+        <v>0.277390907669946</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5016331761807444</v>
+        <v>0.4232594829279972</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2332012702103754</v>
+        <v>0.3115749634631236</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1069177300045556</v>
+        <v>0.02854403675180656</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2388687323282059</v>
+        <v>0.3172424255809498</v>
       </c>
       <c r="N6" t="n">
-        <v>0.259292282992643</v>
+        <v>0.2592922829926004</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2680706911339694</v>
+        <v>0.1852079266388492</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3464674858218485</v>
+        <v>0.3464674858218466</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2328570122472806</v>
+        <v>0.3112307055000242</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008730331652119283</v>
+        <v>0.008730331652117174</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1350943738517993</v>
+        <v>0.1350943738517978</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1283690288805756</v>
+        <v>0.1283690288805733</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3745666610662793</v>
+        <v>0.2961929678135323</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3852243430843321</v>
+        <v>0.3852243430843312</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5608874839427345</v>
+        <v>0.5608874839427356</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7013723267635511</v>
+        <v>0.622998633510801</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.7500873578284553</v>
+        <v>0.7500873578284591</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.294389240137618</v>
+        <v>0.2943892401376157</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4783009494158149</v>
+        <v>0.4783009494158142</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.5096619431327553</v>
+        <v>0.509661943132758</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2792849915695051</v>
+        <v>0.2792849915695049</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3077820368686399</v>
+        <v>0.3077820368686397</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3465854124358805</v>
+        <v>0.3465854124358801</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2765033456223359</v>
+        <v>0.2765033456223356</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1680712619514389</v>
+        <v>0.1680712619514372</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8836094157478522</v>
+        <v>0.8836094157478481</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5115326829636168</v>
+        <v>0.511532682963617</v>
       </c>
       <c r="I7" t="n">
-        <v>0.274866581951404</v>
+        <v>0.2748665819514046</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4991088504622036</v>
+        <v>0.4991088504622023</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3090506377445841</v>
+        <v>0.3090506377445836</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1043934042860131</v>
+        <v>0.1043934042860121</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3147180998624101</v>
+        <v>0.3147180998624096</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3344390678291852</v>
+        <v>0.3344390678291843</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2600209095349731</v>
+        <v>0.2600209095349728</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4240233914613972</v>
+        <v>0.4240233914613968</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3087063797814863</v>
+        <v>0.3087063797814839</v>
       </c>
       <c r="R7" t="n">
-        <v>0.006206005933576619</v>
+        <v>0.006206005933576578</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2109437413860034</v>
+        <v>0.210943741386004</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2042183964147782</v>
+        <v>0.204218396414779</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3708920372091106</v>
+        <v>0.3708920372091109</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3827000173657907</v>
+        <v>0.3827000173657908</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6323787379910676</v>
+        <v>0.6323787379910665</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6988480010450118</v>
+        <v>0.6988480010450083</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8238726192123784</v>
+        <v>0.8238726192123774</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3702386076718218</v>
+        <v>0.3702386076718213</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4757766236972716</v>
+        <v>0.4757766236972737</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.583807847744486</v>
+        <v>0.5838078477444852</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3105218095910836</v>
+        <v>0.3105218095910842</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4374249566129861</v>
+        <v>0.4374249566129845</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4762283321802265</v>
+        <v>0.4762283321802248</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4061462653666831</v>
+        <v>0.3537479190148447</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2146386005151156</v>
+        <v>0.2146386005151144</v>
       </c>
       <c r="G8" t="n">
-        <v>1.013252335492194</v>
+        <v>1.033657481733252</v>
       </c>
       <c r="H8" t="n">
-        <v>0.641175602707962</v>
+        <v>0.6411756027079617</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4045095016957517</v>
+        <v>0.4045095016957496</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6287517702065479</v>
+        <v>0.6287517702065475</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4386935574889279</v>
+        <v>0.4386935574889285</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2340363240303586</v>
+        <v>0.2340363240303572</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4443610196067569</v>
+        <v>0.4443610196066528</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3878007957338543</v>
+        <v>0.3878007957338534</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3346791731913956</v>
+        <v>0.3346791731913957</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4935431825346017</v>
+        <v>0.4935431825345974</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.32060415282834</v>
+        <v>0.3206041528283392</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1358489256779241</v>
+        <v>0.1358489256779221</v>
       </c>
       <c r="S8" t="n">
-        <v>0.34058666113035</v>
+        <v>0.3405866611303491</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3338613161591256</v>
+        <v>0.333861316159124</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4405371071779565</v>
+        <v>0.4530217856911566</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5123429371101358</v>
+        <v>0.4847491449377394</v>
       </c>
       <c r="W8" t="n">
         <v>0.7620409972674576</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7197648887975379</v>
+        <v>0.7197648887975365</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.050276010031323</v>
+        <v>1.050276010031322</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.499881527416169</v>
+        <v>0.3996474818397844</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6054195434416191</v>
+        <v>0.6054195434416186</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8162441692415605</v>
+        <v>0.8162441692415593</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.517111428370444</v>
+        <v>0.5171114283704441</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6455734024628025</v>
+        <v>0.6455734024628005</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6843767780300432</v>
+        <v>0.6843767780300409</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6142947112164983</v>
+        <v>0.5912232787073872</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5058626275455984</v>
+        <v>0.2754160728395753</v>
       </c>
       <c r="G9" t="n">
-        <v>1.221400781342012</v>
+        <v>1.221400866243861</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8493240485577791</v>
+        <v>0.8493240485577783</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6126579475455673</v>
+        <v>0.6126579475455655</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8369002160563653</v>
+        <v>0.8369002160563641</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6468420033387446</v>
+        <v>0.646842003338744</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4421847698801759</v>
+        <v>0.442184769880174</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6525094654565724</v>
+        <v>0.6525094654565704</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6722304334233473</v>
+        <v>0.6722304334233447</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6312744366169523</v>
+        <v>0.6312744366169524</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8024817498933104</v>
+        <v>0.8024817498933086</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6464978302774973</v>
+        <v>0.6464978302774962</v>
       </c>
       <c r="R9" t="n">
-        <v>0.343997371527741</v>
+        <v>0.343997371527738</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5487351069801684</v>
+        <v>0.5487351069801655</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5420097620089416</v>
+        <v>0.5420097620089406</v>
       </c>
       <c r="U9" t="n">
-        <v>0.709833700941901</v>
+        <v>0.7098337009418989</v>
       </c>
       <c r="V9" t="n">
-        <v>0.720491382959953</v>
+        <v>0.8358488563994806</v>
       </c>
       <c r="W9" t="n">
-        <v>0.9701701035852279</v>
+        <v>0.9701701035852273</v>
       </c>
       <c r="X9" t="n">
-        <v>1.036639366639169</v>
+        <v>1.036639366639168</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.161663984806539</v>
+        <v>1.161663984806538</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.7080299732659839</v>
+        <v>0.6477600441455547</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.813567989291437</v>
+        <v>0.8135679892914347</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9215992133386488</v>
+        <v>0.9215992133386457</v>
       </c>
     </row>
   </sheetData>

--- a/Results/GWP 20a/ammonia climate change GWP 20a results.xlsx
+++ b/Results/GWP 20a/ammonia climate change GWP 20a results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.029517151457775</v>
+        <v>3.021656197814499</v>
       </c>
       <c r="C2" t="n">
-        <v>3.00105003712397</v>
+        <v>2.990294444143725</v>
       </c>
       <c r="D2" t="n">
-        <v>3.020369228257385</v>
+        <v>3.013562111128056</v>
       </c>
       <c r="E2" t="n">
-        <v>3.011186103055957</v>
+        <v>2.998547279545932</v>
       </c>
       <c r="F2" t="n">
-        <v>3.017219728720153</v>
+        <v>3.008033671275108</v>
       </c>
       <c r="G2" t="n">
-        <v>3.064889695315811</v>
+        <v>3.043686510404564</v>
       </c>
       <c r="H2" t="n">
-        <v>3.036972629413836</v>
+        <v>3.02542837380971</v>
       </c>
       <c r="I2" t="n">
-        <v>3.019283356439285</v>
+        <v>3.008033374849211</v>
       </c>
       <c r="J2" t="n">
-        <v>3.040020745117327</v>
+        <v>3.026265335594323</v>
       </c>
       <c r="K2" t="n">
-        <v>3.03043383932133</v>
+        <v>3.020638057206735</v>
       </c>
       <c r="L2" t="n">
-        <v>3.04016882439494</v>
+        <v>3.034988281257211</v>
       </c>
       <c r="M2" t="n">
-        <v>3.055195460566962</v>
+        <v>3.041944773706896</v>
       </c>
       <c r="N2" t="n">
-        <v>3.033119206965476</v>
+        <v>3.023165969923934</v>
       </c>
       <c r="O2" t="n">
-        <v>3.435897779488248</v>
+        <v>3.423962681930253</v>
       </c>
       <c r="P2" t="n">
-        <v>3.032847669678684</v>
+        <v>3.017033405321013</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.023936094341043</v>
+        <v>3.013290768256203</v>
       </c>
       <c r="R2" t="n">
-        <v>3.02226704354705</v>
+        <v>3.011682434958633</v>
       </c>
       <c r="S2" t="n">
-        <v>3.042710880890488</v>
+        <v>3.027774768314989</v>
       </c>
       <c r="T2" t="n">
-        <v>3.029829481957865</v>
+        <v>3.018495970827866</v>
       </c>
       <c r="U2" t="n">
-        <v>3.821550331817575</v>
+        <v>3.811105528853037</v>
       </c>
       <c r="V2" t="n">
-        <v>3.015314385586323</v>
+        <v>3.005940363512868</v>
       </c>
       <c r="W2" t="n">
-        <v>3.812902444353943</v>
+        <v>3.803828229622847</v>
       </c>
       <c r="X2" t="n">
-        <v>3.028953670778078</v>
+        <v>3.017543724398143</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.028957112433592</v>
+        <v>3.016275928968209</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.313585699584028</v>
+        <v>3.302028923329102</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.037851675340054</v>
+        <v>3.027793500319067</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.044334246467995</v>
+        <v>3.038755485686222</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.263099018184493</v>
+        <v>2.2693315324409</v>
       </c>
       <c r="C3" t="n">
-        <v>2.110193046485065</v>
+        <v>2.09797438859193</v>
       </c>
       <c r="D3" t="n">
-        <v>2.199218586381104</v>
+        <v>2.21309155714096</v>
       </c>
       <c r="E3" t="n">
-        <v>2.133161338178871</v>
+        <v>2.105353223169212</v>
       </c>
       <c r="F3" t="n">
-        <v>2.176875745374094</v>
+        <v>2.173723984093964</v>
       </c>
       <c r="G3" t="n">
-        <v>2.515250863812786</v>
+        <v>2.426518956858908</v>
       </c>
       <c r="H3" t="n">
-        <v>2.318786720798129</v>
+        <v>2.298716491675436</v>
       </c>
       <c r="I3" t="n">
-        <v>2.191554854252255</v>
+        <v>2.173615479683216</v>
       </c>
       <c r="J3" t="n">
-        <v>2.338599386767199</v>
+        <v>2.302875958330982</v>
       </c>
       <c r="K3" t="n">
-        <v>2.271153047305723</v>
+        <v>2.263631261595486</v>
       </c>
       <c r="L3" t="n">
-        <v>2.33996281080916</v>
+        <v>2.36537459308628</v>
       </c>
       <c r="M3" t="n">
-        <v>2.452174948315057</v>
+        <v>2.41990464709705</v>
       </c>
       <c r="N3" t="n">
-        <v>2.290048251373357</v>
+        <v>2.28140146745713</v>
       </c>
       <c r="O3" t="n">
-        <v>2.937593241613296</v>
+        <v>2.932600030672214</v>
       </c>
       <c r="P3" t="n">
-        <v>2.286985058115052</v>
+        <v>2.23664288047961</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.224513136533406</v>
+        <v>2.210917486873511</v>
       </c>
       <c r="R3" t="n">
-        <v>2.213070350263941</v>
+        <v>2.199892811157569</v>
       </c>
       <c r="S3" t="n">
-        <v>2.357410726088567</v>
+        <v>2.313289608281259</v>
       </c>
       <c r="T3" t="n">
-        <v>2.266996344996164</v>
+        <v>2.248463701100079</v>
       </c>
       <c r="U3" t="n">
-        <v>3.659025132449849</v>
+        <v>3.645532273741522</v>
       </c>
       <c r="V3" t="n">
-        <v>2.162204721269574</v>
+        <v>2.157682038125785</v>
       </c>
       <c r="W3" t="n">
-        <v>3.623400164752122</v>
+        <v>3.617046871262525</v>
       </c>
       <c r="X3" t="n">
-        <v>2.260494574329965</v>
+        <v>2.241426664106751</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.260076602584244</v>
+        <v>2.231956451232772</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.714491494126178</v>
+        <v>2.698028233452128</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.323675046011652</v>
+        <v>2.31427983867396</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.37116998263935</v>
+        <v>2.393248977335215</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6710028568488194</v>
+        <v>0.6113385048333252</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4502102604342557</v>
+        <v>0.3623375886307807</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5676728560478153</v>
+        <v>0.519912072246088</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4639452324513842</v>
+        <v>0.3503126423622508</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5320978099334183</v>
+        <v>0.457465800899071</v>
       </c>
       <c r="G4" t="n">
-        <v>1.070552011899414</v>
+        <v>0.860181019982599</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7552159100518474</v>
+        <v>0.6539469679859107</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5554074343366682</v>
+        <v>0.4574624526322028</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7891761587619518</v>
+        <v>0.6629779086338536</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6813572679649015</v>
+        <v>0.5998381383007881</v>
       </c>
       <c r="L4" t="n">
-        <v>0.791318402685713</v>
+        <v>0.7619305203801505</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9671846727114023</v>
+        <v>0.8466439318651791</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7116897308357059</v>
+        <v>8.577289212489287</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6792040410436314</v>
+        <v>0.6102474429785583</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7086225922680629</v>
+        <v>0.5591219370297758</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6079622493021981</v>
+        <v>0.5168471296846305</v>
       </c>
       <c r="R4" t="n">
-        <v>0.589109552782756</v>
+        <v>0.4986802652187046</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8200321002067018</v>
+        <v>0.6804505733178547</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6745307735264381</v>
+        <v>0.5756422872430593</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8465719188847201</v>
+        <v>0.7563975770307411</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5074208387888022</v>
+        <v>0.4309819820027431</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8072834680955167</v>
+        <v>0.7257167582296326</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6646380833577088</v>
+        <v>0.5648862257643403</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6591258585429751</v>
+        <v>0.5464653459179989</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.6341477740745969</v>
+        <v>0.5401614838515232</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.7651451381695693</v>
+        <v>0.6806621599210259</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.837490008365723</v>
+        <v>0.802392178718632</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.144374678477942</v>
+        <v>7.464412217651067</v>
       </c>
       <c r="C5" t="n">
-        <v>3.35821255069371</v>
+        <v>3.137465823121525</v>
       </c>
       <c r="D5" t="n">
-        <v>5.900822133228699</v>
+        <v>6.531402232082055</v>
       </c>
       <c r="E5" t="n">
-        <v>3.504795617175097</v>
+        <v>2.773253748915252</v>
       </c>
       <c r="F5" t="n">
-        <v>5.264829292448467</v>
+        <v>5.326871437734455</v>
       </c>
       <c r="G5" t="n">
-        <v>15.00989363579995</v>
+        <v>12.44940504663688</v>
       </c>
       <c r="H5" t="n">
-        <v>10.31279622132313</v>
+        <v>9.786190421937727</v>
       </c>
       <c r="I5" t="n">
-        <v>5.705049430285589</v>
+        <v>5.263571855869501</v>
       </c>
       <c r="J5" t="n">
-        <v>9.851509680100238</v>
+        <v>8.898014737975435</v>
       </c>
       <c r="K5" t="n">
-        <v>8.251298652796557</v>
+        <v>8.16371946547844</v>
       </c>
       <c r="L5" t="n">
-        <v>10.06787501766784</v>
+        <v>11.02676518865526</v>
       </c>
       <c r="M5" t="n">
-        <v>14.58051070939806</v>
+        <v>13.65220989811076</v>
       </c>
       <c r="N5" t="n">
-        <v>10.93190211160765</v>
+        <v>8.577289212489287</v>
       </c>
       <c r="O5" t="n">
-        <v>7.134295624133706</v>
+        <v>7.274798491624944</v>
       </c>
       <c r="P5" t="n">
-        <v>7.970879206807577</v>
+        <v>6.593831746723421</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.615670641458692</v>
+        <v>6.328533128992754</v>
       </c>
       <c r="R5" t="n">
-        <v>6.514953604752875</v>
+        <v>6.232573399717013</v>
       </c>
       <c r="S5" t="n">
-        <v>10.23311214020522</v>
+        <v>9.028264567382857</v>
       </c>
       <c r="T5" t="n">
-        <v>8.206918547187389</v>
+        <v>7.748155616066336</v>
       </c>
       <c r="U5" t="n">
-        <v>11.07233539955368</v>
+        <v>10.78643335937785</v>
       </c>
       <c r="V5" t="n">
-        <v>4.190835560720376</v>
+        <v>4.192959197089943</v>
       </c>
       <c r="W5" t="n">
-        <v>10.47531341963526</v>
+        <v>10.38708723678071</v>
       </c>
       <c r="X5" t="n">
-        <v>7.858482053432613</v>
+        <v>7.388428249867992</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.596244357661712</v>
+        <v>6.849295162460468</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.631834225339718</v>
+        <v>6.305583513074324</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.68929619220323</v>
+        <v>9.541609259071102</v>
       </c>
       <c r="AB5" t="n">
-        <v>12.16009557577805</v>
+        <v>13.10370714940658</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8190574999557473</v>
+        <v>0.6419605382443014</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5982649035411838</v>
+        <v>0.5029334657543124</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5973895685801367</v>
+        <v>0.6605079493696188</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4936619449837059</v>
+        <v>0.4909085194857825</v>
       </c>
       <c r="F6" t="n">
-        <v>0.680152453040346</v>
+        <v>0.4880878343100476</v>
       </c>
       <c r="G6" t="n">
-        <v>1.218606655006341</v>
+        <v>1.000776897106131</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9032705531587752</v>
+        <v>0.794542845109442</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5851241468689899</v>
+        <v>0.4880844860431799</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9372308018688804</v>
+        <v>0.6935999420448317</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7110739804972237</v>
+        <v>0.7404340154243185</v>
       </c>
       <c r="L6" t="n">
-        <v>0.821035115218035</v>
+        <v>0.9025263975036844</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9969013852437248</v>
+        <v>0.9872398089887113</v>
       </c>
       <c r="N6" t="n">
-        <v>0.742522416186002</v>
+        <v>8.577289212489287</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8333329340446007</v>
+        <v>0.6421816480633417</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8627524116863536</v>
+        <v>0.7054331848575101</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6376789618345206</v>
+        <v>0.6574430068081611</v>
       </c>
       <c r="R6" t="n">
-        <v>0.618826265315077</v>
+        <v>0.6392761423422357</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9680867433136299</v>
+        <v>0.7110726067288332</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7042474860587598</v>
+        <v>0.6062643206540368</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8818397313140464</v>
+        <v>0.791120157692223</v>
       </c>
       <c r="V6" t="n">
-        <v>0.65547548189573</v>
+        <v>0.5715778591262743</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9614129468517739</v>
+        <v>0.8720277247326875</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8126927264646371</v>
+        <v>0.7054821028878709</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6978213692588291</v>
+        <v>0.5849778290399469</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6638644866069187</v>
+        <v>0.5707835172625009</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.7948618507018915</v>
+        <v>0.8212580370445577</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8695896039968168</v>
+        <v>0.8359007928104447</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8108593483221643</v>
+        <v>0.7449957629758297</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5900667519076008</v>
+        <v>0.4959948467732861</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7075293475211595</v>
+        <v>0.6535693303885931</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6038017239247291</v>
+        <v>0.4839699005047554</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6719543014067627</v>
+        <v>0.5911230590415762</v>
       </c>
       <c r="G7" t="n">
-        <v>1.210408503372757</v>
+        <v>0.9938382781251056</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8950724015251923</v>
+        <v>0.7876042261284163</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6952639258100133</v>
+        <v>0.5911197107747074</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9290326502352967</v>
+        <v>0.796635166776359</v>
       </c>
       <c r="K7" t="n">
-        <v>0.821213759438247</v>
+        <v>0.733495396443291</v>
       </c>
       <c r="L7" t="n">
-        <v>0.93117489415906</v>
+        <v>0.8955877785226594</v>
       </c>
       <c r="M7" t="n">
-        <v>1.107041164184748</v>
+        <v>0.9803011900076839</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8515462223090504</v>
+        <v>8.577289212489287</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8186765229481735</v>
+        <v>0.7435207789030881</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8480950741726037</v>
+        <v>0.6923952729543075</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.7478187407755436</v>
+        <v>0.6505043878271354</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7289660442561007</v>
+        <v>0.6323375233612102</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9598885916800461</v>
+        <v>0.8141078314603618</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8143872649997831</v>
+        <v>0.7092995453855655</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9916937703125004</v>
+        <v>0.8939451476123389</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6472773302621476</v>
+        <v>0.564639240145248</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9471399595688632</v>
+        <v>0.8593740163721388</v>
       </c>
       <c r="X7" t="n">
-        <v>0.8044945748310544</v>
+        <v>0.6985434839068453</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8045334499133229</v>
+        <v>0.68422315131101</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.7740042655479422</v>
+        <v>0.6738187419940284</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.9050016296429148</v>
+        <v>0.8143194180635319</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9773464998390674</v>
+        <v>0.9360494368611388</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8741856516694688</v>
+        <v>0.8058249743073772</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8139684922463933</v>
+        <v>0.709985750853858</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9314310878599521</v>
+        <v>0.8675602344691647</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7422017807670164</v>
+        <v>0.6164067212050626</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7602963811394712</v>
+        <v>0.6758130720523639</v>
       </c>
       <c r="G8" t="n">
-        <v>1.467606606615473</v>
+        <v>1.239588256945315</v>
       </c>
       <c r="H8" t="n">
-        <v>1.118974141863985</v>
+        <v>1.001595130208988</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9191656661488067</v>
+        <v>0.8051106148552806</v>
       </c>
       <c r="J8" t="n">
-        <v>1.152934390574089</v>
+        <v>1.010626070856931</v>
       </c>
       <c r="K8" t="n">
-        <v>1.04511549977704</v>
+        <v>0.947486300523865</v>
       </c>
       <c r="L8" t="n">
-        <v>1.155076634497851</v>
+        <v>1.10957868260323</v>
       </c>
       <c r="M8" t="n">
-        <v>1.330942904523553</v>
+        <v>1.194292094088296</v>
       </c>
       <c r="N8" t="n">
-        <v>0.950975135265531</v>
+        <v>8.577289212489287</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9526956591601911</v>
+        <v>0.8717965877469442</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9737294408781095</v>
+        <v>0.8126734358630551</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.7795883058282754</v>
+        <v>0.6812338308166833</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9528677845948936</v>
+        <v>0.846328427441782</v>
       </c>
       <c r="S8" t="n">
-        <v>1.183790332018839</v>
+        <v>1.028098735540933</v>
       </c>
       <c r="T8" t="n">
-        <v>1.038289005338576</v>
+        <v>0.9232904494661359</v>
       </c>
       <c r="U8" t="n">
-        <v>1.13758267945637</v>
+        <v>1.033524711912934</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8273753808649573</v>
+        <v>0.7369172078316127</v>
       </c>
       <c r="W8" t="n">
-        <v>1.171073257471003</v>
+        <v>1.073395021008148</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8509811976842282</v>
+        <v>0.7433105003089306</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.188221973985227</v>
+        <v>1.050729507663333</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.8343477977229556</v>
+        <v>0.7318028962582753</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.128903369981707</v>
+        <v>1.028310322144103</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.368982711111931</v>
+        <v>1.310030536092411</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.253757284531686</v>
+        <v>1.157690312372139</v>
       </c>
       <c r="C9" t="n">
-        <v>1.207828120927376</v>
+        <v>1.072663667177529</v>
       </c>
       <c r="D9" t="n">
-        <v>1.325290716540936</v>
+        <v>1.230238150792836</v>
       </c>
       <c r="E9" t="n">
-        <v>1.181205371588274</v>
+        <v>1.022794163500455</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8866076555227338</v>
+        <v>0.7897863717055157</v>
       </c>
       <c r="G9" t="n">
-        <v>1.828169931780441</v>
+        <v>1.570507144682529</v>
       </c>
       <c r="H9" t="n">
-        <v>1.512833770544967</v>
+        <v>1.364273046532659</v>
       </c>
       <c r="I9" t="n">
-        <v>1.313025294829789</v>
+        <v>1.16778853117895</v>
       </c>
       <c r="J9" t="n">
-        <v>1.546794019255072</v>
+        <v>1.373303987180602</v>
       </c>
       <c r="K9" t="n">
-        <v>1.438975128458022</v>
+        <v>1.310164216847536</v>
       </c>
       <c r="L9" t="n">
-        <v>1.548936263178833</v>
+        <v>1.472256598926904</v>
       </c>
       <c r="M9" t="n">
-        <v>1.724802533204521</v>
+        <v>1.556970010411926</v>
       </c>
       <c r="N9" t="n">
-        <v>1.469307591328828</v>
+        <v>8.577289212489287</v>
       </c>
       <c r="O9" t="n">
-        <v>1.494771493274933</v>
+        <v>1.374914441679641</v>
       </c>
       <c r="P9" t="n">
-        <v>1.536793073539015</v>
+        <v>1.335607143493726</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.365580169183227</v>
+        <v>1.227173254384559</v>
       </c>
       <c r="R9" t="n">
-        <v>1.346727413275877</v>
+        <v>1.209006343765453</v>
       </c>
       <c r="S9" t="n">
-        <v>1.577649960699822</v>
+        <v>1.390776651864605</v>
       </c>
       <c r="T9" t="n">
-        <v>1.432148634019559</v>
+        <v>1.285968365789808</v>
       </c>
       <c r="U9" t="n">
-        <v>1.609740879274845</v>
+        <v>1.470824202827996</v>
       </c>
       <c r="V9" t="n">
-        <v>1.466827217213708</v>
+        <v>1.330530713038095</v>
       </c>
       <c r="W9" t="n">
-        <v>1.564901328588638</v>
+        <v>1.43604283677638</v>
       </c>
       <c r="X9" t="n">
-        <v>1.422255943850829</v>
+        <v>1.275212304311087</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.422294818933099</v>
+        <v>1.260891971715253</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.286338557628559</v>
+        <v>1.1516256764685</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.522762998662688</v>
+        <v>1.390988238467776</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.595107868858843</v>
+        <v>1.512718257265382</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.903683044453699</v>
+        <v>2.903115089151721</v>
       </c>
       <c r="C2" t="n">
-        <v>2.893016583477059</v>
+        <v>2.891329516011936</v>
       </c>
       <c r="D2" t="n">
-        <v>2.907865591575815</v>
+        <v>2.907253358233416</v>
       </c>
       <c r="E2" t="n">
-        <v>2.905175234512539</v>
+        <v>2.904533793437152</v>
       </c>
       <c r="F2" t="n">
-        <v>2.894642706673324</v>
+        <v>2.89399021661554</v>
       </c>
       <c r="G2" t="n">
-        <v>2.912506801323141</v>
+        <v>2.911469764306843</v>
       </c>
       <c r="H2" t="n">
-        <v>2.912522883293939</v>
+        <v>2.911935741970223</v>
       </c>
       <c r="I2" t="n">
-        <v>2.905394564035773</v>
+        <v>2.905961157519203</v>
       </c>
       <c r="J2" t="n">
-        <v>2.909181919030814</v>
+        <v>2.908540129814734</v>
       </c>
       <c r="K2" t="n">
-        <v>2.905477693931031</v>
+        <v>2.906396215513958</v>
       </c>
       <c r="L2" t="n">
-        <v>2.883696471206872</v>
+        <v>2.883097366836825</v>
       </c>
       <c r="M2" t="n">
-        <v>2.903446582506072</v>
+        <v>2.90293611254301</v>
       </c>
       <c r="N2" t="n">
-        <v>2.905725311275333</v>
+        <v>2.905174276275956</v>
       </c>
       <c r="O2" t="n">
-        <v>3.235392262995642</v>
+        <v>3.230293806837829</v>
       </c>
       <c r="P2" t="n">
-        <v>2.904416942119512</v>
+        <v>2.903760606392615</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.907130063889786</v>
+        <v>2.906545305709119</v>
       </c>
       <c r="R2" t="n">
-        <v>2.872859422491605</v>
+        <v>2.872583034289188</v>
       </c>
       <c r="S2" t="n">
-        <v>2.897212260888517</v>
+        <v>2.89622987416129</v>
       </c>
       <c r="T2" t="n">
-        <v>2.898898040074532</v>
+        <v>2.899794274173982</v>
       </c>
       <c r="U2" t="n">
-        <v>3.669813017002517</v>
+        <v>3.661644811648771</v>
       </c>
       <c r="V2" t="n">
-        <v>2.91526148339244</v>
+        <v>2.914622640560661</v>
       </c>
       <c r="W2" t="n">
-        <v>3.691972339635393</v>
+        <v>3.682885456740803</v>
       </c>
       <c r="X2" t="n">
-        <v>2.950315331453846</v>
+        <v>2.949547752198361</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.930703898051854</v>
+        <v>2.930019756289362</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.179746736463551</v>
+        <v>3.177219907831197</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.942013832636397</v>
+        <v>2.941660844722038</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.907536946936429</v>
+        <v>2.907388559969863</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.945592116436683</v>
+        <v>1.945769235553029</v>
       </c>
       <c r="C3" t="n">
-        <v>1.93707054380301</v>
+        <v>1.935052889057939</v>
       </c>
       <c r="D3" t="n">
-        <v>1.975364186104035</v>
+        <v>1.975228660810013</v>
       </c>
       <c r="E3" t="n">
-        <v>1.956199321100129</v>
+        <v>1.955871429804852</v>
       </c>
       <c r="F3" t="n">
-        <v>1.880908673385139</v>
+        <v>1.880483553557065</v>
       </c>
       <c r="G3" t="n">
-        <v>2.008194326537206</v>
+        <v>2.005049709999233</v>
       </c>
       <c r="H3" t="n">
-        <v>2.008791085732487</v>
+        <v>2.008832035827103</v>
       </c>
       <c r="I3" t="n">
-        <v>1.957719170876368</v>
+        <v>1.966008903708877</v>
       </c>
       <c r="J3" t="n">
-        <v>1.984636719743798</v>
+        <v>1.984297400381794</v>
       </c>
       <c r="K3" t="n">
-        <v>1.958371138735983</v>
+        <v>1.969113524155323</v>
       </c>
       <c r="L3" t="n">
-        <v>1.803716689577727</v>
+        <v>1.803677147266935</v>
       </c>
       <c r="M3" t="n">
-        <v>1.948259964177406</v>
+        <v>1.948802255258511</v>
       </c>
       <c r="N3" t="n">
-        <v>1.960071518771642</v>
+        <v>1.960367357224314</v>
       </c>
       <c r="O3" t="n">
-        <v>2.461446865539132</v>
+        <v>2.453738745888045</v>
       </c>
       <c r="P3" t="n">
-        <v>1.950818525086784</v>
+        <v>1.950369271488965</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.970097789247949</v>
+        <v>1.9701567666677</v>
       </c>
       <c r="R3" t="n">
-        <v>1.724667406239514</v>
+        <v>1.726932692135383</v>
       </c>
       <c r="S3" t="n">
-        <v>1.899693442694609</v>
+        <v>1.89693133195673</v>
       </c>
       <c r="T3" t="n">
-        <v>1.911231300796275</v>
+        <v>1.921883047811062</v>
       </c>
       <c r="U3" t="n">
-        <v>3.253710272144192</v>
+        <v>3.240462133787953</v>
       </c>
       <c r="V3" t="n">
-        <v>2.027762261477225</v>
+        <v>2.027440232239305</v>
       </c>
       <c r="W3" t="n">
-        <v>3.450941143817617</v>
+        <v>3.436204478737115</v>
       </c>
       <c r="X3" t="n">
-        <v>2.27789190849233</v>
+        <v>2.276648344451268</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.138509701676235</v>
+        <v>2.137854389035995</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.452952388883699</v>
+        <v>2.449910540194059</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.219234125422251</v>
+        <v>2.220943964422077</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.973164731825626</v>
+        <v>1.976279220727342</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1445039884565515</v>
+        <v>0.1268640646573685</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1633035363945418</v>
+        <v>0.1449388474923759</v>
       </c>
       <c r="D4" t="n">
-        <v>0.191747782267598</v>
+        <v>0.17360771763294</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1613589616125196</v>
+        <v>0.1428889821975032</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04238921446638068</v>
+        <v>0.02379443171244244</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2441723814256137</v>
+        <v>0.2212339638749498</v>
       </c>
       <c r="H4" t="n">
-        <v>0.244354034683843</v>
+        <v>0.2264973959431189</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1638363894739852</v>
+        <v>0.15901171612422</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2063955936692337</v>
+        <v>0.1879231963362563</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1647753798825858</v>
+        <v>0.1639258963115313</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.08125355064425938</v>
+        <v>-0.09924531749660587</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1499782906949204</v>
+        <v>0.1328967606241638</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1115677676272723</v>
+        <v>0.108898240801468</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07862734545812079</v>
+        <v>0.06013604520329613</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1527937002015394</v>
+        <v>0.1341554788458513</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.183439658694451</v>
+        <v>0.1656099386507632</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2036630011719477</v>
+        <v>-0.2180095404541156</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07141351138030867</v>
+        <v>0.04909239398504364</v>
       </c>
       <c r="T4" t="n">
-        <v>0.09045516278311781</v>
+        <v>0.08935393183342778</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2290333186851031</v>
+        <v>0.2119778116232794</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2738166043212411</v>
+        <v>0.2553828377565925</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5650431902155231</v>
+        <v>0.5456531194033222</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6712371220350896</v>
+        <v>0.6513423538494665</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4442661825003344</v>
+        <v>0.4277362450034117</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2518544164595413</v>
+        <v>0.2342384791192201</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5774678740138756</v>
+        <v>0.5622561057477019</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1882256214908034</v>
+        <v>0.175195950253082</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.2464989677763295</v>
+        <v>-0.2514907503222391</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05489211406296668</v>
+        <v>0.03946072971444503</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5481573162672171</v>
+        <v>0.5360662237733775</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0295170366296314</v>
+        <v>0.01992963354111418</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.136572315825947</v>
+        <v>-2.157887581973995</v>
       </c>
       <c r="G5" t="n">
-        <v>1.322804971767944</v>
+        <v>1.237638646853148</v>
       </c>
       <c r="H5" t="n">
-        <v>1.575792448571778</v>
+        <v>1.567362888240544</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04974694010129876</v>
+        <v>0.2793337643899575</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7476041286109085</v>
+        <v>0.7333140142083872</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09675652404273927</v>
+        <v>0.3660365998761232</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.840493875375524</v>
+        <v>-3.848780082533287</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.185946642443669</v>
+        <v>-0.1788338821872807</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1115677676272723</v>
+        <v>0.108898240801468</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.253480504473247</v>
+        <v>-1.270054013920114</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1058182991884464</v>
+        <v>-0.1261849897924988</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3924569141505768</v>
+        <v>0.3850313783336482</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.888938293893637</v>
+        <v>-6.831930301782332</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.392240005532325</v>
+        <v>-1.470393719131219</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.311269257421653</v>
+        <v>-1.010980424405638</v>
       </c>
       <c r="U5" t="n">
-        <v>1.183832225138987</v>
+        <v>1.153081973896082</v>
       </c>
       <c r="V5" t="n">
-        <v>1.823793467239986</v>
+        <v>1.80816001368137</v>
       </c>
       <c r="W5" t="n">
-        <v>7.124744309747867</v>
+        <v>7.087936396889164</v>
       </c>
       <c r="X5" t="n">
-        <v>8.801638025342774</v>
+        <v>8.758860755718535</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.187145788277408</v>
+        <v>5.157282433234673</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.405997568064687</v>
+        <v>1.402912495413217</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.44914841772832</v>
+        <v>7.486318457948347</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.5080684920126342</v>
+        <v>0.5913322134008405</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.159114468740321</v>
+        <v>0.1398699452092708</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1779140166783117</v>
+        <v>0.2038637592206868</v>
       </c>
       <c r="D6" t="n">
-        <v>0.254623487683484</v>
+        <v>0.1866135981848452</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1759694418962892</v>
+        <v>0.2018138939258146</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05699969475015081</v>
+        <v>0.08271934344075231</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3070480868414976</v>
+        <v>0.2342398444268542</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3072297400997274</v>
+        <v>0.2395032764950234</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2267120948898706</v>
+        <v>0.1720175966761242</v>
       </c>
       <c r="J6" t="n">
-        <v>0.269271299085119</v>
+        <v>0.2468481080645667</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1793858601663557</v>
+        <v>0.1769317768634353</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0183778452283743</v>
+        <v>-0.04032040576829496</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2128539961108064</v>
+        <v>0.1459026411760664</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1115677676272723</v>
+        <v>0.108898240801468</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1479361054701732</v>
+        <v>0.1241720399831645</v>
       </c>
       <c r="P6" t="n">
-        <v>0.222028360217273</v>
+        <v>0.1454034769680233</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2463153641103372</v>
+        <v>0.1786158192026651</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1407872957560632</v>
+        <v>-0.2050036599022104</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1342892167961941</v>
+        <v>0.1080173057133529</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1050656430668865</v>
+        <v>0.1023598123853315</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2973598016551706</v>
+        <v>0.2739311350835614</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3366923097371262</v>
+        <v>0.2683887183084959</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5840189134481659</v>
+        <v>0.562908747937466</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6858476023188593</v>
+        <v>0.7102672655777766</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4667292116705112</v>
+        <v>0.4461336177064384</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2664648967433106</v>
+        <v>0.2472443596711229</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5920783542976448</v>
+        <v>0.6211810174760113</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2030261318785352</v>
+        <v>0.1885890080255524</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.223026724224158</v>
+        <v>0.20507285017766</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2418262721621479</v>
+        <v>0.2231476330126683</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2702705180352039</v>
+        <v>0.2518165031532326</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2398816973801257</v>
+        <v>0.2210977677177957</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1209119502339872</v>
+        <v>0.1020032172327347</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3226951171932196</v>
+        <v>0.2994427493952423</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3228767704514494</v>
+        <v>0.3047061814634136</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2423591252415908</v>
+        <v>0.2372205016445141</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2849183294368399</v>
+        <v>0.266131981856549</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2432981156501925</v>
+        <v>0.2421346818318253</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.002730814876653664</v>
+        <v>-0.02103653197631142</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2285010264625266</v>
+        <v>0.2111055461444566</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1115677676272723</v>
+        <v>0.108898240801468</v>
       </c>
       <c r="O7" t="n">
-        <v>0.156817023735841</v>
+        <v>0.1380113791397697</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2309833784792598</v>
+        <v>0.2120308127823243</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2619623944620575</v>
+        <v>0.243818724171055</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1251402654043424</v>
+        <v>-0.1398007549338202</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1499362471479143</v>
+        <v>0.1273011795053368</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1689778985507237</v>
+        <v>0.1675627173537199</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3112717768190899</v>
+        <v>0.2921771445225241</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3523393400888477</v>
+        <v>0.3335916232768852</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6435659259831296</v>
+        <v>0.623861904923613</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7497598578026951</v>
+        <v>0.7295511393697588</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5282396958221224</v>
+        <v>0.5089734422556748</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3303771522271473</v>
+        <v>0.3124472646395136</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.655990609781482</v>
+        <v>0.6404648912679943</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2667483572584098</v>
+        <v>0.2534047357733745</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2435143226586937</v>
+        <v>0.2228758707778112</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3426431182779651</v>
+        <v>0.3167828824383858</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3710873641510211</v>
+        <v>0.3454517525789517</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2979255886840039</v>
+        <v>0.2743545922045809</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1539139066214411</v>
+        <v>0.1316200128129081</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4401687561060241</v>
+        <v>0.4088023054683894</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4236936165672658</v>
+        <v>0.3983414308891297</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3431759713574081</v>
+        <v>0.3308557510702304</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3857351755526558</v>
+        <v>0.3597672312822656</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3441149617660087</v>
+        <v>0.3357699312575426</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09808603123916262</v>
+        <v>0.07259871744940548</v>
       </c>
       <c r="M8" t="n">
-        <v>0.329317872578232</v>
+        <v>0.3047407955703738</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1115677676272723</v>
+        <v>0.108898240801468</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2128102750763331</v>
+        <v>0.189351402763602</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2827820765386543</v>
+        <v>0.2594111040016511</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2666634623205843</v>
+        <v>0.2467189810206442</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.02432341928852511</v>
+        <v>-0.04616550550810392</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2507530932637316</v>
+        <v>0.2209364289310546</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2697947446665411</v>
+        <v>0.2611979667794386</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3735295306310576</v>
+        <v>0.3492916569267848</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4300025986307969</v>
+        <v>0.4058986665548057</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7443985590276887</v>
+        <v>0.7175120575516949</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7618232607848989</v>
+        <v>0.7394015706703343</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.7070673754822128</v>
+        <v>0.6770730702231866</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3493725936510246</v>
+        <v>0.3288416626563005</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7568074558972988</v>
+        <v>0.7341001406937115</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.4514758195341784</v>
+        <v>0.426253089194094</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2976264797458424</v>
+        <v>0.3459212702474327</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3663545689767608</v>
+        <v>0.4310310940176037</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3947988148498164</v>
+        <v>0.459699964158169</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3528867222575309</v>
+        <v>0.4135098426341311</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1303412787193179</v>
+        <v>0.1553525658917541</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4472234552691716</v>
+        <v>0.5073262467082101</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4474050672660612</v>
+        <v>0.5125896424683472</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3668874220562036</v>
+        <v>0.4451039626494478</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4094466262514526</v>
+        <v>0.474015442861484</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3678264124648044</v>
+        <v>0.4500181428367593</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1217974819379585</v>
+        <v>0.1868469290286212</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3530293232771389</v>
+        <v>0.4189890071493913</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1115677676272723</v>
+        <v>0.108898240801468</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2982246861842721</v>
+        <v>0.3684436648600062</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3759895700885185</v>
+        <v>0.4472945531106702</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3864907325380115</v>
+        <v>0.4517022214840202</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.0006119685897296723</v>
+        <v>0.06808270607111305</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2744645439625277</v>
+        <v>0.3351846405102721</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2935061953653363</v>
+        <v>0.3754461783586557</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4375351288215041</v>
+        <v>0.5010984698804781</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5344841549963967</v>
+        <v>0.6188321335533221</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7680942227977425</v>
+        <v>0.8317453659285464</v>
       </c>
       <c r="X9" t="n">
-        <v>0.8742881546173064</v>
+        <v>0.9374346003746941</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.6527679926367348</v>
+        <v>0.7168569032606107</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.4248029948456668</v>
+        <v>0.479914571366481</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.7805189065960947</v>
+        <v>0.8483483522729296</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3912766540730214</v>
+        <v>0.4612881967783086</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.014525911090848</v>
+        <v>3.004920922433874</v>
       </c>
       <c r="C2" t="n">
-        <v>2.989282037650697</v>
+        <v>2.977737747552375</v>
       </c>
       <c r="D2" t="n">
-        <v>3.013234786634417</v>
+        <v>3.007801249119874</v>
       </c>
       <c r="E2" t="n">
-        <v>3.001667207839651</v>
+        <v>2.988231310966243</v>
       </c>
       <c r="F2" t="n">
-        <v>3.004317915601563</v>
+        <v>2.994172354437881</v>
       </c>
       <c r="G2" t="n">
-        <v>3.054439635897065</v>
+        <v>3.031699272293013</v>
       </c>
       <c r="H2" t="n">
-        <v>3.020143604686298</v>
+        <v>3.008974926935863</v>
       </c>
       <c r="I2" t="n">
-        <v>3.004672464093312</v>
+        <v>2.995522859531542</v>
       </c>
       <c r="J2" t="n">
-        <v>3.030370960993768</v>
+        <v>3.014860436272361</v>
       </c>
       <c r="K2" t="n">
-        <v>3.017000604273382</v>
+        <v>3.006165317801735</v>
       </c>
       <c r="L2" t="n">
-        <v>3.026836965503008</v>
+        <v>3.02009437444145</v>
       </c>
       <c r="M2" t="n">
-        <v>3.042473813625783</v>
+        <v>3.027736999497662</v>
       </c>
       <c r="N2" t="n">
-        <v>3.018969970784519</v>
+        <v>3.007959550600314</v>
       </c>
       <c r="O2" t="n">
-        <v>3.413760755473371</v>
+        <v>3.399529777235148</v>
       </c>
       <c r="P2" t="n">
-        <v>3.029239909967549</v>
+        <v>3.010045344812231</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.010293797269318</v>
+        <v>2.998501516229474</v>
       </c>
       <c r="R2" t="n">
-        <v>3.009046929349387</v>
+        <v>3.003400339211148</v>
       </c>
       <c r="S2" t="n">
-        <v>3.032293923859763</v>
+        <v>3.015648124548343</v>
       </c>
       <c r="T2" t="n">
-        <v>3.013678548098795</v>
+        <v>3.001849718611822</v>
       </c>
       <c r="U2" t="n">
-        <v>3.800687437193624</v>
+        <v>3.788958782976779</v>
       </c>
       <c r="V2" t="n">
-        <v>3.000308169743694</v>
+        <v>2.989603293983162</v>
       </c>
       <c r="W2" t="n">
-        <v>3.801105521605745</v>
+        <v>3.791482022495701</v>
       </c>
       <c r="X2" t="n">
-        <v>3.022041513852848</v>
+        <v>3.009162169922744</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.018193182460539</v>
+        <v>3.00407217623327</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.294641577102798</v>
+        <v>3.281903717585465</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.021068149798683</v>
+        <v>3.009632224392421</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.034368757287941</v>
+        <v>3.027012262018983</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.213982526598388</v>
+        <v>2.214828919104609</v>
       </c>
       <c r="C3" t="n">
-        <v>2.085330583970418</v>
+        <v>2.074529590634869</v>
       </c>
       <c r="D3" t="n">
-        <v>2.20611031807914</v>
+        <v>2.236887830058373</v>
       </c>
       <c r="E3" t="n">
-        <v>2.122978990967153</v>
+        <v>2.096531088951571</v>
       </c>
       <c r="F3" t="n">
-        <v>2.142303238351377</v>
+        <v>2.139348545155991</v>
       </c>
       <c r="G3" t="n">
-        <v>2.498228683193081</v>
+        <v>2.405622665600653</v>
       </c>
       <c r="H3" t="n">
-        <v>2.25608490939921</v>
+        <v>2.245801915443121</v>
       </c>
       <c r="I3" t="n">
-        <v>2.144897977456842</v>
+        <v>2.149081960120355</v>
       </c>
       <c r="J3" t="n">
-        <v>2.327421970196206</v>
+        <v>2.286246426966519</v>
       </c>
       <c r="K3" t="n">
-        <v>2.232224802543843</v>
+        <v>2.224328989803753</v>
       </c>
       <c r="L3" t="n">
-        <v>2.302586984306732</v>
+        <v>2.323897756916749</v>
       </c>
       <c r="M3" t="n">
-        <v>2.418796186581197</v>
+        <v>2.383004387684412</v>
       </c>
       <c r="N3" t="n">
-        <v>2.246782440025404</v>
+        <v>2.237638141026836</v>
       </c>
       <c r="O3" t="n">
-        <v>2.881393320175517</v>
+        <v>2.871727326203672</v>
       </c>
       <c r="P3" t="n">
-        <v>2.31884443753468</v>
+        <v>2.25148136627833</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.184810980219706</v>
+        <v>2.170078193557854</v>
       </c>
       <c r="R3" t="n">
-        <v>2.176353305392141</v>
+        <v>2.20566077985943</v>
       </c>
       <c r="S3" t="n">
-        <v>2.340698068951062</v>
+        <v>2.291452265694076</v>
       </c>
       <c r="T3" t="n">
-        <v>2.209274749834124</v>
+        <v>2.194270948773528</v>
       </c>
       <c r="U3" t="n">
-        <v>3.592546631257756</v>
+        <v>3.574789779500309</v>
       </c>
       <c r="V3" t="n">
-        <v>2.112887403349104</v>
+        <v>2.105914396953141</v>
       </c>
       <c r="W3" t="n">
-        <v>3.624445120987655</v>
+        <v>3.617928070553607</v>
       </c>
       <c r="X3" t="n">
-        <v>2.268897857464209</v>
+        <v>2.246388462246935</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.24089638012659</v>
+        <v>2.209560409297088</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.664302651011676</v>
+        <v>2.646892337575506</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.261517815783976</v>
+        <v>2.249336872969383</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.357479983085299</v>
+        <v>2.373960055490174</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5915291525438037</v>
+        <v>0.5229096276152509</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4102383582859004</v>
+        <v>0.3241874080252021</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5769453078618212</v>
+        <v>0.5554442425493368</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4462841840257969</v>
+        <v>0.3343927884877649</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4762251475824164</v>
+        <v>0.4014996075149239</v>
       </c>
       <c r="G4" t="n">
-        <v>1.04237303545057</v>
+        <v>0.8253834079237535</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6549835859711571</v>
+        <v>0.568701473399432</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4802299358970731</v>
+        <v>0.416754183810872</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7700126205277762</v>
+        <v>0.6347336848316663</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6194819504556595</v>
+        <v>0.5369656457453854</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7305881754939588</v>
+        <v>0.6943007481735759</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9130990730762302</v>
+        <v>0.7865872689118614</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6417268511522557</v>
+        <v>6.961714305217533</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6094487707200756</v>
+        <v>0.5348917863329984</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7577305386300608</v>
+        <v>0.5807923357295427</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5437254800610782</v>
+        <v>0.4503994814637744</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5296415333179071</v>
+        <v>0.5057339406116819</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7922270304583934</v>
+        <v>0.6440783102549318</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5819577977423094</v>
+        <v>0.4882189676215942</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7513061365871346</v>
+        <v>0.6528814899618933</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4276145585595631</v>
+        <v>0.3468846442157927</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8204394057415014</v>
+        <v>0.7366385825700738</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6764213430886694</v>
+        <v>0.5708164690722738</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6272414497295513</v>
+        <v>0.5090038132104813</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.5660774265112291</v>
+        <v>0.470386527096593</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.6654267483272883</v>
+        <v>0.5761259505430014</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8142102257713654</v>
+        <v>0.769897092018014</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.51528541564571</v>
+        <v>5.688529073796865</v>
       </c>
       <c r="C5" t="n">
-        <v>2.575945927976265</v>
+        <v>2.441277874211597</v>
       </c>
       <c r="D5" t="n">
-        <v>5.986231654814092</v>
+        <v>7.138962077489985</v>
       </c>
       <c r="E5" t="n">
-        <v>3.197061404797795</v>
+        <v>2.57831298374949</v>
       </c>
       <c r="F5" t="n">
-        <v>3.988987854051696</v>
+        <v>4.0784842589188</v>
       </c>
       <c r="G5" t="n">
-        <v>13.69493565048393</v>
+        <v>11.22710769649442</v>
       </c>
       <c r="H5" t="n">
-        <v>7.832176297695618</v>
+        <v>7.688553861833299</v>
       </c>
       <c r="I5" t="n">
-        <v>4.100475517989567</v>
+        <v>4.419635551966699</v>
       </c>
       <c r="J5" t="n">
-        <v>9.094935958611957</v>
+        <v>8.077129551169758</v>
       </c>
       <c r="K5" t="n">
-        <v>6.366531233371113</v>
+        <v>6.298423090791939</v>
       </c>
       <c r="L5" t="n">
-        <v>8.556068628749651</v>
+        <v>9.360279884017617</v>
       </c>
       <c r="M5" t="n">
-        <v>12.79143390544708</v>
+        <v>11.84095234469155</v>
       </c>
       <c r="N5" t="n">
-        <v>8.748625033562307</v>
+        <v>6.961714305217533</v>
       </c>
       <c r="O5" t="n">
-        <v>5.685471183873944</v>
+        <v>5.750657406804682</v>
       </c>
       <c r="P5" t="n">
-        <v>8.572918406061191</v>
+        <v>6.827011041596116</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.186068542373928</v>
+        <v>4.909758771042638</v>
       </c>
       <c r="R5" t="n">
-        <v>5.165191532235784</v>
+        <v>6.300521762571636</v>
       </c>
       <c r="S5" t="n">
-        <v>9.256865457604571</v>
+        <v>8.014484812789563</v>
       </c>
       <c r="T5" t="n">
-        <v>6.079496859421569</v>
+        <v>5.789727293096608</v>
       </c>
       <c r="U5" t="n">
-        <v>8.863915538960283</v>
+        <v>8.478070440183991</v>
       </c>
       <c r="V5" t="n">
-        <v>2.685440426132006</v>
+        <v>2.641081265252274</v>
       </c>
       <c r="W5" t="n">
-        <v>10.33511393430827</v>
+        <v>10.24404991576326</v>
       </c>
       <c r="X5" t="n">
-        <v>7.830124339222693</v>
+        <v>7.311532292498919</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.710267390386841</v>
+        <v>5.946082507063114</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.201006245067547</v>
+        <v>4.897772366841374</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.381373442795499</v>
+        <v>7.185907935114036</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.20926485037391</v>
+        <v>11.94166323727822</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6166258638661175</v>
+        <v>0.5484237941726332</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5418616528483516</v>
+        <v>0.4477864099005029</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7085686024242707</v>
+        <v>0.5809584091067217</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4713808953481108</v>
+        <v>0.4579917903630645</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5013218589047308</v>
+        <v>0.4270137740723083</v>
       </c>
       <c r="G6" t="n">
-        <v>1.067469746772885</v>
+        <v>0.9489824097990522</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7866068805336067</v>
+        <v>0.6923004752747339</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5053266472193887</v>
+        <v>0.5403531856861717</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9016359150902253</v>
+        <v>0.7583326867069674</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7511052450181104</v>
+        <v>0.5624798123027703</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7556848868162747</v>
+        <v>0.8178997500488753</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9381957843985437</v>
+        <v>0.9101862707871602</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6675077478747684</v>
+        <v>6.961714305217533</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7464447417678798</v>
+        <v>0.5612657202870994</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8947175863682133</v>
+        <v>0.7093709711769228</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6753487746235287</v>
+        <v>0.4759136480211584</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6612648278803559</v>
+        <v>0.6293329424869807</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9238503250208439</v>
+        <v>0.6695924768123157</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6070545090646247</v>
+        <v>0.5137331341789781</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7821140678725396</v>
+        <v>0.6827144921456589</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5592378531220136</v>
+        <v>0.3723988107731767</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9574385049949673</v>
+        <v>0.7678830418767484</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8080446376511187</v>
+        <v>0.6944154709475748</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6605865449729766</v>
+        <v>0.5416954168847754</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6977007210736791</v>
+        <v>0.4959006936539794</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6905234596496032</v>
+        <v>0.6997249524183021</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8415029994114267</v>
+        <v>0.7980380619817833</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7163234238534352</v>
+        <v>0.6420743420538086</v>
       </c>
       <c r="C7" t="n">
-        <v>0.535032629595535</v>
+        <v>0.4433521224637604</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7017395791714546</v>
+        <v>0.6746089569878954</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5710784553354304</v>
+        <v>0.453557502926323</v>
       </c>
       <c r="F7" t="n">
-        <v>0.60101941889205</v>
+        <v>0.5206643219534823</v>
       </c>
       <c r="G7" t="n">
-        <v>1.167167306760203</v>
+        <v>0.9445481223623111</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7797778572807915</v>
+        <v>0.6878661878379903</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6050242072067078</v>
+        <v>0.5359188982494297</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8948068918374089</v>
+        <v>0.7538983992702251</v>
       </c>
       <c r="K7" t="n">
-        <v>0.744276221765294</v>
+        <v>0.6561303601839439</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8553824468035925</v>
+        <v>0.8134654626121388</v>
       </c>
       <c r="M7" t="n">
-        <v>1.037893344385864</v>
+        <v>0.9057519833504183</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7665211224618907</v>
+        <v>6.961714305217533</v>
       </c>
       <c r="O7" t="n">
-        <v>0.733883981207867</v>
+        <v>0.6536974897877964</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8821657491178524</v>
+        <v>0.6995980391843404</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6685197513707128</v>
+        <v>0.569564195902333</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6544358046275407</v>
+        <v>0.6248986550502394</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9170213017680268</v>
+        <v>0.7632430246934887</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7067520690519432</v>
+        <v>0.6073836820601523</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8814915457611568</v>
+        <v>0.7762004749751371</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5524088298691967</v>
+        <v>0.4660493586543444</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9452336770511354</v>
+        <v>0.8558032970086307</v>
       </c>
       <c r="X7" t="n">
-        <v>0.8012156143983032</v>
+        <v>0.6899811835108335</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.7577469410022788</v>
+        <v>0.6324873632754212</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6908716978208629</v>
+        <v>0.5895512415351516</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.7902210196369215</v>
+        <v>0.6952906649815599</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.939004497081</v>
+        <v>0.8890618064565748</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.772368301844902</v>
+        <v>0.6953860455984587</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7342603065920077</v>
+        <v>0.632534789629622</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9009672561679297</v>
+        <v>0.8637916241537578</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6940655155107206</v>
+        <v>0.5703928899241342</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6793705035437321</v>
+        <v>0.5951431336622757</v>
       </c>
       <c r="G8" t="n">
-        <v>1.39608486987153</v>
+        <v>1.161904518945317</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9790055342772646</v>
+        <v>0.8770488550038521</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8042518842031823</v>
+        <v>0.7251015654152917</v>
       </c>
       <c r="J8" t="n">
-        <v>1.094034568833882</v>
+        <v>0.9430810664360866</v>
       </c>
       <c r="K8" t="n">
-        <v>0.943503898761767</v>
+        <v>0.8453130273498057</v>
       </c>
       <c r="L8" t="n">
-        <v>1.054610123800067</v>
+        <v>1.002648129777994</v>
       </c>
       <c r="M8" t="n">
-        <v>1.237121021382329</v>
+        <v>1.094934650516382</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8547581762424437</v>
+        <v>6.961714305217533</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8529812827323426</v>
+        <v>0.7668600403769219</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9937864727213409</v>
+        <v>0.8056658140462621</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6964259413975243</v>
+        <v>0.5961741540156026</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8536634816240147</v>
+        <v>0.8140813222161003</v>
       </c>
       <c r="S8" t="n">
-        <v>1.116248978764504</v>
+        <v>0.9524256918593517</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9059797460484158</v>
+        <v>0.7965663492260135</v>
       </c>
       <c r="U8" t="n">
-        <v>1.011183899193548</v>
+        <v>0.899381594069707</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7125358069492982</v>
+        <v>0.6182626502929839</v>
       </c>
       <c r="W8" t="n">
-        <v>1.144489493467349</v>
+        <v>1.045012666623355</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8422447923992857</v>
+        <v>0.7290439853653187</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.099389692305241</v>
+        <v>0.9570212250799286</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.7442568818194691</v>
+        <v>0.6403390721816388</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.9894486966333945</v>
+        <v>0.8844733321474205</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.287798580293253</v>
+        <v>1.220173056388038</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.065582485198938</v>
+        <v>0.9639006297050275</v>
       </c>
       <c r="C9" t="n">
-        <v>1.027702333580094</v>
+        <v>0.898575761147186</v>
       </c>
       <c r="D9" t="n">
-        <v>1.194409283156016</v>
+        <v>1.12983259567132</v>
       </c>
       <c r="E9" t="n">
-        <v>1.030649607137067</v>
+        <v>0.8779936083500078</v>
       </c>
       <c r="F9" t="n">
-        <v>0.763088384636054</v>
+        <v>0.6683706059037703</v>
       </c>
       <c r="G9" t="n">
-        <v>1.659837061676386</v>
+        <v>1.399771801659933</v>
       </c>
       <c r="H9" t="n">
-        <v>1.272447561265351</v>
+        <v>1.143089826521418</v>
       </c>
       <c r="I9" t="n">
-        <v>1.097693911191267</v>
+        <v>0.9911425369328557</v>
       </c>
       <c r="J9" t="n">
-        <v>1.387476595821969</v>
+        <v>1.209122037953652</v>
       </c>
       <c r="K9" t="n">
-        <v>1.236945925749854</v>
+        <v>1.11135399886737</v>
       </c>
       <c r="L9" t="n">
-        <v>1.348052150788152</v>
+        <v>1.268689101295563</v>
       </c>
       <c r="M9" t="n">
-        <v>1.530563048370424</v>
+        <v>1.360975622033845</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25919082644645</v>
+        <v>6.961714305217533</v>
       </c>
       <c r="O9" t="n">
-        <v>1.274438913014942</v>
+        <v>1.153487900991823</v>
       </c>
       <c r="P9" t="n">
-        <v>1.43305679575912</v>
+        <v>1.209002871212287</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.161189506286893</v>
+        <v>1.024787875199954</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1471055086121</v>
+        <v>1.080122293733666</v>
       </c>
       <c r="S9" t="n">
-        <v>1.409691005752588</v>
+        <v>1.218466663376915</v>
       </c>
       <c r="T9" t="n">
-        <v>1.199421773036503</v>
+        <v>1.062607320743576</v>
       </c>
       <c r="U9" t="n">
-        <v>1.37448133184442</v>
+        <v>1.23158867871026</v>
       </c>
       <c r="V9" t="n">
-        <v>1.210571212420967</v>
+        <v>1.07521054889574</v>
       </c>
       <c r="W9" t="n">
-        <v>1.437903381035697</v>
+        <v>1.311026935692057</v>
       </c>
       <c r="X9" t="n">
-        <v>1.293885318382863</v>
+        <v>1.145204822194259</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.250416644986838</v>
+        <v>1.087711001958848</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.097077557090371</v>
+        <v>0.9643481558288912</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.282890723621482</v>
+        <v>1.150514303664986</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.431674201065561</v>
+        <v>1.344285445140001</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.004461522372055</v>
+        <v>2.993704286083266</v>
       </c>
       <c r="C2" t="n">
-        <v>2.986088133746045</v>
+        <v>2.973179169266134</v>
       </c>
       <c r="D2" t="n">
-        <v>3.012077744015567</v>
+        <v>3.006090059820969</v>
       </c>
       <c r="E2" t="n">
-        <v>2.997074426008706</v>
+        <v>2.983401361808401</v>
       </c>
       <c r="F2" t="n">
-        <v>2.995715568935442</v>
+        <v>2.984673760201456</v>
       </c>
       <c r="G2" t="n">
-        <v>3.046582188767974</v>
+        <v>3.023249526712759</v>
       </c>
       <c r="H2" t="n">
-        <v>3.01150497350046</v>
+        <v>2.999988632796625</v>
       </c>
       <c r="I2" t="n">
-        <v>3.001245374598829</v>
+        <v>2.989338709809477</v>
       </c>
       <c r="J2" t="n">
-        <v>3.023674032871156</v>
+        <v>3.007401118271578</v>
       </c>
       <c r="K2" t="n">
-        <v>3.010015992951109</v>
+        <v>2.994727074639386</v>
       </c>
       <c r="L2" t="n">
-        <v>3.017117430566019</v>
+        <v>3.008779293605888</v>
       </c>
       <c r="M2" t="n">
-        <v>3.031727821250708</v>
+        <v>3.016405375863915</v>
       </c>
       <c r="N2" t="n">
-        <v>3.00783775106837</v>
+        <v>2.995262703401123</v>
       </c>
       <c r="O2" t="n">
-        <v>3.394156122978841</v>
+        <v>3.377887207515207</v>
       </c>
       <c r="P2" t="n">
-        <v>3.024530012592384</v>
+        <v>3.004223319467502</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.995478381325885</v>
+        <v>2.982912892594884</v>
       </c>
       <c r="R2" t="n">
-        <v>3.001772016351285</v>
+        <v>2.995013857550892</v>
       </c>
       <c r="S2" t="n">
-        <v>3.024363992454244</v>
+        <v>3.007133908903144</v>
       </c>
       <c r="T2" t="n">
-        <v>3.006960585789981</v>
+        <v>2.993365681091113</v>
       </c>
       <c r="U2" t="n">
-        <v>3.786018250906677</v>
+        <v>3.771206933615795</v>
       </c>
       <c r="V2" t="n">
-        <v>3.000075877271722</v>
+        <v>2.988724585304755</v>
       </c>
       <c r="W2" t="n">
-        <v>3.788459942473355</v>
+        <v>3.776961558344381</v>
       </c>
       <c r="X2" t="n">
-        <v>3.025046383576484</v>
+        <v>3.011137766632613</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.024586549025551</v>
+        <v>3.007283865400357</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.288555869064393</v>
+        <v>3.274753792457812</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.015667963051719</v>
+        <v>3.002261503898954</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.02721069411092</v>
+        <v>3.018371321593318</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.173059757386417</v>
+        <v>2.169998832300358</v>
       </c>
       <c r="C3" t="n">
-        <v>2.094535504464051</v>
+        <v>2.081593485156299</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228442853667764</v>
+        <v>2.259541761117164</v>
       </c>
       <c r="E3" t="n">
-        <v>2.120838696120583</v>
+        <v>2.096990469535405</v>
       </c>
       <c r="F3" t="n">
-        <v>2.111374502855864</v>
+        <v>2.106311819476156</v>
       </c>
       <c r="G3" t="n">
-        <v>2.472468785825285</v>
+        <v>2.380000594206514</v>
       </c>
       <c r="H3" t="n">
-        <v>2.224984486459966</v>
+        <v>2.216530223456968</v>
       </c>
       <c r="I3" t="n">
-        <v>2.151066998670874</v>
+        <v>2.139816015726281</v>
       </c>
       <c r="J3" t="n">
-        <v>2.310127182743765</v>
+        <v>2.267829096518155</v>
       </c>
       <c r="K3" t="n">
-        <v>2.212578918197877</v>
+        <v>2.177295770275555</v>
       </c>
       <c r="L3" t="n">
-        <v>2.263783147142166</v>
+        <v>2.277997391717097</v>
       </c>
       <c r="M3" t="n">
-        <v>2.372929694476344</v>
+        <v>2.337229054823425</v>
       </c>
       <c r="N3" t="n">
-        <v>2.197912388989841</v>
+        <v>2.181889060175932</v>
       </c>
       <c r="O3" t="n">
-        <v>2.825446253079728</v>
+        <v>2.810682699147954</v>
       </c>
       <c r="P3" t="n">
-        <v>2.315670518064923</v>
+        <v>2.244716122716509</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.109497106333171</v>
+        <v>2.093549620553586</v>
       </c>
       <c r="R3" t="n">
-        <v>2.154972021640239</v>
+        <v>2.180629384948489</v>
       </c>
       <c r="S3" t="n">
-        <v>2.314658456254162</v>
+        <v>2.265555110180444</v>
       </c>
       <c r="T3" t="n">
-        <v>2.191929495386156</v>
+        <v>2.168593378195403</v>
       </c>
       <c r="U3" t="n">
-        <v>3.53809501800025</v>
+        <v>3.508189835317334</v>
       </c>
       <c r="V3" t="n">
-        <v>2.141595922249938</v>
+        <v>2.134303397715203</v>
       </c>
       <c r="W3" t="n">
-        <v>3.589826628077989</v>
+        <v>3.581154663459959</v>
       </c>
       <c r="X3" t="n">
-        <v>2.320992281252635</v>
+        <v>2.295433344627467</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.317163466559466</v>
+        <v>2.267416003160079</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.661623366804279</v>
+        <v>2.642309239816913</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.253630665787898</v>
+        <v>2.231678926194728</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.33709629317188</v>
+        <v>2.347316016283808</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5194924583398972</v>
+        <v>0.4509364288023366</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4189311713353023</v>
+        <v>0.3373374968763544</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6055211854383972</v>
+        <v>0.5908394409071062</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4360518066836363</v>
+        <v>0.3345601595384415</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4207028909359777</v>
+        <v>0.3489324847201433</v>
       </c>
       <c r="G4" t="n">
-        <v>0.995264761745654</v>
+        <v>0.7846635131946685</v>
       </c>
       <c r="H4" t="n">
-        <v>0.599051478982829</v>
+        <v>0.5219210158720616</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4831645897402297</v>
+        <v>0.4016252365256062</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7360551541890907</v>
+        <v>0.605243717358375</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5822327587130141</v>
+        <v>0.462489296049708</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6624467633961186</v>
+        <v>0.6212155736164425</v>
       </c>
       <c r="M4" t="n">
-        <v>0.833947868449522</v>
+        <v>0.7138525939991159</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5576285146067166</v>
+        <v>5.042007288042453</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5392102682237375</v>
+        <v>0.465285801164692</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7461752873401216</v>
+        <v>0.5697537498717062</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4180237477743471</v>
+        <v>0.3290426750647912</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4891132506013963</v>
+        <v>0.4657286409618305</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7443000135068099</v>
+        <v>0.6026301964845736</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5477205292713206</v>
+        <v>0.4471117296499826</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6691212197734892</v>
+        <v>0.5591491323338141</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4669220013426283</v>
+        <v>0.3919713724837046</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7707420260707232</v>
+        <v>0.6931089649941781</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7520079351479034</v>
+        <v>0.6478556114045044</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7423895446102702</v>
+        <v>0.6001019606881984</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.5609520387196578</v>
+        <v>0.4691309144170134</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.6460743610341003</v>
+        <v>0.5475941405452373</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7752084129551091</v>
+        <v>0.727322293227378</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.250880017482555</v>
+        <v>4.332814020114644</v>
       </c>
       <c r="C5" t="n">
-        <v>2.716515263958426</v>
+        <v>2.579399721993859</v>
       </c>
       <c r="D5" t="n">
-        <v>6.304005209724657</v>
+        <v>7.400619806973491</v>
       </c>
       <c r="E5" t="n">
-        <v>3.034732089323258</v>
+        <v>2.546120308779971</v>
       </c>
       <c r="F5" t="n">
-        <v>2.88454514743171</v>
+        <v>2.924785372985711</v>
       </c>
       <c r="G5" t="n">
-        <v>12.03954429175318</v>
+        <v>9.787533700492958</v>
       </c>
       <c r="H5" t="n">
-        <v>6.515812912789048</v>
+        <v>6.45875317168948</v>
       </c>
       <c r="I5" t="n">
-        <v>4.106400647423959</v>
+        <v>3.965683970538863</v>
       </c>
       <c r="J5" t="n">
-        <v>8.061101969583666</v>
+        <v>7.107763839782042</v>
       </c>
       <c r="K5" t="n">
-        <v>5.296611026910789</v>
+        <v>4.535717864343332</v>
       </c>
       <c r="L5" t="n">
-        <v>6.985278898383148</v>
+        <v>7.555647460900432</v>
       </c>
       <c r="M5" t="n">
-        <v>10.72135891000643</v>
+        <v>9.854320195075708</v>
       </c>
       <c r="N5" t="n">
-        <v>6.870557366239977</v>
+        <v>5.042007288042453</v>
       </c>
       <c r="O5" t="n">
-        <v>4.364862723036253</v>
+        <v>4.35336735602296</v>
       </c>
       <c r="P5" t="n">
-        <v>7.939330597422645</v>
+        <v>6.248990092951697</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.741507863735054</v>
+        <v>2.472051602951899</v>
       </c>
       <c r="R5" t="n">
-        <v>4.287457058936383</v>
+        <v>5.259878468570383</v>
       </c>
       <c r="S5" t="n">
-        <v>7.995729192038427</v>
+        <v>6.864649284462942</v>
       </c>
       <c r="T5" t="n">
-        <v>5.285879565295808</v>
+        <v>4.789189756598449</v>
       </c>
       <c r="U5" t="n">
-        <v>6.986474419157287</v>
+        <v>6.364637505375476</v>
       </c>
       <c r="V5" t="n">
-        <v>3.287079100036909</v>
+        <v>3.254901189405972</v>
       </c>
       <c r="W5" t="n">
-        <v>9.004767830683626</v>
+        <v>8.937148475699351</v>
       </c>
       <c r="X5" t="n">
-        <v>8.890512286180927</v>
+        <v>8.339524174632748</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.515202744283048</v>
+        <v>7.304339681036744</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.712802498494623</v>
+        <v>4.421113475410813</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.795433390165971</v>
+        <v>6.356825827897234</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.992378700188778</v>
+        <v>10.50851130629887</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.54506922317303</v>
+        <v>0.5629905267805632</v>
       </c>
       <c r="C6" t="n">
-        <v>0.444507936168434</v>
+        <v>0.3623137050668395</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7267099286221075</v>
+        <v>0.7028935388853327</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4616285715167681</v>
+        <v>0.446614257516668</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5418916341196871</v>
+        <v>0.3739086929106279</v>
       </c>
       <c r="G6" t="n">
-        <v>1.020841526578786</v>
+        <v>0.8096397213851523</v>
       </c>
       <c r="H6" t="n">
-        <v>0.62462824381596</v>
+        <v>0.5468972240625467</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5087413545733611</v>
+        <v>0.4266014447160909</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8572438973728007</v>
+        <v>0.7172978153366034</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7034215018967238</v>
+        <v>0.5745433940279348</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6880235282292488</v>
+        <v>0.733269671594669</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9551366116332306</v>
+        <v>0.7388288021896008</v>
       </c>
       <c r="N6" t="n">
-        <v>0.583859055334176</v>
+        <v>5.042007288042453</v>
       </c>
       <c r="O6" t="n">
-        <v>0.565440808951196</v>
+        <v>0.5819163674404928</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8721273352708806</v>
+        <v>0.6863431005981419</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5392124909580569</v>
+        <v>0.4410967730430178</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6103019937851057</v>
+        <v>0.4907048491523151</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7698767783399407</v>
+        <v>0.7146842944627999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5732972941044526</v>
+        <v>0.4720879378404673</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6991223323571579</v>
+        <v>0.5883474039400954</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5881107445263382</v>
+        <v>0.5040254704619306</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8013625678895197</v>
+        <v>0.8097542325629685</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7775846999810357</v>
+        <v>0.6728318195949902</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.7749376884100051</v>
+        <v>0.6320802423315823</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5865288035527889</v>
+        <v>0.58118501239524</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.7672631042178081</v>
+        <v>0.659648238523465</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8026740053563408</v>
+        <v>0.7545546493959411</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6293432973542171</v>
+        <v>0.5567867902162271</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5287820103496221</v>
+        <v>0.443187858290246</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7153720244527172</v>
+        <v>0.6966898023209972</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5459026456979561</v>
+        <v>0.4404105209523323</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5305537299502975</v>
+        <v>0.4547828461340337</v>
       </c>
       <c r="G7" t="n">
-        <v>1.105115600759972</v>
+        <v>0.8905138746085586</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7089023179971471</v>
+        <v>0.6277713772859529</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5930154287545497</v>
+        <v>0.5074755979394983</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8459059932034101</v>
+        <v>0.711094078772265</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6920835977273336</v>
+        <v>0.5683396574635989</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7722976024104375</v>
+        <v>0.727065935030334</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9437987074638402</v>
+        <v>0.8197029554130058</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6674793536210367</v>
+        <v>5.042007288042453</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6487267838486578</v>
+        <v>0.570801923104459</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8556918029650412</v>
+        <v>0.6752698718114741</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5278745867886666</v>
+        <v>0.4348930364786827</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5989640896157157</v>
+        <v>0.571579002375721</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8541508525211295</v>
+        <v>0.7084805578984649</v>
       </c>
       <c r="T7" t="n">
-        <v>0.657571368285641</v>
+        <v>0.5529620910638725</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7827590448910993</v>
+        <v>0.66877623461359</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5767728403569482</v>
+        <v>0.4978217338975954</v>
       </c>
       <c r="W7" t="n">
-        <v>0.880592865085042</v>
+        <v>0.7989593264080685</v>
       </c>
       <c r="X7" t="n">
-        <v>0.8618587741622215</v>
+        <v>0.753705972818397</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8566647313751281</v>
+        <v>0.7101743855178857</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6708028777339776</v>
+        <v>0.574981275830904</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.7559252000484195</v>
+        <v>0.6534445019591294</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8850592519694279</v>
+        <v>0.8331726546412703</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6776546892267041</v>
+        <v>0.6021482462641843</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7023809178829913</v>
+        <v>0.6073554587962872</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8889709319860859</v>
+        <v>0.8608574028270388</v>
       </c>
       <c r="E8" t="n">
-        <v>0.652789646911605</v>
+        <v>0.5413173541093448</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5983834524857577</v>
+        <v>0.518652910964099</v>
       </c>
       <c r="G8" t="n">
-        <v>1.304693690830408</v>
+        <v>1.079316703113194</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8825012255305175</v>
+        <v>0.7919389777919965</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7666143362879191</v>
+        <v>0.6716431984455398</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01950490073678</v>
+        <v>0.8752616792783079</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8656825052607027</v>
+        <v>0.7325072579696414</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9458965099438067</v>
+        <v>0.8912335355363772</v>
       </c>
       <c r="M8" t="n">
-        <v>1.117397614997196</v>
+        <v>0.9838705559192396</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7439594763481253</v>
+        <v>5.042007288042453</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7522303152490972</v>
+        <v>0.6685175313578291</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9526531946687623</v>
+        <v>0.7667817782012145</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5515641223117054</v>
+        <v>0.4569063735399668</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7725629971490857</v>
+        <v>0.7357466028817643</v>
       </c>
       <c r="S8" t="n">
-        <v>1.027749760054499</v>
+        <v>0.8726481584045076</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8311702758190096</v>
+        <v>0.7171296915699149</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8956093026040137</v>
+        <v>0.7753153775516823</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7158697510967524</v>
+        <v>0.629422872641899</v>
       </c>
       <c r="W8" t="n">
-        <v>1.054216395110186</v>
+        <v>0.9631502756606037</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8970311593873149</v>
+        <v>0.7866081290508019</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.154432408725452</v>
+        <v>0.9923209620152492</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.7167869896888343</v>
+        <v>0.6181358467558297</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.9295241075817893</v>
+        <v>0.8176121024651729</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.189531445893212</v>
+        <v>1.121443207381977</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9207359062422042</v>
+        <v>0.8234742631727019</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9419317492796514</v>
+        <v>0.8227949203173763</v>
       </c>
       <c r="D9" t="n">
-        <v>1.128521763382746</v>
+        <v>1.076296864348127</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9309513752228976</v>
+        <v>0.7939562343431378</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6630199863124161</v>
+        <v>0.5740793824900823</v>
       </c>
       <c r="G9" t="n">
-        <v>1.518265391133209</v>
+        <v>1.270120978146865</v>
       </c>
       <c r="H9" t="n">
-        <v>1.122052056927177</v>
+        <v>1.007378439313085</v>
       </c>
       <c r="I9" t="n">
-        <v>1.006165167684577</v>
+        <v>0.8870826599666303</v>
       </c>
       <c r="J9" t="n">
-        <v>1.25905573213344</v>
+        <v>1.090701140799397</v>
       </c>
       <c r="K9" t="n">
-        <v>1.105233336657363</v>
+        <v>0.947946719490729</v>
       </c>
       <c r="L9" t="n">
-        <v>1.185447341340466</v>
+        <v>1.106672997057466</v>
       </c>
       <c r="M9" t="n">
-        <v>1.35694844639387</v>
+        <v>1.199310017440139</v>
       </c>
       <c r="N9" t="n">
-        <v>1.080629092551067</v>
+        <v>5.042007288042453</v>
       </c>
       <c r="O9" t="n">
-        <v>1.10256106812809</v>
+        <v>0.9881646838360764</v>
       </c>
       <c r="P9" t="n">
-        <v>1.318301557039537</v>
+        <v>1.10077114885361</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9410243771619013</v>
+        <v>0.8145001400169872</v>
       </c>
       <c r="R9" t="n">
-        <v>1.012113828545745</v>
+        <v>0.9511860644028514</v>
       </c>
       <c r="S9" t="n">
-        <v>1.267300591451158</v>
+        <v>1.088087619925596</v>
       </c>
       <c r="T9" t="n">
-        <v>1.070721107215669</v>
+        <v>0.9325691530910052</v>
       </c>
       <c r="U9" t="n">
-        <v>1.196546145468375</v>
+        <v>1.048828619190631</v>
       </c>
       <c r="V9" t="n">
-        <v>1.130427605398371</v>
+        <v>1.007735486866757</v>
       </c>
       <c r="W9" t="n">
-        <v>1.293742604015072</v>
+        <v>1.178566388435199</v>
       </c>
       <c r="X9" t="n">
-        <v>1.275008513092251</v>
+        <v>1.133313034845528</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.269814470305157</v>
+        <v>1.089781447545017</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.010543914742631</v>
+        <v>0.8865078833336996</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.169074938978449</v>
+        <v>1.033051563986261</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.298208990899459</v>
+        <v>1.212779716668402</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.996197650045962</v>
+        <v>2.986440352726758</v>
       </c>
       <c r="C2" t="n">
-        <v>2.981618302793335</v>
+        <v>2.969373732505465</v>
       </c>
       <c r="D2" t="n">
-        <v>2.997411939951994</v>
+        <v>2.991404244094946</v>
       </c>
       <c r="E2" t="n">
-        <v>2.98703970837939</v>
+        <v>2.975170244442945</v>
       </c>
       <c r="F2" t="n">
-        <v>2.991549453756452</v>
+        <v>2.981805155986176</v>
       </c>
       <c r="G2" t="n">
-        <v>3.03161975548442</v>
+        <v>3.011194357458953</v>
       </c>
       <c r="H2" t="n">
-        <v>3.002704845886672</v>
+        <v>2.992294638240919</v>
       </c>
       <c r="I2" t="n">
-        <v>2.995999909367459</v>
+        <v>2.984178388242388</v>
       </c>
       <c r="J2" t="n">
-        <v>3.013363057621167</v>
+        <v>2.999101497669393</v>
       </c>
       <c r="K2" t="n">
-        <v>3.008489833163484</v>
+        <v>2.993622247894012</v>
       </c>
       <c r="L2" t="n">
-        <v>3.006361973469461</v>
+        <v>2.998492806051089</v>
       </c>
       <c r="M2" t="n">
-        <v>3.01860919191696</v>
+        <v>3.005102718192138</v>
       </c>
       <c r="N2" t="n">
-        <v>2.99859353903736</v>
+        <v>2.987512842067502</v>
       </c>
       <c r="O2" t="n">
-        <v>3.375823748679799</v>
+        <v>3.360494244125724</v>
       </c>
       <c r="P2" t="n">
-        <v>3.015836776185736</v>
+        <v>2.997599713574871</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.992831400444063</v>
+        <v>2.981222071111544</v>
       </c>
       <c r="R2" t="n">
-        <v>2.994454743736578</v>
+        <v>2.987698298529794</v>
       </c>
       <c r="S2" t="n">
-        <v>3.014272162977699</v>
+        <v>2.998794177571321</v>
       </c>
       <c r="T2" t="n">
-        <v>2.998704381644585</v>
+        <v>2.987089320939499</v>
       </c>
       <c r="U2" t="n">
-        <v>3.77935912342571</v>
+        <v>3.766077453318106</v>
       </c>
       <c r="V2" t="n">
-        <v>3.00270860966322</v>
+        <v>2.992915645544042</v>
       </c>
       <c r="W2" t="n">
-        <v>3.779102781868702</v>
+        <v>3.76959153581853</v>
       </c>
       <c r="X2" t="n">
-        <v>3.020593795065112</v>
+        <v>3.007918090678546</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.037819482443747</v>
+        <v>3.015766752852954</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.276777993790596</v>
+        <v>3.264392202083637</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.011440896589036</v>
+        <v>2.998579365828175</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.017126130848845</v>
+        <v>3.009074116475246</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.154082243936776</v>
+        <v>2.150452891166315</v>
       </c>
       <c r="C3" t="n">
-        <v>2.104415172951752</v>
+        <v>2.091059540351124</v>
       </c>
       <c r="D3" t="n">
-        <v>2.163460044312282</v>
+        <v>2.186616961037769</v>
       </c>
       <c r="E3" t="n">
-        <v>2.089186064912585</v>
+        <v>2.070541942175246</v>
       </c>
       <c r="F3" t="n">
-        <v>2.12177290090931</v>
+        <v>2.118268855554074</v>
       </c>
       <c r="G3" t="n">
-        <v>2.40543196714004</v>
+        <v>2.326087007078509</v>
       </c>
       <c r="H3" t="n">
-        <v>2.202249559387648</v>
+        <v>2.193986278384092</v>
       </c>
       <c r="I3" t="n">
-        <v>2.15367026575878</v>
+        <v>2.135309285807349</v>
       </c>
       <c r="J3" t="n">
-        <v>2.276460963403593</v>
+        <v>2.240838068265504</v>
       </c>
       <c r="K3" t="n">
-        <v>2.241725073995902</v>
+        <v>2.201764617149726</v>
       </c>
       <c r="L3" t="n">
-        <v>2.226776084961259</v>
+        <v>2.236598846941949</v>
       </c>
       <c r="M3" t="n">
-        <v>2.318713071783406</v>
+        <v>2.288315226388756</v>
       </c>
       <c r="N3" t="n">
-        <v>2.172078421593501</v>
+        <v>2.159022174394509</v>
       </c>
       <c r="O3" t="n">
-        <v>2.77736998449239</v>
+        <v>2.761863756664854</v>
       </c>
       <c r="P3" t="n">
-        <v>2.293388334262339</v>
+        <v>2.229577319479455</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.13061735728923</v>
+        <v>2.113804066961663</v>
       </c>
       <c r="R3" t="n">
-        <v>2.14285636474036</v>
+        <v>2.16078748871121</v>
       </c>
       <c r="S3" t="n">
-        <v>2.282700479234166</v>
+        <v>2.238412435040881</v>
       </c>
       <c r="T3" t="n">
-        <v>2.173115634493192</v>
+        <v>2.156226046996115</v>
       </c>
       <c r="U3" t="n">
-        <v>3.549071430496872</v>
+        <v>3.517217684207751</v>
       </c>
       <c r="V3" t="n">
-        <v>2.200069565706428</v>
+        <v>2.196178446837498</v>
       </c>
       <c r="W3" t="n">
-        <v>3.585016891974582</v>
+        <v>3.578602913621354</v>
       </c>
       <c r="X3" t="n">
-        <v>2.328861016512149</v>
+        <v>2.304428527358727</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.452194769480859</v>
+        <v>2.360761512225863</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.633834370046293</v>
+        <v>2.615653209529639</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.263689991750078</v>
+        <v>2.237919914080229</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.304824509403474</v>
+        <v>2.312994614426423</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4824528929032859</v>
+        <v>0.4250432200556757</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4283098587183589</v>
+        <v>0.3593073473323504</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4961688559928659</v>
+        <v>0.4811126565622166</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3790097289180533</v>
+        <v>0.2977421624840468</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4299493775373432</v>
+        <v>0.3726865405749621</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8825618688042403</v>
+        <v>0.7046510909105933</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5559546633820954</v>
+        <v>0.4911700680425113</v>
       </c>
       <c r="I4" t="n">
-        <v>0.480219320974402</v>
+        <v>0.3994932906496654</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6759891540163162</v>
+        <v>0.5677478024695082</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6212987558993044</v>
+        <v>0.5061660298048026</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5972636017914936</v>
+        <v>0.5611812247564434</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7423317188519393</v>
+        <v>0.6425532951092416</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5095155612245422</v>
+        <v>4.45754635868574</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4757354414055006</v>
+        <v>0.4127778362074715</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7042858570964061</v>
+        <v>0.5510933343947148</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4444295550985317</v>
+        <v>0.3661003286836898</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4627659643622767</v>
+        <v>0.4392522965846404</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6866128311540081</v>
+        <v>0.5645853547151972</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5107675794632575</v>
+        <v>0.4323736145586958</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6908181809305095</v>
+        <v>0.586063816965613</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5536203868935975</v>
+        <v>0.4961176683090533</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7662207495264758</v>
+        <v>0.7021884796077602</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7580185736757729</v>
+        <v>0.6676441504687124</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.9499188700053725</v>
+        <v>0.7526616844822075</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.5179622034254078</v>
+        <v>0.4393233648760667</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.6546323748471892</v>
+        <v>0.5621589572581008</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7175338091422727</v>
+        <v>0.6785075179904354</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.713188526497306</v>
+        <v>3.769175731394048</v>
       </c>
       <c r="C5" t="n">
-        <v>3.048360798765801</v>
+        <v>2.913240633959896</v>
       </c>
       <c r="D5" t="n">
-        <v>4.324418532904734</v>
+        <v>5.142544113264734</v>
       </c>
       <c r="E5" t="n">
-        <v>2.124344566359896</v>
+        <v>1.789390876241729</v>
       </c>
       <c r="F5" t="n">
-        <v>3.232875567971309</v>
+        <v>3.308317131334378</v>
       </c>
       <c r="G5" t="n">
-        <v>10.03337050419147</v>
+        <v>8.177388402899554</v>
       </c>
       <c r="H5" t="n">
-        <v>5.907195812256428</v>
+        <v>5.846180482013193</v>
       </c>
       <c r="I5" t="n">
-        <v>4.191549618790947</v>
+        <v>3.835584407665222</v>
       </c>
       <c r="J5" t="n">
-        <v>7.073894644462064</v>
+        <v>6.309673170441192</v>
       </c>
       <c r="K5" t="n">
-        <v>6.123772653847683</v>
+        <v>5.23204500874694</v>
       </c>
       <c r="L5" t="n">
-        <v>5.821828257405921</v>
+        <v>6.242813223971427</v>
       </c>
       <c r="M5" t="n">
-        <v>8.839153622629516</v>
+        <v>8.14602593859666</v>
       </c>
       <c r="N5" t="n">
-        <v>7.079301301114704</v>
+        <v>4.45754635868574</v>
       </c>
       <c r="O5" t="n">
-        <v>3.546769519611418</v>
+        <v>3.512811694694004</v>
       </c>
       <c r="P5" t="n">
-        <v>7.191343511575716</v>
+        <v>5.728851118172259</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.330994889558035</v>
+        <v>3.034660487934754</v>
       </c>
       <c r="R5" t="n">
-        <v>3.993770268550109</v>
+        <v>4.723497669474847</v>
       </c>
       <c r="S5" t="n">
-        <v>7.126927808081179</v>
+        <v>6.128215681392876</v>
       </c>
       <c r="T5" t="n">
-        <v>4.806167310536143</v>
+        <v>4.490346853792426</v>
       </c>
       <c r="U5" t="n">
-        <v>7.263275687640431</v>
+        <v>6.561400555517717</v>
       </c>
       <c r="V5" t="n">
-        <v>4.761923735330461</v>
+        <v>4.807358703839619</v>
       </c>
       <c r="W5" t="n">
-        <v>9.134382683999231</v>
+        <v>9.086666591957977</v>
       </c>
       <c r="X5" t="n">
-        <v>8.930226645490221</v>
+        <v>8.41648603271349</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.57530163475539</v>
+        <v>10.14860016398166</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.007244869597875</v>
+        <v>3.738707681482557</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.181305643184355</v>
+        <v>6.624566038922216</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.953870218638189</v>
+        <v>9.389989312251647</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6009406332876814</v>
+        <v>0.4531872579243933</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4576703495798647</v>
+        <v>0.3874513852010709</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5255293468543714</v>
+        <v>0.5904707456699948</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4974974693024487</v>
+        <v>0.4071002515918251</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4593098683988491</v>
+        <v>0.4008305784436831</v>
       </c>
       <c r="G6" t="n">
-        <v>1.001049609188637</v>
+        <v>0.7327951287793143</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5853151542436009</v>
+        <v>0.6005281571502895</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5095798118359078</v>
+        <v>0.4276373285183851</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7944768944007119</v>
+        <v>0.6771058915772848</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7397864962836986</v>
+        <v>0.6155241189125804</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7157513421758889</v>
+        <v>0.5893252626251648</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7716922097134442</v>
+        <v>0.6706973329779639</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5400712590843622</v>
+        <v>4.45754635868574</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5991224847796439</v>
+        <v>0.4422102249486296</v>
       </c>
       <c r="P6" t="n">
-        <v>0.731068227635386</v>
+        <v>0.6653431007327405</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.562917295482927</v>
+        <v>0.4754584177914669</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5812537047466727</v>
+        <v>0.5486103856924182</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8051005715384031</v>
+        <v>0.592729392583913</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6292553198476534</v>
+        <v>0.5417317036664733</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7228504386118024</v>
+        <v>0.6990586218828132</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5829808777551028</v>
+        <v>0.5242617061777719</v>
       </c>
       <c r="W6" t="n">
-        <v>0.889611241230894</v>
+        <v>0.7357519770785033</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7873790645372784</v>
+        <v>0.6957881883374294</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9855473812635986</v>
+        <v>0.7881970343333106</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6364499438098036</v>
+        <v>0.4674674027447873</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.7731201152315847</v>
+        <v>0.6715170463658792</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7487768128145221</v>
+        <v>0.7088665411384705</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5882581580458345</v>
+        <v>0.5279621219820432</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5341151238609082</v>
+        <v>0.462226249258717</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6019741211354144</v>
+        <v>0.5840315584885839</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4848149940606015</v>
+        <v>0.4006610644104134</v>
       </c>
       <c r="F7" t="n">
-        <v>0.535754642679892</v>
+        <v>0.47560544250133</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9883671339467879</v>
+        <v>0.8075699928369608</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6617599285246439</v>
+        <v>0.5940889699688789</v>
       </c>
       <c r="I7" t="n">
-        <v>0.586024586116951</v>
+        <v>0.5024121925760322</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7817944191588648</v>
+        <v>0.6706667043958749</v>
       </c>
       <c r="K7" t="n">
-        <v>0.727104021041852</v>
+        <v>0.6090849317311692</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7030688669340432</v>
+        <v>0.664100126682812</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8481369839944872</v>
+        <v>0.7454721970356065</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6153208263670911</v>
+        <v>4.45754635868574</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5812066523964419</v>
+        <v>0.515362646109677</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8097570680873492</v>
+        <v>0.6536781442969206</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5502348202410801</v>
+        <v>0.4690192306100565</v>
       </c>
       <c r="R7" t="n">
-        <v>0.568571229504826</v>
+        <v>0.5421711985110075</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7924180962965576</v>
+        <v>0.6675042566415643</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6165728446058059</v>
+        <v>0.5352925164850637</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7981121573892312</v>
+        <v>0.6918870555450988</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6594256520361457</v>
+        <v>0.5990365702354202</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8720260146690235</v>
+        <v>0.8051073815341271</v>
       </c>
       <c r="X7" t="n">
-        <v>0.8638238388183208</v>
+        <v>0.7705630523950794</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.058395901967709</v>
+        <v>0.859217302217998</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6237674685679563</v>
+        <v>0.5422422668024324</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.7604376399897382</v>
+        <v>0.6650778591844676</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8233390742848224</v>
+        <v>0.7814264199168014</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6326301055396588</v>
+        <v>0.5695178607506726</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6974566522661535</v>
+        <v>0.6170839634849327</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7653156495406604</v>
+        <v>0.7388892727148002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5848087300322315</v>
+        <v>0.4951888189151714</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5986606604422879</v>
+        <v>0.5348123048516218</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176377779961457</v>
+        <v>0.9859216097640291</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8251014569298907</v>
+        <v>0.748946684195094</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7493661145221971</v>
+        <v>0.6572699068022467</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9451359475641116</v>
+        <v>0.8255244186220901</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8904455494470989</v>
+        <v>0.7639426459573848</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8664103953392894</v>
+        <v>0.8189578409090271</v>
       </c>
       <c r="M8" t="n">
-        <v>1.011478512399705</v>
+        <v>0.9003299112620294</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6864410263651083</v>
+        <v>4.45754635868574</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6780041282890831</v>
+        <v>0.6068623594819506</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9003423079575557</v>
+        <v>0.7392615670625347</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5712265297626872</v>
+        <v>0.4883085452238803</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7319127579100719</v>
+        <v>0.6970289127372227</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9557596247018043</v>
+        <v>0.8223619708677804</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7799143730110528</v>
+        <v>0.6901502307112777</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9039113214632002</v>
+        <v>0.7918673041489833</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7895252947429923</v>
+        <v>0.7225867001702155</v>
       </c>
       <c r="W8" t="n">
-        <v>1.035390923913659</v>
+        <v>0.959987362791338</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8957193467700435</v>
+        <v>0.8002367181612386</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.338900606796018</v>
+        <v>1.126200559546741</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6659294950254572</v>
+        <v>0.5816933632119319</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.9237791683949843</v>
+        <v>0.8199355734106822</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.110954277940281</v>
+        <v>1.054637521616486</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8439704780565127</v>
+        <v>0.7638718735692427</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9000565934645987</v>
+        <v>0.8012006504656936</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9679155907391039</v>
+        <v>0.9230059596955614</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8253160537327529</v>
+        <v>0.7158485857740345</v>
       </c>
       <c r="F9" t="n">
-        <v>0.647587790266825</v>
+        <v>0.576987661864637</v>
       </c>
       <c r="G9" t="n">
-        <v>1.354308640183167</v>
+        <v>1.146544421209469</v>
       </c>
       <c r="H9" t="n">
-        <v>1.027701398128334</v>
+        <v>0.9330633711758537</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9519660557206391</v>
+        <v>0.8413865937830095</v>
       </c>
       <c r="J9" t="n">
-        <v>1.147735888762555</v>
+        <v>1.00964110560285</v>
       </c>
       <c r="K9" t="n">
-        <v>1.093045490645543</v>
+        <v>0.9480593329381443</v>
       </c>
       <c r="L9" t="n">
-        <v>1.069010336537732</v>
+        <v>1.003074527889788</v>
       </c>
       <c r="M9" t="n">
-        <v>1.214078453598176</v>
+        <v>1.084446598242585</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9812622959707796</v>
+        <v>4.45754635868574</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9840120207668319</v>
+        <v>0.8888266654413302</v>
       </c>
       <c r="P9" t="n">
-        <v>1.220507042947953</v>
+        <v>1.034570398637258</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9161763264774587</v>
+        <v>0.8079936589825666</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9345126991085143</v>
+        <v>0.8811455997179832</v>
       </c>
       <c r="S9" t="n">
-        <v>1.158359565900247</v>
+        <v>1.006478657848539</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9825143142094953</v>
+        <v>0.8742669176920393</v>
       </c>
       <c r="U9" t="n">
-        <v>1.165236682496535</v>
+        <v>1.031593835908379</v>
       </c>
       <c r="V9" t="n">
-        <v>1.152569123534637</v>
+        <v>1.056945292185268</v>
       </c>
       <c r="W9" t="n">
-        <v>1.237967484272712</v>
+        <v>1.144081782741103</v>
       </c>
       <c r="X9" t="n">
-        <v>1.22976530842201</v>
+        <v>1.109537453602055</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.424337371571397</v>
+        <v>1.198191703424975</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.9232505774719237</v>
+        <v>0.8190778599420504</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.126379109593427</v>
+        <v>1.004052260391444</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.18928054388851</v>
+        <v>1.120400821123779</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.929303146848725</v>
+        <v>2.921546539473806</v>
       </c>
       <c r="C2" t="n">
-        <v>2.920843911762379</v>
+        <v>2.910046516557102</v>
       </c>
       <c r="D2" t="n">
-        <v>2.93485623381772</v>
+        <v>2.927336342557571</v>
       </c>
       <c r="E2" t="n">
-        <v>2.925817958404968</v>
+        <v>2.917592214956342</v>
       </c>
       <c r="F2" t="n">
-        <v>2.926845505071711</v>
+        <v>2.919143140676187</v>
       </c>
       <c r="G2" t="n">
-        <v>2.94411999062982</v>
+        <v>2.933201842940748</v>
       </c>
       <c r="H2" t="n">
-        <v>2.933143209806447</v>
+        <v>2.925213534275591</v>
       </c>
       <c r="I2" t="n">
-        <v>2.93054132648101</v>
+        <v>2.924311198370356</v>
       </c>
       <c r="J2" t="n">
-        <v>2.937383076244431</v>
+        <v>2.928431532741834</v>
       </c>
       <c r="K2" t="n">
-        <v>2.936125722671818</v>
+        <v>2.928477673326425</v>
       </c>
       <c r="L2" t="n">
-        <v>2.928506719718972</v>
+        <v>2.921454950034537</v>
       </c>
       <c r="M2" t="n">
-        <v>2.941003278922257</v>
+        <v>2.931967622046483</v>
       </c>
       <c r="N2" t="n">
-        <v>2.932579329073905</v>
+        <v>2.924611637287208</v>
       </c>
       <c r="O2" t="n">
-        <v>3.28443355866438</v>
+        <v>3.268124103335263</v>
       </c>
       <c r="P2" t="n">
-        <v>2.93121748130569</v>
+        <v>2.921865545646379</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.929472867972617</v>
+        <v>2.921463866176523</v>
       </c>
       <c r="R2" t="n">
-        <v>2.915091414669865</v>
+        <v>2.909333050073737</v>
       </c>
       <c r="S2" t="n">
-        <v>2.935335026056159</v>
+        <v>2.926235498846059</v>
       </c>
       <c r="T2" t="n">
-        <v>2.928579252324325</v>
+        <v>2.921474006095384</v>
       </c>
       <c r="U2" t="n">
-        <v>3.701533405941505</v>
+        <v>3.69320321008172</v>
       </c>
       <c r="V2" t="n">
-        <v>2.929449166892982</v>
+        <v>2.921522760757334</v>
       </c>
       <c r="W2" t="n">
-        <v>3.715848905475082</v>
+        <v>3.707937155127057</v>
       </c>
       <c r="X2" t="n">
-        <v>2.942789750409489</v>
+        <v>2.934736279060564</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.933320063377</v>
+        <v>2.925215145439287</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.198227346092243</v>
+        <v>3.187131516738167</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.944605562718903</v>
+        <v>2.938131907240755</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.937879793012642</v>
+        <v>2.930721709788196</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.006906762477032</v>
+        <v>2.000898504447331</v>
       </c>
       <c r="C3" t="n">
-        <v>1.999120309856942</v>
+        <v>1.987396594039949</v>
       </c>
       <c r="D3" t="n">
-        <v>2.046814673132828</v>
+        <v>2.042504107968048</v>
       </c>
       <c r="E3" t="n">
-        <v>1.982168628914964</v>
+        <v>1.972817373224569</v>
       </c>
       <c r="F3" t="n">
-        <v>1.989530833322798</v>
+        <v>1.983914176393863</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1117745224874</v>
+        <v>2.083376515591486</v>
       </c>
       <c r="H3" t="n">
-        <v>2.034727668646231</v>
+        <v>2.027484344219752</v>
       </c>
       <c r="I3" t="n">
-        <v>2.015986312068546</v>
+        <v>2.02091016967068</v>
       </c>
       <c r="J3" t="n">
-        <v>2.064301502387022</v>
+        <v>2.049827820934788</v>
       </c>
       <c r="K3" t="n">
-        <v>2.055535366616747</v>
+        <v>2.050297358741664</v>
       </c>
       <c r="L3" t="n">
-        <v>2.001259834462449</v>
+        <v>2.000243713459001</v>
       </c>
       <c r="M3" t="n">
-        <v>2.093826361128636</v>
+        <v>2.078707915299914</v>
       </c>
       <c r="N3" t="n">
-        <v>2.030397154740906</v>
+        <v>2.022886273709517</v>
       </c>
       <c r="O3" t="n">
-        <v>2.589500039291574</v>
+        <v>2.568846683900009</v>
       </c>
       <c r="P3" t="n">
-        <v>2.020535681529569</v>
+        <v>2.003186273336922</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.008223536186607</v>
+        <v>2.000418233409096</v>
       </c>
       <c r="R3" t="n">
-        <v>1.905273916294274</v>
+        <v>1.913598152933785</v>
       </c>
       <c r="S3" t="n">
-        <v>2.04944929198213</v>
+        <v>2.033943256780657</v>
       </c>
       <c r="T3" t="n">
-        <v>2.00189585739189</v>
+        <v>2.000537082539402</v>
       </c>
       <c r="U3" t="n">
-        <v>3.368827603270975</v>
+        <v>3.361122189886176</v>
       </c>
       <c r="V3" t="n">
-        <v>2.007941302952081</v>
+        <v>2.000725946608436</v>
       </c>
       <c r="W3" t="n">
-        <v>3.510324203045397</v>
+        <v>3.503569277309078</v>
       </c>
       <c r="X3" t="n">
-        <v>2.103459306170406</v>
+        <v>2.095333817400764</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.035683178767878</v>
+        <v>2.027193224917724</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.456635395893753</v>
+        <v>2.443732405440865</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.116260651921447</v>
+        <v>2.119413781716581</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.068092103127416</v>
+        <v>2.066221706664989</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2404293835003443</v>
+        <v>0.2076030729003511</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2528147204928208</v>
+        <v>0.2185580678294355</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3031540553613922</v>
+        <v>0.2730015621724752</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2010625767622215</v>
+        <v>0.1629371583964686</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2126691890579193</v>
+        <v>0.1804555778631974</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4077924500927288</v>
+        <v>0.3392550872639401</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2838046611240603</v>
+        <v>0.2490234660874544</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2544151920377881</v>
+        <v>0.2388311669428203</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3313850481765145</v>
+        <v>0.2850733164108717</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3174935159621389</v>
+        <v>0.2858934182447871</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2314333726952326</v>
+        <v>0.2065685280505965</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3790301084598</v>
+        <v>0.3317541351051891</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2774353688520462</v>
+        <v>1.691331155839079</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2329801238282346</v>
+        <v>0.1990637028952031</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2620526718291429</v>
+        <v>0.2112063943696881</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2423464616702915</v>
+        <v>0.2066692399759585</v>
       </c>
       <c r="R4" t="n">
-        <v>0.07990133082034195</v>
+        <v>0.06964609164386594</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3085622339498775</v>
+        <v>0.2605670260378257</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2322526618393293</v>
+        <v>0.2067837750241002</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4178469545352547</v>
+        <v>0.380939762890143</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2399985484302168</v>
+        <v>0.2053330676802365</v>
       </c>
       <c r="W4" t="n">
-        <v>0.662257247173683</v>
+        <v>0.6284121071826684</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3927667748633394</v>
+        <v>0.3565872491127752</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2832873898056363</v>
+        <v>0.2439985149242677</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2525626191885513</v>
+        <v>0.2168693743092995</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4132772102131098</v>
+        <v>0.3949424314741777</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3364576670718317</v>
+        <v>0.3101134474439061</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9913014168904355</v>
+        <v>0.9744110647334638</v>
       </c>
       <c r="C5" t="n">
-        <v>1.312998048892962</v>
+        <v>1.270383496150649</v>
       </c>
       <c r="D5" t="n">
-        <v>2.330375612236361</v>
+        <v>2.36862321173994</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3224998128200814</v>
+        <v>0.2083341722513289</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5578361348116949</v>
+        <v>0.5550145610009878</v>
       </c>
       <c r="G5" t="n">
-        <v>3.665931452297937</v>
+        <v>3.070769488076802</v>
       </c>
       <c r="H5" t="n">
-        <v>2.041787169961279</v>
+        <v>1.988006160225235</v>
       </c>
       <c r="I5" t="n">
-        <v>1.390666191023084</v>
+        <v>1.720678750587575</v>
       </c>
       <c r="J5" t="n">
-        <v>2.565309609364151</v>
+        <v>2.328203880279109</v>
       </c>
       <c r="K5" t="n">
-        <v>2.41257330685337</v>
+        <v>2.416346524346536</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8419013045830086</v>
+        <v>0.9542312176463241</v>
       </c>
       <c r="M5" t="n">
-        <v>3.564630144074131</v>
+        <v>3.28545707821566</v>
       </c>
       <c r="N5" t="n">
-        <v>4.10109359523655</v>
+        <v>1.691331155839079</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8525262779010547</v>
+        <v>0.8163735408389614</v>
       </c>
       <c r="P5" t="n">
-        <v>1.381364885969129</v>
+        <v>1.048663297311581</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.086204271789528</v>
+        <v>1.01780441169553</v>
       </c>
       <c r="R5" t="n">
-        <v>-2.156849439352784</v>
+        <v>-1.707516722813245</v>
       </c>
       <c r="S5" t="n">
-        <v>1.997418647431826</v>
+        <v>1.741939438325783</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9232152497965329</v>
+        <v>1.045819999398898</v>
       </c>
       <c r="U5" t="n">
-        <v>4.244020094674255</v>
+        <v>4.199874417784792</v>
       </c>
       <c r="V5" t="n">
-        <v>1.016173873759244</v>
+        <v>0.9657472515433397</v>
       </c>
       <c r="W5" t="n">
-        <v>9.073872070492907</v>
+        <v>9.040100460432779</v>
       </c>
       <c r="X5" t="n">
-        <v>4.037405484969272</v>
+        <v>3.957948336108887</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.908985045244413</v>
+        <v>1.82004843663253</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.179962967975662</v>
+        <v>1.114301742550831</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.337233096129592</v>
+        <v>4.597070266045457</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.048700525406081</v>
+        <v>3.164098618276756</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2574421616314958</v>
+        <v>0.2228112789811756</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3341377222257722</v>
+        <v>0.2337662739102587</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3201668334925439</v>
+        <v>0.3461020235475468</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2180753548933729</v>
+        <v>0.23603761977154</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2939921907908712</v>
+        <v>0.1956637839440211</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4891154518256796</v>
+        <v>0.3544632933447623</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3008174392552116</v>
+        <v>0.3221239274625273</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2714279701689395</v>
+        <v>0.3119316283178915</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3483978263076657</v>
+        <v>0.3002815224916985</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3345062940932907</v>
+        <v>0.3589938796198596</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2484461508263836</v>
+        <v>0.2217767341314191</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4603531101927513</v>
+        <v>0.4048545964802611</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2949235660927129</v>
+        <v>1.691331155839079</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3200743209650293</v>
+        <v>0.2780606642931328</v>
       </c>
       <c r="P6" t="n">
-        <v>0.276646051045583</v>
+        <v>0.2901485614499131</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3236694634032425</v>
+        <v>0.2797697013510319</v>
       </c>
       <c r="R6" t="n">
-        <v>0.09691410895149365</v>
+        <v>0.1427465530189382</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3255750120810291</v>
+        <v>0.2757752321186505</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3135756635722805</v>
+        <v>0.2219919811049228</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4373746464209026</v>
+        <v>0.4011911189692873</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3213215501631684</v>
+        <v>0.2784335290553079</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6845209207294244</v>
+        <v>0.7074271281324379</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4097795529944911</v>
+        <v>0.3717954551935998</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3051709220900654</v>
+        <v>0.2665822338036081</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3338856209215018</v>
+        <v>0.2320775803901229</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4946002119460614</v>
+        <v>0.4680428928492499</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3542792879737488</v>
+        <v>0.3263395052926677</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3338090649107835</v>
+        <v>0.297850158175822</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3461944019032597</v>
+        <v>0.3088051531049046</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3965337367718313</v>
+        <v>0.3632486474479444</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2944422581726601</v>
+        <v>0.2531842436719373</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3060488704683578</v>
+        <v>0.2707026631386657</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5011721315031673</v>
+        <v>0.4295021725394078</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3771843425344991</v>
+        <v>0.3392705513629232</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3477948734482271</v>
+        <v>0.3290782522182892</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4247647295869532</v>
+        <v>0.375320401686342</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4108731973725777</v>
+        <v>0.376140503520257</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3248130541056711</v>
+        <v>0.2968156133260663</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4724097898702381</v>
+        <v>0.4220012203806591</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3708150502624847</v>
+        <v>1.691331155839079</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3260020863349764</v>
+        <v>0.2889531872991537</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3550746343358854</v>
+        <v>0.3010958787736389</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3357261430807307</v>
+        <v>0.2969163252514292</v>
       </c>
       <c r="R7" t="n">
-        <v>0.173281012230781</v>
+        <v>0.1598931769193364</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4019419153603165</v>
+        <v>0.3508141113132959</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3256323432497676</v>
+        <v>0.2970308602995675</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5124435213437843</v>
+        <v>0.4751020848798484</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3333782298406557</v>
+        <v>0.2955801529557064</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7556369285841215</v>
+        <v>0.7186591924581399</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4861464562737788</v>
+        <v>0.446834334388246</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3791819849705723</v>
+        <v>0.3392887501980563</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3459423005989897</v>
+        <v>0.3071164595847689</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5066568916235487</v>
+        <v>0.4851895167496478</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.4298373484822696</v>
+        <v>0.4003605327193757</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3642991136439368</v>
+        <v>0.3256834119856793</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4767437629568971</v>
+        <v>0.4303556463767226</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5270830978254688</v>
+        <v>0.4847991407197625</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3717129869972336</v>
+        <v>0.3248330714217414</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3521269906327594</v>
+        <v>0.3131359675551407</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6524694427845963</v>
+        <v>0.5704855459213856</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5077337035881363</v>
+        <v>0.4608210446347425</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4783442345018645</v>
+        <v>0.4506287454901072</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5553140906405905</v>
+        <v>0.4968708949581609</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5414225584262151</v>
+        <v>0.4976909967920745</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4553624151593092</v>
+        <v>0.4183661065978831</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6029591509237473</v>
+        <v>0.5435517136526616</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4238017046863354</v>
+        <v>1.691331155839079</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4006613648654967</v>
+        <v>0.3581786420147626</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4245091145655892</v>
+        <v>0.3654276992746261</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3465522532234904</v>
+        <v>0.3063320025236949</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3038303732844184</v>
+        <v>0.2814436701911543</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5324912764139546</v>
+        <v>0.4723646045851134</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4561817043034053</v>
+        <v>0.4185813535713865</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5947245790920436</v>
+        <v>0.551441384452534</v>
       </c>
       <c r="V8" t="n">
-        <v>0.435776118832934</v>
+        <v>0.3908578675961898</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8862059540725336</v>
+        <v>0.8402281038164119</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5061432011582386</v>
+        <v>0.4648393828540356</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6079714204136784</v>
+        <v>0.5529989140415397</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3745736962423512</v>
+        <v>0.3332088675590154</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.637206252677186</v>
+        <v>0.6067400100214658</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.6649070279976405</v>
+        <v>0.6198065190858754</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5434281265951632</v>
+        <v>0.497813365975231</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6489036590482358</v>
+        <v>0.5971625237102894</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6992429939168077</v>
+        <v>0.6516060180533296</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5756666887412336</v>
+        <v>0.5211406110367155</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3941598019778079</v>
+        <v>0.3552873481790476</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8038814027249208</v>
+        <v>0.7178595548215261</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6798935996794753</v>
+        <v>0.6276279219683102</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6505041305932026</v>
+        <v>0.6174356228236748</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7274739867319282</v>
+        <v>0.6636777722917273</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7135824545175532</v>
+        <v>0.664497874125642</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6275223112506474</v>
+        <v>0.5851729839314521</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7751190470152137</v>
+        <v>0.7103585909860453</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6735243074074598</v>
+        <v>1.691331155839079</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6599190500098824</v>
+        <v>0.6069618841340646</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6957009379613895</v>
+        <v>0.6254754557387433</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6384354143024834</v>
+        <v>0.5852737075335478</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4759902693757574</v>
+        <v>0.448250547524721</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7046511725052925</v>
+        <v>0.6391714819186813</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6283416003947437</v>
+        <v>0.5853882309049532</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8164508068451661</v>
+        <v>0.7645873687693191</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7435115298456699</v>
+        <v>0.6859424463811008</v>
       </c>
       <c r="W9" t="n">
-        <v>1.058346185729097</v>
+        <v>1.007016563063524</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7888557134187548</v>
+        <v>0.7351917049936301</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.681891242115548</v>
+        <v>0.6276461208034404</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.5925264533741184</v>
+        <v>0.542180014970493</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8093661487685245</v>
+        <v>0.7735468873550333</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.7325466056272463</v>
+        <v>0.6887179033247618</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.897637829218847</v>
+        <v>2.890174906383817</v>
       </c>
       <c r="C2" t="n">
-        <v>2.898432500372414</v>
+        <v>2.887484862912825</v>
       </c>
       <c r="D2" t="n">
-        <v>2.909477951653687</v>
+        <v>2.901860290444161</v>
       </c>
       <c r="E2" t="n">
-        <v>2.890758700351969</v>
+        <v>2.882993099140927</v>
       </c>
       <c r="F2" t="n">
-        <v>2.894250402882909</v>
+        <v>2.886712579967775</v>
       </c>
       <c r="G2" t="n">
-        <v>2.916191873068616</v>
+        <v>2.90851661123391</v>
       </c>
       <c r="H2" t="n">
-        <v>2.909300934741068</v>
+        <v>2.901925248046926</v>
       </c>
       <c r="I2" t="n">
-        <v>2.904677911114009</v>
+        <v>2.898581385275869</v>
       </c>
       <c r="J2" t="n">
-        <v>2.910083749922877</v>
+        <v>2.902568940449894</v>
       </c>
       <c r="K2" t="n">
-        <v>2.904956460940483</v>
+        <v>2.897892819163497</v>
       </c>
       <c r="L2" t="n">
-        <v>2.890490939532483</v>
+        <v>2.882942087427535</v>
       </c>
       <c r="M2" t="n">
-        <v>2.905290609932533</v>
+        <v>2.89791123591276</v>
       </c>
       <c r="N2" t="n">
-        <v>2.913334492684346</v>
+        <v>2.905860561543886</v>
       </c>
       <c r="O2" t="n">
-        <v>3.248105350616296</v>
+        <v>3.232002920369363</v>
       </c>
       <c r="P2" t="n">
-        <v>2.897840457664246</v>
+        <v>2.890278885333593</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.90744005285045</v>
+        <v>2.899994835742599</v>
       </c>
       <c r="R2" t="n">
-        <v>2.875337174982684</v>
+        <v>2.867602524567786</v>
       </c>
       <c r="S2" t="n">
-        <v>2.90459049572052</v>
+        <v>2.89673318094291</v>
       </c>
       <c r="T2" t="n">
-        <v>2.901223125127236</v>
+        <v>2.894491411743268</v>
       </c>
       <c r="U2" t="n">
-        <v>3.655340074687817</v>
+        <v>3.644319887159098</v>
       </c>
       <c r="V2" t="n">
-        <v>2.910234703199872</v>
+        <v>2.902685007949389</v>
       </c>
       <c r="W2" t="n">
-        <v>3.666703217888016</v>
+        <v>3.65529691153037</v>
       </c>
       <c r="X2" t="n">
-        <v>2.945473966744227</v>
+        <v>2.938112210274757</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.91863142623013</v>
+        <v>2.911169239566408</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.169676073623196</v>
+        <v>3.15802224099405</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.936029891098233</v>
+        <v>2.928719014640396</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.906447346271592</v>
+        <v>2.899028419287162</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.902590156881385</v>
+        <v>1.895589746799063</v>
       </c>
       <c r="C3" t="n">
-        <v>1.965006432524328</v>
+        <v>1.952304892645022</v>
       </c>
       <c r="D3" t="n">
-        <v>1.986836260655402</v>
+        <v>1.978731324840135</v>
       </c>
       <c r="E3" t="n">
-        <v>1.853332057791319</v>
+        <v>1.844169989420726</v>
       </c>
       <c r="F3" t="n">
-        <v>1.878154888322956</v>
+        <v>1.870616717607824</v>
       </c>
       <c r="G3" t="n">
-        <v>2.034140163332094</v>
+        <v>2.025642015031772</v>
       </c>
       <c r="H3" t="n">
-        <v>1.985681448617139</v>
+        <v>1.979300688116597</v>
       </c>
       <c r="I3" t="n">
-        <v>1.952586077145543</v>
+        <v>1.955345886415703</v>
       </c>
       <c r="J3" t="n">
-        <v>1.990993425700428</v>
+        <v>1.983629089379585</v>
       </c>
       <c r="K3" t="n">
-        <v>1.95466236334774</v>
+        <v>1.950498598067296</v>
       </c>
       <c r="L3" t="n">
-        <v>1.852693189436099</v>
+        <v>1.84509102171468</v>
       </c>
       <c r="M3" t="n">
-        <v>1.961027779383065</v>
+        <v>1.954565981276424</v>
       </c>
       <c r="N3" t="n">
-        <v>2.014291335908975</v>
+        <v>2.007210796400647</v>
       </c>
       <c r="O3" t="n">
-        <v>2.529254093441244</v>
+        <v>2.507820123475326</v>
       </c>
       <c r="P3" t="n">
-        <v>1.904065246436142</v>
+        <v>1.896364509967825</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.97227578506562</v>
+        <v>1.96540197961217</v>
       </c>
       <c r="R3" t="n">
-        <v>1.742621614739561</v>
+        <v>1.733672385257903</v>
       </c>
       <c r="S3" t="n">
-        <v>1.95209871331943</v>
+        <v>1.942312160393836</v>
       </c>
       <c r="T3" t="n">
-        <v>1.928018289403925</v>
+        <v>1.926226180641285</v>
       </c>
       <c r="U3" t="n">
-        <v>3.211780995872601</v>
+        <v>3.19975043330824</v>
       </c>
       <c r="V3" t="n">
-        <v>1.992073243187481</v>
+        <v>1.984459952186798</v>
       </c>
       <c r="W3" t="n">
-        <v>3.342104887841313</v>
+        <v>3.328877369345087</v>
       </c>
       <c r="X3" t="n">
-        <v>2.243220850964328</v>
+        <v>2.236939517199795</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.052186040925628</v>
+        <v>2.045188064568531</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.409215794370634</v>
+        <v>2.394938291484546</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.176355460766223</v>
+        <v>2.170437545222813</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.965143141797709</v>
+        <v>1.958408628742552</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06735450516461521</v>
+        <v>0.04685585162748285</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1937631187222502</v>
+        <v>0.1733745662300072</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2010941347915401</v>
+        <v>0.1788476401313241</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0103484199423975</v>
+        <v>-0.03426596497551933</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02909196640707504</v>
+        <v>0.00774728200944011</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2769309657296259</v>
+        <v>0.2540338455103967</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1990946473316908</v>
+        <v>0.1795813661365143</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1468754687681414</v>
+        <v>0.1418108978845457</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2076760095585956</v>
+        <v>0.1865933070999045</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1500218171974247</v>
+        <v>0.1340332268892832</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0133729015745379</v>
+        <v>-0.03484216574477007</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1611311575441042</v>
+        <v>0.1414742781592483</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2446555398293443</v>
+        <v>1.527690475611856</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1669883639487496</v>
+        <v>0.1461283222226495</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06964328666907035</v>
+        <v>0.04803034169789757</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1780751303292261</v>
+        <v>0.1577764711256222</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1845416432406487</v>
+        <v>-0.2081095847932289</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1458880716856206</v>
+        <v>0.1209345797278116</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1078520717674881</v>
+        <v>0.09561276535305108</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1868509598103064</v>
+        <v>0.1646733924102711</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2078975261123308</v>
+        <v>0.186428977978558</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4189278264702466</v>
+        <v>0.3990139851277604</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6076856842242362</v>
+        <v>0.5883297513249707</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3031140672639907</v>
+        <v>0.279197674076267</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1865762926173644</v>
+        <v>0.1653275364093974</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5010105053133265</v>
+        <v>0.4822292855513716</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1666865076850448</v>
+        <v>0.1466021232126607</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.402918545062881</v>
+        <v>-1.435862737969051</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7011380777499729</v>
+        <v>0.669148588818923</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8290755779060247</v>
+        <v>0.7651400724095598</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.860871417872141</v>
+        <v>-2.955024181373358</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.213894528498044</v>
+        <v>-2.263457915173732</v>
       </c>
       <c r="G5" t="n">
-        <v>1.852346204481062</v>
+        <v>1.786172304008109</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8499731779805144</v>
+        <v>0.8329234398857328</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1257536448517724</v>
+        <v>0.118516318844847</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8635832122727702</v>
+        <v>0.8235873217233159</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.02436562855084456</v>
+        <v>0.01569835881204307</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.25510278920124</v>
+        <v>-2.299241892429185</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1697063267208614</v>
+        <v>0.1504637662369283</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6202818601253242</v>
+        <v>1.527690475611856</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2346581270886496</v>
+        <v>0.1969080361016601</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.347450486071966</v>
+        <v>-1.398164610686407</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4137117862370327</v>
+        <v>0.3844281457509748</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.2766675185898</v>
+        <v>-6.368813074019371</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.07246718458675239</v>
+        <v>-0.1693543144540846</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7697252807872939</v>
+        <v>-0.6619669004124539</v>
       </c>
       <c r="U5" t="n">
-        <v>0.563850053781115</v>
+        <v>0.5581983248899463</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8935298931067602</v>
+        <v>0.8465866833375335</v>
       </c>
       <c r="W5" t="n">
-        <v>4.435540034479223</v>
+        <v>4.411963052660995</v>
       </c>
       <c r="X5" t="n">
-        <v>7.750445373070665</v>
+        <v>7.736181723125158</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.668616426365007</v>
+        <v>2.634357721595196</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5341741124648565</v>
+        <v>0.4906095114802344</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.142237878224781</v>
+        <v>6.138286694085171</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2370202123979518</v>
+        <v>0.2097553507000816</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07791239929365709</v>
+        <v>0.09842312120126438</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2043210128512911</v>
+        <v>0.1799733177851902</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2116520289205813</v>
+        <v>0.1854463916865074</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0506684007680602</v>
+        <v>-0.027667213420338</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09010878711753773</v>
+        <v>0.05931455158322227</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2874888598586661</v>
+        <v>0.3056011150841801</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2096525414607348</v>
+        <v>0.2311486357102975</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1574333628971871</v>
+        <v>0.1933781674583297</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2182339036876375</v>
+        <v>0.2381605766736878</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1605797113264663</v>
+        <v>0.1856004964630665</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04764391913592333</v>
+        <v>-0.02824341418958698</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2221479782545605</v>
+        <v>0.1930415477330304</v>
       </c>
       <c r="N6" t="n">
-        <v>0.256267335498231</v>
+        <v>1.527690475611856</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1786001596176223</v>
+        <v>0.2027071176766492</v>
       </c>
       <c r="P6" t="n">
-        <v>0.07909966385509372</v>
+        <v>0.05401769721940876</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1886330244582684</v>
+        <v>0.2093437406994041</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1235248225301901</v>
+        <v>-0.2015108332380448</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1564459658146629</v>
+        <v>0.1725018493015931</v>
       </c>
       <c r="T6" t="n">
-        <v>0.168868892477943</v>
+        <v>0.1022115169082332</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1987816276141742</v>
+        <v>0.1760709726844746</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2689143468227892</v>
+        <v>0.1930277295337401</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4337257162457195</v>
+        <v>0.4097155365832104</v>
       </c>
       <c r="X6" t="n">
-        <v>0.618243578353278</v>
+        <v>0.6398970208987526</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3176476902250859</v>
+        <v>0.2931390798478385</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2475931133278221</v>
+        <v>0.1719262879645786</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5620273260237805</v>
+        <v>0.5337965551251551</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1782183281918455</v>
+        <v>0.1544345204336107</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1437729930553535</v>
+        <v>0.1216729149297804</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2701816066129836</v>
+        <v>0.2481916295323058</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2775126226822828</v>
+        <v>0.2536647034336234</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06607006794833956</v>
+        <v>0.04055109832677881</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1055104542978177</v>
+        <v>0.08256434531173819</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3533494536203634</v>
+        <v>0.3288509088126959</v>
       </c>
       <c r="H7" t="n">
-        <v>0.275513135222429</v>
+        <v>0.2543984294388132</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2232939566588807</v>
+        <v>0.2166279611868456</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2840944974493349</v>
+        <v>0.2614103704022035</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2264403050881616</v>
+        <v>0.2088502901915824</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06304558631620061</v>
+        <v>0.03997489755752823</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2375496454348394</v>
+        <v>0.2162913414615454</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3210740277200811</v>
+        <v>1.527690475611856</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2430738605574548</v>
+        <v>0.220612274714921</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1457287832777721</v>
+        <v>0.1225142941901688</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2544936182199637</v>
+        <v>0.2325935344279199</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1081231553499118</v>
+        <v>-0.1332925214909287</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2223065595763571</v>
+        <v>0.1957516430301092</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1842705596582211</v>
+        <v>0.1704298286553502</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2627415286832095</v>
+        <v>0.242963855319855</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2843160140030687</v>
+        <v>0.2612460412808562</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4953463143609839</v>
+        <v>0.4738310484300581</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6841041721149744</v>
+        <v>0.6631468146272684</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3809053288295521</v>
+        <v>0.3588135660975861</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2629947805080992</v>
+        <v>0.2401445997116956</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5774289932040604</v>
+        <v>0.5570463488536711</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2431049955757827</v>
+        <v>0.221419186514959</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1619366494028377</v>
+        <v>0.1371800263840397</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3650660088519166</v>
+        <v>0.3349918164363931</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3723970249212115</v>
+        <v>0.3404648903377097</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1201029361309719</v>
+        <v>0.08938982556443745</v>
       </c>
       <c r="F8" t="n">
-        <v>0.135626306194337</v>
+        <v>0.1091780847020447</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4641424023038768</v>
+        <v>0.4304341793429534</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3703975374613613</v>
+        <v>0.3411986163429003</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3181783588978122</v>
+        <v>0.3034281480909321</v>
       </c>
       <c r="J8" t="n">
-        <v>0.378978899688265</v>
+        <v>0.34821055730629</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3213247073270932</v>
+        <v>0.2956504770956687</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1579299885551355</v>
+        <v>0.1267750844616161</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3324340476734533</v>
+        <v>0.3030915283655542</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3564870167773704</v>
+        <v>1.527690475611856</v>
       </c>
       <c r="O8" t="n">
-        <v>0.295163101592447</v>
+        <v>0.2676685555799957</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1938118962107243</v>
+        <v>0.1658478636746292</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2575798969487692</v>
+        <v>0.2340899293665713</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.01323875311097855</v>
+        <v>-0.04649233458684229</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3171909618152879</v>
+        <v>0.2825518299341981</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2791549618971537</v>
+        <v>0.2572300155594371</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3208653213839475</v>
+        <v>0.2955232504299802</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3568914471943851</v>
+        <v>0.3277125465847797</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5902457943696432</v>
+        <v>0.5606452464788304</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6942220596173678</v>
+        <v>0.6711773616003575</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5499930304790158</v>
+        <v>0.5151832617392149</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2797333096165657</v>
+        <v>0.25432740568533</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6723133954429918</v>
+        <v>0.643846535757758</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.4181306321318287</v>
+        <v>0.3826909521706769</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2970377825326319</v>
+        <v>0.2700316834799262</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4942022568904965</v>
+        <v>0.4643217444025191</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5015332729597879</v>
+        <v>0.469794818303836</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2737605703130376</v>
+        <v>0.2410398772087148</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1664195069157041</v>
+        <v>0.1424629860792901</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5773701248961862</v>
+        <v>0.5449810422840969</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4995337854999429</v>
+        <v>0.4705285443090262</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4473146069363935</v>
+        <v>0.4327580760570588</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5081151477268441</v>
+        <v>0.4775404852724144</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4504609553656725</v>
+        <v>0.4249804050617952</v>
       </c>
       <c r="L9" t="n">
-        <v>0.287066236593711</v>
+        <v>0.2561050124277415</v>
       </c>
       <c r="M9" t="n">
-        <v>0.461570295712353</v>
+        <v>0.4324214563317587</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5450946779975965</v>
+        <v>1.527690475611856</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4908759296964278</v>
+        <v>0.4595348605922219</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3986304785412347</v>
+        <v>0.3663214015271641</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4785142894957859</v>
+        <v>0.4487236678993223</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1158974949276018</v>
+        <v>0.08283759337928386</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4463272098538676</v>
+        <v>0.4118817579003224</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4082912099357354</v>
+        <v>0.386559943525563</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4886628716533856</v>
+        <v>0.4604193993018033</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5899874319749646</v>
+        <v>0.555582856035796</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7193669646384931</v>
+        <v>0.689961163300272</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9081248223924872</v>
+        <v>0.8792769294974817</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.6049259791070637</v>
+        <v>0.5749436809677991</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.4443559469178981</v>
+        <v>0.4154146266004821</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8014496434815748</v>
+        <v>0.7731764637238834</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.4671256458532916</v>
+        <v>0.437549301385172</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.88191530883585</v>
+        <v>2.875607235465576</v>
       </c>
       <c r="C2" t="n">
-        <v>2.88294287305254</v>
+        <v>2.873459095158727</v>
       </c>
       <c r="D2" t="n">
-        <v>2.89636839694121</v>
+        <v>2.890149284263963</v>
       </c>
       <c r="E2" t="n">
-        <v>2.880202827693149</v>
+        <v>2.873600635610273</v>
       </c>
       <c r="F2" t="n">
-        <v>2.887986514092946</v>
+        <v>2.881715297370735</v>
       </c>
       <c r="G2" t="n">
-        <v>2.905667414658481</v>
+        <v>2.899457735121208</v>
       </c>
       <c r="H2" t="n">
-        <v>2.902321409055248</v>
+        <v>2.896100746273499</v>
       </c>
       <c r="I2" t="n">
-        <v>2.89917080941902</v>
+        <v>2.893375387614502</v>
       </c>
       <c r="J2" t="n">
-        <v>2.900114846202645</v>
+        <v>2.893882206016294</v>
       </c>
       <c r="K2" t="n">
-        <v>2.897843543223922</v>
+        <v>2.891767030525739</v>
       </c>
       <c r="L2" t="n">
-        <v>2.878481308430799</v>
+        <v>2.872146196863068</v>
       </c>
       <c r="M2" t="n">
-        <v>2.899053930155554</v>
+        <v>2.892872245017226</v>
       </c>
       <c r="N2" t="n">
-        <v>2.906394950078572</v>
+        <v>2.900189468819016</v>
       </c>
       <c r="O2" t="n">
-        <v>3.222660698417593</v>
+        <v>3.209213884148673</v>
       </c>
       <c r="P2" t="n">
-        <v>2.88693488355357</v>
+        <v>2.880567108753572</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.899817251343609</v>
+        <v>2.893625404074023</v>
       </c>
       <c r="R2" t="n">
-        <v>2.868067491583402</v>
+        <v>2.861373342321575</v>
       </c>
       <c r="S2" t="n">
-        <v>2.89205441209768</v>
+        <v>2.885652389212509</v>
       </c>
       <c r="T2" t="n">
-        <v>2.895128074791678</v>
+        <v>2.889161927166258</v>
       </c>
       <c r="U2" t="n">
-        <v>3.638858769314695</v>
+        <v>3.631819038009864</v>
       </c>
       <c r="V2" t="n">
-        <v>2.903685788997231</v>
+        <v>2.897385167182419</v>
       </c>
       <c r="W2" t="n">
-        <v>3.645521475479026</v>
+        <v>3.638352293263384</v>
       </c>
       <c r="X2" t="n">
-        <v>2.949236469581324</v>
+        <v>2.943179056710271</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.906856506932224</v>
+        <v>2.90063709837685</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.14809698678541</v>
+        <v>3.138974081470733</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.93207441110816</v>
+        <v>2.925892249140668</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.899588786057424</v>
+        <v>2.893646924634744</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.842844636098445</v>
+        <v>1.836314202901765</v>
       </c>
       <c r="C3" t="n">
-        <v>1.916045292004713</v>
+        <v>1.904486769224161</v>
       </c>
       <c r="D3" t="n">
-        <v>1.945483469005108</v>
+        <v>1.939582785938545</v>
       </c>
       <c r="E3" t="n">
-        <v>1.830629997430825</v>
+        <v>1.822007220918259</v>
       </c>
       <c r="F3" t="n">
-        <v>1.885521192033417</v>
+        <v>1.879247124058125</v>
       </c>
       <c r="G3" t="n">
-        <v>2.011486330102814</v>
+        <v>2.005655488396481</v>
       </c>
       <c r="H3" t="n">
-        <v>1.988069526588972</v>
+        <v>1.98215601921418</v>
       </c>
       <c r="I3" t="n">
-        <v>1.965486027834551</v>
+        <v>1.96261421488526</v>
       </c>
       <c r="J3" t="n">
-        <v>1.972168965355027</v>
+        <v>1.966174742362157</v>
       </c>
       <c r="K3" t="n">
-        <v>1.956022231689926</v>
+        <v>1.95113770568978</v>
       </c>
       <c r="L3" t="n">
-        <v>1.818989313749223</v>
+        <v>1.812270645589115</v>
       </c>
       <c r="M3" t="n">
-        <v>1.968068430553348</v>
+        <v>1.962385561019375</v>
       </c>
       <c r="N3" t="n">
-        <v>2.017001992873142</v>
+        <v>2.011198864473463</v>
       </c>
       <c r="O3" t="n">
-        <v>2.460059468997065</v>
+        <v>2.441666062951265</v>
       </c>
       <c r="P3" t="n">
-        <v>1.878625893918507</v>
+        <v>1.871673524684984</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.970056608737996</v>
+        <v>1.964351157550043</v>
       </c>
       <c r="R3" t="n">
-        <v>1.742774448469455</v>
+        <v>1.733470752593357</v>
       </c>
       <c r="S3" t="n">
-        <v>1.914947272266588</v>
+        <v>1.907751712340112</v>
       </c>
       <c r="T3" t="n">
-        <v>1.936612344947702</v>
+        <v>1.932517740731869</v>
       </c>
       <c r="U3" t="n">
-        <v>3.194085206224863</v>
+        <v>3.187412456123985</v>
       </c>
       <c r="V3" t="n">
-        <v>1.997475293241283</v>
+        <v>1.99099925863002</v>
       </c>
       <c r="W3" t="n">
-        <v>3.297410434442976</v>
+        <v>3.290354162157677</v>
       </c>
       <c r="X3" t="n">
-        <v>2.321805984363231</v>
+        <v>2.31705724972965</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.020367095315731</v>
+        <v>2.014464157083161</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.348626237771054</v>
+        <v>2.337515281478434</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.200361447591255</v>
+        <v>2.194724675601679</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.967832081778368</v>
+        <v>1.963859417467961</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.02841105728537803</v>
+        <v>-0.04474453983432793</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1199182322173773</v>
+        <v>0.1040345484993327</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1348432216137148</v>
+        <v>0.1195145910163945</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04775431957240093</v>
+        <v>-0.06741000828152791</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04016599898592584</v>
+        <v>0.02424882923172199</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2398799044897739</v>
+        <v>0.2246578255479007</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2020852319625976</v>
+        <v>0.186739092221887</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1664977597239641</v>
+        <v>0.1559549124415734</v>
       </c>
       <c r="J4" t="n">
-        <v>0.176927856502414</v>
+        <v>0.1614501117356036</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1515056774777205</v>
+        <v>0.1377877792432243</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.06719967157864898</v>
+        <v>-0.08383856300609333</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1714685538662284</v>
+        <v>0.1564721564489442</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2480977517424564</v>
+        <v>1.795835503947679</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08479360352738675</v>
+        <v>0.06829204497842767</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02828734826972001</v>
+        <v>0.01127951060800897</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1737996186401758</v>
+        <v>0.158778963365118</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.184828523462447</v>
+        <v>-0.2055229108102032</v>
       </c>
       <c r="S4" t="n">
-        <v>0.08611477827495073</v>
+        <v>0.06872009273631971</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1208332123583409</v>
+        <v>0.1083619383910943</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1810790247990496</v>
+        <v>0.1626700248271936</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2159393251782862</v>
+        <v>0.199711408947445</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3728660986447618</v>
+        <v>0.3583873817270811</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7320124225987632</v>
+        <v>0.7185102656980135</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2521826156495739</v>
+        <v>0.2325660469994441</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1088897548349737</v>
+        <v>0.0926861951185835</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5381590772074129</v>
+        <v>0.5232478218749911</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1700082845810355</v>
+        <v>0.1577097776930821</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.784918746915537</v>
+        <v>-2.824987969503363</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4191171121540778</v>
+        <v>-0.4536121079000485</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1636459247114088</v>
+        <v>-0.1886202305568637</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.123188638915672</v>
+        <v>-3.218494394515489</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.910907490053342</v>
+        <v>-1.947076577146594</v>
       </c>
       <c r="G5" t="n">
-        <v>1.505108780993883</v>
+        <v>1.483323165670093</v>
       </c>
       <c r="H5" t="n">
-        <v>1.077002973761291</v>
+        <v>1.050806326127184</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3970466333119793</v>
+        <v>0.4592909472336854</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5570650585937331</v>
+        <v>0.5309500120267832</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1365348027179451</v>
+        <v>0.1392270040462579</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.132398170878371</v>
+        <v>-3.175413705052289</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4842118439640704</v>
+        <v>0.4650499129721135</v>
       </c>
       <c r="N5" t="n">
-        <v>0.684536742349158</v>
+        <v>1.795835503947679</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9034220988522539</v>
+        <v>-0.9451877313550098</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.804758839818983</v>
+        <v>-1.854601381128574</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5038527705300615</v>
+        <v>0.4846557835773426</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.192787851401768</v>
+        <v>-6.319221528811441</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8944152442030541</v>
+        <v>-0.950457438159244</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4212217159716674</v>
+        <v>-0.395319691229058</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6186466484873184</v>
+        <v>0.613638781286292</v>
       </c>
       <c r="V5" t="n">
-        <v>1.176031092521726</v>
+        <v>1.13810233163233</v>
       </c>
       <c r="W5" t="n">
-        <v>3.891512048504718</v>
+        <v>3.88149691873251</v>
       </c>
       <c r="X5" t="n">
-        <v>9.880282914698682</v>
+        <v>9.886518762716367</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.946924792264563</v>
+        <v>1.921817027006982</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.506273238190176</v>
+        <v>-0.5426106550649989</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.991620515431699</v>
+        <v>6.974127689045308</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4698834062420409</v>
+        <v>0.5008030410741421</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02585352593229068</v>
+        <v>0.001382252132994505</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1741828154350445</v>
+        <v>0.1501613404666549</v>
       </c>
       <c r="D6" t="n">
-        <v>0.189107804831384</v>
+        <v>0.1656413829837186</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006510263645267099</v>
+        <v>-0.06209902644495999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09443058220359347</v>
+        <v>0.07037562119904475</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2941444877074422</v>
+        <v>0.2707846175152227</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2107855732994343</v>
+        <v>0.2328658841892108</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1751981010608011</v>
+        <v>0.2020817044088977</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1856281978392518</v>
+        <v>0.1667610935721708</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2057702606953894</v>
+        <v>0.1430987610797922</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.01293508836098094</v>
+        <v>-0.03771177103877135</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2257331370838977</v>
+        <v>0.2025989484162665</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2579873511565858</v>
+        <v>1.795835503947679</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1438042036487577</v>
+        <v>0.07488006519937355</v>
       </c>
       <c r="P6" t="n">
-        <v>0.08728807002071413</v>
+        <v>0.06244802717849374</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2280642018578443</v>
+        <v>0.2049057553324398</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1761281821256112</v>
+        <v>-0.15939611884288</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09481511961178719</v>
+        <v>0.1148468847036422</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1750977955760092</v>
+        <v>0.1136729202276613</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2364722410982846</v>
+        <v>0.2142100458493732</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2246396665151235</v>
+        <v>0.2050223907840131</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4318997477347087</v>
+        <v>0.4096584106333043</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7407127639355998</v>
+        <v>0.723821247534582</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2646746623496747</v>
+        <v>0.246020294513318</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1175900961718093</v>
+        <v>0.09799717695515101</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5468594185442494</v>
+        <v>0.5693746138423138</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1799057809115749</v>
+        <v>0.1645421855429585</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04452886766439729</v>
+        <v>0.02696625587735663</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1928581571671517</v>
+        <v>0.1757453442110163</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2077831465634902</v>
+        <v>0.1912253867280794</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0251856053773739</v>
+        <v>0.004300787430156335</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1131059239356993</v>
+        <v>0.09595962494340628</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3128198294395488</v>
+        <v>0.2963686212595843</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2750251569123722</v>
+        <v>0.2584498879335719</v>
       </c>
       <c r="I7" t="n">
-        <v>0.239437684673739</v>
+        <v>0.2276657081532587</v>
       </c>
       <c r="J7" t="n">
-        <v>0.24986778145219</v>
+        <v>0.2331609074472871</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2244456024274961</v>
+        <v>0.2094985749549076</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005740253371126325</v>
+        <v>-0.0121277672944099</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2444084788160036</v>
+        <v>0.2281829521606275</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3210376766922313</v>
+        <v>1.795835503947679</v>
       </c>
       <c r="O7" t="n">
-        <v>0.157400752613111</v>
+        <v>0.1396698927043497</v>
       </c>
       <c r="P7" t="n">
-        <v>0.100894497355445</v>
+        <v>0.0826573583339304</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2467395435899508</v>
+        <v>0.2304897590768011</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1118885985126723</v>
+        <v>-0.1338121150985196</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1590547032247255</v>
+        <v>0.1404308884480037</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1937731373081156</v>
+        <v>0.1800727341027772</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2528699059303612</v>
+        <v>0.2381790686721565</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2888792501280617</v>
+        <v>0.2714222046591292</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4458060235945363</v>
+        <v>0.4300981774387656</v>
       </c>
       <c r="X7" t="n">
-        <v>0.8049523475485381</v>
+        <v>0.7902210614096959</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3262511736809142</v>
+        <v>0.309690071765985</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1818296797847478</v>
+        <v>0.1643969908302677</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.611099002157187</v>
+        <v>0.5949586175866755</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2429482095308101</v>
+        <v>0.2294205734047666</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05910583212358936</v>
+        <v>0.03909375423982978</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2778201462151682</v>
+        <v>0.253617459190561</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2927451356115071</v>
+        <v>0.2690975017076227</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07266964506347665</v>
+        <v>0.04716583339723237</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1386480526158476</v>
+        <v>0.1183293662048487</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4123766118494309</v>
+        <v>0.3878733107834083</v>
       </c>
       <c r="H8" t="n">
-        <v>0.35998714596039</v>
+        <v>0.3363220029131148</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3243996737217557</v>
+        <v>0.3055378231328018</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3348297705002063</v>
+        <v>0.3110330224268321</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3094075914755136</v>
+        <v>0.2873706899344531</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09070224241914403</v>
+        <v>0.0657443476851349</v>
       </c>
       <c r="M8" t="n">
-        <v>0.329370467863591</v>
+        <v>0.306055067139949</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3514394965199277</v>
+        <v>1.795835503947679</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2031289565342914</v>
+        <v>0.1809169749687997</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1429474056043032</v>
+        <v>0.1204714531552314</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2474842442624467</v>
+        <v>0.2296969397148025</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.02692660946465564</v>
+        <v>-0.05594000011897453</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2440166922727425</v>
+        <v>0.2183030034275475</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2787351263561333</v>
+        <v>0.2579448490823226</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3042483302240019</v>
+        <v>0.28458355065507</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3529414974105478</v>
+        <v>0.3302294746163449</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5307818452961405</v>
+        <v>0.5079832131571868</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8121479755692579</v>
+        <v>0.7954538668207181</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4786169234283935</v>
+        <v>0.4512308978087153</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1950992062775399</v>
+        <v>0.1753032491812809</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6960609912052036</v>
+        <v>0.6728307325662201</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.4014332422441377</v>
+        <v>0.3759684379545157</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1785192843394634</v>
+        <v>0.1570883643373901</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3905083114336844</v>
+        <v>0.3671150499981055</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4054333008300233</v>
+        <v>0.382595092515169</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2081433450845632</v>
+        <v>0.1815347894095413</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1640030201793354</v>
+        <v>0.1461369166984946</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5104699748832354</v>
+        <v>0.4877383164265876</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4726753111789058</v>
+        <v>0.4498195937206606</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4370878389402729</v>
+        <v>0.4190354139403478</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4475179357187229</v>
+        <v>0.4245306132343766</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4220957566940298</v>
+        <v>0.4008682807419975</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2033904076376596</v>
+        <v>0.1792419384926787</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4420586330825373</v>
+        <v>0.4195526579477167</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5186878309587644</v>
+        <v>1.795835503947679</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3764804246794638</v>
+        <v>0.3516699058949279</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3245623507525104</v>
+        <v>0.2990717012635099</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.444389689033639</v>
+        <v>0.4218594542438046</v>
       </c>
       <c r="R9" t="n">
-        <v>0.08576155575385966</v>
+        <v>0.05755759068856911</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3567048574912585</v>
+        <v>0.3318005942350928</v>
       </c>
       <c r="T9" t="n">
-        <v>0.391423291574649</v>
+        <v>0.3714424398898691</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4527977370969248</v>
+        <v>0.4311637553808235</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5599913686322292</v>
+        <v>0.5334703157817926</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6434561778610698</v>
+        <v>0.6214678832258536</v>
       </c>
       <c r="X9" t="n">
-        <v>1.002602501815072</v>
+        <v>0.9815907671967877</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5239013279474479</v>
+        <v>0.5010597775530741</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.3410986696249058</v>
+        <v>0.3188398375608758</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8087491564237201</v>
+        <v>0.7863283233737639</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.4405983637973434</v>
+        <v>0.4207902791918569</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.98884240934683</v>
+        <v>2.977993700329684</v>
       </c>
       <c r="C2" t="n">
-        <v>2.970252045994637</v>
+        <v>2.958031850449989</v>
       </c>
       <c r="D2" t="n">
-        <v>2.991264285416625</v>
+        <v>2.981872780796694</v>
       </c>
       <c r="E2" t="n">
-        <v>2.980201134449723</v>
+        <v>2.966873244366556</v>
       </c>
       <c r="F2" t="n">
-        <v>2.979752547564898</v>
+        <v>2.96851941692396</v>
       </c>
       <c r="G2" t="n">
-        <v>3.035705475486148</v>
+        <v>3.013005462579586</v>
       </c>
       <c r="H2" t="n">
-        <v>3.000048186752245</v>
+        <v>2.988325250428882</v>
       </c>
       <c r="I2" t="n">
-        <v>2.98109153391319</v>
+        <v>2.971153639069443</v>
       </c>
       <c r="J2" t="n">
-        <v>3.00831414047569</v>
+        <v>2.992625539289874</v>
       </c>
       <c r="K2" t="n">
-        <v>2.989018293620277</v>
+        <v>2.978359867581373</v>
       </c>
       <c r="L2" t="n">
-        <v>3.003728465680887</v>
+        <v>2.995735001712151</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0232074968096</v>
+        <v>3.00801586225596</v>
       </c>
       <c r="N2" t="n">
-        <v>2.994281576634469</v>
+        <v>2.982044253958755</v>
       </c>
       <c r="O2" t="n">
-        <v>3.372218671797433</v>
+        <v>3.355839480472261</v>
       </c>
       <c r="P2" t="n">
-        <v>2.999630351589457</v>
+        <v>2.982526940985715</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.984810473104713</v>
+        <v>2.972832452750198</v>
       </c>
       <c r="R2" t="n">
-        <v>2.976281774316338</v>
+        <v>2.968138935755712</v>
       </c>
       <c r="S2" t="n">
-        <v>2.999295285042836</v>
+        <v>2.984549284845188</v>
       </c>
       <c r="T2" t="n">
-        <v>2.983957336079184</v>
+        <v>2.972673265916692</v>
       </c>
       <c r="U2" t="n">
-        <v>3.771086625004214</v>
+        <v>3.757976742969788</v>
       </c>
       <c r="V2" t="n">
-        <v>2.983591350866594</v>
+        <v>2.97217973904436</v>
       </c>
       <c r="W2" t="n">
-        <v>3.772682147875633</v>
+        <v>3.761744019409973</v>
       </c>
       <c r="X2" t="n">
-        <v>3.003045474865894</v>
+        <v>2.989922646535959</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.00106852328331</v>
+        <v>2.986945276663884</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.264563770399614</v>
+        <v>3.25095873630608</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.002692193539658</v>
+        <v>2.991052836461634</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.013490107777254</v>
+        <v>3.005024352082893</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.127666779401293</v>
+        <v>2.123217088203999</v>
       </c>
       <c r="C3" t="n">
-        <v>2.047180315770126</v>
+        <v>2.035623657936989</v>
       </c>
       <c r="D3" t="n">
-        <v>2.145854730903215</v>
+        <v>2.151872871037604</v>
       </c>
       <c r="E3" t="n">
-        <v>2.066489385044821</v>
+        <v>2.044372871195924</v>
       </c>
       <c r="F3" t="n">
-        <v>2.06343830370837</v>
+        <v>2.056271034717159</v>
       </c>
       <c r="G3" t="n">
-        <v>2.46030027859426</v>
+        <v>2.371715125135562</v>
       </c>
       <c r="H3" t="n">
-        <v>2.209155042921613</v>
+        <v>2.198479590372453</v>
       </c>
       <c r="I3" t="n">
-        <v>2.073041319539205</v>
+        <v>2.075147360256478</v>
       </c>
       <c r="J3" t="n">
-        <v>2.266237833124203</v>
+        <v>2.227416466683422</v>
       </c>
       <c r="K3" t="n">
-        <v>2.12913376563324</v>
+        <v>2.126042407342685</v>
       </c>
       <c r="L3" t="n">
-        <v>2.233961265721906</v>
+        <v>2.249856254760433</v>
       </c>
       <c r="M3" t="n">
-        <v>2.375755310450224</v>
+        <v>2.340392278637943</v>
       </c>
       <c r="N3" t="n">
-        <v>2.167181127625297</v>
+        <v>2.152836484223815</v>
       </c>
       <c r="O3" t="n">
-        <v>2.765178034901607</v>
+        <v>2.748608668652916</v>
       </c>
       <c r="P3" t="n">
-        <v>2.204539979463294</v>
+        <v>2.15560397685622</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.099419136399383</v>
+        <v>2.086931215259181</v>
       </c>
       <c r="R3" t="n">
-        <v>2.038636787281419</v>
+        <v>2.05362888949444</v>
       </c>
       <c r="S3" t="n">
-        <v>2.201658061837664</v>
+        <v>2.169558900137268</v>
       </c>
       <c r="T3" t="n">
-        <v>2.09354031918758</v>
+        <v>2.086009835521037</v>
       </c>
       <c r="U3" t="n">
-        <v>3.515236117886608</v>
+        <v>3.494299919377081</v>
       </c>
       <c r="V3" t="n">
-        <v>2.090321492255077</v>
+        <v>2.081871667107322</v>
       </c>
       <c r="W3" t="n">
-        <v>3.559824687646417</v>
+        <v>3.551613913915142</v>
       </c>
       <c r="X3" t="n">
-        <v>2.229953961094444</v>
+        <v>2.209273960309866</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.215344394394401</v>
+        <v>2.187556105279387</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.583064282339437</v>
+        <v>2.5662447348364</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.227045289528088</v>
+        <v>2.216974671448984</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.304545177277349</v>
+        <v>2.316694593523714</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4476429688585269</v>
+        <v>0.3841265178657556</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3436691620394627</v>
+        <v>0.2701749499843926</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4749991731848762</v>
+        <v>0.4279425162058547</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3500357937128364</v>
+        <v>0.2585158520997646</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3449687984885857</v>
+        <v>0.2771101284123965</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9769828589776004</v>
+        <v>0.7796004786848025</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5742173795649679</v>
+        <v>0.5008261289840497</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3600932652566689</v>
+        <v>0.3068648793476934</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6671186573697354</v>
+        <v>0.5489782824055841</v>
       </c>
       <c r="K4" t="n">
-        <v>0.449629662637851</v>
+        <v>0.3882625454188595</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6157878230759285</v>
+        <v>0.5845226783825733</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8407503846039829</v>
+        <v>0.7282308046696757</v>
       </c>
       <c r="N4" t="n">
-        <v>0.509080865512972</v>
+        <v>4.709786997503773</v>
       </c>
       <c r="O4" t="n">
-        <v>0.457640157028784</v>
+        <v>0.3879327268849848</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5694977391875917</v>
+        <v>0.4353315564693594</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4021003942215068</v>
+        <v>0.3258278521642814</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3057648180115263</v>
+        <v>0.2728124185870443</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5657130084052813</v>
+        <v>0.4581748606862448</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3924638190557203</v>
+        <v>0.324029763650284</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6402558420315774</v>
+        <v>0.5509554832349678</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3851941206724318</v>
+        <v>0.3156225088332261</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7311647932030079</v>
+        <v>0.6601632135361473</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6080731276292817</v>
+        <v>0.518869452852014</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.580399783465829</v>
+        <v>0.4804595593880135</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.448098325375708</v>
+        <v>0.3683878546930263</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.6040826525320054</v>
+        <v>0.5316354679755766</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7240101698392294</v>
+        <v>0.6864107070265153</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.39178945383287</v>
+        <v>3.449609586918848</v>
       </c>
       <c r="C5" t="n">
-        <v>1.737898165381946</v>
+        <v>1.618679098227292</v>
       </c>
       <c r="D5" t="n">
-        <v>4.411188519881663</v>
+        <v>4.817875315193156</v>
       </c>
       <c r="E5" t="n">
-        <v>1.82199114075279</v>
+        <v>1.365460303026934</v>
       </c>
       <c r="F5" t="n">
-        <v>1.809888920318657</v>
+        <v>1.800099282669756</v>
       </c>
       <c r="G5" t="n">
-        <v>12.38243857209159</v>
+        <v>10.15822641931799</v>
       </c>
       <c r="H5" t="n">
-        <v>6.625988320740007</v>
+        <v>6.504684001373261</v>
       </c>
       <c r="I5" t="n">
-        <v>2.121779541828035</v>
+        <v>2.40482823099262</v>
       </c>
       <c r="J5" t="n">
-        <v>7.327695402538609</v>
+        <v>6.4469211276587</v>
       </c>
       <c r="K5" t="n">
-        <v>3.547086321225292</v>
+        <v>3.645698129337939</v>
       </c>
       <c r="L5" t="n">
-        <v>6.599954063683457</v>
+        <v>7.249033355590507</v>
       </c>
       <c r="M5" t="n">
-        <v>10.9026576677791</v>
+        <v>10.06394527642067</v>
       </c>
       <c r="N5" t="n">
-        <v>7.051768993276221</v>
+        <v>4.709786997503774</v>
       </c>
       <c r="O5" t="n">
-        <v>3.482249631435729</v>
+        <v>3.432157660367561</v>
       </c>
       <c r="P5" t="n">
-        <v>5.62857928333616</v>
+        <v>4.436100379015596</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.824594013333977</v>
+        <v>2.653303583680071</v>
       </c>
       <c r="R5" t="n">
-        <v>1.051697459140111</v>
+        <v>1.759642286677863</v>
       </c>
       <c r="S5" t="n">
-        <v>5.284208046755992</v>
+        <v>4.601819531141233</v>
       </c>
       <c r="T5" t="n">
-        <v>2.759214287085642</v>
+        <v>2.73873620638343</v>
       </c>
       <c r="U5" t="n">
-        <v>7.188286736390332</v>
+        <v>6.772052969682973</v>
       </c>
       <c r="V5" t="n">
-        <v>2.340456085921089</v>
+        <v>2.287997107918704</v>
       </c>
       <c r="W5" t="n">
-        <v>9.073108961012441</v>
+        <v>9.00172248494537</v>
       </c>
       <c r="X5" t="n">
-        <v>6.936399963315976</v>
+        <v>6.50863603593403</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.236119041227113</v>
+        <v>5.612348394554044</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.426953906030758</v>
+        <v>3.203956419420986</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.645558944525329</v>
+        <v>6.546735030510101</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.771251754869741</v>
+        <v>10.39415218916623</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5692544452041547</v>
+        <v>0.4055838585324169</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3654667041015305</v>
+        <v>0.2916322906510548</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5966106495305042</v>
+        <v>0.4493998568725172</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4716472700584647</v>
+        <v>0.3708743525496171</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4665802748342133</v>
+        <v>0.2985674690790591</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9987804010396679</v>
+        <v>0.891958979134657</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6958288559105958</v>
+        <v>0.5222834696507116</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3818908073187369</v>
+        <v>0.3283222200143558</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6889161994318028</v>
+        <v>0.5704356230722459</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4714272046999192</v>
+        <v>0.5006210458687127</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7373992994215561</v>
+        <v>0.6968811788324312</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9623618609496095</v>
+        <v>0.749688145336339</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5316573170020369</v>
+        <v>4.709786997503774</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4802166085178488</v>
+        <v>0.5053306150209532</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6965963708719389</v>
+        <v>0.5526785057222137</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5237118705671349</v>
+        <v>0.3472851928309434</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4273762943571547</v>
+        <v>0.3851709190368997</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6873244847509091</v>
+        <v>0.4796322013529064</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4142613611177882</v>
+        <v>0.3454871043169463</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7672100849727055</v>
+        <v>0.6680931147859276</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5068055970180598</v>
+        <v>0.3370798494998878</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7583734056306596</v>
+        <v>0.6870242007822339</v>
       </c>
       <c r="X6" t="n">
-        <v>0.62987066969135</v>
+        <v>0.6312279533018673</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6100396470396403</v>
+        <v>0.5094167870407063</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.4698958674377763</v>
+        <v>0.480746355142879</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.7256941288776328</v>
+        <v>0.6439939684254302</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7480371351227771</v>
+        <v>0.7104836918106628</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5626648446000275</v>
+        <v>0.4937989669100329</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4586910377809637</v>
+        <v>0.37984739902867</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5900210489263776</v>
+        <v>0.5376149652501311</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4650576694543376</v>
+        <v>0.3681883011440414</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4599906742300868</v>
+        <v>0.3867825774566733</v>
       </c>
       <c r="G7" t="n">
-        <v>1.092004734719102</v>
+        <v>0.889272927729079</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6892392553064692</v>
+        <v>0.610498578028326</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4751151409981701</v>
+        <v>0.4165373283919701</v>
       </c>
       <c r="J7" t="n">
-        <v>0.782140533111236</v>
+        <v>0.6586507314498619</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5646515383793526</v>
+        <v>0.4979349944631363</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7308096988174299</v>
+        <v>0.6941951274268511</v>
       </c>
       <c r="M7" t="n">
-        <v>0.955772260345483</v>
+        <v>0.8379032537139512</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6241027412544733</v>
+        <v>4.709786997503774</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5723032671066487</v>
+        <v>0.4972465095798479</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6841608492654547</v>
+        <v>0.5446453391642239</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5171222699630074</v>
+        <v>0.435500301208559</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4207866937530276</v>
+        <v>0.3824848676313214</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6807348841467821</v>
+        <v>0.5678473097305216</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5074856947972215</v>
+        <v>0.4337022126945614</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7600830305546534</v>
+        <v>0.6650139960161955</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5002159964139337</v>
+        <v>0.425294957877503</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8461866689445081</v>
+        <v>0.7698356625804247</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7230950033707837</v>
+        <v>0.6285419018962916</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.7007644258028323</v>
+        <v>0.5949111395333969</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5631202011172091</v>
+        <v>0.4780603037373029</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.7191045282735063</v>
+        <v>0.6413079170198526</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8390320455807307</v>
+        <v>0.7960831560707929</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6108561430865359</v>
+        <v>0.5388516574596088</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6370715766064238</v>
+        <v>0.5472932376607846</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7684015877518378</v>
+        <v>0.7050608038822472</v>
       </c>
       <c r="E8" t="n">
-        <v>0.574116278161302</v>
+        <v>0.4704633988079943</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5284639347957775</v>
+        <v>0.450902690029628</v>
       </c>
       <c r="G8" t="n">
-        <v>1.297380860624427</v>
+        <v>1.08209778292724</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8676197941319284</v>
+        <v>0.7779444166604418</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6534956798236298</v>
+        <v>0.5839831670240859</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9605210719366959</v>
+        <v>0.8260965700819769</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7430320772048113</v>
+        <v>0.6653808330952525</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9091902376428903</v>
+        <v>0.8616409660589663</v>
       </c>
       <c r="M8" t="n">
-        <v>1.134152799170873</v>
+        <v>1.00534909234617</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7015648386057201</v>
+        <v>4.709786997503774</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6778573940467755</v>
+        <v>0.5962483681372865</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7829168830933192</v>
+        <v>0.6372561932478816</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5397284113256194</v>
+        <v>0.4564999446918497</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5991672325784865</v>
+        <v>0.5499307062634369</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8591154229722411</v>
+        <v>0.7352931483626368</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6858662336226804</v>
+        <v>0.6011480513266753</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8753189136107878</v>
+        <v>0.7730877800105873</v>
       </c>
       <c r="V8" t="n">
-        <v>0.642861114572172</v>
+        <v>0.5592594984942357</v>
       </c>
       <c r="W8" t="n">
-        <v>1.024592793585206</v>
+        <v>0.9373055548996232</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7576332472384738</v>
+        <v>0.6607591205551216</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.008352265811548</v>
+        <v>0.884004092032577</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6088931676337336</v>
+        <v>0.5208394787302864</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8974850670989656</v>
+        <v>0.8087537556519692</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.153406132093613</v>
+        <v>1.091378872156459</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8901695386531334</v>
+        <v>0.7944084148925218</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9201065816848235</v>
+        <v>0.8044044106893559</v>
       </c>
       <c r="D9" t="n">
-        <v>1.051436592830238</v>
+        <v>0.9621719769108191</v>
       </c>
       <c r="E9" t="n">
-        <v>0.895567149006168</v>
+        <v>0.7641387268824187</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6127051384435632</v>
+        <v>0.5256066158157103</v>
       </c>
       <c r="G9" t="n">
-        <v>1.553420296279026</v>
+        <v>1.313829947452273</v>
       </c>
       <c r="H9" t="n">
-        <v>1.150654799210328</v>
+        <v>1.035055589689015</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9365306849020295</v>
+        <v>0.8410943400526576</v>
       </c>
       <c r="J9" t="n">
-        <v>1.243556077015096</v>
+        <v>1.083207743110549</v>
       </c>
       <c r="K9" t="n">
-        <v>1.026067082283212</v>
+        <v>0.9224920061238224</v>
       </c>
       <c r="L9" t="n">
-        <v>1.192225242721289</v>
+        <v>1.118752139087537</v>
       </c>
       <c r="M9" t="n">
-        <v>1.417187804249342</v>
+        <v>1.262460265374642</v>
       </c>
       <c r="N9" t="n">
-        <v>1.085518285158332</v>
+        <v>4.709786997503774</v>
       </c>
       <c r="O9" t="n">
-        <v>1.078455480480652</v>
+        <v>0.9632382586318318</v>
       </c>
       <c r="P9" t="n">
-        <v>1.19996449148088</v>
+        <v>1.019570427167669</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9785378315229293</v>
+        <v>0.8600573209317529</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8822022376568871</v>
+        <v>0.8070418792920062</v>
       </c>
       <c r="S9" t="n">
-        <v>1.142150428050642</v>
+        <v>0.9924043213912074</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9689012387010797</v>
+        <v>0.8582592243552482</v>
       </c>
       <c r="U9" t="n">
-        <v>1.222036028272437</v>
+        <v>1.089964075041037</v>
       </c>
       <c r="V9" t="n">
-        <v>1.116161645333968</v>
+        <v>0.9928846542630019</v>
       </c>
       <c r="W9" t="n">
-        <v>1.307602212848367</v>
+        <v>1.19439267424111</v>
       </c>
       <c r="X9" t="n">
-        <v>1.184510547274643</v>
+        <v>1.053098913556976</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.162179969706693</v>
+        <v>1.019468151194082</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.943799417389471</v>
+        <v>0.8278879595489728</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.180520072177365</v>
+        <v>1.06586492868054</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.30044758948459</v>
+        <v>1.220640167731479</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.941127694755778</v>
+        <v>2.929582538008893</v>
       </c>
       <c r="C2" t="n">
-        <v>2.934233675651778</v>
+        <v>2.920062282092445</v>
       </c>
       <c r="D2" t="n">
-        <v>2.947085878019756</v>
+        <v>2.935712115829877</v>
       </c>
       <c r="E2" t="n">
-        <v>2.940881432457335</v>
+        <v>2.929111513111641</v>
       </c>
       <c r="F2" t="n">
-        <v>2.931281816022702</v>
+        <v>2.919621773859435</v>
       </c>
       <c r="G2" t="n">
-        <v>2.994629227492148</v>
+        <v>2.974058089835773</v>
       </c>
       <c r="H2" t="n">
-        <v>2.961688848611114</v>
+        <v>2.950169219567782</v>
       </c>
       <c r="I2" t="n">
-        <v>2.940736527896773</v>
+        <v>2.930140531511094</v>
       </c>
       <c r="J2" t="n">
-        <v>2.960625114920472</v>
+        <v>2.946406594242207</v>
       </c>
       <c r="K2" t="n">
-        <v>2.943762881469308</v>
+        <v>2.934311178291128</v>
       </c>
       <c r="L2" t="n">
-        <v>2.925644342423813</v>
+        <v>2.914857127877542</v>
       </c>
       <c r="M2" t="n">
-        <v>2.943463117298434</v>
+        <v>2.931600331521598</v>
       </c>
       <c r="N2" t="n">
-        <v>2.946010548233961</v>
+        <v>2.934408229401249</v>
       </c>
       <c r="O2" t="n">
-        <v>3.293294532245243</v>
+        <v>3.273808084114343</v>
       </c>
       <c r="P2" t="n">
-        <v>2.95397110277461</v>
+        <v>2.939860420267309</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.943732403917937</v>
+        <v>2.931978223110833</v>
       </c>
       <c r="R2" t="n">
-        <v>2.916951699702323</v>
+        <v>2.905854624657609</v>
       </c>
       <c r="S2" t="n">
-        <v>2.935077365681442</v>
+        <v>2.922964804231109</v>
       </c>
       <c r="T2" t="n">
-        <v>2.934481963196045</v>
+        <v>2.924362140053183</v>
       </c>
       <c r="U2" t="n">
-        <v>3.706270690996383</v>
+        <v>3.69247491116958</v>
       </c>
       <c r="V2" t="n">
-        <v>2.950526157354796</v>
+        <v>2.938907324291117</v>
       </c>
       <c r="W2" t="n">
-        <v>3.722043298316714</v>
+        <v>3.708332781560042</v>
       </c>
       <c r="X2" t="n">
-        <v>2.978272088045762</v>
+        <v>2.966375193227868</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.989340660544431</v>
+        <v>2.975467378343562</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.216836674208999</v>
+        <v>3.203005330718029</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.958523323772425</v>
+        <v>2.948011362938448</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.968260584793798</v>
+        <v>2.957831680769242</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.976354063993925</v>
+        <v>1.966816874872727</v>
       </c>
       <c r="C3" t="n">
-        <v>1.978848431690387</v>
+        <v>1.964571277630371</v>
       </c>
       <c r="D3" t="n">
-        <v>2.018855249280557</v>
+        <v>2.010541845054107</v>
       </c>
       <c r="E3" t="n">
-        <v>1.974542992452751</v>
+        <v>1.963400800834296</v>
       </c>
       <c r="F3" t="n">
-        <v>1.905955951965369</v>
+        <v>1.895597471226768</v>
       </c>
       <c r="G3" t="n">
-        <v>2.355477761710542</v>
+        <v>2.28200093333132</v>
       </c>
       <c r="H3" t="n">
-        <v>2.123772511576104</v>
+        <v>2.11441587534378</v>
       </c>
       <c r="I3" t="n">
-        <v>1.973441933025993</v>
+        <v>1.970698308968865</v>
       </c>
       <c r="J3" t="n">
-        <v>2.114667953018071</v>
+        <v>2.0861941809853</v>
       </c>
       <c r="K3" t="n">
-        <v>1.995153541879947</v>
+        <v>2.000488259864261</v>
       </c>
       <c r="L3" t="n">
-        <v>1.866511329389131</v>
+        <v>1.862357011534273</v>
       </c>
       <c r="M3" t="n">
-        <v>1.997928063330641</v>
+        <v>1.985973326177137</v>
       </c>
       <c r="N3" t="n">
-        <v>2.011158414497967</v>
+        <v>2.001210830217</v>
       </c>
       <c r="O3" t="n">
-        <v>2.548624032836566</v>
+        <v>2.525553283487845</v>
       </c>
       <c r="P3" t="n">
-        <v>2.067604003000767</v>
+        <v>2.039841783653304</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.994897509192326</v>
+        <v>1.983875450042678</v>
       </c>
       <c r="R3" t="n">
-        <v>1.80295653795031</v>
+        <v>1.796628401689234</v>
       </c>
       <c r="S3" t="n">
-        <v>1.933526681716131</v>
+        <v>1.91996871776977</v>
       </c>
       <c r="T3" t="n">
-        <v>1.92873300164343</v>
+        <v>1.929388547974756</v>
       </c>
       <c r="U3" t="n">
-        <v>3.284265053952141</v>
+        <v>3.269813652053946</v>
       </c>
       <c r="V3" t="n">
-        <v>2.04307093391766</v>
+        <v>2.033014409839031</v>
       </c>
       <c r="W3" t="n">
-        <v>3.436884954516595</v>
+        <v>3.42367179803123</v>
       </c>
       <c r="X3" t="n">
-        <v>2.241410032721012</v>
+        <v>2.229361808691621</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.320264283931873</v>
+        <v>2.294116877304742</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.475318559530773</v>
+        <v>2.461294470308514</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.100466809355773</v>
+        <v>2.098304067982039</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.169597517818782</v>
+        <v>2.167742489761939</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1889115543501877</v>
+        <v>0.1468918239718421</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2174085996493226</v>
+        <v>0.174576623443386</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2562119752165631</v>
+        <v>0.2161282252049735</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1861299084030187</v>
+        <v>0.1415713810752096</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0776978247321202</v>
+        <v>0.03438041072583346</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7932359785285321</v>
+        <v>0.649263641621117</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4211592457443006</v>
+        <v>0.3794278625209216</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1844931447320879</v>
+        <v>0.1531946172688927</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4087354132428857</v>
+        <v>0.3365548999590726</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2186772005252662</v>
+        <v>0.2003039912416967</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01401996706669581</v>
+        <v>-0.01943845748510076</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2243446626430927</v>
+        <v>0.1784437064006704</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2440656306098674</v>
+        <v>0.7345620924510728</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1699812742560933</v>
+        <v>0.1270765482715513</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3339837561825177</v>
+        <v>0.262985232140108</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.218332942562167</v>
+        <v>0.1739521892678396</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.08416743128573968</v>
+        <v>-0.1211258727103136</v>
       </c>
       <c r="S4" t="n">
-        <v>0.120570304166687</v>
+        <v>0.07214147664384765</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1138449591954619</v>
+        <v>0.08792502756039057</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2780195080055825</v>
+        <v>0.2322477131444473</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2923265801464739</v>
+        <v>0.2497167591072946</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5420053007717491</v>
+        <v>0.4997797925738349</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6084745638256909</v>
+        <v>0.5624817901277631</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7298497918702227</v>
+        <v>0.6602692146342128</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2798651704525047</v>
+        <v>0.2363597176153809</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.3854031864779569</v>
+        <v>0.3550538792294594</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4934344105251682</v>
+        <v>0.4634466468472102</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1621573059510543</v>
+        <v>-0.2050256160097819</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3259347030213094</v>
+        <v>0.2696743482705907</v>
       </c>
       <c r="D5" t="n">
-        <v>1.016415768809732</v>
+        <v>1.008064885674518</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2390726761512493</v>
+        <v>-0.3272897965633548</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.195273158161963</v>
+        <v>-2.261792060376715</v>
       </c>
       <c r="G5" t="n">
-        <v>9.117052714931953</v>
+        <v>7.519336481254184</v>
       </c>
       <c r="H5" t="n">
-        <v>4.294015610465067</v>
+        <v>4.255397512398434</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3026743738929742</v>
+        <v>-0.1458875603923261</v>
       </c>
       <c r="J5" t="n">
-        <v>3.297209213506013</v>
+        <v>2.794582279649745</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3601612828333701</v>
+        <v>0.6996723306599381</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.911964278367112</v>
+        <v>-2.817196546285549</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4578292285461722</v>
+        <v>0.3508903418654843</v>
       </c>
       <c r="N5" t="n">
-        <v>1.317756056339143</v>
+        <v>0.7345620924510728</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4198376397621438</v>
+        <v>-0.4758451362689813</v>
       </c>
       <c r="P5" t="n">
-        <v>2.189084907878068</v>
+        <v>1.677860069551313</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3341141857151397</v>
+        <v>0.2530864165692954</v>
       </c>
       <c r="R5" t="n">
-        <v>-5.433663720853643</v>
+        <v>-5.381277304029042</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.187372428678784</v>
+        <v>-1.328660532461636</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.588371693600126</v>
+        <v>-1.336093704574197</v>
       </c>
       <c r="U5" t="n">
-        <v>1.355359323857702</v>
+        <v>1.273359326183073</v>
       </c>
       <c r="V5" t="n">
-        <v>1.525930066792822</v>
+        <v>1.471951596471945</v>
       </c>
       <c r="W5" t="n">
-        <v>6.07461355925049</v>
+        <v>6.027227327677561</v>
       </c>
       <c r="X5" t="n">
-        <v>7.234970171595956</v>
+        <v>7.121488575516293</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.372284892631491</v>
+        <v>8.867275744259205</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.280093263951031</v>
+        <v>1.215355695326289</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.292016156307011</v>
+        <v>3.455805735496525</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.56440489377573</v>
+        <v>5.749214635258038</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2034356240352989</v>
+        <v>0.2283991570194447</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3103063625871802</v>
+        <v>0.2560839564909885</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2707360449016739</v>
+        <v>0.2976355582525771</v>
       </c>
       <c r="E6" t="n">
-        <v>0.279027671340876</v>
+        <v>0.1535161206946052</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1705955876699775</v>
+        <v>0.04632515034522899</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8077600482136428</v>
+        <v>0.661208381240513</v>
       </c>
       <c r="H6" t="n">
-        <v>0.514057008682158</v>
+        <v>0.3913726021403168</v>
       </c>
       <c r="I6" t="n">
-        <v>0.277390907669946</v>
+        <v>0.2347019503164966</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4232594829279972</v>
+        <v>0.4180622330066762</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3115749634631236</v>
+        <v>0.2122487308610922</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02854403675180656</v>
+        <v>0.06206887556250275</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3172424255809498</v>
+        <v>0.1903884460200657</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2592922829926004</v>
+        <v>0.7345620924510728</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1852079266388492</v>
+        <v>0.2136480682699015</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3464674858218466</v>
+        <v>0.2731596871014175</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3112307055000242</v>
+        <v>0.1858969288872352</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008730331652117174</v>
+        <v>-0.03961853966271088</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1350943738517978</v>
+        <v>0.08408621626324228</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1283690288805733</v>
+        <v>0.09986976717978663</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2961929678135323</v>
+        <v>0.3186680351791717</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3852243430843312</v>
+        <v>0.2616614987266902</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5608874839427356</v>
+        <v>0.5159232090448886</v>
       </c>
       <c r="X6" t="n">
-        <v>0.622998633510801</v>
+        <v>0.6439891231753658</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.7500873578284591</v>
+        <v>0.6792345664019239</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2943892401376157</v>
+        <v>0.317867050662984</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4783009494158142</v>
+        <v>0.3669986188488543</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.509661943132758</v>
+        <v>0.4773284033474998</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2792849915695049</v>
+        <v>0.2339963669527979</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3077820368686397</v>
+        <v>0.2616811664243423</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3465854124358801</v>
+        <v>0.3032327681859298</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2765033456223356</v>
+        <v>0.2286759240561659</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1680712619514372</v>
+        <v>0.1214849537067899</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8836094157478481</v>
+        <v>0.736368184602074</v>
       </c>
       <c r="H7" t="n">
-        <v>0.511532682963617</v>
+        <v>0.4665324055018784</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2748665819514046</v>
+        <v>0.240299160249849</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4991088504622023</v>
+        <v>0.4236594429400291</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3090506377445836</v>
+        <v>0.2874085342226528</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1043934042860121</v>
+        <v>0.06766608549585558</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3147180998624096</v>
+        <v>0.2655482493816264</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3344390678291843</v>
+        <v>0.7345620924510728</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2600209095349728</v>
+        <v>0.2138473416176258</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4240233914613968</v>
+        <v>0.3497560254861825</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3087063797814839</v>
+        <v>0.2610567322487958</v>
       </c>
       <c r="R7" t="n">
-        <v>0.006206005933576578</v>
+        <v>-0.03402132972935731</v>
       </c>
       <c r="S7" t="n">
-        <v>0.210943741386004</v>
+        <v>0.1592460196248028</v>
       </c>
       <c r="T7" t="n">
-        <v>0.204218396414779</v>
+        <v>0.1750295705413469</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3708920372091109</v>
+        <v>0.3235010984392727</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3827000173657908</v>
+        <v>0.3368213020882513</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6323787379910665</v>
+        <v>0.5868843355547895</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6988480010450083</v>
+        <v>0.6495863331087199</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8238726192123774</v>
+        <v>0.7522867466022903</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3702386076718213</v>
+        <v>0.3234642605963371</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4757766236972737</v>
+        <v>0.4421584222104152</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5838078477444852</v>
+        <v>0.5505511898281661</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3105218095910842</v>
+        <v>0.2620021569997683</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4374249566129845</v>
+        <v>0.3813220883517697</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4762283321802248</v>
+        <v>0.4228736901133573</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3537479190148447</v>
+        <v>0.2995238413297167</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2146386005151144</v>
+        <v>0.1637664263345527</v>
       </c>
       <c r="G8" t="n">
-        <v>1.033657481733252</v>
+        <v>0.8750102480698604</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6411756027079617</v>
+        <v>0.5861733274293056</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4045095016957496</v>
+        <v>0.3599400821772769</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6287517702065475</v>
+        <v>0.5433003648674564</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4386935574889285</v>
+        <v>0.4070494561500799</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2340363240303572</v>
+        <v>0.1873070074232825</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4443610196066528</v>
+        <v>0.3851891713092128</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3878007957338534</v>
+        <v>0.7345620924510728</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3346791731913957</v>
+        <v>0.2823098192754733</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4935431825345974</v>
+        <v>0.4134335903649836</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3206041528283392</v>
+        <v>0.2710541274185355</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1358489256779221</v>
+        <v>0.08561959219807046</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3405866611303491</v>
+        <v>0.2788869415522315</v>
       </c>
       <c r="T8" t="n">
-        <v>0.333861316159124</v>
+        <v>0.294670492468775</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4530217856911566</v>
+        <v>0.3988467350526262</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4847491449377394</v>
+        <v>0.431049068031662</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7620409972674576</v>
+        <v>0.7065432663818473</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7197648887975365</v>
+        <v>0.6679822701792599</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.050276010031322</v>
+        <v>0.9624677922903153</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3996474818397844</v>
+        <v>0.349767881025027</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6054195434416186</v>
+        <v>0.5617993441378425</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8162441692415593</v>
+        <v>0.7659126693839685</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5171114283704441</v>
+        <v>0.4509972734521225</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6455734024628005</v>
+        <v>0.570834077124886</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6843767780300409</v>
+        <v>0.612385678886474</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5912232787073872</v>
+        <v>0.5165605833348508</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2754160728395753</v>
+        <v>0.2182022502727334</v>
       </c>
       <c r="G9" t="n">
-        <v>1.221400866243861</v>
+        <v>1.045521167151699</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8493240485577783</v>
+        <v>0.7756853162024218</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6126579475455655</v>
+        <v>0.5494520709503938</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8369002160563641</v>
+        <v>0.7328123536405734</v>
       </c>
       <c r="K9" t="n">
-        <v>0.646842003338744</v>
+        <v>0.5965614449231968</v>
       </c>
       <c r="L9" t="n">
-        <v>0.442184769880174</v>
+        <v>0.376818996196399</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6525094654565704</v>
+        <v>0.5747011600821709</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6722304334233447</v>
+        <v>0.7345620924510728</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6312744366169524</v>
+        <v>0.553873151142352</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8024817498933086</v>
+        <v>0.6964235603700796</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6464978302774962</v>
+        <v>0.5702097147984199</v>
       </c>
       <c r="R9" t="n">
-        <v>0.343997371527738</v>
+        <v>0.2751315809711876</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5487351069801655</v>
+        <v>0.4683989303253478</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5420097620089406</v>
+        <v>0.4841824812418907</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7098337009418989</v>
+        <v>0.6334181558130683</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8358488563994806</v>
+        <v>0.7523157244951757</v>
       </c>
       <c r="W9" t="n">
-        <v>0.9701701035852273</v>
+        <v>0.8960372462553332</v>
       </c>
       <c r="X9" t="n">
-        <v>1.036639366639168</v>
+        <v>0.9587392438092638</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.161663984806538</v>
+        <v>1.061439657302833</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6477600441455547</v>
+        <v>0.5770577357699578</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8135679892914347</v>
+        <v>0.7513113329109596</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9215992133386457</v>
+        <v>0.8597041005287106</v>
       </c>
     </row>
   </sheetData>

--- a/Results/GWP 20a/ammonia climate change GWP 20a results.xlsx
+++ b/Results/GWP 20a/ammonia climate change GWP 20a results.xlsx
@@ -798,7 +798,7 @@
         <v>0.8466439318651791</v>
       </c>
       <c r="N4" t="n">
-        <v>8.577289212489287</v>
+        <v>0.6283920753388644</v>
       </c>
       <c r="O4" t="n">
         <v>0.6102474429785583</v>
@@ -974,7 +974,7 @@
         <v>0.9872398089887113</v>
       </c>
       <c r="N6" t="n">
-        <v>8.577289212489287</v>
+        <v>0.6603263987140341</v>
       </c>
       <c r="O6" t="n">
         <v>0.6421816480633417</v>
@@ -1062,7 +1062,7 @@
         <v>0.9803011900076839</v>
       </c>
       <c r="N7" t="n">
-        <v>8.577289212489287</v>
+        <v>0.7620493334813696</v>
       </c>
       <c r="O7" t="n">
         <v>0.7435207789030881</v>
@@ -1150,7 +1150,7 @@
         <v>1.194292094088296</v>
       </c>
       <c r="N8" t="n">
-        <v>8.577289212489287</v>
+        <v>0.8573143022612257</v>
       </c>
       <c r="O8" t="n">
         <v>0.8717965877469442</v>
@@ -1238,7 +1238,7 @@
         <v>1.556970010411926</v>
       </c>
       <c r="N9" t="n">
-        <v>8.577289212489287</v>
+        <v>1.33871815388561</v>
       </c>
       <c r="O9" t="n">
         <v>1.374914441679641</v>
@@ -1634,7 +1634,7 @@
         <v>0.1428889821975032</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02379443171244244</v>
+        <v>0.02379443171244246</v>
       </c>
       <c r="G4" t="n">
         <v>0.2212339638749498</v>
@@ -1658,7 +1658,7 @@
         <v>0.1328967606241638</v>
       </c>
       <c r="N4" t="n">
-        <v>0.108898240801468</v>
+        <v>0.1501235304984708</v>
       </c>
       <c r="O4" t="n">
         <v>0.06013604520329613</v>
@@ -1670,7 +1670,7 @@
         <v>0.1656099386507632</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2180095404541156</v>
+        <v>-0.2180095404541155</v>
       </c>
       <c r="S4" t="n">
         <v>0.04909239398504364</v>
@@ -1834,7 +1834,7 @@
         <v>0.1459026411760664</v>
       </c>
       <c r="N6" t="n">
-        <v>0.108898240801468</v>
+        <v>0.1634898595958399</v>
       </c>
       <c r="O6" t="n">
         <v>0.1241720399831645</v>
@@ -1922,7 +1922,7 @@
         <v>0.2111055461444566</v>
       </c>
       <c r="N7" t="n">
-        <v>0.108898240801468</v>
+        <v>0.2283323160187646</v>
       </c>
       <c r="O7" t="n">
         <v>0.1380113791397697</v>
@@ -2010,7 +2010,7 @@
         <v>0.3047407955703738</v>
       </c>
       <c r="N8" t="n">
-        <v>0.108898240801468</v>
+        <v>0.2631849016475273</v>
       </c>
       <c r="O8" t="n">
         <v>0.189351402763602</v>
@@ -2098,7 +2098,7 @@
         <v>0.4189890071493913</v>
       </c>
       <c r="N9" t="n">
-        <v>0.108898240801468</v>
+        <v>0.4362157770236998</v>
       </c>
       <c r="O9" t="n">
         <v>0.3684436648600062</v>
@@ -2518,7 +2518,7 @@
         <v>0.7865872689118614</v>
       </c>
       <c r="N4" t="n">
-        <v>6.961714305217533</v>
+        <v>0.5572323305931769</v>
       </c>
       <c r="O4" t="n">
         <v>0.5348917863329984</v>
@@ -2694,7 +2694,7 @@
         <v>0.9101862707871602</v>
       </c>
       <c r="N6" t="n">
-        <v>6.961714305217533</v>
+        <v>0.5834830909269865</v>
       </c>
       <c r="O6" t="n">
         <v>0.5612657202870994</v>
@@ -2782,7 +2782,7 @@
         <v>0.9057519833504183</v>
       </c>
       <c r="N7" t="n">
-        <v>6.961714305217533</v>
+        <v>0.6763970450317341</v>
       </c>
       <c r="O7" t="n">
         <v>0.6536974897877964</v>
@@ -2870,7 +2870,7 @@
         <v>1.094934650516382</v>
       </c>
       <c r="N8" t="n">
-        <v>6.961714305217533</v>
+        <v>0.7602569846510007</v>
       </c>
       <c r="O8" t="n">
         <v>0.7668600403769219</v>
@@ -2958,7 +2958,7 @@
         <v>1.360975622033845</v>
       </c>
       <c r="N9" t="n">
-        <v>6.961714305217533</v>
+        <v>1.13162068371516</v>
       </c>
       <c r="O9" t="n">
         <v>1.153487900991823</v>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.993704286083266</v>
+        <v>2.993704286083269</v>
       </c>
       <c r="C2" t="n">
-        <v>2.973179169266134</v>
+        <v>2.973179169266136</v>
       </c>
       <c r="D2" t="n">
         <v>3.006090059820969</v>
       </c>
       <c r="E2" t="n">
-        <v>2.983401361808401</v>
+        <v>2.983401361808403</v>
       </c>
       <c r="F2" t="n">
-        <v>2.984673760201456</v>
+        <v>2.984673760201459</v>
       </c>
       <c r="G2" t="n">
-        <v>3.023249526712759</v>
+        <v>3.023249526712761</v>
       </c>
       <c r="H2" t="n">
-        <v>2.999988632796625</v>
+        <v>2.999988632796627</v>
       </c>
       <c r="I2" t="n">
-        <v>2.989338709809477</v>
+        <v>2.98933870980948</v>
       </c>
       <c r="J2" t="n">
-        <v>3.007401118271578</v>
+        <v>3.007401118271581</v>
       </c>
       <c r="K2" t="n">
-        <v>2.994727074639386</v>
+        <v>2.994727074639388</v>
       </c>
       <c r="L2" t="n">
-        <v>3.008779293605888</v>
+        <v>3.008779293605891</v>
       </c>
       <c r="M2" t="n">
-        <v>3.016405375863915</v>
+        <v>3.016405375863917</v>
       </c>
       <c r="N2" t="n">
-        <v>2.995262703401123</v>
+        <v>2.995262703401124</v>
       </c>
       <c r="O2" t="n">
-        <v>3.377887207515207</v>
+        <v>3.377887207515208</v>
       </c>
       <c r="P2" t="n">
-        <v>3.004223319467502</v>
+        <v>3.004223319467503</v>
       </c>
       <c r="Q2" t="n">
         <v>2.982912892594884</v>
       </c>
       <c r="R2" t="n">
-        <v>2.995013857550892</v>
+        <v>2.995013857550895</v>
       </c>
       <c r="S2" t="n">
-        <v>3.007133908903144</v>
+        <v>3.007133908903147</v>
       </c>
       <c r="T2" t="n">
-        <v>2.993365681091113</v>
+        <v>2.993365681091114</v>
       </c>
       <c r="U2" t="n">
-        <v>3.771206933615795</v>
+        <v>3.771206933615797</v>
       </c>
       <c r="V2" t="n">
-        <v>2.988724585304755</v>
+        <v>2.988724585304758</v>
       </c>
       <c r="W2" t="n">
         <v>3.776961558344381</v>
       </c>
       <c r="X2" t="n">
-        <v>3.011137766632613</v>
+        <v>3.011137766632617</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.007283865400357</v>
+        <v>3.007283865400359</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.274753792457812</v>
+        <v>3.274753792457815</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.002261503898954</v>
+        <v>3.002261503898956</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.018371321593318</v>
+        <v>3.018371321593319</v>
       </c>
     </row>
     <row r="3">
@@ -3257,7 +3257,7 @@
         <v>2.169998832300358</v>
       </c>
       <c r="C3" t="n">
-        <v>2.081593485156299</v>
+        <v>2.0815934851563</v>
       </c>
       <c r="D3" t="n">
         <v>2.259541761117164</v>
@@ -3266,19 +3266,19 @@
         <v>2.096990469535405</v>
       </c>
       <c r="F3" t="n">
-        <v>2.106311819476156</v>
+        <v>2.106311819476155</v>
       </c>
       <c r="G3" t="n">
-        <v>2.380000594206514</v>
+        <v>2.380000594206515</v>
       </c>
       <c r="H3" t="n">
-        <v>2.216530223456968</v>
+        <v>2.216530223456967</v>
       </c>
       <c r="I3" t="n">
         <v>2.139816015726281</v>
       </c>
       <c r="J3" t="n">
-        <v>2.267829096518155</v>
+        <v>2.267829096518154</v>
       </c>
       <c r="K3" t="n">
         <v>2.177295770275555</v>
@@ -3290,13 +3290,13 @@
         <v>2.337229054823425</v>
       </c>
       <c r="N3" t="n">
-        <v>2.181889060175932</v>
+        <v>2.181889060175931</v>
       </c>
       <c r="O3" t="n">
         <v>2.810682699147954</v>
       </c>
       <c r="P3" t="n">
-        <v>2.244716122716509</v>
+        <v>2.24471612271651</v>
       </c>
       <c r="Q3" t="n">
         <v>2.093549620553586</v>
@@ -3311,22 +3311,22 @@
         <v>2.168593378195403</v>
       </c>
       <c r="U3" t="n">
-        <v>3.508189835317334</v>
+        <v>3.508189835317335</v>
       </c>
       <c r="V3" t="n">
         <v>2.134303397715203</v>
       </c>
       <c r="W3" t="n">
-        <v>3.581154663459959</v>
+        <v>3.581154663459956</v>
       </c>
       <c r="X3" t="n">
         <v>2.295433344627467</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.267416003160079</v>
+        <v>2.26741600316008</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.642309239816913</v>
+        <v>2.642309239816914</v>
       </c>
       <c r="AA3" t="n">
         <v>2.231678926194728</v>
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4509364288023366</v>
+        <v>0.4509364288023376</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3373374968763544</v>
+        <v>0.3373374968763546</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5908394409071062</v>
+        <v>0.5908394409071066</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3345601595384415</v>
+        <v>0.334560159538442</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3489324847201433</v>
+        <v>0.3489324847201439</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7846635131946685</v>
+        <v>0.7846635131946695</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5219210158720616</v>
+        <v>0.521921015872062</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4016252365256062</v>
+        <v>0.401625236525607</v>
       </c>
       <c r="J4" t="n">
-        <v>0.605243717358375</v>
+        <v>0.6052437173583749</v>
       </c>
       <c r="K4" t="n">
-        <v>0.462489296049708</v>
+        <v>0.4624892960497082</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6212155736164425</v>
+        <v>0.6212155736164413</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7138525939991159</v>
+        <v>0.7138525939991175</v>
       </c>
       <c r="N4" t="n">
-        <v>5.042007288042453</v>
+        <v>0.4685394693149096</v>
       </c>
       <c r="O4" t="n">
-        <v>0.465285801164692</v>
+        <v>0.4652858011646928</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5697537498717062</v>
+        <v>0.5697537498717069</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3290426750647912</v>
+        <v>0.3290426750647917</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4657286409618305</v>
+        <v>0.4657286409618304</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6026301964845736</v>
+        <v>0.6026301964845742</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4471117296499826</v>
+        <v>0.4471117296499839</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5591491323338141</v>
+        <v>0.559149132333816</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3919713724837046</v>
+        <v>0.3919713724837041</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6931089649941781</v>
+        <v>0.6931089649941783</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6478556114045044</v>
+        <v>0.6478556114045048</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6001019606881984</v>
+        <v>0.6001019606881994</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.4691309144170134</v>
+        <v>0.4691309144170138</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5475941405452373</v>
+        <v>0.5475941405452376</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.727322293227378</v>
+        <v>0.7273222932273783</v>
       </c>
     </row>
     <row r="5">
@@ -3430,13 +3430,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.332814020114644</v>
+        <v>4.332814020114633</v>
       </c>
       <c r="C5" t="n">
-        <v>2.579399721993859</v>
+        <v>2.579399721993858</v>
       </c>
       <c r="D5" t="n">
-        <v>7.400619806973491</v>
+        <v>7.400619806973489</v>
       </c>
       <c r="E5" t="n">
         <v>2.546120308779971</v>
@@ -3445,70 +3445,70 @@
         <v>2.924785372985711</v>
       </c>
       <c r="G5" t="n">
-        <v>9.787533700492958</v>
+        <v>9.787533700492972</v>
       </c>
       <c r="H5" t="n">
-        <v>6.45875317168948</v>
+        <v>6.458753171689494</v>
       </c>
       <c r="I5" t="n">
-        <v>3.965683970538863</v>
+        <v>3.965683970538861</v>
       </c>
       <c r="J5" t="n">
-        <v>7.107763839782042</v>
+        <v>7.107763839782036</v>
       </c>
       <c r="K5" t="n">
-        <v>4.535717864343332</v>
+        <v>4.535717864343331</v>
       </c>
       <c r="L5" t="n">
-        <v>7.555647460900432</v>
+        <v>7.555647460900408</v>
       </c>
       <c r="M5" t="n">
-        <v>9.854320195075708</v>
+        <v>9.854320195075687</v>
       </c>
       <c r="N5" t="n">
-        <v>5.042007288042453</v>
+        <v>5.042007288042454</v>
       </c>
       <c r="O5" t="n">
-        <v>4.35336735602296</v>
+        <v>4.353367356022974</v>
       </c>
       <c r="P5" t="n">
-        <v>6.248990092951697</v>
+        <v>6.24899009295171</v>
       </c>
       <c r="Q5" t="n">
         <v>2.472051602951899</v>
       </c>
       <c r="R5" t="n">
-        <v>5.259878468570383</v>
+        <v>5.259878468570382</v>
       </c>
       <c r="S5" t="n">
-        <v>6.864649284462942</v>
+        <v>6.864649284462947</v>
       </c>
       <c r="T5" t="n">
-        <v>4.789189756598449</v>
+        <v>4.789189756598447</v>
       </c>
       <c r="U5" t="n">
-        <v>6.364637505375476</v>
+        <v>6.364637505375523</v>
       </c>
       <c r="V5" t="n">
-        <v>3.254901189405972</v>
+        <v>3.254901189405979</v>
       </c>
       <c r="W5" t="n">
-        <v>8.937148475699351</v>
+        <v>8.937148475699336</v>
       </c>
       <c r="X5" t="n">
-        <v>8.339524174632748</v>
+        <v>8.33952417463278</v>
       </c>
       <c r="Y5" t="n">
         <v>7.304339681036744</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.421113475410813</v>
+        <v>4.421113475410801</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.356825827897234</v>
+        <v>6.35682582789723</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.50851130629887</v>
+        <v>10.50851130629886</v>
       </c>
     </row>
     <row r="6">
@@ -3521,61 +3521,61 @@
         <v>0.5629905267805632</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3623137050668395</v>
+        <v>0.3623137050668393</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7028935388853327</v>
+        <v>0.7028935388853328</v>
       </c>
       <c r="E6" t="n">
-        <v>0.446614257516668</v>
+        <v>0.4466142575166678</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3739086929106279</v>
+        <v>0.3739086929106282</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8096397213851523</v>
+        <v>0.8096397213851533</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5468972240625467</v>
+        <v>0.5468972240625473</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4266014447160909</v>
+        <v>0.4266014447160911</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7172978153366034</v>
+        <v>0.7172978153366032</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5745433940279348</v>
+        <v>0.5745433940279353</v>
       </c>
       <c r="L6" t="n">
-        <v>0.733269671594669</v>
+        <v>0.7332696715946693</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7388288021896008</v>
+        <v>0.7388288021896006</v>
       </c>
       <c r="N6" t="n">
-        <v>5.042007288042453</v>
+        <v>0.4941668875411535</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5819163674404928</v>
+        <v>0.5819163674404932</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6863431005981419</v>
+        <v>0.6863431005981432</v>
       </c>
       <c r="Q6" t="n">
         <v>0.4410967730430178</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4907048491523151</v>
+        <v>0.490704849152315</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7146842944627999</v>
+        <v>0.7146842944628</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4720879378404673</v>
+        <v>0.472087937840467</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5883474039400954</v>
+        <v>0.5883474039400971</v>
       </c>
       <c r="V6" t="n">
         <v>0.5040254704619306</v>
@@ -3584,19 +3584,19 @@
         <v>0.8097542325629685</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6728318195949902</v>
+        <v>0.6728318195949895</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6320802423315823</v>
+        <v>0.6320802423315877</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.58118501239524</v>
+        <v>0.5811850123952397</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.659648238523465</v>
+        <v>0.6596482385234649</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7545546493959411</v>
+        <v>0.7545546493959425</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5567867902162271</v>
+        <v>0.5567867902162269</v>
       </c>
       <c r="C7" t="n">
-        <v>0.443187858290246</v>
+        <v>0.4431878582902457</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6966898023209972</v>
+        <v>0.6966898023209975</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4404105209523323</v>
+        <v>0.4404105209523331</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4547828461340337</v>
+        <v>0.4547828461340342</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8905138746085586</v>
+        <v>0.890513874608559</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6277713772859529</v>
+        <v>0.6277713772859531</v>
       </c>
       <c r="I7" t="n">
         <v>0.5074755979394983</v>
       </c>
       <c r="J7" t="n">
-        <v>0.711094078772265</v>
+        <v>0.7110940787722659</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5683396574635989</v>
+        <v>0.5683396574635983</v>
       </c>
       <c r="L7" t="n">
-        <v>0.727065935030334</v>
+        <v>0.7270659350303335</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8197029554130058</v>
+        <v>0.8197029554130072</v>
       </c>
       <c r="N7" t="n">
-        <v>5.042007288042453</v>
+        <v>0.5743898307288</v>
       </c>
       <c r="O7" t="n">
-        <v>0.570801923104459</v>
+        <v>0.5708019231044595</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6752698718114741</v>
+        <v>0.6752698718114745</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4348930364786827</v>
+        <v>0.434893036478683</v>
       </c>
       <c r="R7" t="n">
-        <v>0.571579002375721</v>
+        <v>0.5715790023757207</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7084805578984649</v>
+        <v>0.7084805578984648</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5529620910638725</v>
+        <v>0.5529620910638737</v>
       </c>
       <c r="U7" t="n">
-        <v>0.66877623461359</v>
+        <v>0.6687762346135938</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4978217338975954</v>
+        <v>0.497821733897595</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7989593264080685</v>
+        <v>0.7989593264080683</v>
       </c>
       <c r="X7" t="n">
-        <v>0.753705972818397</v>
+        <v>0.7537059728183974</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.7101743855178857</v>
+        <v>0.7101743855178866</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.574981275830904</v>
+        <v>0.5749812758309037</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6534445019591294</v>
+        <v>0.6534445019591297</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8331726546412703</v>
+        <v>0.8331726546412717</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6021482462641843</v>
+        <v>0.6021482462641856</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6073554587962872</v>
+        <v>0.6073554587962879</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8608574028270388</v>
+        <v>0.8608574028270395</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5413173541093448</v>
+        <v>0.5413173541093443</v>
       </c>
       <c r="F8" t="n">
-        <v>0.518652910964099</v>
+        <v>0.5186529109640996</v>
       </c>
       <c r="G8" t="n">
         <v>1.079316703113194</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7919389777919965</v>
+        <v>0.7919389777919975</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6716431984455398</v>
+        <v>0.6716431984455402</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8752616792783079</v>
+        <v>0.8752616792783077</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7325072579696414</v>
+        <v>0.7325072579696413</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8912335355363772</v>
+        <v>0.8912335355363769</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9838705559192396</v>
+        <v>0.9838705559192401</v>
       </c>
       <c r="N8" t="n">
-        <v>5.042007288042453</v>
+        <v>0.6464627934278472</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6685175313578291</v>
+        <v>0.66851753135783</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7667817782012145</v>
+        <v>0.7667817782012157</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4569063735399668</v>
+        <v>0.4569063735399677</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7357466028817643</v>
+        <v>0.7357466028817637</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8726481584045076</v>
+        <v>0.8726481584045087</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7171296915699149</v>
+        <v>0.7171296915699159</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7753153775516823</v>
+        <v>0.7753153775516818</v>
       </c>
       <c r="V8" t="n">
-        <v>0.629422872641899</v>
+        <v>0.6294228726419003</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9631502756606037</v>
+        <v>0.9631502756606044</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7866081290508019</v>
+        <v>0.7866081290508046</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9923209620152492</v>
+        <v>0.9923209620152502</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6181358467558297</v>
+        <v>0.6181358467558294</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8176121024651729</v>
+        <v>0.8176121024651725</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.121443207381977</v>
+        <v>1.121443207381978</v>
       </c>
     </row>
     <row r="9">
@@ -3782,64 +3782,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8234742631727019</v>
+        <v>0.8234742631727022</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8227949203173763</v>
+        <v>0.8227949203173766</v>
       </c>
       <c r="D9" t="n">
-        <v>1.076296864348127</v>
+        <v>1.076296864348128</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7939562343431378</v>
+        <v>0.793956234343137</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5740793824900823</v>
+        <v>0.5740793824900817</v>
       </c>
       <c r="G9" t="n">
-        <v>1.270120978146865</v>
+        <v>1.270120978146864</v>
       </c>
       <c r="H9" t="n">
-        <v>1.007378439313085</v>
+        <v>1.007378439313086</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8870826599666303</v>
+        <v>0.88708265996663</v>
       </c>
       <c r="J9" t="n">
-        <v>1.090701140799397</v>
+        <v>1.090701140799398</v>
       </c>
       <c r="K9" t="n">
         <v>0.947946719490729</v>
       </c>
       <c r="L9" t="n">
-        <v>1.106672997057466</v>
+        <v>1.106672997057465</v>
       </c>
       <c r="M9" t="n">
         <v>1.199310017440139</v>
       </c>
       <c r="N9" t="n">
-        <v>5.042007288042453</v>
+        <v>0.9539968927559319</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9881646838360764</v>
+        <v>0.988164683836077</v>
       </c>
       <c r="P9" t="n">
-        <v>1.10077114885361</v>
+        <v>1.100771148853611</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8145001400169872</v>
+        <v>0.8145001400169876</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9511860644028514</v>
+        <v>0.9511860644028511</v>
       </c>
       <c r="S9" t="n">
         <v>1.088087619925596</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9325691530910052</v>
+        <v>0.9325691530910056</v>
       </c>
       <c r="U9" t="n">
-        <v>1.048828619190631</v>
+        <v>1.048828619190634</v>
       </c>
       <c r="V9" t="n">
         <v>1.007735486866757</v>
@@ -3851,16 +3851,16 @@
         <v>1.133313034845528</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.089781447545017</v>
+        <v>1.089781447545016</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.8865078833336996</v>
+        <v>0.8865078833336982</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.033051563986261</v>
+        <v>1.033051563986262</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.212779716668402</v>
+        <v>1.212779716668403</v>
       </c>
     </row>
   </sheetData>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.986440352726758</v>
+        <v>2.986440352726757</v>
       </c>
       <c r="C2" t="n">
         <v>2.969373732505465</v>
@@ -4038,7 +4038,7 @@
         <v>2.975170244442945</v>
       </c>
       <c r="F2" t="n">
-        <v>2.981805155986176</v>
+        <v>2.981805155986177</v>
       </c>
       <c r="G2" t="n">
         <v>3.011194357458953</v>
@@ -4050,22 +4050,22 @@
         <v>2.984178388242388</v>
       </c>
       <c r="J2" t="n">
-        <v>2.999101497669393</v>
+        <v>2.999101497669391</v>
       </c>
       <c r="K2" t="n">
-        <v>2.993622247894012</v>
+        <v>2.993622247894013</v>
       </c>
       <c r="L2" t="n">
-        <v>2.998492806051089</v>
+        <v>2.99849280605109</v>
       </c>
       <c r="M2" t="n">
-        <v>3.005102718192138</v>
+        <v>3.005102718192137</v>
       </c>
       <c r="N2" t="n">
         <v>2.987512842067502</v>
       </c>
       <c r="O2" t="n">
-        <v>3.360494244125724</v>
+        <v>3.360494244125723</v>
       </c>
       <c r="P2" t="n">
         <v>2.997599713574871</v>
@@ -4074,19 +4074,19 @@
         <v>2.981222071111544</v>
       </c>
       <c r="R2" t="n">
-        <v>2.987698298529794</v>
+        <v>2.987698298529793</v>
       </c>
       <c r="S2" t="n">
         <v>2.998794177571321</v>
       </c>
       <c r="T2" t="n">
-        <v>2.987089320939499</v>
+        <v>2.987089320939498</v>
       </c>
       <c r="U2" t="n">
-        <v>3.766077453318106</v>
+        <v>3.766077453318105</v>
       </c>
       <c r="V2" t="n">
-        <v>2.992915645544042</v>
+        <v>2.992915645544041</v>
       </c>
       <c r="W2" t="n">
         <v>3.76959153581853</v>
@@ -4095,16 +4095,16 @@
         <v>3.007918090678546</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.015766752852954</v>
+        <v>3.015766752852953</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.264392202083637</v>
+        <v>3.264392202083636</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.998579365828175</v>
+        <v>2.998579365828176</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.009074116475246</v>
+        <v>3.009074116475248</v>
       </c>
     </row>
     <row r="3">
@@ -4120,25 +4120,25 @@
         <v>2.091059540351124</v>
       </c>
       <c r="D3" t="n">
-        <v>2.186616961037769</v>
+        <v>2.186616961037768</v>
       </c>
       <c r="E3" t="n">
-        <v>2.070541942175246</v>
+        <v>2.070541942175245</v>
       </c>
       <c r="F3" t="n">
         <v>2.118268855554074</v>
       </c>
       <c r="G3" t="n">
-        <v>2.326087007078509</v>
+        <v>2.32608700707851</v>
       </c>
       <c r="H3" t="n">
-        <v>2.193986278384092</v>
+        <v>2.193986278384091</v>
       </c>
       <c r="I3" t="n">
-        <v>2.135309285807349</v>
+        <v>2.135309285807348</v>
       </c>
       <c r="J3" t="n">
-        <v>2.240838068265504</v>
+        <v>2.240838068265503</v>
       </c>
       <c r="K3" t="n">
         <v>2.201764617149726</v>
@@ -4150,10 +4150,10 @@
         <v>2.288315226388756</v>
       </c>
       <c r="N3" t="n">
-        <v>2.159022174394509</v>
+        <v>2.159022174394508</v>
       </c>
       <c r="O3" t="n">
-        <v>2.761863756664854</v>
+        <v>2.761863756664853</v>
       </c>
       <c r="P3" t="n">
         <v>2.229577319479455</v>
@@ -4171,28 +4171,28 @@
         <v>2.156226046996115</v>
       </c>
       <c r="U3" t="n">
-        <v>3.517217684207751</v>
+        <v>3.517217684207752</v>
       </c>
       <c r="V3" t="n">
-        <v>2.196178446837498</v>
+        <v>2.196178446837499</v>
       </c>
       <c r="W3" t="n">
-        <v>3.578602913621354</v>
+        <v>3.578602913621355</v>
       </c>
       <c r="X3" t="n">
         <v>2.304428527358727</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.360761512225863</v>
+        <v>2.360761512225861</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.615653209529639</v>
+        <v>2.615653209529638</v>
       </c>
       <c r="AA3" t="n">
         <v>2.237919914080229</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.312994614426423</v>
+        <v>2.312994614426422</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4250432200556757</v>
+        <v>0.4250432200556756</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3593073473323504</v>
+        <v>0.3593073473323486</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4811126565622166</v>
+        <v>0.4811126565622144</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2977421624840468</v>
+        <v>0.2977421624840453</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3726865405749621</v>
+        <v>0.3726865405749614</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7046510909105933</v>
+        <v>0.7046510909105891</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4911700680425113</v>
+        <v>0.4911700680425107</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3994932906496654</v>
+        <v>0.3994932906496645</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5677478024695082</v>
+        <v>0.5677478024695057</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5061660298048026</v>
+        <v>0.5061660298048012</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5611812247564434</v>
+        <v>0.5611812247564424</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6425532951092416</v>
+        <v>0.6425532951092392</v>
       </c>
       <c r="N4" t="n">
-        <v>4.45754635868574</v>
+        <v>0.4371574805288559</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4127778362074715</v>
+        <v>0.4127778362074711</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5510933343947148</v>
+        <v>0.5510933343947123</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3661003286836898</v>
+        <v>0.366100328683689</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4392522965846404</v>
+        <v>0.4392522965846406</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5645853547151972</v>
+        <v>0.5645853547151947</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4323736145586958</v>
+        <v>0.4323736145586936</v>
       </c>
       <c r="U4" t="n">
-        <v>0.586063816965613</v>
+        <v>0.5860638169656094</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4961176683090533</v>
+        <v>0.496117668309053</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7021884796077602</v>
+        <v>0.7021884796077604</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6676441504687124</v>
+        <v>0.6676441504687117</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7526616844822075</v>
+        <v>0.7526616844822066</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.4393233648760667</v>
+        <v>0.4393233648760655</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5621589572581008</v>
+        <v>0.5621589572581001</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6785075179904354</v>
+        <v>0.6785075179904358</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.769175731394048</v>
+        <v>3.769175731394055</v>
       </c>
       <c r="C5" t="n">
-        <v>2.913240633959896</v>
+        <v>2.91324063395989</v>
       </c>
       <c r="D5" t="n">
-        <v>5.142544113264734</v>
+        <v>5.142544113264703</v>
       </c>
       <c r="E5" t="n">
-        <v>1.789390876241729</v>
+        <v>1.789390876241728</v>
       </c>
       <c r="F5" t="n">
-        <v>3.308317131334378</v>
+        <v>3.30831713133436</v>
       </c>
       <c r="G5" t="n">
-        <v>8.177388402899554</v>
+        <v>8.177388402899538</v>
       </c>
       <c r="H5" t="n">
-        <v>5.846180482013193</v>
+        <v>5.846180482013196</v>
       </c>
       <c r="I5" t="n">
-        <v>3.835584407665222</v>
+        <v>3.835584407665218</v>
       </c>
       <c r="J5" t="n">
-        <v>6.309673170441192</v>
+        <v>6.30967317044118</v>
       </c>
       <c r="K5" t="n">
-        <v>5.23204500874694</v>
+        <v>5.232045008746944</v>
       </c>
       <c r="L5" t="n">
-        <v>6.242813223971427</v>
+        <v>6.242813223971431</v>
       </c>
       <c r="M5" t="n">
-        <v>8.14602593859666</v>
+        <v>8.146025938596653</v>
       </c>
       <c r="N5" t="n">
-        <v>4.45754635868574</v>
+        <v>4.457546358685735</v>
       </c>
       <c r="O5" t="n">
-        <v>3.512811694694004</v>
+        <v>3.512811694693989</v>
       </c>
       <c r="P5" t="n">
-        <v>5.728851118172259</v>
+        <v>5.728851118172227</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.034660487934754</v>
+        <v>3.034660487934745</v>
       </c>
       <c r="R5" t="n">
-        <v>4.723497669474847</v>
+        <v>4.723497669474844</v>
       </c>
       <c r="S5" t="n">
-        <v>6.128215681392876</v>
+        <v>6.128215681392871</v>
       </c>
       <c r="T5" t="n">
         <v>4.490346853792426</v>
       </c>
       <c r="U5" t="n">
-        <v>6.561400555517717</v>
+        <v>6.561400555517725</v>
       </c>
       <c r="V5" t="n">
-        <v>4.807358703839619</v>
+        <v>4.807358703839616</v>
       </c>
       <c r="W5" t="n">
-        <v>9.086666591957977</v>
+        <v>9.086666591957975</v>
       </c>
       <c r="X5" t="n">
-        <v>8.41648603271349</v>
+        <v>8.416486032713467</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.14860016398166</v>
+        <v>10.14860016398165</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.738707681482557</v>
+        <v>3.738707681482556</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.624566038922216</v>
+        <v>6.624566038922211</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.389989312251647</v>
+        <v>9.389989312251625</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4531872579243933</v>
+        <v>0.4531872579243866</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3874513852010709</v>
+        <v>0.3874513852010605</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5904707456699948</v>
+        <v>0.5904707456699942</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4071002515918251</v>
+        <v>0.4071002515918228</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4008305784436831</v>
+        <v>0.4008305784436723</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7327951287793143</v>
+        <v>0.7327951287793022</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6005281571502895</v>
+        <v>0.6005281571502885</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4276373285183851</v>
+        <v>0.4276373285183744</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6771058915772848</v>
+        <v>0.6771058915772838</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6155241189125804</v>
+        <v>0.6155241189125781</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5893252626251648</v>
+        <v>0.5893252626251551</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6706973329779639</v>
+        <v>0.6706973329779512</v>
       </c>
       <c r="N6" t="n">
-        <v>4.45754635868574</v>
+        <v>0.4664773873887191</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4422102249486296</v>
+        <v>0.4422102249486352</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6653431007327405</v>
+        <v>0.6653431007327389</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4754584177914669</v>
+        <v>0.4754584177914645</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5486103856924182</v>
+        <v>0.548610385692415</v>
       </c>
       <c r="S6" t="n">
-        <v>0.592729392583913</v>
+        <v>0.5927293925839066</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5417317036664733</v>
+        <v>0.5417317036664717</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6990586218828132</v>
+        <v>0.6990586218828096</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5242617061777719</v>
+        <v>0.5242617061777642</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7357519770785033</v>
+        <v>0.7357519770785029</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6957881883374294</v>
+        <v>0.6957881883374222</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.7881970343333106</v>
+        <v>0.7881970343333009</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.4674674027447873</v>
+        <v>0.4674674027447764</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6715170463658792</v>
+        <v>0.6715170463658793</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7088665411384705</v>
+        <v>0.7088665411384709</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5279621219820432</v>
+        <v>0.5279621219820412</v>
       </c>
       <c r="C7" t="n">
-        <v>0.462226249258717</v>
+        <v>0.462226249258715</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5840315584885839</v>
+        <v>0.5840315584885807</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4006610644104134</v>
+        <v>0.4006610644104114</v>
       </c>
       <c r="F7" t="n">
-        <v>0.47560544250133</v>
+        <v>0.4756054425013264</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8075699928369608</v>
+        <v>0.8075699928369562</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5940889699688789</v>
+        <v>0.5940889699688773</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5024121925760322</v>
+        <v>0.5024121925760305</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6706667043958749</v>
+        <v>0.6706667043958714</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6090849317311692</v>
+        <v>0.6090849317311674</v>
       </c>
       <c r="L7" t="n">
-        <v>0.664100126682812</v>
+        <v>0.6641001266828106</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7454721970356065</v>
+        <v>0.7454721970356037</v>
       </c>
       <c r="N7" t="n">
-        <v>4.45754635868574</v>
+        <v>0.5400763824552197</v>
       </c>
       <c r="O7" t="n">
-        <v>0.515362646109677</v>
+        <v>0.5153626461096744</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6536781442969206</v>
+        <v>0.6536781442969183</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4690192306100565</v>
+        <v>0.4690192306100555</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5421711985110075</v>
+        <v>0.542171198511007</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6675042566415643</v>
+        <v>0.6675042566415615</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5352925164850637</v>
+        <v>0.5352925164850615</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6918870555450988</v>
+        <v>0.6918870555450977</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5990365702354202</v>
+        <v>0.5990365702354191</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8051073815341271</v>
+        <v>0.8051073815341248</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7705630523950794</v>
+        <v>0.7705630523950781</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.859217302217998</v>
+        <v>0.8592173022179929</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5422422668024324</v>
+        <v>0.5422422668024315</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6650778591844676</v>
+        <v>0.6650778591844664</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7814264199168014</v>
+        <v>0.7814264199168006</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5695178607506726</v>
+        <v>0.5695178607506722</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6170839634849327</v>
+        <v>0.6170839634849284</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7388892727148002</v>
+        <v>0.7388892727147983</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4951888189151714</v>
+        <v>0.4951888189151689</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5348123048516218</v>
+        <v>0.5348123048516199</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9859216097640291</v>
+        <v>0.9859216097640255</v>
       </c>
       <c r="H8" t="n">
-        <v>0.748946684195094</v>
+        <v>0.7489466841950905</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6572699068022467</v>
+        <v>0.6572699068022442</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8255244186220901</v>
+        <v>0.8255244186220881</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7639426459573848</v>
+        <v>0.7639426459573804</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8189578409090271</v>
+        <v>0.8189578409090233</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9003299112620294</v>
+        <v>0.9003299112620253</v>
       </c>
       <c r="N8" t="n">
-        <v>4.45754635868574</v>
+        <v>0.6071061106801445</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6068623594819506</v>
+        <v>0.606862359481946</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7392615670625347</v>
+        <v>0.7392615670625332</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4883085452238803</v>
+        <v>0.4883085452238764</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6970289127372227</v>
+        <v>0.6970289127372205</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8223619708677804</v>
+        <v>0.8223619708677773</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6901502307112777</v>
+        <v>0.6901502307112752</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7918673041489833</v>
+        <v>0.7918673041489842</v>
       </c>
       <c r="V8" t="n">
         <v>0.7225867001702155</v>
       </c>
       <c r="W8" t="n">
-        <v>0.959987362791338</v>
+        <v>0.959987362791336</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8002367181612386</v>
+        <v>0.8002367181612352</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.126200559546741</v>
+        <v>1.126200559546737</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5816933632119319</v>
+        <v>0.5816933632119301</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8199355734106822</v>
+        <v>0.8199355734106807</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.054637521616486</v>
+        <v>1.054637521616483</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7638718735692427</v>
+        <v>0.763871873569241</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8012006504656936</v>
+        <v>0.801200650465691</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9230059596955614</v>
+        <v>0.9230059596955574</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7158485857740345</v>
+        <v>0.7158485857740329</v>
       </c>
       <c r="F9" t="n">
-        <v>0.576987661864637</v>
+        <v>0.5769876618646351</v>
       </c>
       <c r="G9" t="n">
-        <v>1.146544421209469</v>
+        <v>1.146544421209466</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9330633711758537</v>
+        <v>0.9330633711758531</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8413865937830095</v>
+        <v>0.8413865937830078</v>
       </c>
       <c r="J9" t="n">
-        <v>1.00964110560285</v>
+        <v>1.009641105602848</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9480593329381443</v>
+        <v>0.9480593329381419</v>
       </c>
       <c r="L9" t="n">
-        <v>1.003074527889788</v>
+        <v>1.003074527889787</v>
       </c>
       <c r="M9" t="n">
-        <v>1.084446598242585</v>
+        <v>1.084446598242581</v>
       </c>
       <c r="N9" t="n">
-        <v>4.45754635868574</v>
+        <v>0.8790507836621957</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8888266654413302</v>
+        <v>0.8888266654413278</v>
       </c>
       <c r="P9" t="n">
-        <v>1.034570398637258</v>
+        <v>1.034570398637255</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8079936589825666</v>
+        <v>0.8079936589825637</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8811455997179832</v>
+        <v>0.8811455997179809</v>
       </c>
       <c r="S9" t="n">
-        <v>1.006478657848539</v>
+        <v>1.006478657848538</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8742669176920393</v>
+        <v>0.874266917692036</v>
       </c>
       <c r="U9" t="n">
-        <v>1.031593835908379</v>
+        <v>1.031593835908376</v>
       </c>
       <c r="V9" t="n">
-        <v>1.056945292185268</v>
+        <v>1.056945292185266</v>
       </c>
       <c r="W9" t="n">
-        <v>1.144081782741103</v>
+        <v>1.144081782741101</v>
       </c>
       <c r="X9" t="n">
-        <v>1.109537453602055</v>
+        <v>1.109537453602051</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.198191703424975</v>
+        <v>1.198191703424973</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.8190778599420504</v>
+        <v>0.8190778599420477</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.004052260391444</v>
+        <v>1.004052260391441</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.120400821123779</v>
+        <v>1.120400821123778</v>
       </c>
     </row>
   </sheetData>
@@ -5098,7 +5098,7 @@
         <v>0.3317541351051891</v>
       </c>
       <c r="N4" t="n">
-        <v>1.691331155839079</v>
+        <v>0.24222476271739</v>
       </c>
       <c r="O4" t="n">
         <v>0.1990637028952031</v>
@@ -5274,7 +5274,7 @@
         <v>0.4048545964802611</v>
       </c>
       <c r="N6" t="n">
-        <v>1.691331155839079</v>
+        <v>0.2576771052945594</v>
       </c>
       <c r="O6" t="n">
         <v>0.2780606642931328</v>
@@ -5362,7 +5362,7 @@
         <v>0.4220012203806591</v>
       </c>
       <c r="N7" t="n">
-        <v>1.691331155839079</v>
+        <v>0.3324718479928603</v>
       </c>
       <c r="O7" t="n">
         <v>0.2889531872991537</v>
@@ -5450,7 +5450,7 @@
         <v>0.5435517136526616</v>
       </c>
       <c r="N8" t="n">
-        <v>1.691331155839079</v>
+        <v>0.3813758021183459</v>
       </c>
       <c r="O8" t="n">
         <v>0.3581786420147626</v>
@@ -5538,7 +5538,7 @@
         <v>0.7103585909860453</v>
       </c>
       <c r="N9" t="n">
-        <v>1.691331155839079</v>
+        <v>0.6208292185982461</v>
       </c>
       <c r="O9" t="n">
         <v>0.6069618841340646</v>
@@ -5809,7 +5809,7 @@
         <v>2.902685007949389</v>
       </c>
       <c r="W2" t="n">
-        <v>3.65529691153037</v>
+        <v>3.655296911530369</v>
       </c>
       <c r="X2" t="n">
         <v>2.938112210274757</v>
@@ -5958,7 +5958,7 @@
         <v>0.1414742781592483</v>
       </c>
       <c r="N4" t="n">
-        <v>1.527690475611856</v>
+        <v>0.224032542418378</v>
       </c>
       <c r="O4" t="n">
         <v>0.1461283222226495</v>
@@ -6034,7 +6034,7 @@
         <v>0.118516318844847</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8235873217233159</v>
+        <v>0.8235873217233158</v>
       </c>
       <c r="K5" t="n">
         <v>0.01569835881204307</v>
@@ -6064,7 +6064,7 @@
         <v>-0.1693543144540846</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6619669004124539</v>
+        <v>-0.6619669004124541</v>
       </c>
       <c r="U5" t="n">
         <v>0.5581983248899463</v>
@@ -6119,7 +6119,7 @@
         <v>0.2311486357102975</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1933781674583297</v>
+        <v>0.1933781674583298</v>
       </c>
       <c r="J6" t="n">
         <v>0.2381605766736878</v>
@@ -6134,13 +6134,13 @@
         <v>0.1930415477330304</v>
       </c>
       <c r="N6" t="n">
-        <v>1.527690475611856</v>
+        <v>0.2315830583589296</v>
       </c>
       <c r="O6" t="n">
         <v>0.2027071176766492</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05401769721940876</v>
+        <v>0.05401769721940872</v>
       </c>
       <c r="Q6" t="n">
         <v>0.2093437406994041</v>
@@ -6189,13 +6189,13 @@
         <v>0.1216729149297804</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2481916295323058</v>
+        <v>0.2481916295323057</v>
       </c>
       <c r="D7" t="n">
         <v>0.2536647034336234</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04055109832677881</v>
+        <v>0.04055109832677876</v>
       </c>
       <c r="F7" t="n">
         <v>0.08256434531173819</v>
@@ -6219,16 +6219,16 @@
         <v>0.03997489755752823</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2162913414615454</v>
+        <v>0.2162913414615455</v>
       </c>
       <c r="N7" t="n">
-        <v>1.527690475611856</v>
+        <v>0.2988496057206765</v>
       </c>
       <c r="O7" t="n">
         <v>0.220612274714921</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1225142941901688</v>
+        <v>0.1225142941901689</v>
       </c>
       <c r="Q7" t="n">
         <v>0.2325935344279199</v>
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1371800263840397</v>
+        <v>0.1371800263840396</v>
       </c>
       <c r="C8" t="n">
         <v>0.3349918164363931</v>
@@ -6283,7 +6283,7 @@
         <v>0.3404648903377097</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08938982556443745</v>
+        <v>0.08938982556443742</v>
       </c>
       <c r="F8" t="n">
         <v>0.1091780847020447</v>
@@ -6307,10 +6307,10 @@
         <v>0.1267750844616161</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3030915283655542</v>
+        <v>0.3030915283655543</v>
       </c>
       <c r="N8" t="n">
-        <v>1.527690475611856</v>
+        <v>0.3303857320817539</v>
       </c>
       <c r="O8" t="n">
         <v>0.2676685555799957</v>
@@ -6322,7 +6322,7 @@
         <v>0.2340899293665713</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.04649233458684229</v>
+        <v>-0.04649233458684224</v>
       </c>
       <c r="S8" t="n">
         <v>0.2825518299341981</v>
@@ -6331,7 +6331,7 @@
         <v>0.2572300155594371</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2955232504299802</v>
+        <v>0.2955232504299801</v>
       </c>
       <c r="V8" t="n">
         <v>0.3277125465847797</v>
@@ -6395,19 +6395,19 @@
         <v>0.2561050124277415</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4324214563317587</v>
+        <v>0.4324214563317586</v>
       </c>
       <c r="N9" t="n">
-        <v>1.527690475611856</v>
+        <v>0.5149797205908889</v>
       </c>
       <c r="O9" t="n">
         <v>0.4595348605922219</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3663214015271641</v>
+        <v>0.366321401527164</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4487236678993223</v>
+        <v>0.4487236678993222</v>
       </c>
       <c r="R9" t="n">
         <v>0.08283759337928386</v>
@@ -6818,7 +6818,7 @@
         <v>0.1564721564489442</v>
       </c>
       <c r="N4" t="n">
-        <v>1.795835503947679</v>
+        <v>0.2329230942787951</v>
       </c>
       <c r="O4" t="n">
         <v>0.06829204497842767</v>
@@ -6994,7 +6994,7 @@
         <v>0.2025989484162665</v>
       </c>
       <c r="N6" t="n">
-        <v>1.795835503947679</v>
+        <v>0.2393970495573405</v>
       </c>
       <c r="O6" t="n">
         <v>0.07488006519937355</v>
@@ -7082,7 +7082,7 @@
         <v>0.2281829521606275</v>
       </c>
       <c r="N7" t="n">
-        <v>1.795835503947679</v>
+        <v>0.3046338899904782</v>
       </c>
       <c r="O7" t="n">
         <v>0.1396698927043497</v>
@@ -7170,7 +7170,7 @@
         <v>0.306055067139949</v>
       </c>
       <c r="N8" t="n">
-        <v>1.795835503947679</v>
+        <v>0.3315429282658818</v>
       </c>
       <c r="O8" t="n">
         <v>0.1809169749687997</v>
@@ -7258,7 +7258,7 @@
         <v>0.4195526579477167</v>
       </c>
       <c r="N9" t="n">
-        <v>1.795835503947679</v>
+        <v>0.4960035957775669</v>
       </c>
       <c r="O9" t="n">
         <v>0.3516699058949279</v>
@@ -7678,7 +7678,7 @@
         <v>0.7282308046696757</v>
       </c>
       <c r="N4" t="n">
-        <v>4.709786997503773</v>
+        <v>0.4298793844528412</v>
       </c>
       <c r="O4" t="n">
         <v>0.3879327268849848</v>
@@ -7766,7 +7766,7 @@
         <v>10.06394527642067</v>
       </c>
       <c r="N5" t="n">
-        <v>4.709786997503774</v>
+        <v>4.709786997503773</v>
       </c>
       <c r="O5" t="n">
         <v>3.432157660367561</v>
@@ -7854,7 +7854,7 @@
         <v>0.749688145336339</v>
       </c>
       <c r="N6" t="n">
-        <v>4.709786997503774</v>
+        <v>0.4521286724091398</v>
       </c>
       <c r="O6" t="n">
         <v>0.5053306150209532</v>
@@ -7942,7 +7942,7 @@
         <v>0.8379032537139512</v>
       </c>
       <c r="N7" t="n">
-        <v>4.709786997503774</v>
+        <v>0.5395518334971173</v>
       </c>
       <c r="O7" t="n">
         <v>0.4972465095798479</v>
@@ -8030,7 +8030,7 @@
         <v>1.00534909234617</v>
       </c>
       <c r="N8" t="n">
-        <v>4.709786997503774</v>
+        <v>0.6121225064182438</v>
       </c>
       <c r="O8" t="n">
         <v>0.5962483681372865</v>
@@ -8118,7 +8118,7 @@
         <v>1.262460265374642</v>
       </c>
       <c r="N9" t="n">
-        <v>4.709786997503774</v>
+        <v>0.9641088451578044</v>
       </c>
       <c r="O9" t="n">
         <v>0.9632382586318318</v>
@@ -8538,7 +8538,7 @@
         <v>0.1784437064006704</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7345620924510728</v>
+        <v>0.2014002281762152</v>
       </c>
       <c r="O4" t="n">
         <v>0.1270765482715513</v>
@@ -8714,7 +8714,7 @@
         <v>0.1903884460200657</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7345620924510728</v>
+        <v>0.2139078104301517</v>
       </c>
       <c r="O6" t="n">
         <v>0.2136480682699015</v>
@@ -8802,7 +8802,7 @@
         <v>0.2655482493816264</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7345620924510728</v>
+        <v>0.2885047711571713</v>
       </c>
       <c r="O7" t="n">
         <v>0.2138473416176258</v>
@@ -8890,7 +8890,7 @@
         <v>0.3851891713092128</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7345620924510728</v>
+        <v>0.3371131356454451</v>
       </c>
       <c r="O8" t="n">
         <v>0.2823098192754733</v>
@@ -8978,7 +8978,7 @@
         <v>0.5747011600821709</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7345620924510728</v>
+        <v>0.5976576818577144</v>
       </c>
       <c r="O9" t="n">
         <v>0.553873151142352</v>

--- a/Results/GWP 20a/ammonia climate change GWP 20a results.xlsx
+++ b/Results/GWP 20a/ammonia climate change GWP 20a results.xlsx
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.021656197814499</v>
+        <v>3.0216561978145</v>
       </c>
       <c r="C2" t="n">
-        <v>2.990294444143725</v>
+        <v>2.990294444143726</v>
       </c>
       <c r="D2" t="n">
-        <v>3.013562111128056</v>
+        <v>3.013562111128057</v>
       </c>
       <c r="E2" t="n">
         <v>2.998547279545932</v>
@@ -601,16 +601,16 @@
         <v>3.008033671275108</v>
       </c>
       <c r="G2" t="n">
-        <v>3.043686510404564</v>
+        <v>3.043686510404566</v>
       </c>
       <c r="H2" t="n">
-        <v>3.02542837380971</v>
+        <v>3.025428373809711</v>
       </c>
       <c r="I2" t="n">
         <v>3.008033374849211</v>
       </c>
       <c r="J2" t="n">
-        <v>3.026265335594323</v>
+        <v>3.026265335594324</v>
       </c>
       <c r="K2" t="n">
         <v>3.020638057206735</v>
@@ -625,37 +625,37 @@
         <v>3.023165969923934</v>
       </c>
       <c r="O2" t="n">
-        <v>3.423962681930253</v>
+        <v>3.423962681930254</v>
       </c>
       <c r="P2" t="n">
         <v>3.017033405321013</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.013290768256203</v>
+        <v>3.013290768256204</v>
       </c>
       <c r="R2" t="n">
-        <v>3.011682434958633</v>
+        <v>3.011682434958634</v>
       </c>
       <c r="S2" t="n">
-        <v>3.027774768314989</v>
+        <v>3.02777476831499</v>
       </c>
       <c r="T2" t="n">
-        <v>3.018495970827866</v>
+        <v>3.018495970827867</v>
       </c>
       <c r="U2" t="n">
-        <v>3.811105528853037</v>
+        <v>3.81110552885304</v>
       </c>
       <c r="V2" t="n">
-        <v>3.005940363512868</v>
+        <v>3.005940363512869</v>
       </c>
       <c r="W2" t="n">
-        <v>3.803828229622847</v>
+        <v>3.803828229622849</v>
       </c>
       <c r="X2" t="n">
-        <v>3.017543724398143</v>
+        <v>3.017543724398144</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.016275928968209</v>
+        <v>3.01627592896821</v>
       </c>
       <c r="Z2" t="n">
         <v>3.302028923329102</v>
@@ -664,7 +664,7 @@
         <v>3.027793500319067</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.038755485686222</v>
+        <v>3.038755485686223</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.2693315324409</v>
+        <v>1.13291875353647</v>
       </c>
       <c r="C3" t="n">
-        <v>2.09797438859193</v>
+        <v>0.9560946124296377</v>
       </c>
       <c r="D3" t="n">
-        <v>2.21309155714096</v>
+        <v>1.07475792037788</v>
       </c>
       <c r="E3" t="n">
-        <v>2.105353223169212</v>
+        <v>0.9631745309883415</v>
       </c>
       <c r="F3" t="n">
-        <v>2.173723984093964</v>
+        <v>1.034012330374716</v>
       </c>
       <c r="G3" t="n">
-        <v>2.426518956858908</v>
+        <v>1.295622196459664</v>
       </c>
       <c r="H3" t="n">
-        <v>2.298716491675436</v>
+        <v>1.163461963254201</v>
       </c>
       <c r="I3" t="n">
-        <v>2.173615479683216</v>
+        <v>1.033887775902341</v>
       </c>
       <c r="J3" t="n">
-        <v>2.302875958330982</v>
+        <v>1.167664076494713</v>
       </c>
       <c r="K3" t="n">
-        <v>2.263631261595486</v>
+        <v>1.127082481908785</v>
       </c>
       <c r="L3" t="n">
-        <v>2.36537459308628</v>
+        <v>1.232370553184512</v>
       </c>
       <c r="M3" t="n">
-        <v>2.41990464709705</v>
+        <v>1.288969848645326</v>
       </c>
       <c r="N3" t="n">
-        <v>2.28140146745713</v>
+        <v>1.145468210424772</v>
       </c>
       <c r="O3" t="n">
-        <v>2.932600030672214</v>
+        <v>1.796153772766886</v>
       </c>
       <c r="P3" t="n">
-        <v>2.23664288047961</v>
+        <v>1.099059582433871</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.210917486873511</v>
+        <v>1.072498086884079</v>
       </c>
       <c r="R3" t="n">
-        <v>2.199892811157569</v>
+        <v>1.061106384615475</v>
       </c>
       <c r="S3" t="n">
-        <v>2.313289608281259</v>
+        <v>1.17843800779039</v>
       </c>
       <c r="T3" t="n">
-        <v>2.248463701100079</v>
+        <v>1.111388001252483</v>
       </c>
       <c r="U3" t="n">
-        <v>3.645532273741522</v>
+        <v>2.512484382793056</v>
       </c>
       <c r="V3" t="n">
-        <v>2.157682038125785</v>
+        <v>1.017347540883103</v>
       </c>
       <c r="W3" t="n">
-        <v>3.617046871262525</v>
+        <v>2.483254892431334</v>
       </c>
       <c r="X3" t="n">
-        <v>2.241426664106751</v>
+        <v>1.104096720258496</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.231956451232772</v>
+        <v>1.094268301594555</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.698028233452128</v>
+        <v>1.56004772919405</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.31427983867396</v>
+        <v>1.179490903185005</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.393248977335215</v>
+        <v>1.261268885008348</v>
       </c>
     </row>
     <row r="4">
@@ -762,82 +762,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6113385048333252</v>
+        <v>0.6113385048333229</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3623375886307807</v>
+        <v>0.3623375886307789</v>
       </c>
       <c r="D4" t="n">
-        <v>0.519912072246088</v>
+        <v>0.519912072246086</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3503126423622508</v>
+        <v>0.3503126423622483</v>
       </c>
       <c r="F4" t="n">
-        <v>0.457465800899071</v>
+        <v>0.4574658008990709</v>
       </c>
       <c r="G4" t="n">
-        <v>0.860181019982599</v>
+        <v>0.8601810199826004</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6539469679859107</v>
+        <v>0.6539469679859088</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4574624526322028</v>
+        <v>0.4574624526322006</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6629779086338536</v>
+        <v>0.6629779086338531</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5998381383007881</v>
+        <v>0.5998381383007875</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7619305203801505</v>
+        <v>0.7619305203801512</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8466439318651791</v>
+        <v>0.8466439318651761</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6283920753388644</v>
+        <v>0.6283920753388641</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6102474429785583</v>
+        <v>0.6102474429785578</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5591219370297758</v>
+        <v>0.5591219370297751</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5168471296846305</v>
+        <v>0.5168471296846304</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4986802652187046</v>
+        <v>0.4986802652187025</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6804505733178547</v>
+        <v>0.6804505733178563</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5756422872430593</v>
+        <v>0.5756422872430575</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7563975770307411</v>
+        <v>0.7563975770307401</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4309819820027431</v>
+        <v>0.4309819820027433</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7257167582296326</v>
+        <v>0.7257167582296321</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5648862257643403</v>
+        <v>0.564886225764339</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5464653459179989</v>
+        <v>0.5464653459179986</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.5401614838515232</v>
+        <v>0.5401614838515231</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.6806621599210259</v>
+        <v>0.6806621599210254</v>
       </c>
       <c r="AB4" t="n">
         <v>0.802392178718632</v>
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.464412217651067</v>
+        <v>7.464412217651007</v>
       </c>
       <c r="C5" t="n">
-        <v>3.137465823121525</v>
+        <v>3.137465823121524</v>
       </c>
       <c r="D5" t="n">
-        <v>6.531402232082055</v>
+        <v>6.531402232082029</v>
       </c>
       <c r="E5" t="n">
-        <v>2.773253748915252</v>
+        <v>2.773253748915251</v>
       </c>
       <c r="F5" t="n">
-        <v>5.326871437734455</v>
+        <v>5.326871437734459</v>
       </c>
       <c r="G5" t="n">
-        <v>12.44940504663688</v>
+        <v>12.44940504663691</v>
       </c>
       <c r="H5" t="n">
-        <v>9.786190421937727</v>
+        <v>9.786190421937725</v>
       </c>
       <c r="I5" t="n">
-        <v>5.263571855869501</v>
+        <v>5.263571855869505</v>
       </c>
       <c r="J5" t="n">
-        <v>8.898014737975435</v>
+        <v>8.898014737975439</v>
       </c>
       <c r="K5" t="n">
-        <v>8.16371946547844</v>
+        <v>8.163719465478433</v>
       </c>
       <c r="L5" t="n">
-        <v>11.02676518865526</v>
+        <v>11.02676518865525</v>
       </c>
       <c r="M5" t="n">
-        <v>13.65220989811076</v>
+        <v>13.65220989811075</v>
       </c>
       <c r="N5" t="n">
-        <v>8.577289212489287</v>
+        <v>8.57728921248928</v>
       </c>
       <c r="O5" t="n">
-        <v>7.274798491624944</v>
+        <v>7.274798491624917</v>
       </c>
       <c r="P5" t="n">
-        <v>6.593831746723421</v>
+        <v>6.593831746723427</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.328533128992754</v>
+        <v>6.328533128992757</v>
       </c>
       <c r="R5" t="n">
-        <v>6.232573399717013</v>
+        <v>6.232573399717012</v>
       </c>
       <c r="S5" t="n">
-        <v>9.028264567382857</v>
+        <v>9.028264567382877</v>
       </c>
       <c r="T5" t="n">
-        <v>7.748155616066336</v>
+        <v>7.748155616066326</v>
       </c>
       <c r="U5" t="n">
-        <v>10.78643335937785</v>
+        <v>10.78643335937784</v>
       </c>
       <c r="V5" t="n">
-        <v>4.192959197089943</v>
+        <v>4.192959197089945</v>
       </c>
       <c r="W5" t="n">
-        <v>10.38708723678071</v>
+        <v>10.3870872367807</v>
       </c>
       <c r="X5" t="n">
-        <v>7.388428249867992</v>
+        <v>7.388428249867979</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.849295162460468</v>
+        <v>6.849295162460459</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.305583513074324</v>
+        <v>6.305583513074321</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.541609259071102</v>
+        <v>9.541609259071119</v>
       </c>
       <c r="AB5" t="n">
-        <v>13.10370714940658</v>
+        <v>13.1037071494066</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6419605382443014</v>
+        <v>0.6419605382443024</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5029334657543124</v>
+        <v>0.5029334657543134</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6605079493696188</v>
+        <v>0.6605079493696202</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4909085194857825</v>
+        <v>0.4909085194857833</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4880878343100476</v>
+        <v>0.4880878343100475</v>
       </c>
       <c r="G6" t="n">
         <v>1.000776897106131</v>
       </c>
       <c r="H6" t="n">
-        <v>0.794542845109442</v>
+        <v>0.7945428451094432</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4880844860431799</v>
+        <v>0.4880844860431789</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6935999420448317</v>
+        <v>0.6935999420448309</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7404340154243185</v>
+        <v>0.7404340154243182</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9025263975036844</v>
+        <v>0.9025263975036896</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9872398089887113</v>
+        <v>0.9872398089887114</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6603263987140341</v>
+        <v>0.6603263987140247</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6421816480633417</v>
+        <v>0.642181648063334</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7054331848575101</v>
+        <v>0.7054331848575087</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6574430068081611</v>
+        <v>0.6574430068081628</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6392761423422357</v>
+        <v>0.6392761423422372</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7110726067288332</v>
+        <v>0.7110726067288337</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6062643206540368</v>
+        <v>0.6062643206540361</v>
       </c>
       <c r="U6" t="n">
-        <v>0.791120157692223</v>
+        <v>0.7911201576922223</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5715778591262743</v>
+        <v>0.571577859126275</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8720277247326875</v>
+        <v>0.8720277247326864</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7054821028878709</v>
+        <v>0.7054821028878684</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5849778290399469</v>
+        <v>0.5849778290399522</v>
       </c>
       <c r="Z6" t="n">
         <v>0.5707835172625009</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.8212580370445577</v>
+        <v>0.8212580370445546</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8359007928104447</v>
+        <v>0.8359007928104443</v>
       </c>
     </row>
     <row r="7">
@@ -1026,82 +1026,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7449957629758297</v>
+        <v>0.7449957629758284</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4959948467732861</v>
+        <v>0.4959948467732844</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6535693303885931</v>
+        <v>0.65356933038859</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4839699005047554</v>
+        <v>0.4839699005047533</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5911230590415762</v>
+        <v>0.5911230590415735</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9938382781251056</v>
+        <v>0.9938382781251068</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7876042261284163</v>
+        <v>0.787604226128414</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5911197107747074</v>
+        <v>0.5911197107747055</v>
       </c>
       <c r="J7" t="n">
-        <v>0.796635166776359</v>
+        <v>0.7966351667763582</v>
       </c>
       <c r="K7" t="n">
-        <v>0.733495396443291</v>
+        <v>0.7334953964432906</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8955877785226594</v>
+        <v>0.895587778522658</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9803011900076839</v>
+        <v>0.9803011900076801</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7620493334813696</v>
+        <v>0.7620493334813684</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7435207789030881</v>
+        <v>0.7435207789030874</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6923952729543075</v>
+        <v>0.6923952729543069</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6505043878271354</v>
+        <v>0.6505043878271347</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6323375233612102</v>
+        <v>0.6323375233612077</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8141078314603618</v>
+        <v>0.8141078314603621</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7092995453855655</v>
+        <v>0.7092995453855634</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8939451476123389</v>
+        <v>0.8939451476123396</v>
       </c>
       <c r="V7" t="n">
-        <v>0.564639240145248</v>
+        <v>0.5646392401452481</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8593740163721388</v>
+        <v>0.8593740163721371</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6985434839068453</v>
+        <v>0.6985434839068433</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.68422315131101</v>
+        <v>0.6842231513110089</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6738187419940284</v>
+        <v>0.6738187419940279</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.8143194180635319</v>
+        <v>0.8143194180635309</v>
       </c>
       <c r="AB7" t="n">
         <v>0.9360494368611388</v>
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8058249743073772</v>
+        <v>0.8058249743073771</v>
       </c>
       <c r="C8" t="n">
-        <v>0.709985750853858</v>
+        <v>0.7099857508538583</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8675602344691647</v>
+        <v>0.8675602344691645</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6164067212050626</v>
+        <v>0.6164067212050631</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6758130720523639</v>
+        <v>0.675813072052364</v>
       </c>
       <c r="G8" t="n">
-        <v>1.239588256945315</v>
+        <v>1.239588256945317</v>
       </c>
       <c r="H8" t="n">
-        <v>1.001595130208988</v>
+        <v>1.001595130208989</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8051106148552806</v>
+        <v>0.8051106148552811</v>
       </c>
       <c r="J8" t="n">
-        <v>1.010626070856931</v>
+        <v>1.010626070856932</v>
       </c>
       <c r="K8" t="n">
-        <v>0.947486300523865</v>
+        <v>0.9474863005238645</v>
       </c>
       <c r="L8" t="n">
-        <v>1.10957868260323</v>
+        <v>1.109578682603231</v>
       </c>
       <c r="M8" t="n">
-        <v>1.194292094088296</v>
+        <v>1.194292094088295</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8573143022612257</v>
+        <v>0.8573143022612246</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8717965877469442</v>
+        <v>0.8717965877469449</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8126734358630551</v>
+        <v>0.8126734358630539</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6812338308166833</v>
+        <v>0.6812338308166823</v>
       </c>
       <c r="R8" t="n">
-        <v>0.846328427441782</v>
+        <v>0.8463284274417815</v>
       </c>
       <c r="S8" t="n">
-        <v>1.028098735540933</v>
+        <v>1.028098735540931</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9232904494661359</v>
+        <v>0.9232904494661368</v>
       </c>
       <c r="U8" t="n">
-        <v>1.033524711912934</v>
+        <v>1.033524711912935</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7369172078316127</v>
+        <v>0.7369172078316137</v>
       </c>
       <c r="W8" t="n">
         <v>1.073395021008148</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7433105003089306</v>
+        <v>0.7433105003089304</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.050729507663333</v>
+        <v>1.050729507663332</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.7318028962582753</v>
+        <v>0.7318028962582762</v>
       </c>
       <c r="AA8" t="n">
         <v>1.028310322144103</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.310030536092411</v>
+        <v>1.310030536092412</v>
       </c>
     </row>
     <row r="9">
@@ -1202,79 +1202,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.157690312372139</v>
+        <v>1.157690312372141</v>
       </c>
       <c r="C9" t="n">
-        <v>1.072663667177529</v>
+        <v>1.07266366717753</v>
       </c>
       <c r="D9" t="n">
-        <v>1.230238150792836</v>
+        <v>1.230238150792835</v>
       </c>
       <c r="E9" t="n">
-        <v>1.022794163500455</v>
+        <v>1.022794163500453</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7897863717055157</v>
+        <v>0.7897863717055146</v>
       </c>
       <c r="G9" t="n">
-        <v>1.570507144682529</v>
+        <v>1.570507144682532</v>
       </c>
       <c r="H9" t="n">
-        <v>1.364273046532659</v>
+        <v>1.36427304653266</v>
       </c>
       <c r="I9" t="n">
         <v>1.16778853117895</v>
       </c>
       <c r="J9" t="n">
-        <v>1.373303987180602</v>
+        <v>1.373303987180603</v>
       </c>
       <c r="K9" t="n">
-        <v>1.310164216847536</v>
+        <v>1.310164216847537</v>
       </c>
       <c r="L9" t="n">
-        <v>1.472256598926904</v>
+        <v>1.472256598926902</v>
       </c>
       <c r="M9" t="n">
-        <v>1.556970010411926</v>
+        <v>1.556970010411925</v>
       </c>
       <c r="N9" t="n">
-        <v>1.33871815388561</v>
+        <v>1.338718153885611</v>
       </c>
       <c r="O9" t="n">
-        <v>1.374914441679641</v>
+        <v>1.374914441679643</v>
       </c>
       <c r="P9" t="n">
-        <v>1.335607143493726</v>
+        <v>1.335607143493727</v>
       </c>
       <c r="Q9" t="n">
         <v>1.227173254384559</v>
       </c>
       <c r="R9" t="n">
-        <v>1.209006343765453</v>
+        <v>1.209006343765454</v>
       </c>
       <c r="S9" t="n">
-        <v>1.390776651864605</v>
+        <v>1.390776651864604</v>
       </c>
       <c r="T9" t="n">
         <v>1.285968365789808</v>
       </c>
       <c r="U9" t="n">
-        <v>1.470824202827996</v>
+        <v>1.470824202827994</v>
       </c>
       <c r="V9" t="n">
-        <v>1.330530713038095</v>
+        <v>1.330530713038097</v>
       </c>
       <c r="W9" t="n">
-        <v>1.43604283677638</v>
+        <v>1.436042836776382</v>
       </c>
       <c r="X9" t="n">
         <v>1.275212304311087</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.260891971715253</v>
+        <v>1.260891971715256</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.1516256764685</v>
+        <v>1.151625676468501</v>
       </c>
       <c r="AA9" t="n">
         <v>1.390988238467776</v>
@@ -1449,16 +1449,16 @@
         <v>2.903115089151721</v>
       </c>
       <c r="C2" t="n">
-        <v>2.891329516011936</v>
+        <v>2.891329516011935</v>
       </c>
       <c r="D2" t="n">
-        <v>2.907253358233416</v>
+        <v>2.907253358233415</v>
       </c>
       <c r="E2" t="n">
-        <v>2.904533793437152</v>
+        <v>2.904533793437154</v>
       </c>
       <c r="F2" t="n">
-        <v>2.89399021661554</v>
+        <v>2.893990216615541</v>
       </c>
       <c r="G2" t="n">
         <v>2.911469764306843</v>
@@ -1485,7 +1485,7 @@
         <v>2.905174276275956</v>
       </c>
       <c r="O2" t="n">
-        <v>3.230293806837829</v>
+        <v>3.230293806837828</v>
       </c>
       <c r="P2" t="n">
         <v>2.903760606392615</v>
@@ -1500,10 +1500,10 @@
         <v>2.89622987416129</v>
       </c>
       <c r="T2" t="n">
-        <v>2.899794274173982</v>
+        <v>2.899794274173983</v>
       </c>
       <c r="U2" t="n">
-        <v>3.661644811648771</v>
+        <v>3.661644811648772</v>
       </c>
       <c r="V2" t="n">
         <v>2.914622640560661</v>
@@ -1512,13 +1512,13 @@
         <v>3.682885456740803</v>
       </c>
       <c r="X2" t="n">
-        <v>2.949547752198361</v>
+        <v>2.949547752198363</v>
       </c>
       <c r="Y2" t="n">
         <v>2.930019756289362</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.177219907831197</v>
+        <v>3.177219907831198</v>
       </c>
       <c r="AA2" t="n">
         <v>2.941660844722038</v>
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.945769235553029</v>
+        <v>0.8000594107493023</v>
       </c>
       <c r="C3" t="n">
-        <v>1.935052889057939</v>
+        <v>0.7897408142869395</v>
       </c>
       <c r="D3" t="n">
-        <v>1.975228660810013</v>
+        <v>0.8305609137731009</v>
       </c>
       <c r="E3" t="n">
-        <v>1.955871429804852</v>
+        <v>0.8105112419257116</v>
       </c>
       <c r="F3" t="n">
-        <v>1.880483553557065</v>
+        <v>0.7324336232928077</v>
       </c>
       <c r="G3" t="n">
-        <v>2.005049709999233</v>
+        <v>0.8614296287220006</v>
       </c>
       <c r="H3" t="n">
-        <v>2.008832035827103</v>
+        <v>0.8653646632492248</v>
       </c>
       <c r="I3" t="n">
-        <v>1.966008903708877</v>
+        <v>0.8210133024274079</v>
       </c>
       <c r="J3" t="n">
-        <v>1.984297400381794</v>
+        <v>0.8399442839837983</v>
       </c>
       <c r="K3" t="n">
-        <v>1.969113524155323</v>
+        <v>0.824227744048615</v>
       </c>
       <c r="L3" t="n">
-        <v>1.803677147266935</v>
+        <v>0.6529271982473178</v>
       </c>
       <c r="M3" t="n">
-        <v>1.948802255258511</v>
+        <v>0.803217609001206</v>
       </c>
       <c r="N3" t="n">
-        <v>1.960367357224314</v>
+        <v>0.8151718519800437</v>
       </c>
       <c r="O3" t="n">
-        <v>2.453738745888045</v>
+        <v>1.306554102363379</v>
       </c>
       <c r="P3" t="n">
-        <v>1.950369271488965</v>
+        <v>0.8048216338471984</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.9701567666677</v>
+        <v>0.8253084509415137</v>
       </c>
       <c r="R3" t="n">
-        <v>1.726932692135383</v>
+        <v>0.5734278834201708</v>
       </c>
       <c r="S3" t="n">
-        <v>1.89693133195673</v>
+        <v>0.7494929468933528</v>
       </c>
       <c r="T3" t="n">
-        <v>1.921883047811062</v>
+        <v>0.7753202532459934</v>
       </c>
       <c r="U3" t="n">
-        <v>3.240462133787953</v>
+        <v>2.096710729898431</v>
       </c>
       <c r="V3" t="n">
-        <v>2.027440232239305</v>
+        <v>0.8846114947194921</v>
       </c>
       <c r="W3" t="n">
-        <v>3.436204478737115</v>
+        <v>2.299834259739151</v>
       </c>
       <c r="X3" t="n">
-        <v>2.276648344451268</v>
+        <v>1.14270999139709</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.137854389035995</v>
+        <v>0.998930809027579</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.449910540194059</v>
+        <v>1.306579479316689</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.220943964422077</v>
+        <v>1.084951636188002</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.976279220727342</v>
+        <v>0.831647293926183</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1268640646573685</v>
+        <v>0.1268640646573686</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1449388474923759</v>
+        <v>0.1449388474923765</v>
       </c>
       <c r="D4" t="n">
-        <v>0.17360771763294</v>
+        <v>0.1736077176329409</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1428889821975032</v>
+        <v>0.1428889821975028</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02379443171244246</v>
+        <v>0.023794431712441</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2212339638749498</v>
+        <v>0.2212339638749489</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2264973959431189</v>
+        <v>0.2264973959431205</v>
       </c>
       <c r="I4" t="n">
-        <v>0.15901171612422</v>
+        <v>0.1590117161242212</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1879231963362563</v>
+        <v>0.1879231963362555</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1639258963115313</v>
+        <v>0.1639258963115315</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.09924531749660587</v>
+        <v>-0.09924531749660517</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1328967606241638</v>
+        <v>0.1328967606241632</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1501235304984708</v>
+        <v>0.1501235304984723</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06013604520329613</v>
+        <v>0.06013604520329749</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1341554788458513</v>
+        <v>0.1341554788458501</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1656099386507632</v>
+        <v>0.1656099386507617</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2180095404541155</v>
+        <v>-0.2180095404541127</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04909239398504364</v>
+        <v>0.04909239398504511</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08935393183342778</v>
+        <v>0.08935393183342763</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2119778116232794</v>
+        <v>0.2119778116232786</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2553828377565925</v>
+        <v>0.2553828377565918</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5456531194033222</v>
+        <v>0.5456531194033217</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6513423538494665</v>
+        <v>0.6513423538494651</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4277362450034117</v>
+        <v>0.4277362450034127</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2342384791192201</v>
+        <v>0.2342384791192196</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5622561057477019</v>
+        <v>0.5622561057477028</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.175195950253082</v>
+        <v>0.1751959502530809</v>
       </c>
     </row>
     <row r="5">
@@ -1710,82 +1710,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.2514907503222391</v>
+        <v>-0.2514907503222407</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03946072971444503</v>
+        <v>0.03946072971444536</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5360662237733775</v>
+        <v>0.5360662237733799</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01992963354111418</v>
+        <v>0.01992963354111577</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.157887581973995</v>
+        <v>-2.157887581973993</v>
       </c>
       <c r="G5" t="n">
-        <v>1.237638646853148</v>
+        <v>1.237638646853155</v>
       </c>
       <c r="H5" t="n">
-        <v>1.567362888240544</v>
+        <v>1.567362888240543</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2793337643899575</v>
+        <v>0.2793337643899576</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7333140142083872</v>
+        <v>0.7333140142083875</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3660365998761232</v>
+        <v>0.3660365998761215</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.848780082533287</v>
+        <v>-3.84878008253329</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1788338821872807</v>
+        <v>-0.1788338821872795</v>
       </c>
       <c r="N5" t="n">
-        <v>0.108898240801468</v>
+        <v>0.1088982408014689</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.270054013920114</v>
+        <v>-1.270054013920115</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1261849897924988</v>
+        <v>-0.1261849897925002</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3850313783336482</v>
+        <v>0.3850313783336493</v>
       </c>
       <c r="R5" t="n">
         <v>-6.831930301782332</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.470393719131219</v>
+        <v>-1.470393719131216</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.010980424405638</v>
+        <v>-1.01098042440564</v>
       </c>
       <c r="U5" t="n">
-        <v>1.153081973896082</v>
+        <v>1.153081973896085</v>
       </c>
       <c r="V5" t="n">
-        <v>1.80816001368137</v>
+        <v>1.808160013681368</v>
       </c>
       <c r="W5" t="n">
-        <v>7.087936396889164</v>
+        <v>7.087936396889136</v>
       </c>
       <c r="X5" t="n">
-        <v>8.758860755718535</v>
+        <v>8.758860755718548</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.157282433234673</v>
+        <v>5.157282433234684</v>
       </c>
       <c r="Z5" t="n">
         <v>1.402912495413217</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.486318457948347</v>
+        <v>7.486318457948368</v>
       </c>
       <c r="AB5" t="n">
         <v>0.5913322134008405</v>
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1398699452092708</v>
+        <v>0.1398699452092711</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2038637592206868</v>
+        <v>0.2038637592206878</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1866135981848452</v>
+        <v>0.186613598184844</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2018138939258146</v>
+        <v>0.201813893925813</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08271934344075231</v>
+        <v>0.08271934344075287</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2342398444268542</v>
+        <v>0.2342398444268544</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2395032764950234</v>
+        <v>0.239503276495025</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1720175966761242</v>
+        <v>0.1720175966761248</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2468481080645667</v>
+        <v>0.2468481080645661</v>
       </c>
       <c r="K6" t="n">
         <v>0.1769317768634353</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.04032040576829496</v>
+        <v>-0.04032040576829343</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1459026411760664</v>
+        <v>0.1459026411760665</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1634898595958399</v>
+        <v>0.1634898595958411</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1241720399831645</v>
+        <v>0.1241720399831643</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1454034769680233</v>
+        <v>0.1454034769680226</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1786158192026651</v>
+        <v>0.1786158192026654</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.2050036599022104</v>
+        <v>-0.2050036599022106</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1080173057133529</v>
+        <v>0.1080173057133522</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1023598123853315</v>
+        <v>0.1023598123853319</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2739311350835614</v>
+        <v>0.2739311350835623</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2683887183084959</v>
+        <v>0.2683887183084952</v>
       </c>
       <c r="W6" t="n">
-        <v>0.562908747937466</v>
+        <v>0.5629087479374484</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7102672655777766</v>
+        <v>0.7102672655777765</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4461336177064384</v>
+        <v>0.4461336177064366</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2472443596711229</v>
+        <v>0.247244359671123</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6211810174760113</v>
+        <v>0.621181017476014</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1885890080255524</v>
+        <v>0.1885890080255516</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.20507285017766</v>
+        <v>0.2050728501776605</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2231476330126683</v>
+        <v>0.2231476330126693</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2518165031532326</v>
+        <v>0.2518165031532328</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2210977677177957</v>
+        <v>0.2210977677177966</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1020032172327347</v>
+        <v>0.1020032172327339</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2994427493952423</v>
+        <v>0.2994427493952432</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3047061814634136</v>
+        <v>0.3047061814634138</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2372205016445141</v>
+        <v>0.2372205016445132</v>
       </c>
       <c r="J7" t="n">
-        <v>0.266131981856549</v>
+        <v>0.2661319818565488</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2421346818318253</v>
+        <v>0.2421346818318247</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.02103653197631142</v>
+        <v>-0.021036531976312</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2111055461444566</v>
+        <v>0.2111055461444561</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2283323160187646</v>
+        <v>0.2283323160187648</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1380113791397697</v>
+        <v>0.1380113791397711</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2120308127823243</v>
+        <v>0.2120308127823263</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.243818724171055</v>
+        <v>0.2438187241710544</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1398007549338202</v>
+        <v>-0.1398007549338203</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1273011795053368</v>
+        <v>0.1273011795053362</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1675627173537199</v>
+        <v>0.1675627173537206</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2921771445225241</v>
+        <v>0.292177144522523</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3335916232768852</v>
+        <v>0.3335916232768844</v>
       </c>
       <c r="W7" t="n">
-        <v>0.623861904923613</v>
+        <v>0.6238619049236099</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7295511393697588</v>
+        <v>0.7295511393697592</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5089734422556748</v>
+        <v>0.508973442255675</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3124472646395136</v>
+        <v>0.3124472646395123</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6404648912679943</v>
+        <v>0.6404648912679949</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2534047357733745</v>
+        <v>0.2534047357733735</v>
       </c>
     </row>
     <row r="8">
@@ -1977,82 +1977,82 @@
         <v>0.2228758707778112</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3167828824383858</v>
+        <v>0.316782882438387</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3454517525789517</v>
+        <v>0.3454517525789516</v>
       </c>
       <c r="E8" t="n">
         <v>0.2743545922045809</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1316200128129081</v>
+        <v>0.1316200128129085</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4088023054683894</v>
+        <v>0.4088023054683905</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3983414308891297</v>
+        <v>0.3983414308891314</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3308557510702304</v>
+        <v>0.3308557510702315</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3597672312822656</v>
+        <v>0.3597672312822661</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3357699312575426</v>
+        <v>0.335769931257542</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07259871744940548</v>
+        <v>0.07259871744940599</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3047407955703738</v>
+        <v>0.304740795570374</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2631849016475273</v>
+        <v>0.2631849016475278</v>
       </c>
       <c r="O8" t="n">
-        <v>0.189351402763602</v>
+        <v>0.1893514027636026</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2594111040016511</v>
+        <v>0.2594111040016537</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2467189810206442</v>
+        <v>0.2467189810206445</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.04616550550810392</v>
+        <v>-0.04616550550810042</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2209364289310546</v>
+        <v>0.2209364289310551</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2611979667794386</v>
+        <v>0.261197966779438</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3492916569267848</v>
+        <v>0.3492916569267857</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4058986665548057</v>
+        <v>0.4058986665548058</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7175120575516949</v>
+        <v>0.7175120575516936</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7394015706703343</v>
+        <v>0.7394015706703344</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6770730702231866</v>
+        <v>0.6770730702231883</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3288416626563005</v>
+        <v>0.3288416626563013</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7341001406937115</v>
+        <v>0.7341001406937133</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.426253089194094</v>
+        <v>0.4262530891940947</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3459212702474327</v>
+        <v>0.3459212702474335</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4310310940176037</v>
+        <v>0.4310310940176051</v>
       </c>
       <c r="D9" t="n">
-        <v>0.459699964158169</v>
+        <v>0.4596999641581693</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4135098426341311</v>
+        <v>0.4135098426341307</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1553525658917541</v>
+        <v>0.1553525658917554</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5073262467082101</v>
+        <v>0.50732624670821</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5125896424683472</v>
+        <v>0.5125896424683476</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4451039626494478</v>
+        <v>0.4451039626494504</v>
       </c>
       <c r="J9" t="n">
-        <v>0.474015442861484</v>
+        <v>0.4740154428614836</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4500181428367593</v>
+        <v>0.4500181428367608</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1868469290286212</v>
+        <v>0.1868469290286241</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4189890071493913</v>
+        <v>0.4189890071493922</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4362157770236998</v>
+        <v>0.4362157770236993</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3684436648600062</v>
+        <v>0.3684436648600055</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4472945531106702</v>
+        <v>0.4472945531106688</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4517022214840202</v>
+        <v>0.4517022214840197</v>
       </c>
       <c r="R9" t="n">
-        <v>0.06808270607111305</v>
+        <v>0.06808270607111425</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3351846405102721</v>
+        <v>0.3351846405102722</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3754461783586557</v>
+        <v>0.3754461783586562</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5010984698804781</v>
+        <v>0.5010984698804787</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6188321335533221</v>
+        <v>0.6188321335533208</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8317453659285464</v>
+        <v>0.8317453659285479</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9374346003746941</v>
+        <v>0.9374346003746954</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.7168569032606107</v>
+        <v>0.7168569032606109</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.479914571366481</v>
+        <v>0.4799145713664807</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8483483522729296</v>
+        <v>0.8483483522729307</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.4612881967783086</v>
+        <v>0.46128819677831</v>
       </c>
     </row>
   </sheetData>
@@ -2318,10 +2318,10 @@
         <v>2.988231310966243</v>
       </c>
       <c r="F2" t="n">
-        <v>2.994172354437881</v>
+        <v>2.994172354437882</v>
       </c>
       <c r="G2" t="n">
-        <v>3.031699272293013</v>
+        <v>3.031699272293014</v>
       </c>
       <c r="H2" t="n">
         <v>3.008974926935863</v>
@@ -2333,10 +2333,10 @@
         <v>3.014860436272361</v>
       </c>
       <c r="K2" t="n">
-        <v>3.006165317801735</v>
+        <v>3.006165317801737</v>
       </c>
       <c r="L2" t="n">
-        <v>3.02009437444145</v>
+        <v>3.020094374441452</v>
       </c>
       <c r="M2" t="n">
         <v>3.027736999497662</v>
@@ -2351,13 +2351,13 @@
         <v>3.010045344812231</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.998501516229474</v>
+        <v>2.998501516229475</v>
       </c>
       <c r="R2" t="n">
         <v>3.003400339211148</v>
       </c>
       <c r="S2" t="n">
-        <v>3.015648124548343</v>
+        <v>3.015648124548345</v>
       </c>
       <c r="T2" t="n">
         <v>3.001849718611822</v>
@@ -2369,22 +2369,22 @@
         <v>2.989603293983162</v>
       </c>
       <c r="W2" t="n">
-        <v>3.791482022495701</v>
+        <v>3.791482022495702</v>
       </c>
       <c r="X2" t="n">
-        <v>3.009162169922744</v>
+        <v>3.009162169922745</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.00407217623327</v>
+        <v>3.004072176233271</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.281903717585465</v>
+        <v>3.281903717585466</v>
       </c>
       <c r="AA2" t="n">
         <v>3.009632224392421</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.027012262018983</v>
+        <v>3.027012262018985</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.214828919104609</v>
+        <v>1.076770449411406</v>
       </c>
       <c r="C3" t="n">
-        <v>2.074529590634869</v>
+        <v>0.9321096136508229</v>
       </c>
       <c r="D3" t="n">
-        <v>2.236887830058373</v>
+        <v>1.099669875742222</v>
       </c>
       <c r="E3" t="n">
-        <v>2.096531088951571</v>
+        <v>0.9543117954864382</v>
       </c>
       <c r="F3" t="n">
-        <v>2.139348545155991</v>
+        <v>0.9986910314058418</v>
       </c>
       <c r="G3" t="n">
-        <v>2.405622665600653</v>
+        <v>1.274267106873631</v>
       </c>
       <c r="H3" t="n">
-        <v>2.245801915443121</v>
+        <v>1.108937076271677</v>
       </c>
       <c r="I3" t="n">
-        <v>2.149081960120355</v>
+        <v>1.00875485417245</v>
       </c>
       <c r="J3" t="n">
-        <v>2.286246426966519</v>
+        <v>1.150724481841164</v>
       </c>
       <c r="K3" t="n">
-        <v>2.224328989803753</v>
+        <v>1.086685136450656</v>
       </c>
       <c r="L3" t="n">
-        <v>2.323897756916749</v>
+        <v>1.189701050794281</v>
       </c>
       <c r="M3" t="n">
-        <v>2.383004387684412</v>
+        <v>1.251032428682746</v>
       </c>
       <c r="N3" t="n">
-        <v>2.237638141026836</v>
+        <v>1.100427300511673</v>
       </c>
       <c r="O3" t="n">
-        <v>2.871727326203672</v>
+        <v>1.733926210375368</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25148136627833</v>
+        <v>1.114687844094906</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.170078193557854</v>
+        <v>1.030484773224034</v>
       </c>
       <c r="R3" t="n">
-        <v>2.20566077985943</v>
+        <v>1.067351752002813</v>
       </c>
       <c r="S3" t="n">
-        <v>2.291452265694076</v>
+        <v>1.15610578624915</v>
       </c>
       <c r="T3" t="n">
-        <v>2.194270948773528</v>
+        <v>1.055545674974766</v>
       </c>
       <c r="U3" t="n">
-        <v>3.574789779500309</v>
+        <v>2.439756681811008</v>
       </c>
       <c r="V3" t="n">
-        <v>2.105914396953141</v>
+        <v>0.9640312116039002</v>
       </c>
       <c r="W3" t="n">
-        <v>3.617928070553607</v>
+        <v>2.484694121200129</v>
       </c>
       <c r="X3" t="n">
-        <v>2.246388462246935</v>
+        <v>1.109508255115859</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.209560409297088</v>
+        <v>1.071354815896314</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.646892337575506</v>
+        <v>1.507677703843813</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.249336872969383</v>
+        <v>1.112528219809328</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.373960055490174</v>
+        <v>1.241566202208863</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5229096276152509</v>
+        <v>0.5229096276152496</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3241874080252021</v>
+        <v>0.3241874080252029</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5554442425493368</v>
+        <v>0.5554442425493386</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3343927884877649</v>
+        <v>0.3343927884877656</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4014996075149239</v>
+        <v>0.4014996075149248</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8253834079237535</v>
+        <v>0.8253834079237534</v>
       </c>
       <c r="H4" t="n">
-        <v>0.568701473399432</v>
+        <v>0.5687014733994329</v>
       </c>
       <c r="I4" t="n">
-        <v>0.416754183810872</v>
+        <v>0.4167541838108722</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6347336848316663</v>
+        <v>0.6347336848316674</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5369656457453854</v>
+        <v>0.5369656457453864</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6943007481735759</v>
+        <v>0.6943007481735861</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7865872689118614</v>
+        <v>0.7865872689118617</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5572323305931769</v>
+        <v>0.5572323305931777</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5348917863329984</v>
+        <v>0.5348917863329993</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5807923357295427</v>
+        <v>0.5807923357295435</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4503994814637744</v>
+        <v>0.4503994814637765</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5057339406116819</v>
+        <v>0.5057339406116822</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6440783102549318</v>
+        <v>0.6440783102549313</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4882189676215942</v>
+        <v>0.4882189676215947</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6528814899618933</v>
+        <v>0.6528814899618937</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3468846442157927</v>
+        <v>0.3468846442157918</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7366385825700738</v>
+        <v>0.7366385825700736</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5708164690722738</v>
+        <v>0.5708164690722772</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5090038132104813</v>
+        <v>0.5090038132104818</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.470386527096593</v>
+        <v>0.4703865270965946</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5761259505430014</v>
+        <v>0.5761259505430025</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.769897092018014</v>
+        <v>0.7698970920180145</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.688529073796865</v>
+        <v>5.688529073797018</v>
       </c>
       <c r="C5" t="n">
-        <v>2.441277874211597</v>
+        <v>2.441277874211594</v>
       </c>
       <c r="D5" t="n">
-        <v>7.138962077489985</v>
+        <v>7.138962077489988</v>
       </c>
       <c r="E5" t="n">
-        <v>2.57831298374949</v>
+        <v>2.578312983749532</v>
       </c>
       <c r="F5" t="n">
-        <v>4.0784842589188</v>
+        <v>4.078484258918802</v>
       </c>
       <c r="G5" t="n">
         <v>11.22710769649442</v>
       </c>
       <c r="H5" t="n">
-        <v>7.688553861833299</v>
+        <v>7.688553861833292</v>
       </c>
       <c r="I5" t="n">
-        <v>4.419635551966699</v>
+        <v>4.419635551966712</v>
       </c>
       <c r="J5" t="n">
-        <v>8.077129551169758</v>
+        <v>8.077129551169783</v>
       </c>
       <c r="K5" t="n">
-        <v>6.298423090791939</v>
+        <v>6.298423090791935</v>
       </c>
       <c r="L5" t="n">
-        <v>9.360279884017617</v>
+        <v>9.360279884017864</v>
       </c>
       <c r="M5" t="n">
-        <v>11.84095234469155</v>
+        <v>11.84095234469153</v>
       </c>
       <c r="N5" t="n">
-        <v>6.961714305217533</v>
+        <v>6.961714305217532</v>
       </c>
       <c r="O5" t="n">
-        <v>5.750657406804682</v>
+        <v>5.750657406804681</v>
       </c>
       <c r="P5" t="n">
-        <v>6.827011041596116</v>
+        <v>6.82701104159612</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.909758771042638</v>
+        <v>4.90975877104264</v>
       </c>
       <c r="R5" t="n">
-        <v>6.300521762571636</v>
+        <v>6.300521762571634</v>
       </c>
       <c r="S5" t="n">
-        <v>8.014484812789563</v>
+        <v>8.014484812789545</v>
       </c>
       <c r="T5" t="n">
-        <v>5.789727293096608</v>
+        <v>5.7897272930966</v>
       </c>
       <c r="U5" t="n">
-        <v>8.478070440183991</v>
+        <v>8.478070440183981</v>
       </c>
       <c r="V5" t="n">
-        <v>2.641081265252274</v>
+        <v>2.641081265252278</v>
       </c>
       <c r="W5" t="n">
-        <v>10.24404991576326</v>
+        <v>10.24404991576325</v>
       </c>
       <c r="X5" t="n">
-        <v>7.311532292498919</v>
+        <v>7.31153229249894</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.946082507063114</v>
+        <v>5.946082507063113</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.897772366841374</v>
+        <v>4.897772366841431</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.185907935114036</v>
+        <v>7.18590793511405</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.94166323727822</v>
+        <v>11.94166323727819</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5484237941726332</v>
+        <v>0.5484237941726366</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4477864099005029</v>
+        <v>0.4477864099005044</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5809584091067217</v>
+        <v>0.5809584091067236</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4579917903630645</v>
+        <v>0.4579917903630666</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4270137740723083</v>
+        <v>0.4270137740723097</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9489824097990522</v>
+        <v>0.9489824097990546</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6923004752747339</v>
+        <v>0.6923004752747347</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5403531856861717</v>
+        <v>0.5403531856861735</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7583326867069674</v>
+        <v>0.7583326867069685</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5624798123027703</v>
+        <v>0.5624798123027712</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8178997500488753</v>
+        <v>0.81789975004888</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9101862707871602</v>
+        <v>0.9101862707871603</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5834830909269865</v>
+        <v>0.5834830909269826</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5612657202870994</v>
+        <v>0.5612657202870828</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7093709711769228</v>
+        <v>0.7093709711769246</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4759136480211584</v>
+        <v>0.4759136480211601</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6293329424869807</v>
+        <v>0.6293329424869825</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6695924768123157</v>
+        <v>0.6695924768123163</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5137331341789781</v>
+        <v>0.5137331341789797</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6827144921456589</v>
+        <v>0.6827144921456608</v>
       </c>
       <c r="V6" t="n">
         <v>0.3723988107731767</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7678830418767484</v>
+        <v>0.7678830418767488</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6944154709475748</v>
+        <v>0.6944154709475769</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5416954168847754</v>
+        <v>0.5416954168847659</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.4959006936539794</v>
+        <v>0.4959006936539812</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6997249524183021</v>
+        <v>0.6997249524183036</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7980380619817833</v>
+        <v>0.7980380619817835</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6420743420538086</v>
+        <v>0.6420743420538101</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4433521224637604</v>
+        <v>0.4433521224637606</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6746089569878954</v>
+        <v>0.6746089569878957</v>
       </c>
       <c r="E7" t="n">
-        <v>0.453557502926323</v>
+        <v>0.4535575029263254</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5206643219534823</v>
+        <v>0.5206643219534826</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9445481223623111</v>
+        <v>0.9445481223623113</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6878661878379903</v>
+        <v>0.6878661878379908</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5359188982494297</v>
+        <v>0.5359188982494303</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7538983992702251</v>
+        <v>0.7538983992702269</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6561303601839439</v>
+        <v>0.6561303601839452</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8134654626121388</v>
+        <v>0.8134654626121317</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9057519833504183</v>
+        <v>0.9057519833504192</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6763970450317341</v>
+        <v>0.6763970450317343</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6536974897877964</v>
+        <v>0.6536974897877965</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6995980391843404</v>
+        <v>0.699598039184342</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.569564195902333</v>
+        <v>0.569564195902334</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6248986550502394</v>
+        <v>0.6248986550502407</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7632430246934887</v>
+        <v>0.7632430246934909</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6073836820601523</v>
+        <v>0.6073836820601526</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7762004749751371</v>
+        <v>0.776200474975137</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4660493586543444</v>
+        <v>0.4660493586543505</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8558032970086307</v>
+        <v>0.8558032970086316</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6899811835108335</v>
+        <v>0.6899811835108354</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6324873632754212</v>
+        <v>0.6324873632754218</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5895512415351516</v>
+        <v>0.589551241535153</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6952906649815599</v>
+        <v>0.6952906649815609</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8890618064565748</v>
+        <v>0.8890618064565754</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6953860455984587</v>
+        <v>0.6953860455984607</v>
       </c>
       <c r="C8" t="n">
-        <v>0.632534789629622</v>
+        <v>0.6325347896296233</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8637916241537578</v>
+        <v>0.8637916241537582</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5703928899241342</v>
+        <v>0.5703928899241363</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5951431336622757</v>
+        <v>0.595143133662277</v>
       </c>
       <c r="G8" t="n">
-        <v>1.161904518945317</v>
+        <v>1.161904518945319</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8770488550038521</v>
+        <v>0.8770488550038533</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7251015654152917</v>
+        <v>0.7251015654152927</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9430810664360866</v>
+        <v>0.943081066436089</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8453130273498057</v>
+        <v>0.8453130273498072</v>
       </c>
       <c r="L8" t="n">
-        <v>1.002648129777994</v>
+        <v>1.002648129778</v>
       </c>
       <c r="M8" t="n">
-        <v>1.094934650516382</v>
+        <v>1.094934650516384</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7602569846510007</v>
+        <v>0.7602569846510016</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7668600403769219</v>
+        <v>0.7668600403769231</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8056658140462621</v>
+        <v>0.8056658140462626</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5961741540156026</v>
+        <v>0.5961741540156046</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8140813222161003</v>
+        <v>0.8140813222161012</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9524256918593517</v>
+        <v>0.9524256918593534</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7965663492260135</v>
+        <v>0.7965663492260145</v>
       </c>
       <c r="U8" t="n">
-        <v>0.899381594069707</v>
+        <v>0.8993815940697083</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6182626502929839</v>
+        <v>0.6182626502929878</v>
       </c>
       <c r="W8" t="n">
-        <v>1.045012666623355</v>
+        <v>1.045012666623357</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7290439853653187</v>
+        <v>0.729043985365321</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9570212250799286</v>
+        <v>0.9570212250799291</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6403390721816388</v>
+        <v>0.6403390721816395</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8844733321474205</v>
+        <v>0.8844733321474229</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.220173056388038</v>
+        <v>1.220173056388039</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9639006297050275</v>
+        <v>0.9639006297050312</v>
       </c>
       <c r="C9" t="n">
-        <v>0.898575761147186</v>
+        <v>0.898575761147188</v>
       </c>
       <c r="D9" t="n">
-        <v>1.12983259567132</v>
+        <v>1.129832595671321</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8779936083500078</v>
+        <v>0.8779936083500109</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6683706059037703</v>
+        <v>0.6683706059037718</v>
       </c>
       <c r="G9" t="n">
-        <v>1.399771801659933</v>
+        <v>1.399771801659935</v>
       </c>
       <c r="H9" t="n">
-        <v>1.143089826521418</v>
+        <v>1.14308982652142</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9911425369328557</v>
+        <v>0.9911425369328579</v>
       </c>
       <c r="J9" t="n">
-        <v>1.209122037953652</v>
+        <v>1.209122037953654</v>
       </c>
       <c r="K9" t="n">
-        <v>1.11135399886737</v>
+        <v>1.111353998867372</v>
       </c>
       <c r="L9" t="n">
-        <v>1.268689101295563</v>
+        <v>1.268689101295566</v>
       </c>
       <c r="M9" t="n">
-        <v>1.360975622033845</v>
+        <v>1.360975622033846</v>
       </c>
       <c r="N9" t="n">
-        <v>1.13162068371516</v>
+        <v>1.131620683715163</v>
       </c>
       <c r="O9" t="n">
-        <v>1.153487900991823</v>
+        <v>1.153487900991825</v>
       </c>
       <c r="P9" t="n">
-        <v>1.209002871212287</v>
+        <v>1.209002871212288</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.024787875199954</v>
+        <v>1.024787875199956</v>
       </c>
       <c r="R9" t="n">
-        <v>1.080122293733666</v>
+        <v>1.080122293733668</v>
       </c>
       <c r="S9" t="n">
-        <v>1.218466663376915</v>
+        <v>1.21846666337692</v>
       </c>
       <c r="T9" t="n">
-        <v>1.062607320743576</v>
+        <v>1.062607320743578</v>
       </c>
       <c r="U9" t="n">
-        <v>1.23158867871026</v>
+        <v>1.231588678710262</v>
       </c>
       <c r="V9" t="n">
         <v>1.07521054889574</v>
       </c>
       <c r="W9" t="n">
-        <v>1.311026935692057</v>
+        <v>1.311026935692059</v>
       </c>
       <c r="X9" t="n">
-        <v>1.145204822194259</v>
+        <v>1.145204822194262</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.087711001958848</v>
+        <v>1.087711001958849</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.9643481558288912</v>
+        <v>0.9643481558288938</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.150514303664986</v>
+        <v>1.150514303664988</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.344285445140001</v>
+        <v>1.344285445140004</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.993704286083269</v>
+        <v>2.993704286083266</v>
       </c>
       <c r="C2" t="n">
-        <v>2.973179169266136</v>
+        <v>2.973179169266135</v>
       </c>
       <c r="D2" t="n">
-        <v>3.006090059820969</v>
+        <v>3.006090059820968</v>
       </c>
       <c r="E2" t="n">
-        <v>2.983401361808403</v>
+        <v>2.983401361808401</v>
       </c>
       <c r="F2" t="n">
-        <v>2.984673760201459</v>
+        <v>2.984673760201456</v>
       </c>
       <c r="G2" t="n">
-        <v>3.023249526712761</v>
+        <v>3.02324952671276</v>
       </c>
       <c r="H2" t="n">
-        <v>2.999988632796627</v>
+        <v>2.999988632796625</v>
       </c>
       <c r="I2" t="n">
-        <v>2.98933870980948</v>
+        <v>2.989338709809476</v>
       </c>
       <c r="J2" t="n">
-        <v>3.007401118271581</v>
+        <v>3.007401118271578</v>
       </c>
       <c r="K2" t="n">
-        <v>2.994727074639388</v>
+        <v>2.994727074639385</v>
       </c>
       <c r="L2" t="n">
-        <v>3.008779293605891</v>
+        <v>3.008779293605889</v>
       </c>
       <c r="M2" t="n">
-        <v>3.016405375863917</v>
+        <v>3.016405375863916</v>
       </c>
       <c r="N2" t="n">
-        <v>2.995262703401124</v>
+        <v>2.995262703401123</v>
       </c>
       <c r="O2" t="n">
-        <v>3.377887207515208</v>
+        <v>3.377887207515207</v>
       </c>
       <c r="P2" t="n">
-        <v>3.004223319467503</v>
+        <v>3.004223319467501</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.982912892594884</v>
+        <v>2.982912892594882</v>
       </c>
       <c r="R2" t="n">
-        <v>2.995013857550895</v>
+        <v>2.995013857550891</v>
       </c>
       <c r="S2" t="n">
-        <v>3.007133908903147</v>
+        <v>3.007133908903143</v>
       </c>
       <c r="T2" t="n">
-        <v>2.993365681091114</v>
+        <v>2.993365681091111</v>
       </c>
       <c r="U2" t="n">
-        <v>3.771206933615797</v>
+        <v>3.771206933615794</v>
       </c>
       <c r="V2" t="n">
-        <v>2.988724585304758</v>
+        <v>2.988724585304755</v>
       </c>
       <c r="W2" t="n">
-        <v>3.776961558344381</v>
+        <v>3.77696155834438</v>
       </c>
       <c r="X2" t="n">
-        <v>3.011137766632617</v>
+        <v>3.011137766632614</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.007283865400359</v>
+        <v>3.007283865400355</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.274753792457815</v>
+        <v>3.274753792457813</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.002261503898956</v>
+        <v>3.002261503898954</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.018371321593319</v>
+        <v>3.018371321593318</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.169998832300358</v>
+        <v>1.030471543580382</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0815934851563</v>
+        <v>0.9395952278341063</v>
       </c>
       <c r="D3" t="n">
-        <v>2.259541761117164</v>
+        <v>1.123246143316457</v>
       </c>
       <c r="E3" t="n">
-        <v>2.096990469535405</v>
+        <v>0.9549004602299765</v>
       </c>
       <c r="F3" t="n">
-        <v>2.106311819476155</v>
+        <v>0.9645940502266166</v>
       </c>
       <c r="G3" t="n">
-        <v>2.380000594206515</v>
+        <v>1.247867593340861</v>
       </c>
       <c r="H3" t="n">
-        <v>2.216530223456967</v>
+        <v>1.078734155441893</v>
       </c>
       <c r="I3" t="n">
-        <v>2.139816015726281</v>
+        <v>0.9992750286605729</v>
       </c>
       <c r="J3" t="n">
-        <v>2.267829096518154</v>
+        <v>1.131779735932577</v>
       </c>
       <c r="K3" t="n">
-        <v>2.177295770275555</v>
+        <v>1.038106339674663</v>
       </c>
       <c r="L3" t="n">
-        <v>2.277997391717097</v>
+        <v>1.142297956862682</v>
       </c>
       <c r="M3" t="n">
-        <v>2.337229054823425</v>
+        <v>1.203742848017415</v>
       </c>
       <c r="N3" t="n">
-        <v>2.181889060175931</v>
+        <v>1.042818649967034</v>
       </c>
       <c r="O3" t="n">
-        <v>2.810682699147954</v>
+        <v>1.671466680321134</v>
       </c>
       <c r="P3" t="n">
-        <v>2.24471612271651</v>
+        <v>1.107802774092624</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.093549620553586</v>
+        <v>0.9513611010880775</v>
       </c>
       <c r="R3" t="n">
-        <v>2.180629384948489</v>
+        <v>1.041544606873207</v>
       </c>
       <c r="S3" t="n">
-        <v>2.265555110180444</v>
+        <v>1.129413099633342</v>
       </c>
       <c r="T3" t="n">
-        <v>2.168593378195403</v>
+        <v>1.029070060110601</v>
       </c>
       <c r="U3" t="n">
-        <v>3.508189835317335</v>
+        <v>2.371193876394665</v>
       </c>
       <c r="V3" t="n">
-        <v>2.134303397715203</v>
+        <v>0.993538100304857</v>
       </c>
       <c r="W3" t="n">
-        <v>3.581154663459956</v>
+        <v>2.44707495873272</v>
       </c>
       <c r="X3" t="n">
-        <v>2.295433344627467</v>
+        <v>1.160409884311767</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.26741600316008</v>
+        <v>1.131369856449045</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.642309239816914</v>
+        <v>1.503191263569507</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.231678926194728</v>
+        <v>1.094358753194562</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.347316016283808</v>
+        <v>1.214091433961081</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4509364288023376</v>
+        <v>0.4509364288023384</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3373374968763546</v>
+        <v>0.3373374968763563</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5908394409071066</v>
+        <v>0.5908394409071079</v>
       </c>
       <c r="E4" t="n">
         <v>0.334560159538442</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3489324847201439</v>
+        <v>0.3489324847201422</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7846635131946695</v>
+        <v>0.7846635131946715</v>
       </c>
       <c r="H4" t="n">
-        <v>0.521921015872062</v>
+        <v>0.5219210158720624</v>
       </c>
       <c r="I4" t="n">
-        <v>0.401625236525607</v>
+        <v>0.4016252365256072</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6052437173583749</v>
+        <v>0.6052437173583753</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4624892960497082</v>
+        <v>0.4624892960497086</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6212155736164413</v>
+        <v>0.6212155736164432</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7138525939991175</v>
+        <v>0.7138525939991183</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4685394693149096</v>
+        <v>0.4685394693149082</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4652858011646928</v>
+        <v>0.4652858011646915</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5697537498717069</v>
+        <v>0.5697537498717052</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3290426750647917</v>
+        <v>0.3290426750647918</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4657286409618304</v>
+        <v>0.4657286409618315</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6026301964845742</v>
+        <v>0.6026301964845761</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4471117296499839</v>
+        <v>0.4471117296499835</v>
       </c>
       <c r="U4" t="n">
-        <v>0.559149132333816</v>
+        <v>0.5591491323338156</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3919713724837041</v>
+        <v>0.391971372483704</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6931089649941783</v>
+        <v>0.6931089649941787</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6478556114045048</v>
+        <v>0.6478556114045045</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6001019606881994</v>
+        <v>0.6001019606882013</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.4691309144170138</v>
+        <v>0.4691309144170162</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5475941405452376</v>
+        <v>0.5475941405452377</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7273222932273783</v>
+        <v>0.7273222932273778</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.332814020114633</v>
+        <v>4.332814020114641</v>
       </c>
       <c r="C5" t="n">
         <v>2.579399721993858</v>
       </c>
       <c r="D5" t="n">
-        <v>7.400619806973489</v>
+        <v>7.400619806973493</v>
       </c>
       <c r="E5" t="n">
-        <v>2.546120308779971</v>
+        <v>2.546120308779966</v>
       </c>
       <c r="F5" t="n">
-        <v>2.924785372985711</v>
+        <v>2.924785372985708</v>
       </c>
       <c r="G5" t="n">
-        <v>9.787533700492972</v>
+        <v>9.787533700492935</v>
       </c>
       <c r="H5" t="n">
-        <v>6.458753171689494</v>
+        <v>6.458753171689485</v>
       </c>
       <c r="I5" t="n">
-        <v>3.965683970538861</v>
+        <v>3.965683970538865</v>
       </c>
       <c r="J5" t="n">
-        <v>7.107763839782036</v>
+        <v>7.107763839782034</v>
       </c>
       <c r="K5" t="n">
-        <v>4.535717864343331</v>
+        <v>4.535717864343335</v>
       </c>
       <c r="L5" t="n">
-        <v>7.555647460900408</v>
+        <v>7.555647460900417</v>
       </c>
       <c r="M5" t="n">
-        <v>9.854320195075687</v>
+        <v>9.854320195075703</v>
       </c>
       <c r="N5" t="n">
-        <v>5.042007288042454</v>
+        <v>5.042007288042457</v>
       </c>
       <c r="O5" t="n">
-        <v>4.353367356022974</v>
+        <v>4.353367356022961</v>
       </c>
       <c r="P5" t="n">
-        <v>6.24899009295171</v>
+        <v>6.248990092951709</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.472051602951899</v>
+        <v>2.472051602951895</v>
       </c>
       <c r="R5" t="n">
-        <v>5.259878468570382</v>
+        <v>5.259878468570378</v>
       </c>
       <c r="S5" t="n">
-        <v>6.864649284462947</v>
+        <v>6.864649284462939</v>
       </c>
       <c r="T5" t="n">
-        <v>4.789189756598447</v>
+        <v>4.789189756598456</v>
       </c>
       <c r="U5" t="n">
-        <v>6.364637505375523</v>
+        <v>6.364637505375489</v>
       </c>
       <c r="V5" t="n">
-        <v>3.254901189405979</v>
+        <v>3.25490118940597</v>
       </c>
       <c r="W5" t="n">
-        <v>8.937148475699336</v>
+        <v>8.937148475699347</v>
       </c>
       <c r="X5" t="n">
-        <v>8.33952417463278</v>
+        <v>8.339524174632757</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.304339681036744</v>
+        <v>7.304339681036756</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.421113475410801</v>
+        <v>4.421113475410814</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.35682582789723</v>
+        <v>6.356825827897235</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.50851130629886</v>
+        <v>10.50851130629887</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5629905267805632</v>
+        <v>0.5629905267805635</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3623137050668393</v>
+        <v>0.3623137050668383</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7028935388853328</v>
+        <v>0.7028935388853337</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4466142575166678</v>
+        <v>0.4466142575166685</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3739086929106282</v>
+        <v>0.3739086929106279</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8096397213851533</v>
+        <v>0.8096397213851564</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5468972240625473</v>
+        <v>0.5468972240625467</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4266014447160911</v>
+        <v>0.4266014447160928</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7172978153366032</v>
+        <v>0.7172978153366065</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5745433940279353</v>
+        <v>0.5745433940279351</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7332696715946693</v>
+        <v>0.7332696715946704</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7388288021896006</v>
+        <v>0.7388288021896001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4941668875411535</v>
+        <v>0.4941668875411502</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5819163674404932</v>
+        <v>0.5819163674404958</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6863431005981432</v>
+        <v>0.6863431005981416</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4410967730430178</v>
+        <v>0.4410967730430201</v>
       </c>
       <c r="R6" t="n">
-        <v>0.490704849152315</v>
+        <v>0.4907048491523147</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7146842944628</v>
+        <v>0.7146842944628008</v>
       </c>
       <c r="T6" t="n">
-        <v>0.472087937840467</v>
+        <v>0.4720879378404697</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5883474039400971</v>
+        <v>0.5883474039400989</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5040254704619306</v>
+        <v>0.5040254704619304</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8097542325629685</v>
+        <v>0.8097542325629692</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6728318195949895</v>
+        <v>0.6728318195949913</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6320802423315877</v>
+        <v>0.6320802423315838</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5811850123952397</v>
+        <v>0.5811850123952427</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6596482385234649</v>
+        <v>0.659648238523467</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7545546493959425</v>
+        <v>0.7545546493959435</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5567867902162269</v>
+        <v>0.5567867902162278</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4431878582902457</v>
+        <v>0.4431878582902462</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6966898023209975</v>
+        <v>0.6966898023209984</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4404105209523331</v>
+        <v>0.4404105209523332</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4547828461340342</v>
+        <v>0.4547828461340356</v>
       </c>
       <c r="G7" t="n">
-        <v>0.890513874608559</v>
+        <v>0.8905138746085614</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6277713772859531</v>
+        <v>0.6277713772859543</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5074755979394983</v>
+        <v>0.5074755979394989</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7110940787722659</v>
+        <v>0.7110940787722668</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5683396574635983</v>
+        <v>0.5683396574635997</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7270659350303335</v>
+        <v>0.7270659350303333</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8197029554130072</v>
+        <v>0.8197029554130082</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5743898307288</v>
+        <v>0.5743898307288005</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5708019231044595</v>
+        <v>0.5708019231044591</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6752698718114745</v>
+        <v>0.6752698718114744</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.434893036478683</v>
+        <v>0.434893036478684</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5715790023757207</v>
+        <v>0.5715790023757225</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7084805578984648</v>
+        <v>0.7084805578984653</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5529620910638737</v>
+        <v>0.5529620910638735</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6687762346135938</v>
+        <v>0.6687762346135916</v>
       </c>
       <c r="V7" t="n">
-        <v>0.497821733897595</v>
+        <v>0.4978217338975948</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7989593264080683</v>
+        <v>0.7989593264080693</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7537059728183974</v>
+        <v>0.7537059728183956</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.7101743855178866</v>
+        <v>0.7101743855178878</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5749812758309037</v>
+        <v>0.5749812758309057</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6534445019591297</v>
+        <v>0.6534445019591288</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8331726546412717</v>
+        <v>0.8331726546412728</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6021482462641856</v>
+        <v>0.6021482462641865</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6073554587962879</v>
+        <v>0.60735545879629</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8608574028270395</v>
+        <v>0.8608574028270414</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5413173541093443</v>
+        <v>0.5413173541093456</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5186529109640996</v>
+        <v>0.5186529109640993</v>
       </c>
       <c r="G8" t="n">
-        <v>1.079316703113194</v>
+        <v>1.079316703113193</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7919389777919975</v>
+        <v>0.7919389777919981</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6716431984455402</v>
+        <v>0.6716431984455408</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8752616792783077</v>
+        <v>0.8752616792783076</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7325072579696413</v>
+        <v>0.7325072579696434</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8912335355363769</v>
+        <v>0.8912335355363796</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9838705559192401</v>
+        <v>0.9838705559192428</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6464627934278472</v>
+        <v>0.6464627934278496</v>
       </c>
       <c r="O8" t="n">
-        <v>0.66851753135783</v>
+        <v>0.6685175313578332</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7667817782012157</v>
+        <v>0.7667817782012188</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4569063735399677</v>
+        <v>0.4569063735399697</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7357466028817637</v>
+        <v>0.7357466028817664</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8726481584045087</v>
+        <v>0.8726481584045096</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7171296915699159</v>
+        <v>0.7171296915699171</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7753153775516818</v>
+        <v>0.7753153775516827</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6294228726419003</v>
+        <v>0.6294228726418987</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9631502756606044</v>
+        <v>0.9631502756606038</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7866081290508046</v>
+        <v>0.7866081290508026</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9923209620152502</v>
+        <v>0.9923209620152504</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6181358467558294</v>
+        <v>0.6181358467558316</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8176121024651725</v>
+        <v>0.8176121024651734</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.121443207381978</v>
+        <v>1.121443207381982</v>
       </c>
     </row>
     <row r="9">
@@ -3782,64 +3782,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8234742631727022</v>
+        <v>0.8234742631727013</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8227949203173766</v>
+        <v>0.8227949203173771</v>
       </c>
       <c r="D9" t="n">
-        <v>1.076296864348128</v>
+        <v>1.07629686434813</v>
       </c>
       <c r="E9" t="n">
-        <v>0.793956234343137</v>
+        <v>0.7939562343431388</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5740793824900817</v>
+        <v>0.5740793824900823</v>
       </c>
       <c r="G9" t="n">
-        <v>1.270120978146864</v>
+        <v>1.270120978146866</v>
       </c>
       <c r="H9" t="n">
-        <v>1.007378439313086</v>
+        <v>1.007378439313085</v>
       </c>
       <c r="I9" t="n">
-        <v>0.88708265996663</v>
+        <v>0.8870826599666302</v>
       </c>
       <c r="J9" t="n">
-        <v>1.090701140799398</v>
+        <v>1.090701140799397</v>
       </c>
       <c r="K9" t="n">
-        <v>0.947946719490729</v>
+        <v>0.9479467194907292</v>
       </c>
       <c r="L9" t="n">
-        <v>1.106672997057465</v>
+        <v>1.106672997057466</v>
       </c>
       <c r="M9" t="n">
-        <v>1.199310017440139</v>
+        <v>1.19931001744014</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9539968927559319</v>
+        <v>0.9539968927559315</v>
       </c>
       <c r="O9" t="n">
-        <v>0.988164683836077</v>
+        <v>0.9881646838360806</v>
       </c>
       <c r="P9" t="n">
-        <v>1.100771148853611</v>
+        <v>1.100771148853613</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8145001400169876</v>
+        <v>0.814500140016987</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9511860644028511</v>
+        <v>0.9511860644028521</v>
       </c>
       <c r="S9" t="n">
         <v>1.088087619925596</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9325691530910056</v>
+        <v>0.9325691530910069</v>
       </c>
       <c r="U9" t="n">
-        <v>1.048828619190634</v>
+        <v>1.048828619190631</v>
       </c>
       <c r="V9" t="n">
         <v>1.007735486866757</v>
@@ -3848,19 +3848,19 @@
         <v>1.178566388435199</v>
       </c>
       <c r="X9" t="n">
-        <v>1.133313034845528</v>
+        <v>1.13331303484553</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.089781447545016</v>
+        <v>1.089781447545017</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.8865078833336982</v>
+        <v>0.8865078833337002</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.033051563986262</v>
+        <v>1.033051563986259</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.212779716668403</v>
+        <v>1.212779716668402</v>
       </c>
     </row>
   </sheetData>
@@ -4026,19 +4026,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.986440352726757</v>
+        <v>2.986440352726758</v>
       </c>
       <c r="C2" t="n">
         <v>2.969373732505465</v>
       </c>
       <c r="D2" t="n">
-        <v>2.991404244094946</v>
+        <v>2.991404244094944</v>
       </c>
       <c r="E2" t="n">
         <v>2.975170244442945</v>
       </c>
       <c r="F2" t="n">
-        <v>2.981805155986177</v>
+        <v>2.981805155986175</v>
       </c>
       <c r="G2" t="n">
         <v>3.011194357458953</v>
@@ -4062,40 +4062,40 @@
         <v>3.005102718192137</v>
       </c>
       <c r="N2" t="n">
-        <v>2.987512842067502</v>
+        <v>2.987512842067501</v>
       </c>
       <c r="O2" t="n">
         <v>3.360494244125723</v>
       </c>
       <c r="P2" t="n">
-        <v>2.997599713574871</v>
+        <v>2.997599713574872</v>
       </c>
       <c r="Q2" t="n">
         <v>2.981222071111544</v>
       </c>
       <c r="R2" t="n">
-        <v>2.987698298529793</v>
+        <v>2.987698298529794</v>
       </c>
       <c r="S2" t="n">
         <v>2.998794177571321</v>
       </c>
       <c r="T2" t="n">
-        <v>2.987089320939498</v>
+        <v>2.987089320939499</v>
       </c>
       <c r="U2" t="n">
         <v>3.766077453318105</v>
       </c>
       <c r="V2" t="n">
-        <v>2.992915645544041</v>
+        <v>2.992915645544042</v>
       </c>
       <c r="W2" t="n">
-        <v>3.76959153581853</v>
+        <v>3.769591535818528</v>
       </c>
       <c r="X2" t="n">
-        <v>3.007918090678546</v>
+        <v>3.007918090678547</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.015766752852953</v>
+        <v>3.015766752852954</v>
       </c>
       <c r="Z2" t="n">
         <v>3.264392202083636</v>
@@ -4104,7 +4104,7 @@
         <v>2.998579365828176</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.009074116475248</v>
+        <v>3.009074116475247</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.150452891166315</v>
+        <v>1.010296679040627</v>
       </c>
       <c r="C3" t="n">
-        <v>2.091059540351124</v>
+        <v>0.949498325287069</v>
       </c>
       <c r="D3" t="n">
-        <v>2.186616961037768</v>
+        <v>1.047798179979349</v>
       </c>
       <c r="E3" t="n">
-        <v>2.070541942175245</v>
+        <v>0.9275758894924716</v>
       </c>
       <c r="F3" t="n">
-        <v>2.118268855554074</v>
+        <v>0.9770312065201898</v>
       </c>
       <c r="G3" t="n">
-        <v>2.32608700707851</v>
+        <v>1.192126139509293</v>
       </c>
       <c r="H3" t="n">
-        <v>2.193986278384091</v>
+        <v>1.055437595481429</v>
       </c>
       <c r="I3" t="n">
-        <v>2.135309285807348</v>
+        <v>0.9946638669842613</v>
       </c>
       <c r="J3" t="n">
-        <v>2.240838068265503</v>
+        <v>1.103902734571135</v>
       </c>
       <c r="K3" t="n">
-        <v>2.201764617149726</v>
+        <v>1.063499423121385</v>
       </c>
       <c r="L3" t="n">
-        <v>2.236598846941949</v>
+        <v>1.099506146537988</v>
       </c>
       <c r="M3" t="n">
-        <v>2.288315226388756</v>
+        <v>1.153163515783858</v>
       </c>
       <c r="N3" t="n">
-        <v>2.159022174394508</v>
+        <v>1.019193035791748</v>
       </c>
       <c r="O3" t="n">
-        <v>2.761863756664853</v>
+        <v>1.621430996186791</v>
       </c>
       <c r="P3" t="n">
-        <v>2.229577319479455</v>
+        <v>1.092196034016379</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.113804066961663</v>
+        <v>0.9723902847184052</v>
       </c>
       <c r="R3" t="n">
-        <v>2.16078748871121</v>
+        <v>1.021048639086244</v>
       </c>
       <c r="S3" t="n">
-        <v>2.238412435040881</v>
+        <v>1.10136980167111</v>
       </c>
       <c r="T3" t="n">
-        <v>2.156226046996115</v>
+        <v>1.0163148171509</v>
       </c>
       <c r="U3" t="n">
-        <v>3.517217684207752</v>
+        <v>2.380751658716311</v>
       </c>
       <c r="V3" t="n">
-        <v>2.196178446837499</v>
+        <v>1.057652076913577</v>
       </c>
       <c r="W3" t="n">
-        <v>3.578602913621355</v>
+        <v>2.444669728342446</v>
       </c>
       <c r="X3" t="n">
-        <v>2.304428527358727</v>
+        <v>1.169793207448971</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.360761512225861</v>
+        <v>1.228055606583912</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.615653209529638</v>
+        <v>1.475818893160055</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.237919914080229</v>
+        <v>1.10086888401731</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.312994614426422</v>
+        <v>1.178616001439764</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4250432200556756</v>
+        <v>0.425043220055675</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3593073473323486</v>
+        <v>0.359307347332349</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4811126565622144</v>
+        <v>0.481112656562214</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2977421624840453</v>
+        <v>0.2977421624840456</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3726865405749614</v>
+        <v>0.3726865405749607</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7046510909105891</v>
+        <v>0.7046510909105901</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4911700680425107</v>
+        <v>0.4911700680425112</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3994932906496645</v>
+        <v>0.3994932906496641</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5677478024695057</v>
+        <v>0.5677478024695058</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5061660298048012</v>
+        <v>0.5061660298048019</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5611812247564424</v>
+        <v>0.5611812247564429</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6425532951092392</v>
+        <v>0.6425532951092402</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4371574805288559</v>
+        <v>0.4371574805288536</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4127778362074711</v>
+        <v>0.4127778362074693</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5510933343947123</v>
+        <v>0.5510933343947125</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.366100328683689</v>
+        <v>0.3661003286836885</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4392522965846406</v>
+        <v>0.4392522965846402</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5645853547151947</v>
+        <v>0.5645853547151958</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4323736145586936</v>
+        <v>0.4323736145586943</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5860638169656094</v>
+        <v>0.5860638169656119</v>
       </c>
       <c r="V4" t="n">
-        <v>0.496117668309053</v>
+        <v>0.4961176683090523</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7021884796077604</v>
+        <v>0.7021884796077577</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6676441504687117</v>
+        <v>0.6676441504687114</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7526616844822066</v>
+        <v>0.7526616844822048</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.4393233648760655</v>
+        <v>0.4393233648760663</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5621589572581001</v>
+        <v>0.5621589572580998</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6785075179904358</v>
+        <v>0.6785075179904339</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.769175731394055</v>
+        <v>3.76917573139406</v>
       </c>
       <c r="C5" t="n">
-        <v>2.91324063395989</v>
+        <v>2.913240633959891</v>
       </c>
       <c r="D5" t="n">
-        <v>5.142544113264703</v>
+        <v>5.142544113264708</v>
       </c>
       <c r="E5" t="n">
-        <v>1.789390876241728</v>
+        <v>1.78939087624173</v>
       </c>
       <c r="F5" t="n">
-        <v>3.30831713133436</v>
+        <v>3.308317131334372</v>
       </c>
       <c r="G5" t="n">
-        <v>8.177388402899538</v>
+        <v>8.177388402899535</v>
       </c>
       <c r="H5" t="n">
-        <v>5.846180482013196</v>
+        <v>5.846180482013203</v>
       </c>
       <c r="I5" t="n">
-        <v>3.835584407665218</v>
+        <v>3.835584407665219</v>
       </c>
       <c r="J5" t="n">
-        <v>6.30967317044118</v>
+        <v>6.309673170441182</v>
       </c>
       <c r="K5" t="n">
-        <v>5.232045008746944</v>
+        <v>5.232045008746934</v>
       </c>
       <c r="L5" t="n">
-        <v>6.242813223971431</v>
+        <v>6.242813223971436</v>
       </c>
       <c r="M5" t="n">
-        <v>8.146025938596653</v>
+        <v>8.146025938596662</v>
       </c>
       <c r="N5" t="n">
-        <v>4.457546358685735</v>
+        <v>4.457546358685731</v>
       </c>
       <c r="O5" t="n">
-        <v>3.512811694693989</v>
+        <v>3.512811694693986</v>
       </c>
       <c r="P5" t="n">
-        <v>5.728851118172227</v>
+        <v>5.728851118172259</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.034660487934745</v>
+        <v>3.034660487934755</v>
       </c>
       <c r="R5" t="n">
-        <v>4.723497669474844</v>
+        <v>4.723497669474843</v>
       </c>
       <c r="S5" t="n">
         <v>6.128215681392871</v>
       </c>
       <c r="T5" t="n">
-        <v>4.490346853792426</v>
+        <v>4.49034685379242</v>
       </c>
       <c r="U5" t="n">
-        <v>6.561400555517725</v>
+        <v>6.561400555517709</v>
       </c>
       <c r="V5" t="n">
-        <v>4.807358703839616</v>
+        <v>4.80735870383961</v>
       </c>
       <c r="W5" t="n">
         <v>9.086666591957975</v>
       </c>
       <c r="X5" t="n">
-        <v>8.416486032713467</v>
+        <v>8.416486032713474</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.14860016398165</v>
+        <v>10.14860016398164</v>
       </c>
       <c r="Z5" t="n">
         <v>3.738707681482556</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.624566038922211</v>
+        <v>6.624566038922218</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.389989312251625</v>
+        <v>9.389989312251636</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4531872579243866</v>
+        <v>0.4531872579243872</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3874513852010605</v>
+        <v>0.3874513852010611</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5904707456699942</v>
+        <v>0.5904707456699922</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4071002515918228</v>
+        <v>0.4071002515918237</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4008305784436723</v>
+        <v>0.4008305784436721</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7327951287793022</v>
+        <v>0.732795128779303</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6005281571502885</v>
+        <v>0.6005281571502881</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4276373285183744</v>
+        <v>0.4276373285183761</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6771058915772838</v>
+        <v>0.677105891577284</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6155241189125781</v>
+        <v>0.6155241189125789</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5893252626251551</v>
+        <v>0.5893252626251555</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6706973329779512</v>
+        <v>0.6706973329779519</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4664773873887191</v>
+        <v>0.4664773873887308</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4422102249486352</v>
+        <v>0.4422102249486417</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6653431007327389</v>
+        <v>0.6653431007327379</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4754584177914645</v>
+        <v>0.4754584177914659</v>
       </c>
       <c r="R6" t="n">
-        <v>0.548610385692415</v>
+        <v>0.5486103856924176</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5927293925839066</v>
+        <v>0.592729392583908</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5417317036664717</v>
+        <v>0.5417317036664714</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6990586218828096</v>
+        <v>0.699058621882812</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5242617061777642</v>
+        <v>0.5242617061777641</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7357519770785029</v>
+        <v>0.7357519770785026</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6957881883374222</v>
+        <v>0.6957881883374235</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.7881970343333009</v>
+        <v>0.7881970343333041</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.4674674027447764</v>
+        <v>0.4674674027447774</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6715170463658793</v>
+        <v>0.6715170463658778</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7088665411384709</v>
+        <v>0.70886654113847</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5279621219820412</v>
+        <v>0.5279621219820423</v>
       </c>
       <c r="C7" t="n">
-        <v>0.462226249258715</v>
+        <v>0.4622262492587152</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5840315584885807</v>
+        <v>0.5840315584885805</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4006610644104114</v>
+        <v>0.4006610644104119</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4756054425013264</v>
+        <v>0.4756054425013286</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8075699928369562</v>
+        <v>0.8075699928369567</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5940889699688773</v>
+        <v>0.5940889699688781</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5024121925760305</v>
+        <v>0.5024121925760296</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6706667043958714</v>
+        <v>0.6706667043958724</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6090849317311674</v>
+        <v>0.6090849317311675</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6641001266828106</v>
+        <v>0.6641001266828112</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7454721970356037</v>
+        <v>0.7454721970356042</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5400763824552197</v>
+        <v>0.5400763824552199</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5153626461096744</v>
+        <v>0.5153626461096751</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6536781442969183</v>
+        <v>0.6536781442969192</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4690192306100555</v>
+        <v>0.4690192306100552</v>
       </c>
       <c r="R7" t="n">
-        <v>0.542171198511007</v>
+        <v>0.5421711985110061</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6675042566415615</v>
+        <v>0.6675042566415628</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5352925164850615</v>
+        <v>0.5352925164850613</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6918870555450977</v>
+        <v>0.6918870555450964</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5990365702354191</v>
+        <v>0.5990365702354189</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8051073815341248</v>
+        <v>0.8051073815341245</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7705630523950781</v>
+        <v>0.7705630523950788</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8592173022179929</v>
+        <v>0.8592173022179951</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5422422668024315</v>
+        <v>0.5422422668024318</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6650778591844664</v>
+        <v>0.6650778591844668</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7814264199168006</v>
+        <v>0.7814264199167997</v>
       </c>
     </row>
     <row r="8">
@@ -4554,82 +4554,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5695178607506722</v>
+        <v>0.5695178607506706</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6170839634849284</v>
+        <v>0.6170839634849296</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7388892727147983</v>
+        <v>0.7388892727147949</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4951888189151689</v>
+        <v>0.4951888189151685</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5348123048516199</v>
+        <v>0.534812304851619</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9859216097640255</v>
+        <v>0.9859216097640239</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7489466841950905</v>
+        <v>0.7489466841950922</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6572699068022442</v>
+        <v>0.6572699068022445</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8255244186220881</v>
+        <v>0.8255244186220868</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7639426459573804</v>
+        <v>0.7639426459573815</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8189578409090233</v>
+        <v>0.8189578409090243</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9003299112620253</v>
+        <v>0.900329911262027</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6071061106801445</v>
+        <v>0.6071061106801428</v>
       </c>
       <c r="O8" t="n">
-        <v>0.606862359481946</v>
+        <v>0.606862359481947</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7392615670625332</v>
+        <v>0.7392615670625313</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4883085452238764</v>
+        <v>0.4883085452238784</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6970289127372205</v>
+        <v>0.6970289127372199</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8223619708677773</v>
+        <v>0.8223619708677775</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6901502307112752</v>
+        <v>0.6901502307112748</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7918673041489842</v>
+        <v>0.7918673041489813</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7225867001702155</v>
+        <v>0.722586700170214</v>
       </c>
       <c r="W8" t="n">
-        <v>0.959987362791336</v>
+        <v>0.9599873627913355</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8002367181612352</v>
+        <v>0.8002367181612369</v>
       </c>
       <c r="Y8" t="n">
         <v>1.126200559546737</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5816933632119301</v>
+        <v>0.5816933632119308</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8199355734106807</v>
+        <v>0.8199355734106794</v>
       </c>
       <c r="AB8" t="n">
         <v>1.054637521616483</v>
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.763871873569241</v>
+        <v>0.7638718735692405</v>
       </c>
       <c r="C9" t="n">
-        <v>0.801200650465691</v>
+        <v>0.8012006504656921</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9230059596955574</v>
+        <v>0.9230059596955571</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7158485857740329</v>
+        <v>0.7158485857740324</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5769876618646351</v>
+        <v>0.5769876618646355</v>
       </c>
       <c r="G9" t="n">
         <v>1.146544421209466</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9330633711758531</v>
+        <v>0.9330633711758527</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8413865937830078</v>
+        <v>0.8413865937830072</v>
       </c>
       <c r="J9" t="n">
-        <v>1.009641105602848</v>
+        <v>1.009641105602847</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9480593329381419</v>
+        <v>0.9480593329381417</v>
       </c>
       <c r="L9" t="n">
         <v>1.003074527889787</v>
       </c>
       <c r="M9" t="n">
-        <v>1.084446598242581</v>
+        <v>1.084446598242582</v>
       </c>
       <c r="N9" t="n">
         <v>0.8790507836621957</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8888266654413278</v>
+        <v>0.8888266654413273</v>
       </c>
       <c r="P9" t="n">
         <v>1.034570398637255</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8079936589825637</v>
+        <v>0.8079936589825643</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8811455997179809</v>
+        <v>0.8811455997179817</v>
       </c>
       <c r="S9" t="n">
-        <v>1.006478657848538</v>
+        <v>1.006478657848537</v>
       </c>
       <c r="T9" t="n">
-        <v>0.874266917692036</v>
+        <v>0.8742669176920367</v>
       </c>
       <c r="U9" t="n">
-        <v>1.031593835908376</v>
+        <v>1.031593835908377</v>
       </c>
       <c r="V9" t="n">
-        <v>1.056945292185266</v>
+        <v>1.056945292185265</v>
       </c>
       <c r="W9" t="n">
         <v>1.144081782741101</v>
       </c>
       <c r="X9" t="n">
-        <v>1.109537453602051</v>
+        <v>1.109537453602055</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.198191703424973</v>
+        <v>1.198191703424971</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.8190778599420477</v>
+        <v>0.8190778599420485</v>
       </c>
       <c r="AA9" t="n">
         <v>1.004052260391441</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.120400821123778</v>
+        <v>1.120400821123777</v>
       </c>
     </row>
   </sheetData>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.921546539473806</v>
+        <v>2.921546539473805</v>
       </c>
       <c r="C2" t="n">
         <v>2.910046516557102</v>
@@ -4904,13 +4904,13 @@
         <v>2.933201842940748</v>
       </c>
       <c r="H2" t="n">
-        <v>2.925213534275591</v>
+        <v>2.92521353427559</v>
       </c>
       <c r="I2" t="n">
-        <v>2.924311198370356</v>
+        <v>2.924311198370357</v>
       </c>
       <c r="J2" t="n">
-        <v>2.928431532741834</v>
+        <v>2.928431532741833</v>
       </c>
       <c r="K2" t="n">
         <v>2.928477673326425</v>
@@ -4919,7 +4919,7 @@
         <v>2.921454950034537</v>
       </c>
       <c r="M2" t="n">
-        <v>2.931967622046483</v>
+        <v>2.931967622046484</v>
       </c>
       <c r="N2" t="n">
         <v>2.924611637287208</v>
@@ -4949,7 +4949,7 @@
         <v>2.921522760757334</v>
       </c>
       <c r="W2" t="n">
-        <v>3.707937155127057</v>
+        <v>3.707937155127058</v>
       </c>
       <c r="X2" t="n">
         <v>2.934736279060564</v>
@@ -4961,7 +4961,7 @@
         <v>3.187131516738167</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.938131907240755</v>
+        <v>2.938131907240756</v>
       </c>
       <c r="AB2" t="n">
         <v>2.930721709788196</v>
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.000898504447331</v>
+        <v>0.8568044398616445</v>
       </c>
       <c r="C3" t="n">
-        <v>1.987396594039949</v>
+        <v>0.8435636114322231</v>
       </c>
       <c r="D3" t="n">
-        <v>2.042504107968048</v>
+        <v>0.8998966065582051</v>
       </c>
       <c r="E3" t="n">
-        <v>1.972817373224569</v>
+        <v>0.827730621847375</v>
       </c>
       <c r="F3" t="n">
-        <v>1.983914176393863</v>
+        <v>0.8392283042583015</v>
       </c>
       <c r="G3" t="n">
-        <v>2.083376515591486</v>
+        <v>0.9421987917075377</v>
       </c>
       <c r="H3" t="n">
-        <v>2.027484344219752</v>
+        <v>0.8843512925333965</v>
       </c>
       <c r="I3" t="n">
-        <v>2.02091016967068</v>
+        <v>0.8775377695096579</v>
       </c>
       <c r="J3" t="n">
-        <v>2.049827820934788</v>
+        <v>0.9074706414148522</v>
       </c>
       <c r="K3" t="n">
-        <v>2.050297358741664</v>
+        <v>0.907975695054358</v>
       </c>
       <c r="L3" t="n">
-        <v>2.000243713459001</v>
+        <v>0.8561331872994667</v>
       </c>
       <c r="M3" t="n">
-        <v>2.078707915299914</v>
+        <v>0.9374359238369462</v>
       </c>
       <c r="N3" t="n">
-        <v>2.022886273709517</v>
+        <v>0.8795791254850791</v>
       </c>
       <c r="O3" t="n">
-        <v>2.568846683900009</v>
+        <v>1.424562670304776</v>
       </c>
       <c r="P3" t="n">
-        <v>2.003186273336922</v>
+        <v>0.859169753412875</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.000418233409096</v>
+        <v>0.8563168364630896</v>
       </c>
       <c r="R3" t="n">
-        <v>1.913598152933785</v>
+        <v>0.7664108396874936</v>
       </c>
       <c r="S3" t="n">
-        <v>2.033943256780657</v>
+        <v>0.8910284173863325</v>
       </c>
       <c r="T3" t="n">
-        <v>2.000537082539402</v>
+        <v>0.8564415686300264</v>
       </c>
       <c r="U3" t="n">
-        <v>3.361122189886176</v>
+        <v>2.221003102429662</v>
       </c>
       <c r="V3" t="n">
-        <v>2.000725946608436</v>
+        <v>0.8566275969638105</v>
       </c>
       <c r="W3" t="n">
-        <v>3.503569277309078</v>
+        <v>2.368872717100054</v>
       </c>
       <c r="X3" t="n">
-        <v>2.095333817400764</v>
+        <v>0.9546012077943716</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.027193224917724</v>
+        <v>0.8840352764792272</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.443732405440865</v>
+        <v>1.299844835827283</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.119413781716581</v>
+        <v>0.9795122585612567</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.066221706664989</v>
+        <v>0.9244493004462612</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2076030729003511</v>
+        <v>0.2076030729003513</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2185580678294355</v>
+        <v>0.218558067829434</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2730015621724752</v>
+        <v>0.273001562172474</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1629371583964686</v>
+        <v>0.1629371583964675</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1804555778631974</v>
+        <v>0.1804555778631953</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3392550872639401</v>
+        <v>0.3392550872639373</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2490234660874544</v>
+        <v>0.2490234660874535</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2388311669428203</v>
+        <v>0.2388311669428188</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2850733164108717</v>
+        <v>0.2850733164108718</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2858934182447871</v>
+        <v>0.2858934182447857</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2065685280505965</v>
+        <v>0.2065685280505959</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3317541351051891</v>
+        <v>0.3317541351051888</v>
       </c>
       <c r="N4" t="n">
-        <v>0.24222476271739</v>
+        <v>0.2422247627173907</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1990637028952031</v>
+        <v>0.1990637028952024</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2112063943696881</v>
+        <v>0.2112063943696887</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2066692399759585</v>
+        <v>0.2066692399759582</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06964609164386594</v>
+        <v>0.06964609164386493</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2605670260378257</v>
+        <v>0.2605670260378256</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2067837750241002</v>
+        <v>0.2067837750240983</v>
       </c>
       <c r="U4" t="n">
-        <v>0.380939762890143</v>
+        <v>0.3809397628901417</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2053330676802365</v>
+        <v>0.2053330676802372</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6284121071826684</v>
+        <v>0.6284121071826683</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3565872491127752</v>
+        <v>0.3565872491127749</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2439985149242677</v>
+        <v>0.2439985149242664</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2168693743092995</v>
+        <v>0.216869374309298</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.3949424314741777</v>
+        <v>0.3949424314741767</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3101134474439061</v>
+        <v>0.3101134474439055</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9744110647334638</v>
+        <v>0.9744110647334627</v>
       </c>
       <c r="C5" t="n">
         <v>1.270383496150649</v>
       </c>
       <c r="D5" t="n">
-        <v>2.36862321173994</v>
+        <v>2.36862321173993</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2083341722513289</v>
+        <v>0.2083341722513268</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5550145610009878</v>
+        <v>0.5550145610009869</v>
       </c>
       <c r="G5" t="n">
-        <v>3.070769488076802</v>
+        <v>3.070769488076817</v>
       </c>
       <c r="H5" t="n">
-        <v>1.988006160225235</v>
+        <v>1.988006160225224</v>
       </c>
       <c r="I5" t="n">
-        <v>1.720678750587575</v>
+        <v>1.720678750587572</v>
       </c>
       <c r="J5" t="n">
-        <v>2.328203880279109</v>
+        <v>2.328203880279112</v>
       </c>
       <c r="K5" t="n">
         <v>2.416346524346536</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9542312176463241</v>
+        <v>0.9542312176463257</v>
       </c>
       <c r="M5" t="n">
-        <v>3.28545707821566</v>
+        <v>3.285457078215658</v>
       </c>
       <c r="N5" t="n">
-        <v>1.691331155839079</v>
+        <v>1.691331155839091</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8163735408389614</v>
+        <v>0.8163735408389469</v>
       </c>
       <c r="P5" t="n">
-        <v>1.048663297311581</v>
+        <v>1.048663297311585</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01780441169553</v>
+        <v>1.017804411695526</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.707516722813245</v>
+        <v>-1.707516722813238</v>
       </c>
       <c r="S5" t="n">
-        <v>1.741939438325783</v>
+        <v>1.741939438325788</v>
       </c>
       <c r="T5" t="n">
         <v>1.045819999398898</v>
       </c>
       <c r="U5" t="n">
-        <v>4.199874417784792</v>
+        <v>4.199874417784778</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9657472515433397</v>
+        <v>0.9657472515433384</v>
       </c>
       <c r="W5" t="n">
-        <v>9.040100460432779</v>
+        <v>9.040100460432791</v>
       </c>
       <c r="X5" t="n">
-        <v>3.957948336108887</v>
+        <v>3.957948336108892</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.82004843663253</v>
+        <v>1.820048436632517</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.114301742550831</v>
+        <v>1.114301742550828</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.597070266045457</v>
+        <v>4.597070266045452</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.164098618276756</v>
+        <v>3.164098618276755</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2228112789811756</v>
+        <v>0.2228112789811754</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2337662739102587</v>
+        <v>0.2337662739102589</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3461020235475468</v>
+        <v>0.3461020235475456</v>
       </c>
       <c r="E6" t="n">
-        <v>0.23603761977154</v>
+        <v>0.2360376197715388</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1956637839440211</v>
+        <v>0.19566378394402</v>
       </c>
       <c r="G6" t="n">
         <v>0.3544632933447623</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3221239274625273</v>
+        <v>0.3221239274625254</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3119316283178915</v>
+        <v>0.3119316283178906</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3002815224916985</v>
+        <v>0.3002815224916962</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3589938796198596</v>
+        <v>0.3589938796198576</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2217767341314191</v>
+        <v>0.2217767341314204</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4048545964802611</v>
+        <v>0.4048545964802606</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2576771052945594</v>
+        <v>0.2576771052945682</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2780606642931328</v>
+        <v>0.2780606642931305</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2901485614499131</v>
+        <v>0.290148561449913</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2797697013510319</v>
+        <v>0.2797697013510304</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1427465530189382</v>
+        <v>0.1427465530189373</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2757752321186505</v>
+        <v>0.2757752321186497</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2219919811049228</v>
+        <v>0.2219919811049227</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4011911189692873</v>
+        <v>0.4011911189692864</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2784335290553079</v>
+        <v>0.2784335290553089</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7074271281324379</v>
+        <v>0.7074271281324362</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3717954551935998</v>
+        <v>0.3717954551935991</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2665822338036081</v>
+        <v>0.2665822338036093</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2320775803901229</v>
+        <v>0.2320775803901227</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4680428928492499</v>
+        <v>0.4680428928492487</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3263395052926677</v>
+        <v>0.3263395052926652</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.297850158175822</v>
+        <v>0.2978501581758204</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3088051531049046</v>
+        <v>0.3088051531049031</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3632486474479444</v>
+        <v>0.3632486474479428</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2531842436719373</v>
+        <v>0.2531842436719361</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2707026631386657</v>
+        <v>0.2707026631386645</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4295021725394078</v>
+        <v>0.4295021725394065</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3392705513629232</v>
+        <v>0.3392705513629223</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3290782522182892</v>
+        <v>0.3290782522182875</v>
       </c>
       <c r="J7" t="n">
-        <v>0.375320401686342</v>
+        <v>0.3753204016863412</v>
       </c>
       <c r="K7" t="n">
-        <v>0.376140503520257</v>
+        <v>0.3761405035202552</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2968156133260663</v>
+        <v>0.2968156133260654</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4220012203806591</v>
+        <v>0.4220012203806581</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3324718479928603</v>
+        <v>0.3324718479928599</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2889531872991537</v>
+        <v>0.2889531872991516</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3010958787736389</v>
+        <v>0.3010958787736379</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2969163252514292</v>
+        <v>0.2969163252514273</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1598931769193364</v>
+        <v>0.1598931769193351</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3508141113132959</v>
+        <v>0.3508141113132945</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2970308602995675</v>
+        <v>0.2970308602995671</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4751020848798484</v>
+        <v>0.4751020848798467</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2955801529557064</v>
+        <v>0.2955801529557066</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7186591924581399</v>
+        <v>0.7186591924581376</v>
       </c>
       <c r="X7" t="n">
-        <v>0.446834334388246</v>
+        <v>0.4468343343882446</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3392887501980563</v>
+        <v>0.3392887501980546</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3071164595847689</v>
+        <v>0.3071164595847672</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4851895167496478</v>
+        <v>0.4851895167496462</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.4003605327193757</v>
+        <v>0.4003605327193744</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3256834119856793</v>
+        <v>0.3256834119856785</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4303556463767226</v>
+        <v>0.4303556463767225</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4847991407197625</v>
+        <v>0.4847991407197624</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3248330714217414</v>
+        <v>0.3248330714217418</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3131359675551407</v>
+        <v>0.3131359675551398</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5704855459213856</v>
+        <v>0.5704855459213846</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4608210446347425</v>
+        <v>0.4608210446347422</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4506287454901072</v>
+        <v>0.4506287454901063</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4968708949581609</v>
+        <v>0.4968708949581601</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4976909967920745</v>
+        <v>0.4976909967920746</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4183661065978831</v>
+        <v>0.418366106597884</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5435517136526616</v>
+        <v>0.5435517136526614</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3813758021183459</v>
+        <v>0.3813758021183445</v>
       </c>
       <c r="O8" t="n">
         <v>0.3581786420147626</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3654276992746261</v>
+        <v>0.3654276992746263</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3063320025236949</v>
+        <v>0.3063320025236931</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2814436701911543</v>
+        <v>0.2814436701911534</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4723646045851134</v>
+        <v>0.4723646045851136</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4185813535713865</v>
+        <v>0.4185813535713864</v>
       </c>
       <c r="U8" t="n">
-        <v>0.551441384452534</v>
+        <v>0.5514413844525325</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3908578675961898</v>
+        <v>0.3908578675961905</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8402281038164119</v>
+        <v>0.8402281038164109</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4648393828540356</v>
+        <v>0.4648393828540367</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5529989140415397</v>
+        <v>0.5529989140415383</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3332088675590154</v>
+        <v>0.3332088675590161</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6067400100214658</v>
+        <v>0.606740010021465</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.6198065190858754</v>
+        <v>0.6198065190858748</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.497813365975231</v>
+        <v>0.4978133659752298</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5971625237102894</v>
+        <v>0.5971625237102881</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6516060180533296</v>
+        <v>0.6516060180533284</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5211406110367155</v>
+        <v>0.5211406110367144</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3552873481790476</v>
+        <v>0.3552873481790463</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7178595548215261</v>
+        <v>0.7178595548215249</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6276279219683102</v>
+        <v>0.6276279219683082</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6174356228236748</v>
+        <v>0.6174356228236736</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6636777722917273</v>
+        <v>0.663677772291726</v>
       </c>
       <c r="K9" t="n">
-        <v>0.664497874125642</v>
+        <v>0.6644978741256403</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5851729839314521</v>
+        <v>0.5851729839314512</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7103585909860453</v>
+        <v>0.7103585909860434</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6208292185982461</v>
+        <v>0.6208292185982448</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6069618841340646</v>
+        <v>0.606961884134063</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6254754557387433</v>
+        <v>0.6254754557387414</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5852737075335478</v>
+        <v>0.5852737075335462</v>
       </c>
       <c r="R9" t="n">
-        <v>0.448250547524721</v>
+        <v>0.44825054752472</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6391714819186813</v>
+        <v>0.6391714819186797</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5853882309049532</v>
+        <v>0.585388230904952</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7645873687693191</v>
+        <v>0.7645873687693168</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6859424463811008</v>
+        <v>0.685942446381101</v>
       </c>
       <c r="W9" t="n">
-        <v>1.007016563063524</v>
+        <v>1.007016563063523</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7351917049936301</v>
+        <v>0.7351917049936286</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.6276461208034404</v>
+        <v>0.6276461208034405</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.542180014970493</v>
+        <v>0.5421800149704933</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.7735468873550333</v>
+        <v>0.773546887355032</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.6887179033247618</v>
+        <v>0.6887179033247602</v>
       </c>
     </row>
   </sheetData>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.890174906383817</v>
+        <v>2.890174906383816</v>
       </c>
       <c r="C2" t="n">
         <v>2.887484862912825</v>
@@ -5758,7 +5758,7 @@
         <v>2.882993099140927</v>
       </c>
       <c r="F2" t="n">
-        <v>2.886712579967775</v>
+        <v>2.886712579967774</v>
       </c>
       <c r="G2" t="n">
         <v>2.90851661123391</v>
@@ -5767,7 +5767,7 @@
         <v>2.901925248046926</v>
       </c>
       <c r="I2" t="n">
-        <v>2.898581385275869</v>
+        <v>2.898581385275868</v>
       </c>
       <c r="J2" t="n">
         <v>2.902568940449894</v>
@@ -5797,16 +5797,16 @@
         <v>2.867602524567786</v>
       </c>
       <c r="S2" t="n">
-        <v>2.89673318094291</v>
+        <v>2.896733180942909</v>
       </c>
       <c r="T2" t="n">
         <v>2.894491411743268</v>
       </c>
       <c r="U2" t="n">
-        <v>3.644319887159098</v>
+        <v>3.644319887159097</v>
       </c>
       <c r="V2" t="n">
-        <v>2.902685007949389</v>
+        <v>2.902685007949388</v>
       </c>
       <c r="W2" t="n">
         <v>3.655296911530369</v>
@@ -5815,7 +5815,7 @@
         <v>2.938112210274757</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.911169239566408</v>
+        <v>2.911169239566407</v>
       </c>
       <c r="Z2" t="n">
         <v>3.15802224099405</v>
@@ -5824,7 +5824,7 @@
         <v>2.928719014640396</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.899028419287162</v>
+        <v>2.899028419287161</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.895589746799063</v>
+        <v>0.7482624892607328</v>
       </c>
       <c r="C3" t="n">
-        <v>1.952304892645022</v>
+        <v>0.8077876893172125</v>
       </c>
       <c r="D3" t="n">
-        <v>1.978731324840135</v>
+        <v>0.8343379394776183</v>
       </c>
       <c r="E3" t="n">
-        <v>1.844169989420726</v>
+        <v>0.6950177894312191</v>
       </c>
       <c r="F3" t="n">
-        <v>1.870616717607824</v>
+        <v>0.7223617694817014</v>
       </c>
       <c r="G3" t="n">
-        <v>2.025642015031772</v>
+        <v>0.8829020376340205</v>
       </c>
       <c r="H3" t="n">
-        <v>1.979300688116597</v>
+        <v>0.8349292947281158</v>
       </c>
       <c r="I3" t="n">
-        <v>1.955345886415703</v>
+        <v>0.8101197855900137</v>
       </c>
       <c r="J3" t="n">
-        <v>1.983629089379585</v>
+        <v>0.839402375411343</v>
       </c>
       <c r="K3" t="n">
-        <v>1.950498598067296</v>
+        <v>0.8050980229922543</v>
       </c>
       <c r="L3" t="n">
-        <v>1.84509102171468</v>
+        <v>0.6959304227599424</v>
       </c>
       <c r="M3" t="n">
-        <v>1.954565981276424</v>
+        <v>0.8093322067163752</v>
       </c>
       <c r="N3" t="n">
-        <v>2.007210796400647</v>
+        <v>0.8638256154179349</v>
       </c>
       <c r="O3" t="n">
-        <v>2.507820123475326</v>
+        <v>1.362690217241677</v>
       </c>
       <c r="P3" t="n">
-        <v>1.896364509967825</v>
+        <v>0.7490674259772641</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.96540197961217</v>
+        <v>0.8205340692449832</v>
       </c>
       <c r="R3" t="n">
-        <v>1.733672385257903</v>
+        <v>0.5805483529590338</v>
       </c>
       <c r="S3" t="n">
-        <v>1.942312160393836</v>
+        <v>0.796623095229424</v>
       </c>
       <c r="T3" t="n">
-        <v>1.926226180641285</v>
+        <v>0.7799608674118772</v>
       </c>
       <c r="U3" t="n">
-        <v>3.19975043330824</v>
+        <v>2.055140353441115</v>
       </c>
       <c r="V3" t="n">
-        <v>1.984459952186798</v>
+        <v>0.8402621707813683</v>
       </c>
       <c r="W3" t="n">
-        <v>3.328877369345087</v>
+        <v>2.189390405914347</v>
       </c>
       <c r="X3" t="n">
-        <v>2.236939517199795</v>
+        <v>1.101742282890113</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.045188064568531</v>
+        <v>0.9031398771513783</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.394938291484546</v>
+        <v>1.250233958748967</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.170437545222813</v>
+        <v>1.032813443567081</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.958408628742552</v>
+        <v>0.8132903285285318</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04685585162748285</v>
+        <v>0.0468558516274817</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1733745662300072</v>
+        <v>0.1733745662300069</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1788476401313241</v>
+        <v>0.1788476401313246</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.03426596497551933</v>
+        <v>-0.03426596497551992</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00774728200944011</v>
+        <v>0.007747282009440012</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2540338455103967</v>
+        <v>0.2540338455103966</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1795813661365143</v>
+        <v>0.1795813661365149</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1418108978845457</v>
+        <v>0.1418108978845463</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1865933070999045</v>
+        <v>0.1865933070999065</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1340332268892832</v>
+        <v>0.134033226889284</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.03484216574477007</v>
+        <v>-0.03484216574476927</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1414742781592483</v>
+        <v>0.1414742781592478</v>
       </c>
       <c r="N4" t="n">
-        <v>0.224032542418378</v>
+        <v>0.224032542418379</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1461283222226495</v>
+        <v>0.1461283222226496</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04803034169789757</v>
+        <v>0.04803034169789691</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1577764711256222</v>
+        <v>0.1577764711256217</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2081095847932289</v>
+        <v>-0.2081095847932275</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1209345797278116</v>
+        <v>0.1209345797278106</v>
       </c>
       <c r="T4" t="n">
-        <v>0.09561276535305108</v>
+        <v>0.09561276535305216</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1646733924102711</v>
+        <v>0.1646733924102708</v>
       </c>
       <c r="V4" t="n">
         <v>0.186428977978558</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3990139851277604</v>
+        <v>0.3990139851277602</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5883297513249707</v>
+        <v>0.58832975132497</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.279197674076267</v>
+        <v>0.2791976740762661</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1653275364093974</v>
+        <v>0.1653275364093964</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4822292855513716</v>
+        <v>0.4822292855513718</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1466021232126607</v>
+        <v>0.1466021232126606</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.435862737969051</v>
+        <v>-1.435862737969057</v>
       </c>
       <c r="C5" t="n">
-        <v>0.669148588818923</v>
+        <v>0.669148588818926</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7651400724095598</v>
+        <v>0.7651400724095611</v>
       </c>
       <c r="E5" t="n">
         <v>-2.955024181373358</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.263457915173732</v>
+        <v>-2.263457915173731</v>
       </c>
       <c r="G5" t="n">
-        <v>1.786172304008109</v>
+        <v>1.786172304008115</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8329234398857328</v>
+        <v>0.832923439885735</v>
       </c>
       <c r="I5" t="n">
-        <v>0.118516318844847</v>
+        <v>0.1185163188448486</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8235873217233158</v>
+        <v>0.8235873217233198</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01569835881204307</v>
+        <v>0.01569835881204396</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.299241892429185</v>
+        <v>-2.299241892429184</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1504637662369283</v>
+        <v>0.1504637662369289</v>
       </c>
       <c r="N5" t="n">
-        <v>1.527690475611856</v>
+        <v>1.527690475611861</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1969080361016601</v>
+        <v>0.1969080361016585</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.398164610686407</v>
+        <v>-1.398164610686412</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3844281457509748</v>
+        <v>0.3844281457509736</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.368813074019371</v>
+        <v>-6.368813074019378</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1693543144540846</v>
+        <v>-0.169354314454086</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6619669004124541</v>
+        <v>-0.6619669004124534</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5581983248899463</v>
+        <v>0.5581983248899485</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8465866833375335</v>
+        <v>0.8465866833375348</v>
       </c>
       <c r="W5" t="n">
-        <v>4.411963052660995</v>
+        <v>4.411963052660989</v>
       </c>
       <c r="X5" t="n">
-        <v>7.736181723125158</v>
+        <v>7.736181723125161</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.634357721595196</v>
+        <v>2.634357721595198</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.4906095114802344</v>
+        <v>0.4906095114802331</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.138286694085171</v>
+        <v>6.138286694085165</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2097553507000816</v>
+        <v>0.2097553507000825</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09842312120126438</v>
+        <v>0.09842312120126484</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1799733177851902</v>
+        <v>0.1799733177851893</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1854463916865074</v>
+        <v>0.1854463916865072</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.027667213420338</v>
+        <v>-0.02766721342033819</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05931455158322227</v>
+        <v>0.05931455158322294</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3056011150841801</v>
+        <v>0.3056011150841799</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2311486357102975</v>
+        <v>0.2311486357102972</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1933781674583298</v>
+        <v>0.1933781674583287</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2381605766736878</v>
+        <v>0.2381605766736876</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1856004964630665</v>
+        <v>0.1856004964630663</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.02824341418958698</v>
+        <v>-0.02824341418958785</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1930415477330304</v>
+        <v>0.1930415477330302</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2315830583589296</v>
+        <v>0.2315830583589308</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2027071176766492</v>
+        <v>0.2027071176766517</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05401769721940872</v>
+        <v>0.05401769721940911</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2093437406994041</v>
+        <v>0.2093437406994043</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.2015108332380448</v>
+        <v>-0.2015108332380459</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1725018493015931</v>
+        <v>0.1725018493015942</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1022115169082332</v>
+        <v>0.102211516908233</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1760709726844746</v>
+        <v>0.1760709726844736</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1930277295337401</v>
+        <v>0.1930277295337398</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4097155365832104</v>
+        <v>0.4097155365832092</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6398970208987526</v>
+        <v>0.6398970208987503</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2931390798478385</v>
+        <v>0.2931390798478389</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1719262879645786</v>
+        <v>0.1719262879645785</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5337965551251551</v>
+        <v>0.5337965551251561</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1544345204336107</v>
+        <v>0.1544345204336108</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1216729149297804</v>
+        <v>0.1216729149297792</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2481916295323057</v>
+        <v>0.248191629532305</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2536647034336234</v>
+        <v>0.253664703433622</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04055109832677876</v>
+        <v>0.04055109832677896</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08256434531173819</v>
+        <v>0.08256434531173755</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3288509088126959</v>
+        <v>0.3288509088126943</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2543984294388132</v>
+        <v>0.2543984294388118</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2166279611868456</v>
+        <v>0.216627961186845</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2614103704022035</v>
+        <v>0.2614103704022036</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2088502901915824</v>
+        <v>0.208850290191582</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03997489755752823</v>
+        <v>0.03997489755752827</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2162913414615455</v>
+        <v>0.2162913414615452</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2988496057206765</v>
+        <v>0.298849605720676</v>
       </c>
       <c r="O7" t="n">
-        <v>0.220612274714921</v>
+        <v>0.2206122747149206</v>
       </c>
       <c r="P7" t="n">
         <v>0.1225142941901689</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2325935344279199</v>
+        <v>0.2325935344279189</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1332925214909287</v>
+        <v>-0.1332925214909292</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1957516430301092</v>
+        <v>0.1957516430301081</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1704298286553502</v>
+        <v>0.1704298286553498</v>
       </c>
       <c r="U7" t="n">
-        <v>0.242963855319855</v>
+        <v>0.2429638553198544</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2612460412808562</v>
+        <v>0.2612460412808563</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4738310484300581</v>
+        <v>0.4738310484300567</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6631468146272684</v>
+        <v>0.6631468146272693</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3588135660975861</v>
+        <v>0.358813566097585</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2401445997116956</v>
+        <v>0.2401445997116942</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5570463488536711</v>
+        <v>0.5570463488536697</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.221419186514959</v>
+        <v>0.2214191865149573</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1371800263840396</v>
+        <v>0.1371800263840384</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3349918164363931</v>
+        <v>0.3349918164363938</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3404648903377097</v>
+        <v>0.340464890337711</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08938982556443742</v>
+        <v>0.08938982556443759</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1091780847020447</v>
+        <v>0.1091780847020448</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4304341793429534</v>
+        <v>0.430434179342953</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3411986163429003</v>
+        <v>0.3411986163429008</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3034281480909321</v>
+        <v>0.303428148090933</v>
       </c>
       <c r="J8" t="n">
-        <v>0.34821055730629</v>
+        <v>0.3482105573062913</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2956504770956687</v>
+        <v>0.2956504770956698</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1267750844616161</v>
+        <v>0.126775084461616</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3030915283655543</v>
+        <v>0.3030915283655542</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3303857320817539</v>
+        <v>0.3303857320817545</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2676685555799957</v>
+        <v>0.2676685555799958</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1658478636746292</v>
+        <v>0.165847863674629</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2340899293665713</v>
+        <v>0.2340899293665699</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.04649233458684224</v>
+        <v>-0.04649233458684116</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2825518299341981</v>
+        <v>0.2825518299341977</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2572300155594371</v>
+        <v>0.2572300155594369</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2955232504299801</v>
+        <v>0.2955232504299791</v>
       </c>
       <c r="V8" t="n">
         <v>0.3277125465847797</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5606452464788304</v>
+        <v>0.5606452464788299</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6711773616003575</v>
+        <v>0.6711773616003576</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5151832617392149</v>
+        <v>0.5151832617392152</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.25432740568533</v>
+        <v>0.2543274056853296</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.643846535757758</v>
+        <v>0.643846535757759</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3826909521706769</v>
+        <v>0.3826909521706784</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2700316834799262</v>
+        <v>0.2700316834799265</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4643217444025191</v>
+        <v>0.4643217444025176</v>
       </c>
       <c r="D9" t="n">
-        <v>0.469794818303836</v>
+        <v>0.4697948183038356</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2410398772087148</v>
+        <v>0.2410398772087155</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1424629860792901</v>
+        <v>0.1424629860792896</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5449810422840969</v>
+        <v>0.5449810422840983</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4705285443090262</v>
+        <v>0.4705285443090254</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4327580760570588</v>
+        <v>0.4327580760570581</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4775404852724144</v>
+        <v>0.477540485272415</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4249804050617952</v>
+        <v>0.4249804050617942</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2561050124277415</v>
+        <v>0.256105012427741</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4324214563317586</v>
+        <v>0.4324214563317594</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5149797205908889</v>
+        <v>0.5149797205908885</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4595348605922219</v>
+        <v>0.4595348605922213</v>
       </c>
       <c r="P9" t="n">
-        <v>0.366321401527164</v>
+        <v>0.3663214015271634</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4487236678993222</v>
+        <v>0.4487236678993233</v>
       </c>
       <c r="R9" t="n">
-        <v>0.08283759337928386</v>
+        <v>0.08283759337928312</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4118817579003224</v>
+        <v>0.4118817579003214</v>
       </c>
       <c r="T9" t="n">
-        <v>0.386559943525563</v>
+        <v>0.3865599435255624</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4604193993018033</v>
+        <v>0.4604193993018028</v>
       </c>
       <c r="V9" t="n">
-        <v>0.555582856035796</v>
+        <v>0.5555828560357962</v>
       </c>
       <c r="W9" t="n">
-        <v>0.689961163300272</v>
+        <v>0.6899611633002701</v>
       </c>
       <c r="X9" t="n">
-        <v>0.8792769294974817</v>
+        <v>0.8792769294974809</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5749436809677991</v>
+        <v>0.5749436809677986</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.4154146266004821</v>
+        <v>0.4154146266004825</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.7731764637238834</v>
+        <v>0.7731764637238819</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.437549301385172</v>
+        <v>0.4375493013851707</v>
       </c>
     </row>
   </sheetData>
@@ -6612,7 +6612,7 @@
         <v>2.873459095158727</v>
       </c>
       <c r="D2" t="n">
-        <v>2.890149284263963</v>
+        <v>2.890149284263964</v>
       </c>
       <c r="E2" t="n">
         <v>2.873600635610273</v>
@@ -6621,22 +6621,22 @@
         <v>2.881715297370735</v>
       </c>
       <c r="G2" t="n">
-        <v>2.899457735121208</v>
+        <v>2.899457735121209</v>
       </c>
       <c r="H2" t="n">
         <v>2.896100746273499</v>
       </c>
       <c r="I2" t="n">
-        <v>2.893375387614502</v>
+        <v>2.893375387614501</v>
       </c>
       <c r="J2" t="n">
-        <v>2.893882206016294</v>
+        <v>2.893882206016295</v>
       </c>
       <c r="K2" t="n">
         <v>2.891767030525739</v>
       </c>
       <c r="L2" t="n">
-        <v>2.872146196863068</v>
+        <v>2.872146196863069</v>
       </c>
       <c r="M2" t="n">
         <v>2.892872245017226</v>
@@ -6645,46 +6645,46 @@
         <v>2.900189468819016</v>
       </c>
       <c r="O2" t="n">
-        <v>3.209213884148673</v>
+        <v>3.209213884148674</v>
       </c>
       <c r="P2" t="n">
         <v>2.880567108753572</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.893625404074023</v>
+        <v>2.893625404074024</v>
       </c>
       <c r="R2" t="n">
-        <v>2.861373342321575</v>
+        <v>2.861373342321574</v>
       </c>
       <c r="S2" t="n">
         <v>2.885652389212509</v>
       </c>
       <c r="T2" t="n">
-        <v>2.889161927166258</v>
+        <v>2.889161927166257</v>
       </c>
       <c r="U2" t="n">
         <v>3.631819038009864</v>
       </c>
       <c r="V2" t="n">
-        <v>2.897385167182419</v>
+        <v>2.897385167182418</v>
       </c>
       <c r="W2" t="n">
         <v>3.638352293263384</v>
       </c>
       <c r="X2" t="n">
-        <v>2.943179056710271</v>
+        <v>2.943179056710273</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.90063709837685</v>
+        <v>2.900637098376849</v>
       </c>
       <c r="Z2" t="n">
         <v>3.138974081470733</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.925892249140668</v>
+        <v>2.925892249140669</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.893646924634744</v>
+        <v>2.893646924634743</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.836314202901765</v>
+        <v>0.6870356713856245</v>
       </c>
       <c r="C3" t="n">
-        <v>1.904486769224161</v>
+        <v>0.7584903861856294</v>
       </c>
       <c r="D3" t="n">
-        <v>1.939582785938545</v>
+        <v>0.7939335137380785</v>
       </c>
       <c r="E3" t="n">
-        <v>1.822007220918259</v>
+        <v>0.6721938272365662</v>
       </c>
       <c r="F3" t="n">
-        <v>1.879247124058125</v>
+        <v>0.7314435203943546</v>
       </c>
       <c r="G3" t="n">
-        <v>2.005655488396481</v>
+        <v>0.8623412824472299</v>
       </c>
       <c r="H3" t="n">
-        <v>1.98215601921418</v>
+        <v>0.8380253878038694</v>
       </c>
       <c r="I3" t="n">
-        <v>1.96261421488526</v>
+        <v>0.8177849023822359</v>
       </c>
       <c r="J3" t="n">
-        <v>1.966174742362157</v>
+        <v>0.8214675589686521</v>
       </c>
       <c r="K3" t="n">
-        <v>1.95113770568978</v>
+        <v>0.8058992712269414</v>
       </c>
       <c r="L3" t="n">
-        <v>1.812270645589115</v>
+        <v>0.6620956529767728</v>
       </c>
       <c r="M3" t="n">
-        <v>1.962385561019375</v>
+        <v>0.8175686713552881</v>
       </c>
       <c r="N3" t="n">
-        <v>2.011198864473463</v>
+        <v>0.8680902592625189</v>
       </c>
       <c r="O3" t="n">
-        <v>2.441666062951265</v>
+        <v>1.294891310175738</v>
       </c>
       <c r="P3" t="n">
-        <v>1.871673524684984</v>
+        <v>0.723640663617261</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.964351157550043</v>
+        <v>0.8195834548441928</v>
       </c>
       <c r="R3" t="n">
-        <v>1.733470752593357</v>
+        <v>0.580483544687792</v>
       </c>
       <c r="S3" t="n">
-        <v>1.907751712340112</v>
+        <v>0.7609799422430134</v>
       </c>
       <c r="T3" t="n">
-        <v>1.932517740731869</v>
+        <v>0.7866173072971431</v>
       </c>
       <c r="U3" t="n">
-        <v>3.187412456123985</v>
+        <v>2.042848358360646</v>
       </c>
       <c r="V3" t="n">
-        <v>1.99099925863002</v>
+        <v>0.8471680931894451</v>
       </c>
       <c r="W3" t="n">
-        <v>3.290354162157677</v>
+        <v>2.150037911260016</v>
       </c>
       <c r="X3" t="n">
-        <v>2.31705724972965</v>
+        <v>1.18486175462356</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.014464157083161</v>
+        <v>0.8714649211908972</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.337515281478434</v>
+        <v>1.19127767329335</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.194724675601679</v>
+        <v>1.058093800909143</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.963859417467961</v>
+        <v>0.8190689236774857</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.04474453983432793</v>
+        <v>-0.04474453983432877</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1040345484993327</v>
+        <v>0.1040345484993318</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1195145910163945</v>
+        <v>0.1195145910163943</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.06741000828152791</v>
+        <v>-0.06741000828152661</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02424882923172199</v>
+        <v>0.02424882923172021</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2246578255479007</v>
+        <v>0.2246578255479002</v>
       </c>
       <c r="H4" t="n">
-        <v>0.186739092221887</v>
+        <v>0.1867390922218874</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1559549124415734</v>
+        <v>0.1559549124415736</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1614501117356036</v>
+        <v>0.1614501117356034</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1377877792432243</v>
+        <v>0.137787779243224</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.08383856300609333</v>
+        <v>-0.08383856300609487</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1564721564489442</v>
+        <v>0.1564721564489433</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2329230942787951</v>
+        <v>0.2329230942787928</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06829204497842767</v>
+        <v>0.0682920449784276</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01127951060800897</v>
+        <v>0.01127951060800865</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.158778963365118</v>
+        <v>0.1587789633651164</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2055229108102032</v>
+        <v>-0.2055229108102035</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06872009273631971</v>
+        <v>0.06872009273631911</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1083619383910943</v>
+        <v>0.1083619383910925</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1626700248271936</v>
+        <v>0.162670024827193</v>
       </c>
       <c r="V4" t="n">
-        <v>0.199711408947445</v>
+        <v>0.1997114089474455</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3583873817270811</v>
+        <v>0.3583873817270807</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7185102656980135</v>
+        <v>0.7185102656980129</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2325660469994441</v>
+        <v>0.2325660469994426</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0926861951185835</v>
+        <v>0.09268619511858273</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5232478218749911</v>
+        <v>0.5232478218749896</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1577097776930821</v>
+        <v>0.1577097776930828</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.824987969503363</v>
+        <v>-2.824987969503368</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4536121079000485</v>
+        <v>-0.4536121079000496</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1886202305568637</v>
+        <v>-0.1886202305568634</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.218494394515489</v>
+        <v>-3.218494394515483</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.947076577146594</v>
+        <v>-1.947076577146598</v>
       </c>
       <c r="G5" t="n">
-        <v>1.483323165670093</v>
+        <v>1.483323165670096</v>
       </c>
       <c r="H5" t="n">
-        <v>1.050806326127184</v>
+        <v>1.050806326127185</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4592909472336854</v>
+        <v>0.4592909472336858</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5309500120267832</v>
+        <v>0.5309500120267822</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1392270040462579</v>
+        <v>0.1392270040462578</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.175413705052289</v>
+        <v>-3.175413705052288</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4650499129721135</v>
+        <v>0.4650499129721133</v>
       </c>
       <c r="N5" t="n">
-        <v>1.795835503947679</v>
+        <v>1.795835503947684</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9451877313550098</v>
+        <v>-0.9451877313550114</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.854601381128574</v>
+        <v>-1.85460138112858</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4846557835773426</v>
+        <v>0.4846557835773431</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.319221528811441</v>
+        <v>-6.319221528811447</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.950457438159244</v>
+        <v>-0.9504574381592454</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.395319691229058</v>
+        <v>-0.3953196912290601</v>
       </c>
       <c r="U5" t="n">
-        <v>0.613638781286292</v>
+        <v>0.6136387812862926</v>
       </c>
       <c r="V5" t="n">
-        <v>1.13810233163233</v>
+        <v>1.138102331632329</v>
       </c>
       <c r="W5" t="n">
-        <v>3.88149691873251</v>
+        <v>3.881496918732507</v>
       </c>
       <c r="X5" t="n">
-        <v>9.886518762716367</v>
+        <v>9.88651876271636</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.921817027006982</v>
+        <v>1.92181702700698</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.5426106550649989</v>
+        <v>-0.5426106550650021</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.974127689045308</v>
+        <v>6.974127689045316</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.5008030410741421</v>
+        <v>0.5008030410741422</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001382252132994505</v>
+        <v>0.001382252132994727</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1501613404666549</v>
+        <v>0.1501613404666558</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1656413829837186</v>
+        <v>0.1656413829837181</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.06209902644495999</v>
+        <v>-0.06209902644495975</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07037562119904475</v>
+        <v>0.07037562119904492</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2707846175152227</v>
+        <v>0.2707846175152235</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2328658841892108</v>
+        <v>0.2328658841892101</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2020817044088977</v>
+        <v>0.202081704408897</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1667610935721708</v>
+        <v>0.1667610935721713</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1430987610797922</v>
+        <v>0.1430987610797911</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.03771177103877135</v>
+        <v>-0.03771177103877132</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2025989484162665</v>
+        <v>0.2025989484162667</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2393970495573405</v>
+        <v>0.2393970495573399</v>
       </c>
       <c r="O6" t="n">
-        <v>0.07488006519937355</v>
+        <v>0.07488006519937258</v>
       </c>
       <c r="P6" t="n">
-        <v>0.06244802717849374</v>
+        <v>0.06244802717849249</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2049057553324398</v>
+        <v>0.2049057553324396</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.15939611884288</v>
+        <v>-0.1593961188428794</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1148468847036422</v>
+        <v>0.1148468847036416</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1136729202276613</v>
+        <v>0.1136729202276618</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2142100458493732</v>
+        <v>0.2142100458493728</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2050223907840131</v>
+        <v>0.2050223907840137</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4096584106333043</v>
+        <v>0.4096584106333034</v>
       </c>
       <c r="X6" t="n">
-        <v>0.723821247534582</v>
+        <v>0.7238212475345803</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.246020294513318</v>
+        <v>0.2460202945133165</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.09799717695515101</v>
+        <v>0.09799717695515071</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5693746138423138</v>
+        <v>0.5693746138423142</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1645421855429585</v>
+        <v>0.1645421855429577</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02696625587735663</v>
+        <v>0.02696625587735649</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1757453442110163</v>
+        <v>0.1757453442110176</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1912253867280794</v>
+        <v>0.1912253867280803</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004300787430156335</v>
+        <v>0.004300787430154253</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09595962494340628</v>
+        <v>0.09595962494340453</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2963686212595843</v>
+        <v>0.2963686212595835</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2584498879335719</v>
+        <v>0.2584498879335704</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2276657081532587</v>
+        <v>0.2276657081532596</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2331609074472871</v>
+        <v>0.2331609074472874</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2094985749549076</v>
+        <v>0.2094985749549075</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0121277672944099</v>
+        <v>-0.01212776729440897</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2281829521606275</v>
+        <v>0.2281829521606283</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3046338899904782</v>
+        <v>0.3046338899904773</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1396698927043497</v>
+        <v>0.1396698927043487</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0826573583339304</v>
+        <v>0.08265735833392997</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2304897590768011</v>
+        <v>0.2304897590768014</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1338121150985196</v>
+        <v>-0.1338121150985185</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1404308884480037</v>
+        <v>0.1404308884480042</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1800727341027772</v>
+        <v>0.180072734102777</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2381790686721565</v>
+        <v>0.2381790686721549</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2714222046591292</v>
+        <v>0.2714222046591298</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4300981774387656</v>
+        <v>0.4300981774387658</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7902210614096959</v>
+        <v>0.7902210614096987</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.309690071765985</v>
+        <v>0.3096900717659846</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1643969908302677</v>
+        <v>0.164396990830268</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5949586175866755</v>
+        <v>0.5949586175866767</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2294205734047666</v>
+        <v>0.2294205734047676</v>
       </c>
     </row>
     <row r="8">
@@ -7134,22 +7134,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03909375423982978</v>
+        <v>0.03909375423982905</v>
       </c>
       <c r="C8" t="n">
-        <v>0.253617459190561</v>
+        <v>0.2536174591905599</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2690975017076227</v>
+        <v>0.269097501707623</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04716583339723237</v>
+        <v>0.04716583339723168</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1183293662048487</v>
+        <v>0.1183293662048484</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3878733107834083</v>
+        <v>0.3878733107834063</v>
       </c>
       <c r="H8" t="n">
         <v>0.3363220029131148</v>
@@ -7158,61 +7158,61 @@
         <v>0.3055378231328018</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3110330224268321</v>
+        <v>0.3110330224268316</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2873706899344531</v>
+        <v>0.2873706899344524</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0657443476851349</v>
+        <v>0.06574434768513472</v>
       </c>
       <c r="M8" t="n">
-        <v>0.306055067139949</v>
+        <v>0.3060550671399478</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3315429282658818</v>
+        <v>0.3315429282658811</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1809169749687997</v>
+        <v>0.1809169749687992</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1204714531552314</v>
+        <v>0.1204714531552308</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2296969397148025</v>
+        <v>0.229696939714802</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.05594000011897453</v>
+        <v>-0.05594000011897537</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2183030034275475</v>
+        <v>0.218303003427548</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2579448490823226</v>
+        <v>0.257944849082322</v>
       </c>
       <c r="U8" t="n">
-        <v>0.28458355065507</v>
+        <v>0.2845835506550692</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3302294746163449</v>
+        <v>0.3302294746163452</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5079832131571868</v>
+        <v>0.5079832131571866</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7954538668207181</v>
+        <v>0.7954538668207166</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4512308978087153</v>
+        <v>0.4512308978087152</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1753032491812809</v>
+        <v>0.1753032491812793</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6728307325662201</v>
+        <v>0.6728307325662181</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3759684379545157</v>
+        <v>0.3759684379545149</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1570883643373901</v>
+        <v>0.1570883643373883</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3671150499981055</v>
+        <v>0.3671150499981068</v>
       </c>
       <c r="D9" t="n">
-        <v>0.382595092515169</v>
+        <v>0.3825950925151695</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1815347894095413</v>
+        <v>0.1815347894095418</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1461369166984946</v>
+        <v>0.146136916698492</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4877383164265876</v>
+        <v>0.4877383164265883</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4498195937206606</v>
+        <v>0.4498195937206595</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4190354139403478</v>
+        <v>0.4190354139403485</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4245306132343766</v>
+        <v>0.4245306132343761</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4008682807419975</v>
+        <v>0.4008682807419973</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1792419384926787</v>
+        <v>0.1792419384926788</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4195526579477167</v>
+        <v>0.4195526579477183</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4960035957775669</v>
+        <v>0.496003595777567</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3516699058949279</v>
+        <v>0.3516699058949282</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2990717012635099</v>
+        <v>0.2990717012635103</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4218594542438046</v>
+        <v>0.421859454243804</v>
       </c>
       <c r="R9" t="n">
-        <v>0.05755759068856911</v>
+        <v>0.05755759068857078</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3318005942350928</v>
+        <v>0.3318005942350932</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3714424398898691</v>
+        <v>0.3714424398898669</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4311637553808235</v>
+        <v>0.4311637553808222</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5334703157817926</v>
+        <v>0.5334703157817937</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6214678832258536</v>
+        <v>0.6214678832258554</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9815907671967877</v>
+        <v>0.9815907671967875</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5010597775530741</v>
+        <v>0.5010597775530732</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.3188398375608758</v>
+        <v>0.3188398375608746</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.7863283233737639</v>
+        <v>0.7863283233737652</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.4207902791918569</v>
+        <v>0.4207902791918572</v>
       </c>
     </row>
   </sheetData>
@@ -7475,31 +7475,31 @@
         <v>2.981872780796694</v>
       </c>
       <c r="E2" t="n">
-        <v>2.966873244366556</v>
+        <v>2.966873244366555</v>
       </c>
       <c r="F2" t="n">
-        <v>2.96851941692396</v>
+        <v>2.968519416923959</v>
       </c>
       <c r="G2" t="n">
-        <v>3.013005462579586</v>
+        <v>3.013005462579587</v>
       </c>
       <c r="H2" t="n">
         <v>2.988325250428882</v>
       </c>
       <c r="I2" t="n">
-        <v>2.971153639069443</v>
+        <v>2.971153639069442</v>
       </c>
       <c r="J2" t="n">
-        <v>2.992625539289874</v>
+        <v>2.992625539289873</v>
       </c>
       <c r="K2" t="n">
         <v>2.978359867581373</v>
       </c>
       <c r="L2" t="n">
-        <v>2.995735001712151</v>
+        <v>2.995735001712148</v>
       </c>
       <c r="M2" t="n">
-        <v>3.00801586225596</v>
+        <v>3.008015862255961</v>
       </c>
       <c r="N2" t="n">
         <v>2.982044253958755</v>
@@ -7508,10 +7508,10 @@
         <v>3.355839480472261</v>
       </c>
       <c r="P2" t="n">
-        <v>2.982526940985715</v>
+        <v>2.982526940985716</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.972832452750198</v>
+        <v>2.972832452750197</v>
       </c>
       <c r="R2" t="n">
         <v>2.968138935755712</v>
@@ -7526,7 +7526,7 @@
         <v>3.757976742969788</v>
       </c>
       <c r="V2" t="n">
-        <v>2.97217973904436</v>
+        <v>2.972179739044359</v>
       </c>
       <c r="W2" t="n">
         <v>3.761744019409973</v>
@@ -7538,13 +7538,13 @@
         <v>2.986945276663884</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.25095873630608</v>
+        <v>3.250958736306079</v>
       </c>
       <c r="AA2" t="n">
         <v>2.991052836461634</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.005024352082893</v>
+        <v>3.005024352082894</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.123217088203999</v>
+        <v>0.9823188129249228</v>
       </c>
       <c r="C3" t="n">
-        <v>2.035623657936989</v>
+        <v>0.892226781252537</v>
       </c>
       <c r="D3" t="n">
-        <v>2.151872871037604</v>
+        <v>1.012024771495613</v>
       </c>
       <c r="E3" t="n">
-        <v>2.044372871195924</v>
+        <v>0.9006975205228714</v>
       </c>
       <c r="F3" t="n">
-        <v>2.056271034717159</v>
+        <v>0.9130409359154583</v>
       </c>
       <c r="G3" t="n">
-        <v>2.371715125135562</v>
+        <v>1.239577917586712</v>
       </c>
       <c r="H3" t="n">
-        <v>2.198479590372453</v>
+        <v>1.060316541896022</v>
       </c>
       <c r="I3" t="n">
-        <v>2.075147360256478</v>
+        <v>0.9325819282875462</v>
       </c>
       <c r="J3" t="n">
-        <v>2.227416466683422</v>
+        <v>1.090216049170156</v>
       </c>
       <c r="K3" t="n">
-        <v>2.126042407342685</v>
+        <v>0.9852961266815586</v>
       </c>
       <c r="L3" t="n">
-        <v>2.249856254760433</v>
+        <v>1.113448083821809</v>
       </c>
       <c r="M3" t="n">
-        <v>2.340392278637943</v>
+        <v>1.207340678182449</v>
       </c>
       <c r="N3" t="n">
-        <v>2.152836484223815</v>
+        <v>1.013009783777191</v>
       </c>
       <c r="O3" t="n">
-        <v>2.748608668652916</v>
+        <v>1.607790024480943</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15560397685622</v>
+        <v>1.015828677314803</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.086931215259181</v>
+        <v>0.9447799865294026</v>
       </c>
       <c r="R3" t="n">
-        <v>2.05362888949444</v>
+        <v>0.9103000620840555</v>
       </c>
       <c r="S3" t="n">
-        <v>2.169558900137268</v>
+        <v>1.030317665816687</v>
       </c>
       <c r="T3" t="n">
-        <v>2.086009835521037</v>
+        <v>0.9438274518215598</v>
       </c>
       <c r="U3" t="n">
-        <v>3.494299919377081</v>
+        <v>2.357242505415746</v>
       </c>
       <c r="V3" t="n">
-        <v>2.081871667107322</v>
+        <v>0.9395241665745871</v>
       </c>
       <c r="W3" t="n">
-        <v>3.551613913915142</v>
+        <v>2.416907909666325</v>
       </c>
       <c r="X3" t="n">
-        <v>2.209273960309866</v>
+        <v>1.071463056123371</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.187556105279387</v>
+        <v>1.048957588787535</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.5662447348364</v>
+        <v>1.42500231205848</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.216974671448984</v>
+        <v>1.079407023481451</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.316694593523714</v>
+        <v>1.182659756750348</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3841265178657556</v>
+        <v>0.3841265178657501</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2701749499843926</v>
+        <v>0.2701749499843931</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4279425162058547</v>
+        <v>0.4279425162058545</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2585158520997646</v>
+        <v>0.2585158520997636</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2771101284123965</v>
+        <v>0.277110128412397</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7796004786848025</v>
+        <v>0.7796004786848034</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5008261289840497</v>
+        <v>0.5008261289840499</v>
       </c>
       <c r="I4" t="n">
         <v>0.3068648793476934</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5489782824055841</v>
+        <v>0.5489782824055846</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3882625454188595</v>
+        <v>0.3882625454188604</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5845226783825733</v>
+        <v>0.5845226783825617</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7282308046696757</v>
+        <v>0.7282308046696764</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4298793844528412</v>
+        <v>0.4298793844528415</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3879327268849848</v>
+        <v>0.3879327268849849</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4353315564693594</v>
+        <v>0.4353315564693582</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3258278521642814</v>
+        <v>0.3258278521642816</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2728124185870443</v>
+        <v>0.2728124185870446</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4581748606862448</v>
+        <v>0.4581748606862439</v>
       </c>
       <c r="T4" t="n">
-        <v>0.324029763650284</v>
+        <v>0.3240297636502841</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5509554832349678</v>
+        <v>0.5509554832349667</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3156225088332261</v>
+        <v>0.3156225088332263</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6601632135361473</v>
+        <v>0.6601632135361469</v>
       </c>
       <c r="X4" t="n">
-        <v>0.518869452852014</v>
+        <v>0.51886945285201</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4804595593880135</v>
+        <v>0.4804595593880143</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.3683878546930263</v>
+        <v>0.3683878546930246</v>
       </c>
       <c r="AA4" t="n">
         <v>0.5316354679755766</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6864107070265153</v>
+        <v>0.6864107070265169</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.449609586918848</v>
+        <v>3.449609586918802</v>
       </c>
       <c r="C5" t="n">
-        <v>1.618679098227292</v>
+        <v>1.618679098227293</v>
       </c>
       <c r="D5" t="n">
-        <v>4.817875315193156</v>
+        <v>4.817875315193151</v>
       </c>
       <c r="E5" t="n">
-        <v>1.365460303026934</v>
+        <v>1.365460303026925</v>
       </c>
       <c r="F5" t="n">
-        <v>1.800099282669756</v>
+        <v>1.800099282669755</v>
       </c>
       <c r="G5" t="n">
         <v>10.15822641931799</v>
       </c>
       <c r="H5" t="n">
-        <v>6.504684001373261</v>
+        <v>6.50468400137327</v>
       </c>
       <c r="I5" t="n">
-        <v>2.40482823099262</v>
+        <v>2.404828230992622</v>
       </c>
       <c r="J5" t="n">
-        <v>6.4469211276587</v>
+        <v>6.446921127658691</v>
       </c>
       <c r="K5" t="n">
-        <v>3.645698129337939</v>
+        <v>3.645698129337938</v>
       </c>
       <c r="L5" t="n">
-        <v>7.249033355590507</v>
+        <v>7.249033355590304</v>
       </c>
       <c r="M5" t="n">
         <v>10.06394527642067</v>
       </c>
       <c r="N5" t="n">
-        <v>4.709786997503773</v>
+        <v>4.709786997503778</v>
       </c>
       <c r="O5" t="n">
-        <v>3.432157660367561</v>
+        <v>3.432157660367564</v>
       </c>
       <c r="P5" t="n">
-        <v>4.436100379015596</v>
+        <v>4.436100379015594</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.653303583680071</v>
+        <v>2.65330358368005</v>
       </c>
       <c r="R5" t="n">
-        <v>1.759642286677863</v>
+        <v>1.759642286677876</v>
       </c>
       <c r="S5" t="n">
-        <v>4.601819531141233</v>
+        <v>4.601819531141208</v>
       </c>
       <c r="T5" t="n">
-        <v>2.73873620638343</v>
+        <v>2.73873620638342</v>
       </c>
       <c r="U5" t="n">
-        <v>6.772052969682973</v>
+        <v>6.77205296968297</v>
       </c>
       <c r="V5" t="n">
-        <v>2.287997107918704</v>
+        <v>2.287997107918709</v>
       </c>
       <c r="W5" t="n">
-        <v>9.00172248494537</v>
+        <v>9.001722484945342</v>
       </c>
       <c r="X5" t="n">
-        <v>6.50863603593403</v>
+        <v>6.508636035934018</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.612348394554044</v>
+        <v>5.612348394554037</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.203956419420986</v>
+        <v>3.203956419420941</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.546735030510101</v>
+        <v>6.546735030510093</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.39415218916623</v>
+        <v>10.39415218916622</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4055838585324169</v>
+        <v>0.405583858532414</v>
       </c>
       <c r="C6" t="n">
         <v>0.2916322906510548</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4493998568725172</v>
+        <v>0.4493998568725176</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3708743525496171</v>
+        <v>0.3708743525496178</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2985674690790591</v>
+        <v>0.2985674690790575</v>
       </c>
       <c r="G6" t="n">
-        <v>0.891958979134657</v>
+        <v>0.8919589791346564</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5222834696507116</v>
+        <v>0.5222834696507118</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3283222200143558</v>
+        <v>0.3283222200143559</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5704356230722459</v>
+        <v>0.5704356230722463</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5006210458687127</v>
+        <v>0.5006210458687135</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6968811788324312</v>
+        <v>0.6968811788324105</v>
       </c>
       <c r="M6" t="n">
-        <v>0.749688145336339</v>
+        <v>0.7496881453363385</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4521286724091398</v>
+        <v>0.452128672409137</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5053306150209532</v>
+        <v>0.5053306150209533</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5526785057222137</v>
+        <v>0.5526785057222127</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3472851928309434</v>
+        <v>0.3472851928309438</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3851709190368997</v>
+        <v>0.385170919036898</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4796322013529064</v>
+        <v>0.4796322013529057</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3454871043169463</v>
+        <v>0.3454871043169462</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6680931147859276</v>
+        <v>0.6680931147859296</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3370798494998878</v>
+        <v>0.3370798494998877</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6870242007822339</v>
+        <v>0.6870242007822345</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6312279533018673</v>
+        <v>0.6312279533018641</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5094167870407063</v>
+        <v>0.5094167870407096</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.480746355142879</v>
+        <v>0.4807463551428773</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6439939684254302</v>
+        <v>0.6439939684254296</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7104836918106628</v>
+        <v>0.7104836918106635</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4937989669100329</v>
+        <v>0.4937989669100289</v>
       </c>
       <c r="C7" t="n">
-        <v>0.37984739902867</v>
+        <v>0.3798473990286699</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5376149652501311</v>
+        <v>0.5376149652501324</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3681883011440414</v>
+        <v>0.3681883011440401</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3867825774566733</v>
+        <v>0.3867825774566737</v>
       </c>
       <c r="G7" t="n">
-        <v>0.889272927729079</v>
+        <v>0.8892729277290801</v>
       </c>
       <c r="H7" t="n">
-        <v>0.610498578028326</v>
+        <v>0.6104985780283266</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4165373283919701</v>
+        <v>0.4165373283919702</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6586507314498619</v>
+        <v>0.6586507314498617</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4979349944631363</v>
+        <v>0.4979349944631369</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6941951274268511</v>
+        <v>0.6941951274268332</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8379032537139512</v>
+        <v>0.8379032537139517</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5395518334971173</v>
+        <v>0.5395518334971181</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4972465095798479</v>
+        <v>0.4972465095798495</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5446453391642239</v>
+        <v>0.5446453391642248</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.435500301208559</v>
+        <v>0.4355003012085581</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3824848676313214</v>
+        <v>0.3824848676313213</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5678473097305216</v>
+        <v>0.5678473097305207</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4337022126945614</v>
+        <v>0.4337022126945612</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6650139960161955</v>
+        <v>0.6650139960161966</v>
       </c>
       <c r="V7" t="n">
-        <v>0.425294957877503</v>
+        <v>0.4252949578775029</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7698356625804247</v>
+        <v>0.7698356625804244</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6285419018962916</v>
+        <v>0.628541901896287</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5949111395333969</v>
+        <v>0.5949111395333971</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.4780603037373029</v>
+        <v>0.4780603037373019</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6413079170198526</v>
+        <v>0.6413079170198532</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7960831560707929</v>
+        <v>0.7960831560707934</v>
       </c>
     </row>
     <row r="8">
@@ -7994,46 +7994,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5388516574596088</v>
+        <v>0.5388516574596046</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5472932376607846</v>
+        <v>0.5472932376607852</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7050608038822472</v>
+        <v>0.7050608038822465</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4704633988079943</v>
+        <v>0.4704633988079927</v>
       </c>
       <c r="F8" t="n">
-        <v>0.450902690029628</v>
+        <v>0.4509026900296291</v>
       </c>
       <c r="G8" t="n">
-        <v>1.08209778292724</v>
+        <v>1.082097782927239</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7779444166604418</v>
+        <v>0.7779444166604431</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5839831670240859</v>
+        <v>0.583983167024086</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8260965700819769</v>
+        <v>0.8260965700819775</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6653808330952525</v>
+        <v>0.6653808330952522</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8616409660589663</v>
+        <v>0.861640966058956</v>
       </c>
       <c r="M8" t="n">
-        <v>1.00534909234617</v>
+        <v>1.005349092346171</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6121225064182438</v>
+        <v>0.6121225064182445</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5962483681372865</v>
+        <v>0.5962483681372879</v>
       </c>
       <c r="P8" t="n">
         <v>0.6372561932478816</v>
@@ -8042,37 +8042,37 @@
         <v>0.4564999446918497</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5499307062634369</v>
+        <v>0.5499307062634364</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7352931483626368</v>
+        <v>0.7352931483626358</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6011480513266753</v>
+        <v>0.6011480513266756</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7730877800105873</v>
+        <v>0.7730877800105872</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5592594984942357</v>
+        <v>0.5592594984942354</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9373055548996232</v>
+        <v>0.937305554899624</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6607591205551216</v>
+        <v>0.660759120555119</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.884004092032577</v>
+        <v>0.8840040920325772</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5208394787302864</v>
+        <v>0.5208394787302846</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8087537556519692</v>
+        <v>0.8087537556519683</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.091378872156459</v>
+        <v>1.091378872156461</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7944084148925218</v>
+        <v>0.7944084148925145</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8044044106893559</v>
+        <v>0.8044044106893552</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9621719769108191</v>
+        <v>0.9621719769108198</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7641387268824187</v>
+        <v>0.7641387268824169</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5256066158157103</v>
+        <v>0.5256066158157113</v>
       </c>
       <c r="G9" t="n">
-        <v>1.313829947452273</v>
+        <v>1.313829947452274</v>
       </c>
       <c r="H9" t="n">
         <v>1.035055589689015</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8410943400526576</v>
+        <v>0.8410943400526568</v>
       </c>
       <c r="J9" t="n">
-        <v>1.083207743110549</v>
+        <v>1.083207743110548</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9224920061238224</v>
+        <v>0.9224920061238232</v>
       </c>
       <c r="L9" t="n">
-        <v>1.118752139087537</v>
+        <v>1.118752139087518</v>
       </c>
       <c r="M9" t="n">
-        <v>1.262460265374642</v>
+        <v>1.262460265374641</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9641088451578044</v>
+        <v>0.9641088451578033</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9632382586318318</v>
+        <v>0.9632382586318323</v>
       </c>
       <c r="P9" t="n">
-        <v>1.019570427167669</v>
+        <v>1.019570427167668</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8600573209317529</v>
+        <v>0.8600573209317532</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8070418792920062</v>
+        <v>0.8070418792920063</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9924043213912074</v>
+        <v>0.992404321391205</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8582592243552482</v>
+        <v>0.8582592243552474</v>
       </c>
       <c r="U9" t="n">
         <v>1.089964075041037</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9928846542630019</v>
+        <v>0.9928846542630022</v>
       </c>
       <c r="W9" t="n">
-        <v>1.19439267424111</v>
+        <v>1.194392674241109</v>
       </c>
       <c r="X9" t="n">
-        <v>1.053098913556976</v>
+        <v>1.05309891355697</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.019468151194082</v>
+        <v>1.019468151194083</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.8278879595489728</v>
+        <v>0.82788795954897</v>
       </c>
       <c r="AA9" t="n">
         <v>1.06586492868054</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.220640167731479</v>
+        <v>1.220640167731478</v>
       </c>
     </row>
   </sheetData>
@@ -8326,37 +8326,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.929582538008893</v>
+        <v>2.929582538008891</v>
       </c>
       <c r="C2" t="n">
-        <v>2.920062282092445</v>
+        <v>2.920062282092444</v>
       </c>
       <c r="D2" t="n">
-        <v>2.935712115829877</v>
+        <v>2.935712115829876</v>
       </c>
       <c r="E2" t="n">
-        <v>2.929111513111641</v>
+        <v>2.92911151311164</v>
       </c>
       <c r="F2" t="n">
         <v>2.919621773859435</v>
       </c>
       <c r="G2" t="n">
-        <v>2.974058089835773</v>
+        <v>2.974058089835771</v>
       </c>
       <c r="H2" t="n">
-        <v>2.950169219567782</v>
+        <v>2.950169219567781</v>
       </c>
       <c r="I2" t="n">
-        <v>2.930140531511094</v>
+        <v>2.930140531511092</v>
       </c>
       <c r="J2" t="n">
         <v>2.946406594242207</v>
       </c>
       <c r="K2" t="n">
-        <v>2.934311178291128</v>
+        <v>2.934311178291126</v>
       </c>
       <c r="L2" t="n">
-        <v>2.914857127877542</v>
+        <v>2.914857127877541</v>
       </c>
       <c r="M2" t="n">
         <v>2.931600331521598</v>
@@ -8365,43 +8365,43 @@
         <v>2.934408229401249</v>
       </c>
       <c r="O2" t="n">
-        <v>3.273808084114343</v>
+        <v>3.273808084114344</v>
       </c>
       <c r="P2" t="n">
         <v>2.939860420267309</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.931978223110833</v>
+        <v>2.931978223110832</v>
       </c>
       <c r="R2" t="n">
-        <v>2.905854624657609</v>
+        <v>2.905854624657611</v>
       </c>
       <c r="S2" t="n">
-        <v>2.922964804231109</v>
+        <v>2.922964804231108</v>
       </c>
       <c r="T2" t="n">
-        <v>2.924362140053183</v>
+        <v>2.924362140053182</v>
       </c>
       <c r="U2" t="n">
         <v>3.69247491116958</v>
       </c>
       <c r="V2" t="n">
-        <v>2.938907324291117</v>
+        <v>2.938907324291115</v>
       </c>
       <c r="W2" t="n">
         <v>3.708332781560042</v>
       </c>
       <c r="X2" t="n">
-        <v>2.966375193227868</v>
+        <v>2.966375193227866</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.975467378343562</v>
+        <v>2.975467378343561</v>
       </c>
       <c r="Z2" t="n">
         <v>3.203005330718029</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.948011362938448</v>
+        <v>2.948011362938449</v>
       </c>
       <c r="AB2" t="n">
         <v>2.957831680769242</v>
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.966816874872727</v>
+        <v>0.8211961006109315</v>
       </c>
       <c r="C3" t="n">
-        <v>1.964571277630371</v>
+        <v>0.8195648165593742</v>
       </c>
       <c r="D3" t="n">
-        <v>2.010541845054107</v>
+        <v>0.8664696470688538</v>
       </c>
       <c r="E3" t="n">
-        <v>1.963400800834296</v>
+        <v>0.8176536786201977</v>
       </c>
       <c r="F3" t="n">
-        <v>1.895597471226768</v>
+        <v>0.7474243775162452</v>
       </c>
       <c r="G3" t="n">
-        <v>2.28200093333132</v>
+        <v>1.147506146595309</v>
       </c>
       <c r="H3" t="n">
-        <v>2.11441587534378</v>
+        <v>0.9740468813781228</v>
       </c>
       <c r="I3" t="n">
-        <v>1.970698308968865</v>
+        <v>0.8252105671480247</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0861941809853</v>
+        <v>0.9447856169786547</v>
       </c>
       <c r="K3" t="n">
-        <v>2.000488259864261</v>
+        <v>0.8560593417999004</v>
       </c>
       <c r="L3" t="n">
-        <v>1.862357011534273</v>
+        <v>0.713028024256408</v>
       </c>
       <c r="M3" t="n">
-        <v>1.985973326177137</v>
+        <v>0.8410546580879429</v>
       </c>
       <c r="N3" t="n">
-        <v>2.001210830217</v>
+        <v>0.8568045399563929</v>
       </c>
       <c r="O3" t="n">
-        <v>2.525553283487845</v>
+        <v>1.379494924893418</v>
       </c>
       <c r="P3" t="n">
-        <v>2.039841783653304</v>
+        <v>0.8967866876439554</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.983875450042678</v>
+        <v>0.8388548385574238</v>
       </c>
       <c r="R3" t="n">
-        <v>1.796628401689234</v>
+        <v>0.6449483539241513</v>
       </c>
       <c r="S3" t="n">
-        <v>1.91996871776977</v>
+        <v>0.7726866318387599</v>
       </c>
       <c r="T3" t="n">
-        <v>1.929388547974756</v>
+        <v>0.782432982506208</v>
       </c>
       <c r="U3" t="n">
-        <v>3.269813652053946</v>
+        <v>2.126198905261177</v>
       </c>
       <c r="V3" t="n">
-        <v>2.033014409839031</v>
+        <v>0.8897280967552311</v>
       </c>
       <c r="W3" t="n">
-        <v>3.42367179803123</v>
+        <v>2.285920655768707</v>
       </c>
       <c r="X3" t="n">
-        <v>2.229361808691621</v>
+        <v>1.093067665522099</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.294116877304742</v>
+        <v>1.160074099040136</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.461294470308514</v>
+        <v>1.317655715288699</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.098304067982039</v>
+        <v>0.9573271360732776</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.167742489761939</v>
+        <v>1.029231880160359</v>
       </c>
     </row>
     <row r="4">
@@ -8505,82 +8505,82 @@
         <v>0.1468918239718421</v>
       </c>
       <c r="C4" t="n">
-        <v>0.174576623443386</v>
+        <v>0.1745766234433858</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2161282252049735</v>
+        <v>0.2161282252049733</v>
       </c>
       <c r="E4" t="n">
         <v>0.1415713810752096</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03438041072583346</v>
+        <v>0.03438041072583399</v>
       </c>
       <c r="G4" t="n">
-        <v>0.649263641621117</v>
+        <v>0.6492636416211166</v>
       </c>
       <c r="H4" t="n">
         <v>0.3794278625209216</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1531946172688927</v>
+        <v>0.1531946172688926</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3365548999590726</v>
+        <v>0.3365548999590727</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2003039912416967</v>
+        <v>0.2003039912416964</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.01943845748510076</v>
+        <v>-0.01943845748510116</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1784437064006704</v>
+        <v>0.1784437064006705</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2014002281762152</v>
+        <v>0.2014002281762153</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1270765482715513</v>
+        <v>0.1270765482715516</v>
       </c>
       <c r="P4" t="n">
-        <v>0.262985232140108</v>
+        <v>0.2629852321401079</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1739521892678396</v>
+        <v>0.1739521892678401</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1211258727103136</v>
+        <v>-0.1211258727103134</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07214147664384765</v>
+        <v>0.0721414766438475</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08792502756039057</v>
+        <v>0.0879250275603906</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2322477131444473</v>
+        <v>0.2322477131444476</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2497167591072946</v>
+        <v>0.2497167591072947</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4997797925738349</v>
+        <v>0.4997797925738335</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5624817901277631</v>
+        <v>0.562481790127764</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6602692146342128</v>
+        <v>0.6602692146342125</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2363597176153809</v>
+        <v>0.2363597176153805</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.3550538792294594</v>
+        <v>0.3550538792294592</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4634466468472102</v>
+        <v>0.4634466468472105</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.2050256160097819</v>
+        <v>-0.2050256160097814</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2696743482705907</v>
+        <v>0.2696743482705903</v>
       </c>
       <c r="D5" t="n">
-        <v>1.008064885674518</v>
+        <v>1.008064885674517</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3272897965633548</v>
+        <v>-0.3272897965633549</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.261792060376715</v>
+        <v>-2.261792060376713</v>
       </c>
       <c r="G5" t="n">
-        <v>7.519336481254184</v>
+        <v>7.519336481254174</v>
       </c>
       <c r="H5" t="n">
-        <v>4.255397512398434</v>
+        <v>4.255397512398432</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1458875603923261</v>
+        <v>-0.1458875603923252</v>
       </c>
       <c r="J5" t="n">
-        <v>2.794582279649745</v>
+        <v>2.794582279649739</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6996723306599381</v>
+        <v>0.6996723306599388</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.817196546285549</v>
+        <v>-2.81719654628555</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3508903418654843</v>
+        <v>0.3508903418654846</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7345620924510728</v>
+        <v>0.7345620924510706</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4758451362689813</v>
+        <v>-0.4758451362689812</v>
       </c>
       <c r="P5" t="n">
-        <v>1.677860069551313</v>
+        <v>1.677860069551311</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2530864165692954</v>
+        <v>0.2530864165692948</v>
       </c>
       <c r="R5" t="n">
-        <v>-5.381277304029042</v>
+        <v>-5.381277304029046</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.328660532461636</v>
+        <v>-1.328660532461639</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.336093704574197</v>
+        <v>-1.336093704574196</v>
       </c>
       <c r="U5" t="n">
-        <v>1.273359326183073</v>
+        <v>1.273359326183076</v>
       </c>
       <c r="V5" t="n">
         <v>1.471951596471945</v>
       </c>
       <c r="W5" t="n">
-        <v>6.027227327677561</v>
+        <v>6.027227327677548</v>
       </c>
       <c r="X5" t="n">
-        <v>7.121488575516293</v>
+        <v>7.121488575516288</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.867275744259205</v>
+        <v>8.867275744259196</v>
       </c>
       <c r="Z5" t="n">
         <v>1.215355695326289</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.455805735496525</v>
+        <v>3.45580573549652</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.749214635258038</v>
+        <v>5.749214635258047</v>
       </c>
     </row>
     <row r="6">
@@ -8681,82 +8681,82 @@
         <v>0.2283991570194447</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2560839564909885</v>
+        <v>0.2560839564909889</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2976355582525771</v>
+        <v>0.2976355582525764</v>
       </c>
       <c r="E6" t="n">
         <v>0.1535161206946052</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04632515034522899</v>
+        <v>0.04632515034522949</v>
       </c>
       <c r="G6" t="n">
-        <v>0.661208381240513</v>
+        <v>0.661208381240512</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3913726021403168</v>
+        <v>0.391372602140317</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2347019503164966</v>
+        <v>0.2347019503164958</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4180622330066762</v>
+        <v>0.4180622330066755</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2122487308610922</v>
+        <v>0.2122487308610924</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06206887556250275</v>
+        <v>0.0620688755625025</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1903884460200657</v>
+        <v>0.190388446020066</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2139078104301517</v>
+        <v>0.2139078104301518</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2136480682699015</v>
+        <v>0.2136480682699014</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2731596871014175</v>
+        <v>0.2731596871014179</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1858969288872352</v>
+        <v>0.1858969288872351</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.03961853966271088</v>
+        <v>-0.03961853966271077</v>
       </c>
       <c r="S6" t="n">
-        <v>0.08408621626324228</v>
+        <v>0.08408621626324243</v>
       </c>
       <c r="T6" t="n">
-        <v>0.09986976717978663</v>
+        <v>0.09986976717978661</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3186680351791717</v>
+        <v>0.3186680351791712</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2616614987266902</v>
+        <v>0.2616614987266901</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5159232090448886</v>
+        <v>0.5159232090448803</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6439891231753658</v>
+        <v>0.6439891231753664</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6792345664019239</v>
+        <v>0.6792345664019238</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.317867050662984</v>
+        <v>0.3178670506629837</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.3669986188488543</v>
+        <v>0.3669986188488548</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.4773284033474998</v>
+        <v>0.4773284033474995</v>
       </c>
     </row>
     <row r="7">
@@ -8766,73 +8766,73 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2339963669527979</v>
+        <v>0.2339963669527982</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2616811664243423</v>
+        <v>0.2616811664243422</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3032327681859298</v>
+        <v>0.30323276818593</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2286759240561659</v>
+        <v>0.228675924056166</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1214849537067899</v>
+        <v>0.1214849537067901</v>
       </c>
       <c r="G7" t="n">
-        <v>0.736368184602074</v>
+        <v>0.7363681846020729</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4665324055018784</v>
+        <v>0.4665324055018783</v>
       </c>
       <c r="I7" t="n">
-        <v>0.240299160249849</v>
+        <v>0.2402991602498491</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4236594429400291</v>
+        <v>0.4236594429400289</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2874085342226528</v>
+        <v>0.287408534222653</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06766608549585558</v>
+        <v>0.06766608549585609</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2655482493816264</v>
+        <v>0.2655482493816266</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2885047711571713</v>
+        <v>0.2885047711571714</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2138473416176258</v>
+        <v>0.213847341617626</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3497560254861825</v>
+        <v>0.3497560254861826</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2610567322487958</v>
+        <v>0.2610567322487957</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.03402132972935731</v>
+        <v>-0.03402132972935722</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1592460196248028</v>
+        <v>0.159246019624803</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1750295705413469</v>
+        <v>0.1750295705413474</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3235010984392727</v>
+        <v>0.3235010984392728</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3368213020882513</v>
+        <v>0.336821302088251</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5868843355547895</v>
+        <v>0.5868843355547897</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6495863331087199</v>
+        <v>0.6495863331087203</v>
       </c>
       <c r="Y7" t="n">
         <v>0.7522867466022903</v>
@@ -8841,10 +8841,10 @@
         <v>0.3234642605963371</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4421584222104152</v>
+        <v>0.4421584222104148</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5505511898281661</v>
+        <v>0.5505511898281666</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2620021569997683</v>
+        <v>0.2620021569997684</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3813220883517697</v>
+        <v>0.3813220883517693</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4228736901133573</v>
+        <v>0.4228736901133567</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2995238413297167</v>
+        <v>0.2995238413297168</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1637664263345527</v>
+        <v>0.1637664263345524</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8750102480698604</v>
+        <v>0.8750102480698584</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5861733274293056</v>
+        <v>0.5861733274293048</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3599400821772769</v>
+        <v>0.359940082177276</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5433003648674564</v>
+        <v>0.5433003648674563</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4070494561500799</v>
+        <v>0.4070494561500794</v>
       </c>
       <c r="L8" t="n">
         <v>0.1873070074232825</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3851891713092128</v>
+        <v>0.3851891713092127</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3371131356454451</v>
+        <v>0.3371131356454454</v>
       </c>
       <c r="O8" t="n">
         <v>0.2823098192754733</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4134335903649836</v>
+        <v>0.4134335903649831</v>
       </c>
       <c r="Q8" t="n">
         <v>0.2710541274185355</v>
       </c>
       <c r="R8" t="n">
-        <v>0.08561959219807046</v>
+        <v>0.0856195921980696</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2788869415522315</v>
+        <v>0.2788869415522309</v>
       </c>
       <c r="T8" t="n">
-        <v>0.294670492468775</v>
+        <v>0.2946704924687744</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3988467350526262</v>
+        <v>0.3988467350526259</v>
       </c>
       <c r="V8" t="n">
-        <v>0.431049068031662</v>
+        <v>0.4310490680316622</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7065432663818473</v>
+        <v>0.7065432663818463</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6679822701792599</v>
+        <v>0.6679822701792607</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9624677922903153</v>
+        <v>0.9624677922903156</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.349767881025027</v>
+        <v>0.3497678810250268</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5617993441378425</v>
+        <v>0.5617993441378422</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.7659126693839685</v>
+        <v>0.7659126693839678</v>
       </c>
     </row>
     <row r="9">
@@ -8942,73 +8942,73 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4509972734521225</v>
+        <v>0.4509972734521228</v>
       </c>
       <c r="C9" t="n">
-        <v>0.570834077124886</v>
+        <v>0.5708340771248858</v>
       </c>
       <c r="D9" t="n">
         <v>0.612385678886474</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5165605833348508</v>
+        <v>0.5165605833348509</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2182022502727334</v>
+        <v>0.2182022502727338</v>
       </c>
       <c r="G9" t="n">
-        <v>1.045521167151699</v>
+        <v>1.045521167151697</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7756853162024218</v>
+        <v>0.7756853162024216</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5494520709503938</v>
+        <v>0.5494520709503932</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7328123536405734</v>
+        <v>0.732812353640574</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5965614449231968</v>
+        <v>0.5965614449231967</v>
       </c>
       <c r="L9" t="n">
-        <v>0.376818996196399</v>
+        <v>0.3768189961964002</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5747011600821709</v>
+        <v>0.5747011600821711</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5976576818577144</v>
+        <v>0.5976576818577155</v>
       </c>
       <c r="O9" t="n">
-        <v>0.553873151142352</v>
+        <v>0.5538731511423537</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6964235603700796</v>
+        <v>0.6964235603700809</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5702097147984199</v>
+        <v>0.57020971479842</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2751315809711876</v>
+        <v>0.2751315809711875</v>
       </c>
       <c r="S9" t="n">
         <v>0.4683989303253478</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4841824812418907</v>
+        <v>0.484182481241891</v>
       </c>
       <c r="U9" t="n">
         <v>0.6334181558130683</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7523157244951757</v>
+        <v>0.7523157244951768</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8960372462553332</v>
+        <v>0.8960372462553329</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9587392438092638</v>
+        <v>0.9587392438092635</v>
       </c>
       <c r="Y9" t="n">
         <v>1.061439657302833</v>
@@ -9017,10 +9017,10 @@
         <v>0.5770577357699578</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.7513113329109596</v>
+        <v>0.7513113329109592</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8597041005287106</v>
+        <v>0.8597041005287112</v>
       </c>
     </row>
   </sheetData>
